--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -90,285 +90,333 @@
     <t xml:space="preserve">Jaxon Price</t>
   </si>
   <si>
+    <t xml:space="preserve">Jaxson Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Frazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kade Falardeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nate Parsons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Phelan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reid Lunney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Somerville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tobey Drennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Peiper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guelph Gryphons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Westfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Ogston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gillis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylen Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Da Gama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Cantwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Chang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Boyle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Scicluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sawyer Whitaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Cullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anden Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon McMurray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declan Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eli Oughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson McQuade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Kim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Dykyj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayan Alazem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Underwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Velocci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinten Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Stonehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Vivaldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U of T Varsity Blues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elias Rubio Reyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haven Tai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Barber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Gannett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Worthen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Verman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Zidros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Hsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spenser Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomoki Yamamoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woochan Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Leatherland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterloo Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Rusch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Kowara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter Kipp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Pawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junichi Yuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Greaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Todd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhys Jenkyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shephard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Awrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Mustangs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Conners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colin Mayhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ewan Ferguson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Hawke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koby Sernick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parker McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Nuernberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Sillett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ash Abols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilfrid Laurier Golden Hawks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brady Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Boys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Bendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Geldart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Leonard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis Llewellyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffen Duenkler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Larmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Symington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Wellman</t>
+  </si>
+  <si>
     <t xml:space="preserve">Johnny Banks</t>
   </si>
   <si>
-    <t xml:space="preserve">Josh Frazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kade Falardeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nate Parsons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Phelan</t>
+    <t xml:space="preserve">Lucas Bateman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Kong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Goranson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Vieira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Dineen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preston Vieira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Recker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windsor Lancers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callum Barton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cullen Rooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gannon Djekic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Marcotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Colombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaton Ruttle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matteo Tedesco</t>
   </si>
   <si>
     <t xml:space="preserve">Parker Starkiss</t>
   </si>
   <si>
-    <t xml:space="preserve">Reid Lunney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Somerville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tobey Drennan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Peiper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guelph Gryphons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Westfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Ogston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gillis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylen Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marco Da Gama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Cantwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Chang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Boyle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Scicluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sawyer Whitaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Cullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anden Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McMaster Marauders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon McMurray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declan Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eli Oughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson McQuade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Kim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Dykyj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayan Alazem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Underwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolas Velocci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinten Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Stonehouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Leatherland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterloo Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Rusch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Kowara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carter Kipp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Pawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junichi Yuki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Greaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Todd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhys Jenkyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Shephard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Awrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Western Mustangs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Conners</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colin Mayhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ewan Ferguson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Hawke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koby Sernick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parker McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Nuernberger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Sillett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ash Abols</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilfrid Laurier Golden Hawks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brady Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Boys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Bendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Geldart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Leonard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davis Llewellyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Lopez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffen Duenkler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Larmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Symington</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jared Wellman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bateman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Kong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Goranson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Vieira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Dineen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preston Vieira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callum Barton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windsor Lancers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cullen Rooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gannon Djekic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Marcotte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Colombe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaton Ruttle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matteo Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recker</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stephen Vavoulas</t>
   </si>
   <si>
@@ -484,6 +532,21 @@
   </si>
   <si>
     <t xml:space="preserve">Taio Fotiou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenny Leung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kojiro Hirata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ravin Yuvarajan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taisei Hihara</t>
   </si>
   <si>
     <t xml:space="preserve">Aidan Armitage</t>
@@ -601,8 +664,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K107" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K120" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K120"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -621,8 +684,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K61" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K65" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K65"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -978,31 +1041,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="F2" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="G2" t="n">
-        <v>16.4</v>
+        <v>15.7</v>
       </c>
       <c r="H2" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="I2" t="n">
-        <v>53.8</v>
+        <v>56.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23.1</v>
+        <v>19.6</v>
       </c>
       <c r="K2" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="3">
@@ -1013,31 +1076,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>77</v>
+        <v>75.2</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>62.9</v>
+        <v>61.2</v>
       </c>
       <c r="F3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>8.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="K3" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="4">
@@ -1152,11 +1215,15 @@
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7"/>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7"/>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -1164,13 +1231,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1184,31 +1251,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>79.2</v>
+        <v>79.1</v>
       </c>
       <c r="D8" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="E8" t="n">
-        <v>56.7</v>
+        <v>57.8</v>
       </c>
       <c r="F8" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="G8" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="J8" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="K8" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="9">
@@ -1219,31 +1286,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>77.3</v>
+        <v>76.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>73.9</v>
+        <v>73.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="H9" t="n">
-        <v>10.5</v>
+        <v>12.2</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>46.2</v>
       </c>
       <c r="J9" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="10">
@@ -1318,13 +1385,13 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1336,13 +1403,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="J12" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="13">
@@ -1353,31 +1420,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>66.9</v>
       </c>
       <c r="D13" t="n">
-        <v>17.7</v>
+        <v>16.4</v>
       </c>
       <c r="E13" t="n">
-        <v>49.3</v>
+        <v>50.5</v>
       </c>
       <c r="F13" t="n">
-        <v>17.7</v>
+        <v>16.4</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="H13" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="I13" t="n">
-        <v>47.2</v>
+        <v>48.8</v>
       </c>
       <c r="J13" t="n">
-        <v>22.2</v>
+        <v>24.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="14">
@@ -1416,15 +1483,33 @@
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1434,31 +1519,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>73.7</v>
+        <v>77.8</v>
       </c>
       <c r="D16" t="n">
-        <v>9.7</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>67.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9.7</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H16" t="n">
         <v>20</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="J16" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="K16" t="n">
-        <v>70</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="17">
@@ -1469,31 +1554,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>62.5</v>
+        <v>65.9</v>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>56.8</v>
       </c>
       <c r="F17" t="n">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
       <c r="G17" t="n">
-        <v>21.7</v>
+        <v>16.7</v>
       </c>
       <c r="H17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>23.5</v>
       </c>
       <c r="J17" t="n">
-        <v>45.5</v>
+        <v>52.9</v>
       </c>
       <c r="K17" t="n">
-        <v>9.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="18">
@@ -1504,22 +1589,22 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>78.6</v>
+        <v>76.3</v>
       </c>
       <c r="D18" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="E18" t="n">
-        <v>63.2</v>
+        <v>62.7</v>
       </c>
       <c r="F18" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="G18" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="H18" t="n">
-        <v>11.4</v>
+        <v>13.9</v>
       </c>
       <c r="I18" t="n">
         <v>41.7</v>
@@ -1539,31 +1624,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>73.5</v>
+        <v>68.4</v>
       </c>
       <c r="D19" t="n">
-        <v>10.7</v>
+        <v>19.4</v>
       </c>
       <c r="E19" t="n">
-        <v>62.8</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>10.7</v>
+        <v>19.4</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>30.8</v>
+        <v>26.7</v>
       </c>
       <c r="J19" t="n">
-        <v>23.1</v>
+        <v>26.7</v>
       </c>
       <c r="K19" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="20">
@@ -1574,31 +1659,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>79.4</v>
+        <v>78.9</v>
       </c>
       <c r="D20" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="E20" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="F20" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="G20" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I20" t="n">
-        <v>37.5</v>
+        <v>35.8</v>
       </c>
       <c r="J20" t="n">
-        <v>35.4</v>
+        <v>37.7</v>
       </c>
       <c r="K20" t="n">
-        <v>34.8</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="21">
@@ -1609,31 +1694,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
       <c r="D21" t="n">
-        <v>33.3</v>
+        <v>14.9</v>
       </c>
       <c r="E21" t="n">
-        <v>16.7</v>
+        <v>40.5</v>
       </c>
       <c r="F21" t="n">
-        <v>33.3</v>
+        <v>14.9</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>11.8</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>51.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="22">
@@ -1644,31 +1729,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>55.4</v>
+        <v>85.7</v>
       </c>
       <c r="D22" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>40.5</v>
+        <v>85.7</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="J22" t="n">
-        <v>21.2</v>
+        <v>33.3</v>
       </c>
       <c r="K22" t="n">
-        <v>27.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="23">
@@ -1697,13 +1782,13 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
@@ -1711,69 +1796,69 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
       <c r="C25" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -1781,34 +1866,34 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>66.7</v>
+        <v>86.7</v>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>77.6</v>
       </c>
       <c r="F26" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
+        <v>11.1</v>
       </c>
       <c r="I26" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="27">
@@ -1816,34 +1901,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>86.7</v>
+        <v>50</v>
       </c>
       <c r="D27" t="n">
-        <v>9.1</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>77.6</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>9.1</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1851,34 +1936,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="29">
@@ -1886,34 +1971,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>62.5</v>
+        <v>82.1</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>52.5</v>
+        <v>62.1</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="H29" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>9.1</v>
+        <v>53.8</v>
       </c>
       <c r="J29" t="n">
-        <v>54.5</v>
+        <v>15.4</v>
       </c>
       <c r="K29" t="n">
-        <v>9.1</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="30">
@@ -1921,34 +2006,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>82.1</v>
+        <v>76</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>62.1</v>
+        <v>63</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>21.4</v>
+        <v>31.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I30" t="n">
-        <v>53.8</v>
+        <v>33.3</v>
       </c>
       <c r="J30" t="n">
-        <v>15.4</v>
+        <v>33.3</v>
       </c>
       <c r="K30" t="n">
-        <v>69.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="31">
@@ -1956,34 +2041,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>76</v>
+        <v>71.9</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>63</v>
+        <v>67.9</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>31.8</v>
+        <v>16.7</v>
       </c>
       <c r="H31" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I31" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -1991,34 +2076,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>71.9</v>
+        <v>84</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="E32" t="n">
-        <v>67.9</v>
+        <v>78.4</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="G32" t="n">
-        <v>16.7</v>
+        <v>4.5</v>
       </c>
       <c r="H32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="33">
@@ -2026,34 +2111,34 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>84</v>
+        <v>59.3</v>
       </c>
       <c r="D33" t="n">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
       <c r="E33" t="n">
-        <v>78.4</v>
+        <v>50.2</v>
       </c>
       <c r="F33" t="n">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
       <c r="G33" t="n">
-        <v>4.5</v>
+        <v>42.1</v>
       </c>
       <c r="H33" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="I33" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="J33" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>46.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="34">
@@ -2061,34 +2146,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>59.3</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2096,34 +2181,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -2131,34 +2216,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>63.6</v>
+        <v>48.6</v>
       </c>
       <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J36" t="n">
         <v>22.2</v>
       </c>
-      <c r="E36" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="K36" t="n">
         <v>22.2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>80</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
-      <c r="K36" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -2166,34 +2251,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>48.6</v>
+        <v>56.2</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E37" t="n">
-        <v>40.6</v>
+        <v>26.2</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>41.7</v>
       </c>
       <c r="H37" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="J37" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2201,31 +2286,31 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C38" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>26.2</v>
+        <v>50</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I38" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2233,37 +2318,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K39" t="n">
         <v>66.7</v>
-      </c>
-      <c r="H39" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>50</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2271,34 +2356,34 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>27.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G40" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2306,34 +2391,34 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>47.1</v>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E41" t="n">
-        <v>27.5</v>
+        <v>30.4</v>
       </c>
       <c r="F41" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="42">
@@ -2341,34 +2426,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" t="n">
-        <v>47.1</v>
+        <v>66.7</v>
       </c>
       <c r="D42" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E42" t="n">
-        <v>30.4</v>
+        <v>41.7</v>
       </c>
       <c r="F42" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>57.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -2376,34 +2461,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K43" t="n">
         <v>66.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>25</v>
-      </c>
-      <c r="E43" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F43" t="n">
-        <v>25</v>
-      </c>
-      <c r="G43" t="n">
-        <v>25</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>100</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -2411,96 +2496,96 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
-      </c>
-      <c r="G44" t="n">
-        <v>37.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G44"/>
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K44" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>57.7</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45"/>
+        <v>17.6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
+      <c r="I45" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="n">
-        <v>57.7</v>
+        <v>50</v>
       </c>
       <c r="D46" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -2508,34 +2593,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="n">
         <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="48">
@@ -2543,19 +2628,19 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D48" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>42.3</v>
+        <v>66.7</v>
       </c>
       <c r="F48" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>25</v>
@@ -2564,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
@@ -2578,31 +2663,31 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E49" t="n">
-        <v>66.7</v>
+        <v>41.3</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G49" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>50</v>
+      </c>
+      <c r="J49" t="n">
         <v>25</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>50</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>50</v>
@@ -2613,34 +2698,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C50" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D50" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G50" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="H50" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="I50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K50" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
@@ -2648,34 +2733,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>70</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>70</v>
+      </c>
+      <c r="G51" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>66.7</v>
       </c>
-      <c r="D51" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E51" t="n">
-        <v>50</v>
-      </c>
-      <c r="F51" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="J51" t="n">
         <v>33.3</v>
       </c>
-      <c r="H51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>20</v>
-      </c>
-      <c r="J51" t="n">
-        <v>40</v>
-      </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2683,34 +2768,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>36.4</v>
+        <v>62.5</v>
       </c>
       <c r="D52" t="n">
-        <v>70</v>
+        <v>38.5</v>
       </c>
       <c r="E52" t="n">
-        <v>-33.6</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
-        <v>70</v>
+        <v>38.5</v>
       </c>
       <c r="G52" t="n">
-        <v>45.5</v>
+        <v>26.7</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J52" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="53">
@@ -2718,69 +2803,69 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C53" t="n">
-        <v>62.5</v>
+        <v>42.9</v>
       </c>
       <c r="D53" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>42.9</v>
       </c>
       <c r="F53" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" t="s">
         <v>66</v>
       </c>
-      <c r="B54" t="s">
-        <v>67</v>
-      </c>
       <c r="C54" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="D54" t="n">
-        <v>45.5</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="n">
-        <v>8.3</v>
+        <v>58.3</v>
       </c>
       <c r="F54" t="n">
-        <v>45.5</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>75</v>
+      </c>
+      <c r="J54" t="n">
         <v>25</v>
       </c>
-      <c r="H54" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I54" t="n">
-        <v>50</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
@@ -2788,14 +2873,20 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" t="n">
-        <v>100</v>
-      </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
+        <v>80</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>80</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
@@ -2803,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K55" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="56">
@@ -2817,31 +2908,31 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
-        <v>42.2</v>
+        <v>46.7</v>
       </c>
       <c r="F56" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="G56" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="H56" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="I56" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2852,34 +2943,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" t="n">
-        <v>76.9</v>
+        <v>55.6</v>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>51.9</v>
+        <v>5.6</v>
       </c>
       <c r="F57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2887,34 +2978,34 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" t="n">
-        <v>83.3</v>
+        <v>55.6</v>
       </c>
       <c r="D58" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="n">
-        <v>54.7</v>
+        <v>43.1</v>
       </c>
       <c r="F58" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
@@ -2922,19 +3013,19 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>32.1</v>
+        <v>46.7</v>
       </c>
       <c r="F59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
         <v>40</v>
@@ -2943,13 +3034,13 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
+        <v>50</v>
+      </c>
+      <c r="J59" t="n">
+        <v>50</v>
+      </c>
+      <c r="K59" t="n">
         <v>100</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2957,34 +3048,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2992,25 +3083,25 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D61" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="E61" t="n">
-        <v>43.3</v>
+        <v>25</v>
       </c>
       <c r="F61" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>50</v>
@@ -3019,7 +3110,7 @@
         <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3027,34 +3118,28 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
       <c r="G62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>33.3</v>
       </c>
       <c r="J62" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="K62" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="63">
@@ -3062,31 +3147,31 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>83.3</v>
+        <v>78.6</v>
       </c>
       <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G63" t="n">
         <v>16.7</v>
-      </c>
-      <c r="E63" t="n">
-        <v>66.6</v>
-      </c>
-      <c r="F63" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G63" t="n">
-        <v>42.9</v>
       </c>
       <c r="H63" t="n">
         <v>33.3</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3097,34 +3182,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="D64" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="E64" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="F64" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="65">
@@ -3132,194 +3217,188 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="D65" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
-        <v>58.4</v>
+        <v>26.7</v>
       </c>
       <c r="F65" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="G65" t="n">
-        <v>9.1</v>
+        <v>75</v>
       </c>
       <c r="H65" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>-8.3</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C67" t="n">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>45.5</v>
       </c>
       <c r="E67" t="n">
-        <v>50.4</v>
+        <v>8.3</v>
       </c>
       <c r="F67" t="n">
-        <v>11.1</v>
+        <v>45.5</v>
       </c>
       <c r="G67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H67" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="I67" t="n">
         <v>50</v>
       </c>
       <c r="J67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" t="s">
         <v>81</v>
       </c>
-      <c r="B68" t="s">
-        <v>80</v>
-      </c>
       <c r="C68" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="D68" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E68" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="F68" t="n">
-        <v>22.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
       <c r="G68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C69" t="n">
-        <v>88.9</v>
+        <v>78.6</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="E69" t="n">
-        <v>88.9</v>
+        <v>42.2</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="H69" t="n">
         <v>14.3</v>
       </c>
       <c r="I69" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C70" t="n">
-        <v>78.6</v>
+        <v>76.9</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E70" t="n">
-        <v>78.6</v>
+        <v>51.9</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G70" t="n">
         <v>9.1</v>
@@ -3328,258 +3407,258 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C71" t="n">
-        <v>64.3</v>
+        <v>83.3</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E71" t="n">
-        <v>64.3</v>
+        <v>54.7</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G71" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="I71" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C72" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="D72" t="n">
         <v>25</v>
       </c>
       <c r="E72" t="n">
-        <v>55</v>
+        <v>32.1</v>
       </c>
       <c r="F72" t="n">
         <v>25</v>
       </c>
       <c r="G72" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J72" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C73" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>60.7</v>
+        <v>100</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H73" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" t="n">
-        <v>90.9</v>
+        <v>60</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E74" t="n">
-        <v>90.9</v>
+        <v>43.3</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I74" t="n">
         <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C75" t="n">
-        <v>77.8</v>
+        <v>58.8</v>
       </c>
       <c r="D75" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>61.1</v>
+        <v>58.8</v>
       </c>
       <c r="F75" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="H75" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I75" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J75" t="n">
         <v>16.7</v>
       </c>
       <c r="K75" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C76" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="D76" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E76" t="n">
-        <v>66.9</v>
+        <v>66.6</v>
       </c>
       <c r="F76" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="G76" t="n">
-        <v>6.7</v>
+        <v>42.9</v>
       </c>
       <c r="H76" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I76" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K76" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C77" t="n">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="D77" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="E77" t="n">
-        <v>52.4</v>
+        <v>72.7</v>
       </c>
       <c r="F77" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="G77" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="I77" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J77" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78">
@@ -3587,104 +3666,104 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D78" t="n">
-        <v>22.2</v>
+        <v>8.3</v>
       </c>
       <c r="E78" t="n">
-        <v>33.4</v>
+        <v>58.4</v>
       </c>
       <c r="F78" t="n">
-        <v>22.2</v>
+        <v>8.3</v>
       </c>
       <c r="G78" t="n">
-        <v>42.9</v>
+        <v>9.1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I78" t="n">
+        <v>60</v>
+      </c>
+      <c r="J78" t="n">
+        <v>40</v>
+      </c>
+      <c r="K78" t="n">
         <v>100</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C79" t="n">
-        <v>80.8</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>62.6</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" t="s">
         <v>94</v>
       </c>
-      <c r="B80" t="s">
-        <v>91</v>
-      </c>
       <c r="C80" t="n">
-        <v>91.7</v>
+        <v>61.5</v>
       </c>
       <c r="D80" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="n">
-        <v>41.7</v>
+        <v>50.4</v>
       </c>
       <c r="F80" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="G80" t="n">
-        <v>21.4</v>
+        <v>10</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I80" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="K80" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3692,34 +3771,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C81" t="n">
-        <v>60</v>
+        <v>85.7</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E81" t="n">
-        <v>60</v>
+        <v>63.5</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J81" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K81" t="n">
         <v>100</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3727,34 +3806,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C82" t="n">
-        <v>100</v>
+        <v>88.9</v>
       </c>
       <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>88.9</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I82" t="n">
+        <v>80</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
         <v>20</v>
-      </c>
-      <c r="E82" t="n">
-        <v>80</v>
-      </c>
-      <c r="F82" t="n">
-        <v>20</v>
-      </c>
-      <c r="G82" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3762,34 +3841,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="D83" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>66.7</v>
+        <v>78.6</v>
       </c>
       <c r="F83" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="J83" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3797,34 +3876,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C84" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -3832,34 +3911,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C85" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="D85" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="E85" t="n">
-        <v>54.7</v>
+        <v>55</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="G85" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J85" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K85" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="86">
@@ -3867,34 +3946,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C86" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
-        <v>57.1</v>
+        <v>60.7</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
         <v>25</v>
       </c>
       <c r="H86" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I86" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J86" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K86" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3902,34 +3981,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C87" t="n">
-        <v>70</v>
+        <v>90.9</v>
       </c>
       <c r="D87" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>32.5</v>
+        <v>90.9</v>
       </c>
       <c r="F87" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J87" t="n">
         <v>25</v>
       </c>
       <c r="K87" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="88">
@@ -3937,133 +4016,133 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C88" t="n">
-        <v>75</v>
+        <v>77.8</v>
       </c>
       <c r="D88" t="n">
-        <v>21.4</v>
+        <v>16.7</v>
       </c>
       <c r="E88" t="n">
-        <v>53.6</v>
+        <v>61.1</v>
       </c>
       <c r="F88" t="n">
-        <v>21.4</v>
+        <v>16.7</v>
       </c>
       <c r="G88" t="n">
-        <v>46.7</v>
+        <v>4.2</v>
       </c>
       <c r="H88" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I88" t="n">
         <v>66.7</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K88" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C89" t="n">
-        <v>84.6</v>
+        <v>85.7</v>
       </c>
       <c r="D89" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E89" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H89" t="n">
         <v>14.3</v>
       </c>
-      <c r="E89" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F89" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G89" t="n">
-        <v>13</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
       <c r="I89" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="J89" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C90" t="n">
-        <v>68.6</v>
+        <v>66.7</v>
       </c>
       <c r="D90" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="E90" t="n">
-        <v>59.5</v>
+        <v>52.4</v>
       </c>
       <c r="F90" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="G90" t="n">
-        <v>23.1</v>
+        <v>35.7</v>
       </c>
       <c r="H90" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="I90" t="n">
+        <v>50</v>
+      </c>
+      <c r="J90" t="n">
         <v>33.3</v>
       </c>
-      <c r="J90" t="n">
-        <v>16.7</v>
-      </c>
       <c r="K90" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C91" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>33.4</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -4074,34 +4153,34 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" t="s">
         <v>105</v>
       </c>
-      <c r="B92" t="s">
-        <v>91</v>
-      </c>
       <c r="C92" t="n">
-        <v>90.9</v>
+        <v>80.8</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="E92" t="n">
-        <v>70.9</v>
+        <v>62.6</v>
       </c>
       <c r="F92" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="G92" t="n">
-        <v>27.3</v>
+        <v>36</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I92" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="J92" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K92" t="n">
         <v>50</v>
@@ -4109,69 +4188,69 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C93" t="n">
-        <v>60</v>
+        <v>91.7</v>
       </c>
       <c r="D93" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>50</v>
+      </c>
+      <c r="G93" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J93" t="n">
         <v>42.9</v>
       </c>
-      <c r="E93" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F93" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G93" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H93" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>100</v>
-      </c>
       <c r="K93" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C94" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D94" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="F94" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J94" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4179,83 +4258,89 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C95" t="n">
         <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="J95" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E96" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G96" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I96"/>
-      <c r="J96"/>
-      <c r="K96"/>
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>50</v>
+      </c>
+      <c r="J96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C97" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -4266,308 +4351,320 @@
       <c r="H97" t="n">
         <v>0</v>
       </c>
-      <c r="I97"/>
-      <c r="J97"/>
-      <c r="K97"/>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>100</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C98" t="n">
-        <v>61.1</v>
+        <v>83.3</v>
       </c>
       <c r="D98" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="E98" t="n">
-        <v>52</v>
+        <v>54.7</v>
       </c>
       <c r="F98" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="G98" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K98" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D99" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>31.8</v>
+        <v>57.1</v>
       </c>
       <c r="F99" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="H99" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C100" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D100" t="n">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
       <c r="E100" t="n">
-        <v>26.9</v>
+        <v>32.5</v>
       </c>
       <c r="F100" t="n">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
       <c r="G100" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
         <v>37.5</v>
       </c>
-      <c r="H100" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I100" t="n">
-        <v>66.7</v>
-      </c>
       <c r="J100" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K100" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C101" t="n">
+        <v>75</v>
+      </c>
+      <c r="D101" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E101" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G101" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H101" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I101" t="n">
         <v>66.7</v>
       </c>
-      <c r="D101" t="n">
-        <v>25</v>
-      </c>
-      <c r="E101" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F101" t="n">
-        <v>25</v>
-      </c>
-      <c r="G101" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>100</v>
-      </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>61.5</v>
+        <v>84.6</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E102" t="n">
-        <v>61.5</v>
+        <v>70.3</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G102" t="n">
+        <v>13</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J102" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K102" t="n">
         <v>12.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I102" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K102" t="n">
-        <v>42.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C103" t="n">
-        <v>44.4</v>
+        <v>68.6</v>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="E103" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I103" t="n">
         <v>33.3</v>
       </c>
-      <c r="F103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G103" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>100</v>
-      </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C104" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="F104" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I104"/>
-      <c r="J104"/>
-      <c r="K104"/>
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>50</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C105" t="n">
-        <v>71.4</v>
+        <v>90.9</v>
       </c>
       <c r="D105" t="n">
         <v>20</v>
       </c>
       <c r="E105" t="n">
-        <v>51.4</v>
+        <v>70.9</v>
       </c>
       <c r="F105" t="n">
         <v>20</v>
       </c>
       <c r="G105" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J105" t="n">
         <v>33.3</v>
       </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>50</v>
-      </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>71.4</v>
+        <v>60</v>
       </c>
       <c r="D106" t="n">
-        <v>7.1</v>
+        <v>42.9</v>
       </c>
       <c r="E106" t="n">
-        <v>64.3</v>
+        <v>17.1</v>
       </c>
       <c r="F106" t="n">
-        <v>7.1</v>
+        <v>42.9</v>
       </c>
       <c r="G106" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H106" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -4576,40 +4673,477 @@
         <v>100</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107"/>
+      <c r="A107" t="s">
+        <v>122</v>
+      </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C107" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D107" t="n">
-        <v>14.1</v>
+        <v>16.7</v>
       </c>
       <c r="E107" t="n">
-        <v>52.8</v>
+        <v>73.3</v>
       </c>
       <c r="F107" t="n">
-        <v>14.1</v>
+        <v>16.7</v>
       </c>
       <c r="G107" t="n">
-        <v>20.6</v>
+        <v>18.2</v>
       </c>
       <c r="H107" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>49.1</v>
+        <v>33.3</v>
       </c>
       <c r="J107" t="n">
-        <v>28.1</v>
+        <v>50</v>
       </c>
       <c r="K107" t="n">
-        <v>29.2</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>123</v>
+      </c>
+      <c r="B108" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" t="n">
+        <v>100</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>100</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K108" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>124</v>
+      </c>
+      <c r="B109" t="s">
+        <v>125</v>
+      </c>
+      <c r="C109" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G109" t="n">
+        <v>50</v>
+      </c>
+      <c r="H109" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>126</v>
+      </c>
+      <c r="B110" t="s">
+        <v>125</v>
+      </c>
+      <c r="C110" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>127</v>
+      </c>
+      <c r="B111" t="s">
+        <v>125</v>
+      </c>
+      <c r="C111" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>128</v>
+      </c>
+      <c r="B112" t="s">
+        <v>125</v>
+      </c>
+      <c r="C112" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>52</v>
+      </c>
+      <c r="F112" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G112" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>129</v>
+      </c>
+      <c r="B113" t="s">
+        <v>125</v>
+      </c>
+      <c r="C113" t="n">
+        <v>50</v>
+      </c>
+      <c r="D113" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F113" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>75</v>
+      </c>
+      <c r="K113" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+      <c r="B114" t="s">
+        <v>125</v>
+      </c>
+      <c r="C114" t="n">
+        <v>50</v>
+      </c>
+      <c r="D114" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I114" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K114" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>131</v>
+      </c>
+      <c r="B115" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>25</v>
+      </c>
+      <c r="E115" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F115" t="n">
+        <v>25</v>
+      </c>
+      <c r="G115" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>100</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>132</v>
+      </c>
+      <c r="B116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C116" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I116" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K116" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+      <c r="B117" t="s">
+        <v>125</v>
+      </c>
+      <c r="C117" t="n">
+        <v>45</v>
+      </c>
+      <c r="D117" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E117" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G117" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>100</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" t="s">
+        <v>125</v>
+      </c>
+      <c r="C118" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D118" t="n">
+        <v>20</v>
+      </c>
+      <c r="E118" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>50</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>135</v>
+      </c>
+      <c r="B119" t="s">
+        <v>125</v>
+      </c>
+      <c r="C119" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D119" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>100</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120" t="s">
+        <v>136</v>
+      </c>
+      <c r="C120" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E120" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F120" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G120" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H120" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I120" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J120" t="n">
+        <v>28</v>
+      </c>
+      <c r="K120" t="n">
+        <v>31.8</v>
       </c>
     </row>
   </sheetData>
@@ -4641,22 +5175,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -4665,13 +5199,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
@@ -4746,7 +5280,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -4781,7 +5315,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -4816,7 +5350,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -4851,7 +5385,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -4886,37 +5420,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>92.9</v>
+        <v>87.8</v>
       </c>
       <c r="D8" t="n">
-        <v>87.1</v>
+        <v>79.3</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>36.4</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>41.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>24.6</v>
       </c>
       <c r="K8" t="n">
-        <v>7.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9">
@@ -4991,7 +5525,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -5026,7 +5560,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -5059,42 +5593,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65.4</v>
+        <v>65.1</v>
       </c>
       <c r="E13" t="n">
-        <v>9.4</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="G13" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="H13" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -5129,7 +5663,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -5164,7 +5698,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -5199,75 +5733,77 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="D17" t="n">
-        <v>36.8</v>
+        <v>55.8</v>
       </c>
       <c r="E17" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H17" t="n">
         <v>100</v>
       </c>
-      <c r="H17"/>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>66.1</v>
+        <v>65.3</v>
       </c>
       <c r="D18" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="E18" t="n">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
       <c r="F18" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="G18" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H18" t="n">
-        <v>53.7</v>
+        <v>51.5</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="K18" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -5302,10 +5838,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n">
         <v>70</v>
@@ -5337,10 +5873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="n">
         <v>76.8</v>
@@ -5372,10 +5908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="n">
         <v>50</v>
@@ -5407,10 +5943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
         <v>83.3</v>
@@ -5442,10 +5978,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
         <v>37.5</v>
@@ -5477,10 +6013,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
         <v>51.4</v>
@@ -5512,10 +6048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="n">
         <v>80</v>
@@ -5547,10 +6083,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="n">
         <v>66.7</v>
@@ -5582,10 +6118,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" t="n">
         <v>33.3</v>
@@ -5617,10 +6153,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" t="n">
         <v>57.9</v>
@@ -5652,10 +6188,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" t="n">
         <v>62.8</v>
@@ -5687,10 +6223,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -5720,10 +6256,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="n">
         <v>28.6</v>
@@ -5755,10 +6291,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" t="n">
         <v>71.4</v>
@@ -5790,10 +6326,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" t="n">
         <v>66.7</v>
@@ -5825,10 +6361,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" t="n">
         <v>100</v>
@@ -5858,69 +6394,69 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C36" t="n">
-        <v>63</v>
+        <v>44.4</v>
       </c>
       <c r="D36" t="n">
-        <v>57.8</v>
+        <v>49.2</v>
       </c>
       <c r="E36" t="n">
-        <v>13.6</v>
+        <v>9.1</v>
       </c>
       <c r="F36" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="G36" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>23.5</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>87.5</v>
+        <v>52.9</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H37" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -5928,69 +6464,63 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C38" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>74.7</v>
+        <v>7.7</v>
       </c>
       <c r="E38" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38"/>
       <c r="G38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H38" t="n">
-        <v>57.9</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H38"/>
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="J38"/>
       <c r="K38" t="n">
-        <v>19.3</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C39" t="n">
-        <v>61.5</v>
+        <v>35.3</v>
       </c>
       <c r="D39" t="n">
-        <v>63.2</v>
+        <v>57.6</v>
       </c>
       <c r="E39" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F39" t="n">
         <v>20</v>
       </c>
-      <c r="F39" t="n">
-        <v>30.8</v>
-      </c>
       <c r="G39" t="n">
-        <v>15.4</v>
+        <v>11.8</v>
       </c>
       <c r="H39" t="n">
-        <v>66.7</v>
+        <v>23.1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>21.4</v>
+        <v>23.1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -5998,51 +6528,51 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C40" t="n">
-        <v>58.3</v>
+        <v>55.6</v>
       </c>
       <c r="D40" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="E40" t="n">
-        <v>31.4</v>
+        <v>7.1</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H40" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="K40" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>41.2</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -6051,42 +6581,42 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>20</v>
       </c>
-      <c r="H41" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C42" t="n">
-        <v>14.3</v>
+        <v>63</v>
       </c>
       <c r="D42" t="n">
-        <v>44.1</v>
+        <v>57.8</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F42" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="G42" t="n">
-        <v>28.6</v>
+        <v>11.5</v>
       </c>
       <c r="H42" t="n">
         <v>50</v>
@@ -6095,24 +6625,24 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>33.3</v>
+        <v>23.5</v>
       </c>
       <c r="K42" t="n">
-        <v>-14.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43" t="n">
-        <v>38.9</v>
+        <v>87.5</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -6121,11 +6651,11 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
         <v>66.7</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -6133,124 +6663,138 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="D44" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>50</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H44" t="n">
         <v>57.9</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>25</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>28.6</v>
+        <v>24.4</v>
       </c>
       <c r="K44" t="n">
-        <v>-25</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="D45" t="n">
-        <v>41.4</v>
+        <v>63.2</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="G45" t="n">
-        <v>33.3</v>
+        <v>15.4</v>
       </c>
       <c r="H45" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
+        <v>65.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>25</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8.3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C47" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="D47" t="n">
-        <v>57.5</v>
+        <v>41.2</v>
       </c>
       <c r="E47" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>51.9</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="H47" t="n">
-        <v>47.8</v>
+        <v>33.3</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -6259,91 +6803,91 @@
         <v>25</v>
       </c>
       <c r="K47" t="n">
-        <v>8.4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="D48" t="n">
-        <v>59.3</v>
+        <v>44.1</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="G48" t="n">
-        <v>7.1</v>
+        <v>28.6</v>
       </c>
       <c r="H48" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
       <c r="K48" t="n">
-        <v>7.2</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>38.9</v>
       </c>
       <c r="E49" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>6.7</v>
+        <v>66.7</v>
       </c>
       <c r="H49" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>16.6</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>87.5</v>
+        <v>57.9</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -6352,216 +6896,218 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>41.4</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51"/>
+        <v>15</v>
+      </c>
+      <c r="F51" t="n">
+        <v>33.3</v>
+      </c>
       <c r="G51" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-66.7</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C52" t="n">
-        <v>77.8</v>
+        <v>57.1</v>
       </c>
       <c r="D52" t="n">
-        <v>63.4</v>
+        <v>57.5</v>
       </c>
       <c r="E52" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="H52" t="n">
-        <v>27.3</v>
+        <v>47.8</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>27.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C53" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>80</v>
+        <v>59.3</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>50</v>
+        <v>8.3</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C54" t="n">
+        <v>50</v>
+      </c>
+      <c r="D54" t="n">
+        <v>60</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H54" t="n">
         <v>40</v>
       </c>
-      <c r="D54" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>100</v>
-      </c>
-      <c r="G54" t="n">
-        <v>40</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
-        <v>33.3</v>
+        <v>29.4</v>
       </c>
       <c r="K54" t="n">
-        <v>-20</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C55" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>57.1</v>
+        <v>87.5</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55"/>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>39.1</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F56"/>
       <c r="G56" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -6570,59 +7116,59 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>-33.3</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C57" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D57" t="n">
-        <v>53.3</v>
+        <v>63.4</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>28.6</v>
+        <v>27.3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>7.1</v>
+        <v>27.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C58" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D58" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E58" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -6631,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -6645,105 +7191,243 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C59" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D59" t="n">
-        <v>55.2</v>
+        <v>31.6</v>
       </c>
       <c r="E59" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="F59" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H59" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C60" t="n">
-        <v>70.6</v>
+        <v>66.7</v>
       </c>
       <c r="D60" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60"/>
+      <c r="G60" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" t="n">
+        <v>50</v>
+      </c>
+      <c r="D61" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>196</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D62" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" t="n">
+        <v>52</v>
+      </c>
+      <c r="D63" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D64" t="n">
         <v>59.2</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E64" t="n">
         <v>16</v>
       </c>
-      <c r="F60" t="n">
-        <v>50</v>
-      </c>
-      <c r="G60" t="n">
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>5.9</v>
       </c>
-      <c r="H60" t="n">
-        <v>50</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" t="n">
         <v>5.9</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J64" t="n">
         <v>17.4</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61"/>
-      <c r="B61" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" t="n">
-        <v>57</v>
-      </c>
-      <c r="D61" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>12</v>
-      </c>
-      <c r="F61" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="G61" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H61" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-3.9</v>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65"/>
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" t="n">
+        <v>41</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-3.4</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -117,12 +117,15 @@
     <t xml:space="preserve">Tobey Drennan</t>
   </si>
   <si>
+    <t xml:space="preserve">Adrian Crewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guelph Gryphons</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alex Peiper</t>
   </si>
   <si>
-    <t xml:space="preserve">Guelph Gryphons</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andrew Johnston</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
     <t xml:space="preserve">Jaylen Wood</t>
   </si>
   <si>
+    <t xml:space="preserve">Julian Fabrizio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marco Da Gama</t>
   </si>
   <si>
@@ -496,6 +502,9 @@
   </si>
   <si>
     <t xml:space="preserve">J.C. Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Reynolds</t>
   </si>
   <si>
     <t xml:space="preserve">Landon Hutar</t>
@@ -664,8 +673,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K120" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K120"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K122" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K122"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -684,8 +693,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K65" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K66" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K66"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1041,31 +1050,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>62.2</v>
+        <v>60.6</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="E2" t="n">
-        <v>54.9</v>
+        <v>53.4</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="H2" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="I2" t="n">
-        <v>56.5</v>
+        <v>54.2</v>
       </c>
       <c r="J2" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="K2" t="n">
-        <v>43.5</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="3">
@@ -1076,31 +1085,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>75.2</v>
+        <v>74.6</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="E3" t="n">
-        <v>61.2</v>
+        <v>59.4</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="G3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="H3" t="n">
-        <v>8.2</v>
+        <v>7.8</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="J3" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="K3" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="4">
@@ -1251,31 +1260,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>79.1</v>
+        <v>78.9</v>
       </c>
       <c r="D8" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>57.8</v>
+        <v>58.9</v>
       </c>
       <c r="F8" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="H8" t="n">
-        <v>11.3</v>
+        <v>13.5</v>
       </c>
       <c r="I8" t="n">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="J8" t="n">
-        <v>29.2</v>
+        <v>28.6</v>
       </c>
       <c r="K8" t="n">
-        <v>41.7</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="9">
@@ -1286,31 +1295,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>76.1</v>
+        <v>74.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E9" t="n">
-        <v>73.1</v>
+        <v>71.7</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>19.6</v>
+        <v>18.3</v>
       </c>
       <c r="H9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="I9" t="n">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="J9" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>57.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="10">
@@ -1420,22 +1429,22 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.9</v>
+        <v>66.7</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="n">
-        <v>50.5</v>
+        <v>49.3</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="G13" t="n">
-        <v>30.5</v>
+        <v>32.4</v>
       </c>
       <c r="H13" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="I13" t="n">
         <v>48.8</v>
@@ -1519,31 +1528,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>77.8</v>
+        <v>76.7</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="E16" t="n">
-        <v>67.8</v>
+        <v>66.1</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="G16" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="I16" t="n">
-        <v>46.2</v>
+        <v>53.3</v>
       </c>
       <c r="J16" t="n">
-        <v>30.8</v>
+        <v>26.7</v>
       </c>
       <c r="K16" t="n">
-        <v>69.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="17">
@@ -1554,31 +1563,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>65.9</v>
+        <v>66.7</v>
       </c>
       <c r="D17" t="n">
-        <v>9.1</v>
+        <v>10.3</v>
       </c>
       <c r="E17" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="F17" t="n">
-        <v>9.1</v>
+        <v>10.3</v>
       </c>
       <c r="G17" t="n">
-        <v>16.7</v>
+        <v>14.7</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="I17" t="n">
-        <v>23.5</v>
+        <v>26.3</v>
       </c>
       <c r="J17" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="K17" t="n">
-        <v>29.4</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="18">
@@ -1624,31 +1633,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>68.4</v>
+        <v>65.9</v>
       </c>
       <c r="D19" t="n">
-        <v>19.4</v>
+        <v>17.5</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="F19" t="n">
-        <v>19.4</v>
+        <v>17.5</v>
       </c>
       <c r="G19" t="n">
-        <v>27.3</v>
+        <v>30.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="J19" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>35.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1659,31 +1668,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>78.9</v>
+        <v>78.4</v>
       </c>
       <c r="D20" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="E20" t="n">
         <v>61.6</v>
       </c>
       <c r="F20" t="n">
-        <v>17.3</v>
+        <v>16.8</v>
       </c>
       <c r="G20" t="n">
-        <v>22.8</v>
+        <v>23.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I20" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K20" t="n">
         <v>35.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>37.3</v>
       </c>
     </row>
     <row r="21">
@@ -1799,31 +1808,31 @@
         <v>35</v>
       </c>
       <c r="C24" t="n">
+        <v>80</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>100</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>50</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="25">
@@ -1834,31 +1843,31 @@
         <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
       </c>
       <c r="H25" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1869,31 +1878,31 @@
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>86.7</v>
+        <v>66.7</v>
       </c>
       <c r="D26" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="n">
-        <v>77.6</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="G26" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
-        <v>11.1</v>
+        <v>30</v>
       </c>
       <c r="I26" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -1904,31 +1913,31 @@
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>86.7</v>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>77.6</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
@@ -1939,31 +1948,31 @@
         <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>62.5</v>
+        <v>88.9</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>52.5</v>
+        <v>38.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>9.1</v>
+        <v>75</v>
       </c>
       <c r="J28" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>9.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -1974,31 +1983,31 @@
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>82.1</v>
+        <v>63.9</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>16.2</v>
       </c>
       <c r="E29" t="n">
-        <v>62.1</v>
+        <v>47.7</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>16.2</v>
       </c>
       <c r="G29" t="n">
-        <v>21.4</v>
+        <v>30</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>53.8</v>
+        <v>8.3</v>
       </c>
       <c r="J29" t="n">
-        <v>15.4</v>
+        <v>58.3</v>
       </c>
       <c r="K29" t="n">
-        <v>69.2</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="30">
@@ -2009,31 +2018,31 @@
         <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>76</v>
+        <v>83.3</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>25.8</v>
       </c>
       <c r="E30" t="n">
-        <v>63</v>
+        <v>57.5</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>25.8</v>
       </c>
       <c r="G30" t="n">
-        <v>31.8</v>
+        <v>21.1</v>
       </c>
       <c r="H30" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J30" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="K30" t="n">
-        <v>11.1</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="31">
@@ -2044,31 +2053,31 @@
         <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>71.9</v>
+        <v>73.3</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="n">
-        <v>67.9</v>
+        <v>62.2</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>11.1</v>
       </c>
       <c r="G31" t="n">
-        <v>16.7</v>
+        <v>32</v>
       </c>
       <c r="H31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="32">
@@ -2079,31 +2088,31 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>78.4</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="J32" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="K32" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2114,31 +2123,31 @@
         <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>59.3</v>
+        <v>66.7</v>
       </c>
       <c r="D33" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="n">
-        <v>50.2</v>
+        <v>53.4</v>
       </c>
       <c r="F33" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="G33" t="n">
-        <v>42.1</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>13.3</v>
+        <v>9.5</v>
       </c>
       <c r="I33" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J33" t="n">
-        <v>50</v>
+        <v>21.4</v>
       </c>
       <c r="K33" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -2149,31 +2158,31 @@
         <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>78.4</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I34" t="n">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="35">
@@ -2184,31 +2193,31 @@
         <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>63.6</v>
+        <v>60</v>
       </c>
       <c r="D35" t="n">
-        <v>22.2</v>
+        <v>7.9</v>
       </c>
       <c r="E35" t="n">
-        <v>41.4</v>
+        <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>22.2</v>
+        <v>7.9</v>
       </c>
       <c r="G35" t="n">
-        <v>11.1</v>
+        <v>41.7</v>
       </c>
       <c r="H35" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I35" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="36">
@@ -2219,31 +2228,31 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2254,31 +2263,31 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>56.2</v>
+        <v>63.6</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>22.2</v>
       </c>
       <c r="E37" t="n">
-        <v>26.2</v>
+        <v>41.4</v>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>22.2</v>
       </c>
       <c r="G37" t="n">
-        <v>41.7</v>
+        <v>11.1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I37" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -2286,101 +2295,101 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>36.3</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G38" t="n">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="H38" t="n">
-        <v>42.9</v>
+        <v>11.8</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>26.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G39" t="n">
-        <v>26.7</v>
+        <v>41.7</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="J39" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
         <v>52</v>
       </c>
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>27.5</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2391,34 +2400,34 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C41" t="n">
-        <v>47.1</v>
+        <v>60</v>
       </c>
       <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J41" t="n">
         <v>16.7</v>
       </c>
-      <c r="E41" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>28.6</v>
-      </c>
       <c r="K41" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="42">
@@ -2426,22 +2435,22 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C42" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="n">
-        <v>41.7</v>
+        <v>27.5</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2453,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2461,34 +2470,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C43" t="n">
-        <v>87.5</v>
+        <v>47.1</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E43" t="n">
-        <v>67.5</v>
+        <v>30.4</v>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G43" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J43" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K43" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="44">
@@ -2496,61 +2505,69 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44"/>
+        <v>25</v>
+      </c>
+      <c r="G44" t="n">
+        <v>25</v>
+      </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44"/>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C45" t="n">
-        <v>57.7</v>
+        <v>87.5</v>
       </c>
       <c r="D45" t="n">
-        <v>17.6</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>40.1</v>
+        <v>67.5</v>
       </c>
       <c r="F45" t="n">
-        <v>17.6</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>5.6</v>
+        <v>37.5</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="J45" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="K45" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="46">
@@ -2558,69 +2575,61 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
+      <c r="G46"/>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>25</v>
-      </c>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D47" t="n">
-        <v>7.7</v>
+        <v>17.6</v>
       </c>
       <c r="E47" t="n">
-        <v>42.3</v>
+        <v>40.1</v>
       </c>
       <c r="F47" t="n">
-        <v>7.7</v>
+        <v>17.6</v>
       </c>
       <c r="G47" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K47" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="48">
@@ -2628,34 +2637,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C48" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>25</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>50</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="49">
@@ -2663,34 +2672,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>14.3</v>
+        <v>7.7</v>
       </c>
       <c r="E49" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="F49" t="n">
-        <v>14.3</v>
+        <v>7.7</v>
       </c>
       <c r="G49" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="50">
@@ -2698,34 +2707,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C50" t="n">
         <v>66.7</v>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="F50" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -2733,34 +2742,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C51" t="n">
-        <v>36.4</v>
+        <v>55.6</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>14.3</v>
       </c>
       <c r="E51" t="n">
-        <v>-33.6</v>
+        <v>41.3</v>
       </c>
       <c r="F51" t="n">
-        <v>70</v>
+        <v>14.3</v>
       </c>
       <c r="G51" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I51" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2768,34 +2777,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C52" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="D52" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="G52" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I52" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -2803,86 +2812,86 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>42.9</v>
+        <v>36.4</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E53" t="n">
-        <v>42.9</v>
+        <v>-33.6</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J53" t="n">
         <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="D54" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="E54" t="n">
-        <v>58.3</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="G54" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" t="s">
         <v>68</v>
       </c>
-      <c r="B55" t="s">
-        <v>66</v>
-      </c>
       <c r="C55" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2894,13 +2903,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>33.3</v>
       </c>
       <c r="K55" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="56">
@@ -2908,34 +2917,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G56" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
+        <v>75</v>
+      </c>
+      <c r="J56" t="n">
         <v>25</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>75</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2943,34 +2952,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C57" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5.6</v>
+        <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="58">
@@ -2978,34 +2987,34 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C58" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
       <c r="F58" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G58" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3013,34 +3022,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C59" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E59" t="n">
-        <v>46.7</v>
+        <v>5.6</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3048,22 +3057,22 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>43.1</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3072,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -3083,22 +3092,22 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C61" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>46.7</v>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G61" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3110,7 +3119,7 @@
         <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -3118,14 +3127,20 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C62" t="n">
-        <v>80</v>
-      </c>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
+        <v>50</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>50</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
@@ -3133,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3147,31 +3162,31 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C63" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="E63" t="n">
-        <v>67.5</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H63" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3182,20 +3197,14 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C64" t="n">
-        <v>100</v>
-      </c>
-      <c r="D64" t="n">
-        <v>25</v>
-      </c>
-      <c r="E64" t="n">
-        <v>75</v>
-      </c>
-      <c r="F64" t="n">
-        <v>25</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
       <c r="G64" t="n">
         <v>0</v>
       </c>
@@ -3203,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K64" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="65">
@@ -3217,25 +3226,25 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>46.7</v>
+        <v>78.6</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="n">
-        <v>26.7</v>
+        <v>67.5</v>
       </c>
       <c r="F65" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="G65" t="n">
-        <v>75</v>
+        <v>16.7</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
@@ -3244,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3252,34 +3261,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D66" t="n">
+        <v>25</v>
+      </c>
+      <c r="E66" t="n">
         <v>75</v>
       </c>
-      <c r="E66" t="n">
-        <v>-8.3</v>
-      </c>
       <c r="F66" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>50</v>
-      </c>
-      <c r="J66" t="n">
-        <v>25</v>
-      </c>
-      <c r="K66" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="67">
@@ -3287,28 +3296,28 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C67" t="n">
-        <v>53.8</v>
+        <v>46.7</v>
       </c>
       <c r="D67" t="n">
-        <v>45.5</v>
+        <v>20</v>
       </c>
       <c r="E67" t="n">
-        <v>8.3</v>
+        <v>26.7</v>
       </c>
       <c r="F67" t="n">
-        <v>45.5</v>
+        <v>20</v>
       </c>
       <c r="G67" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="H67" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3319,19 +3328,25 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
-      </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
+        <v>66.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>75</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-8.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>75</v>
+      </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3340,45 +3355,45 @@
         <v>50</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" t="s">
         <v>83</v>
       </c>
-      <c r="B69" t="s">
-        <v>81</v>
-      </c>
       <c r="C69" t="n">
-        <v>78.6</v>
+        <v>53.8</v>
       </c>
       <c r="D69" t="n">
-        <v>36.4</v>
+        <v>45.5</v>
       </c>
       <c r="E69" t="n">
-        <v>42.2</v>
+        <v>8.3</v>
       </c>
       <c r="F69" t="n">
-        <v>36.4</v>
+        <v>45.5</v>
       </c>
       <c r="G69" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="H69" t="n">
         <v>14.3</v>
       </c>
       <c r="I69" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J69" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
@@ -3386,34 +3401,28 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C70" t="n">
-        <v>76.9</v>
-      </c>
-      <c r="D70" t="n">
-        <v>25</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
       <c r="G70" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J70" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -3421,28 +3430,28 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C71" t="n">
-        <v>83.3</v>
+        <v>78.6</v>
       </c>
       <c r="D71" t="n">
-        <v>28.6</v>
+        <v>36.4</v>
       </c>
       <c r="E71" t="n">
-        <v>54.7</v>
+        <v>42.2</v>
       </c>
       <c r="F71" t="n">
-        <v>28.6</v>
+        <v>36.4</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="H71" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I71" t="n">
         <v>33.3</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>50</v>
@@ -3456,34 +3465,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C72" t="n">
-        <v>57.1</v>
+        <v>76.9</v>
       </c>
       <c r="D72" t="n">
         <v>25</v>
       </c>
       <c r="E72" t="n">
-        <v>32.1</v>
+        <v>51.9</v>
       </c>
       <c r="F72" t="n">
         <v>25</v>
       </c>
       <c r="G72" t="n">
-        <v>40</v>
+        <v>9.1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="73">
@@ -3491,34 +3500,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C73" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E73" t="n">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G73" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I73" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3526,34 +3535,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C74" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="D74" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E74" t="n">
-        <v>43.3</v>
+        <v>32.1</v>
       </c>
       <c r="F74" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G74" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3561,34 +3570,34 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C75" t="n">
-        <v>58.8</v>
+        <v>100</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>58.8</v>
+        <v>100</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>66.7</v>
       </c>
       <c r="H75" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J75" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
@@ -3596,34 +3605,34 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C76" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="D76" t="n">
         <v>16.7</v>
       </c>
       <c r="E76" t="n">
-        <v>66.6</v>
+        <v>43.3</v>
       </c>
       <c r="F76" t="n">
         <v>16.7</v>
       </c>
       <c r="G76" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="H76" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J76" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -3631,34 +3640,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C77" t="n">
-        <v>81.8</v>
+        <v>58.8</v>
       </c>
       <c r="D77" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>72.7</v>
+        <v>58.8</v>
       </c>
       <c r="F77" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H77" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I77" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K77" t="n">
-        <v>75</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="78">
@@ -3666,174 +3675,174 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C78" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="D78" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="E78" t="n">
-        <v>58.4</v>
+        <v>66.6</v>
       </c>
       <c r="F78" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="G78" t="n">
-        <v>9.1</v>
+        <v>42.9</v>
       </c>
       <c r="H78" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I78" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K78" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E79" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>8.3</v>
       </c>
       <c r="E80" t="n">
-        <v>50.4</v>
+        <v>58.4</v>
       </c>
       <c r="F80" t="n">
-        <v>11.1</v>
+        <v>8.3</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="H80" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="I80" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J80" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C81" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="D81" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>63.5</v>
+        <v>50</v>
       </c>
       <c r="F81" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" t="s">
         <v>96</v>
       </c>
-      <c r="B82" t="s">
-        <v>94</v>
-      </c>
       <c r="C82" t="n">
-        <v>88.9</v>
+        <v>61.5</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="n">
-        <v>88.9</v>
+        <v>50.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H82" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="I82" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K82" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3841,34 +3850,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C83" t="n">
-        <v>78.6</v>
+        <v>85.7</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E83" t="n">
-        <v>78.6</v>
+        <v>63.5</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G83" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -3876,34 +3885,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C84" t="n">
-        <v>64.3</v>
+        <v>88.9</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>64.3</v>
+        <v>88.9</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="I84" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
         <v>20</v>
-      </c>
-      <c r="K84" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -3911,34 +3920,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C85" t="n">
-        <v>80</v>
+        <v>78.6</v>
       </c>
       <c r="D85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>55</v>
+        <v>78.6</v>
       </c>
       <c r="F85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="J85" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3946,34 +3955,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C86" t="n">
-        <v>85.7</v>
+        <v>64.3</v>
       </c>
       <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H86" t="n">
         <v>25</v>
       </c>
-      <c r="E86" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F86" t="n">
-        <v>25</v>
-      </c>
-      <c r="G86" t="n">
-        <v>25</v>
-      </c>
-      <c r="H86" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J86" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -3981,34 +3990,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C87" t="n">
-        <v>90.9</v>
+        <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E87" t="n">
-        <v>90.9</v>
+        <v>55</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J87" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K87" t="n">
-        <v>37.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="88">
@@ -4016,34 +4025,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C88" t="n">
-        <v>77.8</v>
+        <v>85.7</v>
       </c>
       <c r="D88" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E88" t="n">
-        <v>61.1</v>
+        <v>60.7</v>
       </c>
       <c r="F88" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G88" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="H88" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="I88" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J88" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4051,34 +4060,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C89" t="n">
-        <v>85.7</v>
+        <v>90.9</v>
       </c>
       <c r="D89" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>66.9</v>
+        <v>90.9</v>
       </c>
       <c r="F89" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K89" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="90">
@@ -4086,31 +4095,31 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C90" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D90" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E90" t="n">
-        <v>52.4</v>
+        <v>61.1</v>
       </c>
       <c r="F90" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G90" t="n">
-        <v>35.7</v>
+        <v>4.2</v>
       </c>
       <c r="H90" t="n">
         <v>11.1</v>
       </c>
       <c r="I90" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J90" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="K90" t="n">
         <v>33.3</v>
@@ -4118,72 +4127,72 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C91" t="n">
-        <v>55.6</v>
+        <v>85.7</v>
       </c>
       <c r="D91" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E91" t="n">
-        <v>33.4</v>
+        <v>66.9</v>
       </c>
       <c r="F91" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="G91" t="n">
-        <v>42.9</v>
+        <v>6.7</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I91" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>106</v>
+      </c>
+      <c r="B92" t="s">
         <v>107</v>
       </c>
-      <c r="B92" t="s">
-        <v>105</v>
-      </c>
       <c r="C92" t="n">
-        <v>80.8</v>
+        <v>66.7</v>
       </c>
       <c r="D92" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="E92" t="n">
-        <v>62.6</v>
+        <v>52.4</v>
       </c>
       <c r="F92" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="G92" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="H92" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="I92" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J92" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="93">
@@ -4191,34 +4200,34 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C93" t="n">
-        <v>91.7</v>
+        <v>55.6</v>
       </c>
       <c r="D93" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="E93" t="n">
-        <v>41.7</v>
+        <v>33.4</v>
       </c>
       <c r="F93" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="G93" t="n">
-        <v>21.4</v>
+        <v>42.9</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="J93" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4226,34 +4235,34 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C94" t="n">
-        <v>60</v>
+        <v>80.8</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E94" t="n">
-        <v>60</v>
+        <v>62.6</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I94" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
@@ -4261,34 +4270,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C95" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E95" t="n">
-        <v>80</v>
+        <v>41.7</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G95" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>28.6</v>
       </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>66.7</v>
-      </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="96">
@@ -4296,19 +4305,19 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C96" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="F96" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -4317,13 +4326,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4331,31 +4340,31 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C97" t="n">
         <v>100</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E97" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4366,34 +4375,34 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="D98" t="n">
-        <v>28.6</v>
+        <v>8.3</v>
       </c>
       <c r="E98" t="n">
-        <v>54.7</v>
+        <v>66.7</v>
       </c>
       <c r="F98" t="n">
-        <v>28.6</v>
+        <v>8.3</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K98" t="n">
-        <v>16.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="99">
@@ -4401,34 +4410,34 @@
         <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C99" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K99" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4436,34 +4445,34 @@
         <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C100" t="n">
-        <v>70</v>
+        <v>83.3</v>
       </c>
       <c r="D100" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="E100" t="n">
-        <v>32.5</v>
+        <v>54.7</v>
       </c>
       <c r="F100" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="G100" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="J100" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K100" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="101">
@@ -4471,34 +4480,34 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C101" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="D101" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
       <c r="F101" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>46.7</v>
+        <v>25</v>
       </c>
       <c r="H101" t="n">
         <v>14.3</v>
       </c>
       <c r="I101" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
@@ -4506,34 +4515,34 @@
         <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C102" t="n">
-        <v>84.6</v>
+        <v>70</v>
       </c>
       <c r="D102" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="E102" t="n">
-        <v>70.3</v>
+        <v>32.5</v>
       </c>
       <c r="F102" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="G102" t="n">
-        <v>13</v>
+        <v>17.6</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>43.8</v>
+        <v>37.5</v>
       </c>
       <c r="J102" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="K102" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -4541,34 +4550,34 @@
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C103" t="n">
-        <v>68.6</v>
+        <v>75</v>
       </c>
       <c r="D103" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="E103" t="n">
-        <v>59.5</v>
+        <v>53.6</v>
       </c>
       <c r="F103" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="G103" t="n">
-        <v>23.1</v>
+        <v>46.7</v>
       </c>
       <c r="H103" t="n">
-        <v>6.7</v>
+        <v>14.3</v>
       </c>
       <c r="I103" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="J103" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="104">
@@ -4576,34 +4585,34 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>50</v>
+        <v>84.6</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E104" t="n">
-        <v>50</v>
+        <v>70.3</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="105">
@@ -4611,34 +4620,34 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C105" t="n">
-        <v>90.9</v>
+        <v>68.6</v>
       </c>
       <c r="D105" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="E105" t="n">
-        <v>70.9</v>
+        <v>59.5</v>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="G105" t="n">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I105" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J105" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="K105" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="106">
@@ -4646,34 +4655,34 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C106" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D106" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>17.1</v>
+        <v>50</v>
       </c>
       <c r="F106" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J106" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4681,34 +4690,34 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C107" t="n">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="D107" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E107" t="n">
-        <v>73.3</v>
+        <v>70.9</v>
       </c>
       <c r="F107" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G107" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J107" t="n">
         <v>33.3</v>
       </c>
-      <c r="J107" t="n">
-        <v>50</v>
-      </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
@@ -4716,34 +4725,34 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C108" t="n">
+        <v>60</v>
+      </c>
+      <c r="D108" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E108" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
         <v>100</v>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>100</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J108" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K108" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109">
@@ -4751,83 +4760,95 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C109" t="n">
+        <v>90</v>
+      </c>
+      <c r="D109" t="n">
         <v>16.7</v>
       </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
       <c r="E109" t="n">
-        <v>5.6</v>
+        <v>73.3</v>
       </c>
       <c r="F109" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="G109" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="H109" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I109"/>
-      <c r="J109"/>
-      <c r="K109"/>
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>50</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C110" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I110"/>
-      <c r="J110"/>
-      <c r="K110"/>
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K110" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>126</v>
+      </c>
+      <c r="B111" t="s">
         <v>127</v>
       </c>
-      <c r="B111" t="s">
-        <v>125</v>
-      </c>
       <c r="C111" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I111"/>
       <c r="J111"/>
@@ -4838,104 +4859,92 @@
         <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C112" t="n">
-        <v>61.1</v>
+        <v>42.9</v>
       </c>
       <c r="D112" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>52</v>
+        <v>42.9</v>
       </c>
       <c r="F112" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>8.3</v>
+        <v>66.7</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>14.3</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C113" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D113" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="F113" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>75</v>
-      </c>
-      <c r="K113" t="n">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C114" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D114" t="n">
-        <v>23.1</v>
+        <v>9.1</v>
       </c>
       <c r="E114" t="n">
-        <v>26.9</v>
+        <v>52</v>
       </c>
       <c r="F114" t="n">
-        <v>23.1</v>
+        <v>9.1</v>
       </c>
       <c r="G114" t="n">
-        <v>37.5</v>
+        <v>8.3</v>
       </c>
       <c r="H114" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="J114" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>66.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="115">
@@ -4943,34 +4952,34 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C115" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D115" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F115" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H115" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>75</v>
+      </c>
+      <c r="K115" t="n">
         <v>25</v>
-      </c>
-      <c r="E115" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F115" t="n">
-        <v>25</v>
-      </c>
-      <c r="G115" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="n">
-        <v>100</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -4978,34 +4987,34 @@
         <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C116" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E116" t="n">
-        <v>61.5</v>
+        <v>26.9</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="G116" t="n">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="H116" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I116" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J116" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K116" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="117">
@@ -5013,22 +5022,22 @@
         <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C117" t="n">
-        <v>45</v>
+        <v>66.7</v>
       </c>
       <c r="D117" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E117" t="n">
-        <v>28.3</v>
+        <v>41.7</v>
       </c>
       <c r="F117" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G117" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5048,34 +5057,34 @@
         <v>134</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C118" t="n">
-        <v>71.4</v>
+        <v>61.5</v>
       </c>
       <c r="D118" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>51.4</v>
+        <v>61.5</v>
       </c>
       <c r="F118" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J118" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="119">
@@ -5083,67 +5092,137 @@
         <v>135</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C119" t="n">
+        <v>45</v>
+      </c>
+      <c r="D119" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E119" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G119" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>100</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>136</v>
+      </c>
+      <c r="B120" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120" t="n">
         <v>71.4</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D120" t="n">
+        <v>20</v>
+      </c>
+      <c r="E120" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F120" t="n">
+        <v>20</v>
+      </c>
+      <c r="G120" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>50</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>137</v>
+      </c>
+      <c r="B121" t="s">
+        <v>127</v>
+      </c>
+      <c r="C121" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D121" t="n">
         <v>7.1</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E121" t="n">
         <v>64.3</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F121" t="n">
         <v>7.1</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G121" t="n">
         <v>18.2</v>
       </c>
-      <c r="H119" t="n">
+      <c r="H121" t="n">
         <v>12.5</v>
       </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
         <v>100</v>
       </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120"/>
-      <c r="B120" t="s">
-        <v>136</v>
-      </c>
-      <c r="C120" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="D120" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="E120" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F120" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G120" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H120" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I120" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>28</v>
-      </c>
-      <c r="K120" t="n">
-        <v>31.8</v>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122" t="s">
+        <v>138</v>
+      </c>
+      <c r="C122" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E122" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G122" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="I122" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="J122" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K122" t="n">
+        <v>32.4</v>
       </c>
     </row>
   </sheetData>
@@ -5175,22 +5254,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5199,13 +5278,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2">
@@ -5280,7 +5359,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -5315,7 +5394,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5350,7 +5429,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5385,7 +5464,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5420,7 +5499,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -5525,7 +5604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -5560,7 +5639,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -5593,42 +5672,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53.1</v>
       </c>
       <c r="D13" t="n">
-        <v>65.1</v>
+        <v>66.3</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>22.8</v>
       </c>
       <c r="F13" t="n">
-        <v>38.5</v>
+        <v>40.7</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1</v>
+        <v>8.2</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>60.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>26.5</v>
+        <v>28.2</v>
       </c>
       <c r="K13" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -5663,7 +5742,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -5698,7 +5777,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -5733,7 +5812,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -5768,7 +5847,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -5803,7 +5882,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -5838,42 +5917,42 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="n">
-        <v>70</v>
+        <v>55.6</v>
       </c>
       <c r="D20" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-10</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
@@ -5908,42 +5987,42 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="D22" t="n">
-        <v>57.5</v>
+        <v>54.9</v>
       </c>
       <c r="E22" t="n">
-        <v>5.1</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="H22" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>21.1</v>
+        <v>23.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -5978,156 +6057,156 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>37.5</v>
+        <v>58.3</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>52.1</v>
       </c>
       <c r="E24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="H24" t="n">
-        <v>38.5</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>18.2</v>
+        <v>42.9</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>51.4</v>
+        <v>37.5</v>
       </c>
       <c r="D25" t="n">
-        <v>59.4</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
-        <v>13.2</v>
+        <v>4.5</v>
       </c>
       <c r="F25" t="n">
-        <v>42.1</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="H25" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>27</v>
+        <v>18.2</v>
       </c>
       <c r="K25" t="n">
-        <v>11.5</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>80</v>
+        <v>51.4</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>59.4</v>
       </c>
       <c r="E26" t="n">
-        <v>28.6</v>
+        <v>13.2</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>42.1</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>45.5</v>
+        <v>27</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D27" t="n">
-        <v>57.1</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K27" t="n">
         <v>40</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-16.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6136,292 +6215,292 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>57.9</v>
+        <v>33.3</v>
       </c>
       <c r="D29" t="n">
         <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C30" t="n">
-        <v>62.8</v>
+        <v>57.9</v>
       </c>
       <c r="D30" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>9.3</v>
       </c>
       <c r="F30" t="n">
-        <v>41.7</v>
+        <v>12.5</v>
       </c>
       <c r="G30" t="n">
-        <v>9.3</v>
+        <v>16.7</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.3</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31"/>
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H31" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C32" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32"/>
       <c r="G32" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I32" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C33" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="D33" t="n">
-        <v>70.2</v>
+        <v>37.5</v>
       </c>
       <c r="E33" t="n">
-        <v>23.5</v>
+        <v>9.5</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J33" t="n">
-        <v>34.8</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>28.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C34" t="n">
-        <v>66.7</v>
+        <v>71.4</v>
       </c>
       <c r="D34" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>23.5</v>
       </c>
       <c r="F34" t="n">
         <v>50</v>
       </c>
       <c r="G34" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>18.2</v>
+        <v>40</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>19.2</v>
+        <v>34.8</v>
       </c>
       <c r="K34" t="n">
-        <v>6.6</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C35" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D35" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35"/>
+        <v>30</v>
+      </c>
+      <c r="F35" t="n">
+        <v>50</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H35" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C36" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
-        <v>49.2</v>
+        <v>80</v>
       </c>
       <c r="E36" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36"/>
       <c r="G36" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -6429,34 +6508,34 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="D37" t="n">
-        <v>52.9</v>
+        <v>49.2</v>
       </c>
       <c r="E37" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G37" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H37" t="n">
-        <v>37.5</v>
+        <v>46.2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -6464,98 +6543,98 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D38" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>7.7</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38"/>
-      <c r="G38" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38"/>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38"/>
       <c r="K38" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C39" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>57.6</v>
+        <v>7.7</v>
       </c>
       <c r="E39" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39"/>
       <c r="G39" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H39" t="n">
-        <v>23.1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H39"/>
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="J39"/>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C40" t="n">
-        <v>55.6</v>
+        <v>35.3</v>
       </c>
       <c r="D40" t="n">
-        <v>63.2</v>
+        <v>57.6</v>
       </c>
       <c r="E40" t="n">
-        <v>7.1</v>
+        <v>17.6</v>
       </c>
       <c r="F40" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="H40" t="n">
-        <v>28.6</v>
+        <v>23.1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>10.5</v>
+        <v>23.1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -6563,34 +6642,34 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>63.2</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -6598,296 +6677,296 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C42" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>57.8</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C43" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D43" t="n">
-        <v>87.5</v>
+        <v>57.8</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="H43" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C44" t="n">
-        <v>69.2</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
-        <v>74.7</v>
+        <v>87.5</v>
       </c>
       <c r="E44" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C45" t="n">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="D45" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="F45" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G45" t="n">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46" t="n">
-        <v>58.3</v>
+        <v>61.5</v>
       </c>
       <c r="D46" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="E46" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H46" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>12.5</v>
+        <v>21.4</v>
       </c>
       <c r="K46" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C47" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="D47" t="n">
-        <v>41.2</v>
+        <v>65.3</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-20</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C48" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="D48" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" t="n">
         <v>33.3</v>
       </c>
-      <c r="G48" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H48" t="n">
-        <v>50</v>
-      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K48" t="n">
-        <v>-14.3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D49" t="n">
-        <v>38.9</v>
+        <v>44.1</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G49" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>57.9</v>
+        <v>38.9</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -6896,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -6905,382 +6984,382 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-25</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C51" t="n">
         <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>41.4</v>
+        <v>57.9</v>
       </c>
       <c r="E51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-16.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C52" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>57.5</v>
+        <v>41.4</v>
       </c>
       <c r="E52" t="n">
-        <v>18.7</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="G52" t="n">
-        <v>20.8</v>
+        <v>33.3</v>
       </c>
       <c r="H52" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K52" t="n">
-        <v>8.4</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D53" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="F53" t="n">
-        <v>40</v>
+        <v>51.9</v>
       </c>
       <c r="G53" t="n">
-        <v>7.1</v>
+        <v>20.8</v>
       </c>
       <c r="H53" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C54" t="n">
         <v>50</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E54" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H54" t="n">
         <v>40</v>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>29.4</v>
+        <v>8.3</v>
       </c>
       <c r="K54" t="n">
-        <v>16.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
-        <v>33.3</v>
+        <v>29.4</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>87.5</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K56" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C57" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>63.4</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F57" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F57"/>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H57" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C58" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D58" t="n">
-        <v>80</v>
+        <v>63.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D59" t="n">
-        <v>31.6</v>
+        <v>80</v>
       </c>
       <c r="E59" t="n">
-        <v>7.1</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K59" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C60" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D60" t="n">
-        <v>57.1</v>
+        <v>31.6</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60"/>
+        <v>7.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
       <c r="G60" t="n">
-        <v>9.1</v>
+        <v>40</v>
       </c>
       <c r="H60" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-9.1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D61" t="n">
-        <v>39.1</v>
+        <v>57.1</v>
       </c>
       <c r="E61" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F61"/>
       <c r="G61" t="n">
-        <v>33.3</v>
+        <v>9.1</v>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -7289,144 +7368,179 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>-33.3</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D62" t="n">
-        <v>53.3</v>
+        <v>39.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="H62" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-11.1</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C63" t="n">
-        <v>52</v>
+        <v>66.7</v>
       </c>
       <c r="D63" t="n">
-        <v>55.2</v>
+        <v>53.3</v>
       </c>
       <c r="E63" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H63" t="n">
         <v>28.6</v>
       </c>
-      <c r="G63" t="n">
-        <v>8</v>
-      </c>
-      <c r="H63" t="n">
-        <v>47.4</v>
-      </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C64" t="n">
+        <v>52</v>
+      </c>
+      <c r="D64" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>201</v>
+      </c>
+      <c r="B65" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" t="n">
         <v>68.8</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D65" t="n">
         <v>59.2</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E65" t="n">
         <v>16</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
         <v>5.9</v>
       </c>
-      <c r="H64" t="n">
-        <v>50</v>
-      </c>
-      <c r="I64" t="n">
+      <c r="H65" t="n">
+        <v>50</v>
+      </c>
+      <c r="I65" t="n">
         <v>5.9</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J65" t="n">
         <v>17.4</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65"/>
-      <c r="B65" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="D65" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E65" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="G65" t="n">
-        <v>15</v>
-      </c>
-      <c r="H65" t="n">
-        <v>41</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
-        <v>18.4</v>
-      </c>
       <c r="K65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66"/>
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="D66" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J66" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K66" t="n">
         <v>-3.4</v>
       </c>
     </row>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -162,6 +162,9 @@
     <t xml:space="preserve">Nolan Scicluna</t>
   </si>
   <si>
+    <t xml:space="preserve">Ray Gloria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sawyer Whitaker</t>
   </si>
   <si>
@@ -517,6 +520,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rhys Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinny Bouchard Wright</t>
   </si>
   <si>
     <t xml:space="preserve">Alex VanRaay</t>
@@ -673,8 +679,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K122" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K123" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K123"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -693,8 +699,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K66" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K67" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K67"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1050,31 +1056,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>60.6</v>
+        <v>59.7</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="E2" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="H2" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="I2" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
       <c r="J2" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>41.7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -1085,31 +1091,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>74.6</v>
+        <v>73.6</v>
       </c>
       <c r="D3" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="F3" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G3" t="n">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.3</v>
+        <v>35.8</v>
       </c>
       <c r="J3" t="n">
-        <v>33.3</v>
+        <v>35.8</v>
       </c>
       <c r="K3" t="n">
-        <v>23.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="4">
@@ -1260,31 +1266,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>78.9</v>
+        <v>79.6</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="E8" t="n">
-        <v>58.9</v>
+        <v>59.9</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="G8" t="n">
-        <v>25.4</v>
+        <v>24.6</v>
       </c>
       <c r="H8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>49</v>
+        <v>48.1</v>
       </c>
       <c r="J8" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="K8" t="n">
-        <v>40.8</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="9">
@@ -1295,22 +1301,22 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>74.4</v>
+        <v>73.2</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
-        <v>71.7</v>
+        <v>70.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>18.3</v>
+        <v>19.4</v>
       </c>
       <c r="H9" t="n">
-        <v>15.6</v>
+        <v>18.8</v>
       </c>
       <c r="I9" t="n">
         <v>42.9</v>
@@ -1432,28 +1438,28 @@
         <v>66.7</v>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="E13" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="F13" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="G13" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="H13" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="I13" t="n">
-        <v>48.8</v>
+        <v>51.2</v>
       </c>
       <c r="J13" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="K13" t="n">
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="14">
@@ -1528,31 +1534,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="n">
-        <v>66.1</v>
+        <v>63.9</v>
       </c>
       <c r="F16" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="G16" t="n">
-        <v>24.1</v>
+        <v>31.4</v>
       </c>
       <c r="H16" t="n">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
       <c r="I16" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="J16" t="n">
-        <v>26.7</v>
+        <v>23.5</v>
       </c>
       <c r="K16" t="n">
-        <v>66.7</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="17">
@@ -1563,31 +1569,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="D17" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="E17" t="n">
-        <v>56.4</v>
+        <v>55.2</v>
       </c>
       <c r="F17" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="G17" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="H17" t="n">
-        <v>15.4</v>
+        <v>13.8</v>
       </c>
       <c r="I17" t="n">
-        <v>26.3</v>
+        <v>31.8</v>
       </c>
       <c r="J17" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="18">
@@ -1598,31 +1604,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>76.3</v>
+        <v>76.6</v>
       </c>
       <c r="D18" t="n">
-        <v>13.6</v>
+        <v>12.9</v>
       </c>
       <c r="E18" t="n">
-        <v>62.7</v>
+        <v>63.7</v>
       </c>
       <c r="F18" t="n">
-        <v>13.6</v>
+        <v>12.9</v>
       </c>
       <c r="G18" t="n">
-        <v>30.2</v>
+        <v>28.1</v>
       </c>
       <c r="H18" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="I18" t="n">
-        <v>41.7</v>
+        <v>44</v>
       </c>
       <c r="J18" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1633,31 +1639,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>65.9</v>
+        <v>68.8</v>
       </c>
       <c r="D19" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="E19" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="G19" t="n">
-        <v>30.6</v>
+        <v>26.8</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>31.2</v>
+        <v>36.8</v>
       </c>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K19" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="20">
@@ -1668,31 +1674,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>78.4</v>
+        <v>78.7</v>
       </c>
       <c r="D20" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="E20" t="n">
-        <v>61.6</v>
+        <v>62.2</v>
       </c>
       <c r="F20" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="G20" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="H20" t="n">
         <v>1.4</v>
       </c>
       <c r="I20" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="K20" t="n">
         <v>36.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>35.8</v>
       </c>
     </row>
     <row r="21">
@@ -1808,19 +1814,19 @@
         <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>44.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1832,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -1878,31 +1884,31 @@
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>66.7</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>20.7</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>44.3</v>
       </c>
       <c r="F26" t="n">
-        <v>16.7</v>
+        <v>20.7</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
+        <v>23.1</v>
       </c>
       <c r="I26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -1913,31 +1919,31 @@
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>86.7</v>
+        <v>79.2</v>
       </c>
       <c r="D27" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="E27" t="n">
-        <v>77.6</v>
+        <v>72.5</v>
       </c>
       <c r="F27" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="G27" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
-        <v>11.1</v>
+        <v>8.3</v>
       </c>
       <c r="I27" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1983,31 +1989,31 @@
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>63.9</v>
+        <v>61.4</v>
       </c>
       <c r="D29" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="n">
-        <v>47.7</v>
+        <v>44.7</v>
       </c>
       <c r="F29" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="H29" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="I29" t="n">
-        <v>8.3</v>
+        <v>26.7</v>
       </c>
       <c r="J29" t="n">
-        <v>58.3</v>
+        <v>46.7</v>
       </c>
       <c r="K29" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2018,31 +2024,31 @@
         <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="D30" t="n">
-        <v>25.8</v>
+        <v>26.5</v>
       </c>
       <c r="E30" t="n">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="F30" t="n">
-        <v>25.8</v>
+        <v>26.5</v>
       </c>
       <c r="G30" t="n">
-        <v>21.1</v>
+        <v>22.5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
       <c r="J30" t="n">
-        <v>13.3</v>
+        <v>18.8</v>
       </c>
       <c r="K30" t="n">
-        <v>71.4</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="31">
@@ -2053,31 +2059,31 @@
         <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>73.3</v>
+        <v>68.6</v>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>8.8</v>
       </c>
       <c r="E31" t="n">
-        <v>62.2</v>
+        <v>59.8</v>
       </c>
       <c r="F31" t="n">
-        <v>11.1</v>
+        <v>8.8</v>
       </c>
       <c r="G31" t="n">
-        <v>32</v>
+        <v>29.6</v>
       </c>
       <c r="H31" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>9.1</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="32">
@@ -2123,28 +2129,28 @@
         <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="D33" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="E33" t="n">
-        <v>53.4</v>
+        <v>50.4</v>
       </c>
       <c r="F33" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="H33" t="n">
-        <v>9.5</v>
+        <v>8.3</v>
       </c>
       <c r="I33" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="J33" t="n">
-        <v>21.4</v>
+        <v>18.8</v>
       </c>
       <c r="K33" t="n">
         <v>50</v>
@@ -2193,31 +2199,31 @@
         <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="D35" t="n">
-        <v>7.9</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="n">
-        <v>52.1</v>
+        <v>46.2</v>
       </c>
       <c r="F35" t="n">
-        <v>7.9</v>
+        <v>13.3</v>
       </c>
       <c r="G35" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="H35" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I35" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="J35" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="K35" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="36">
@@ -2263,31 +2269,31 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>63.6</v>
+        <v>64.7</v>
       </c>
       <c r="D37" t="n">
-        <v>22.2</v>
+        <v>31.2</v>
       </c>
       <c r="E37" t="n">
-        <v>41.4</v>
+        <v>33.5</v>
       </c>
       <c r="F37" t="n">
-        <v>22.2</v>
+        <v>31.2</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1</v>
+        <v>31.2</v>
       </c>
       <c r="H37" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I37" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="K37" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="38">
@@ -2298,31 +2304,31 @@
         <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>48.8</v>
+        <v>80</v>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>36.3</v>
+        <v>80</v>
       </c>
       <c r="F38" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2333,31 +2339,31 @@
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>56.2</v>
+        <v>52.3</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>12.1</v>
       </c>
       <c r="E39" t="n">
-        <v>26.2</v>
+        <v>40.2</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>12.1</v>
       </c>
       <c r="G39" t="n">
-        <v>41.7</v>
+        <v>14.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="40">
@@ -2365,31 +2371,31 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>26.2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G40" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="H40" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2397,37 +2403,37 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="B41" t="s">
-        <v>52</v>
-      </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>42.9</v>
       </c>
       <c r="I41" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2435,34 +2441,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>27.5</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="43">
@@ -2470,34 +2476,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
       <c r="F43" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2505,34 +2511,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>66.7</v>
+        <v>47.1</v>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E44" t="n">
-        <v>41.7</v>
+        <v>30.4</v>
       </c>
       <c r="F44" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K44" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="45">
@@ -2540,34 +2546,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
-        <v>67.5</v>
+        <v>41.7</v>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G45" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -2575,96 +2581,96 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46"/>
+        <v>20</v>
+      </c>
+      <c r="G46" t="n">
+        <v>37.5</v>
+      </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
+      <c r="I46" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>57.7</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47"/>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J47" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K47" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>40.1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G48" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="49">
@@ -2672,34 +2678,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C49" t="n">
         <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>25</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>66.7</v>
       </c>
     </row>
     <row r="50">
@@ -2707,19 +2713,19 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E50" t="n">
-        <v>66.7</v>
+        <v>42.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G50" t="n">
         <v>25</v>
@@ -2728,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="51">
@@ -2742,31 +2748,31 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D51" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>41.3</v>
+        <v>66.7</v>
       </c>
       <c r="F51" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="H51" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>50</v>
@@ -2777,34 +2783,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D52" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="F52" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="G52" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="H52" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2812,34 +2818,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="E53" t="n">
-        <v>-33.6</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="G53" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I53" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -2847,34 +2853,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>62.5</v>
+        <v>36.4</v>
       </c>
       <c r="D54" t="n">
-        <v>38.5</v>
+        <v>70</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>-33.6</v>
       </c>
       <c r="F54" t="n">
-        <v>38.5</v>
+        <v>70</v>
       </c>
       <c r="G54" t="n">
-        <v>26.7</v>
+        <v>45.5</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J54" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K54" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2882,69 +2888,69 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C55" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="E55" t="n">
-        <v>42.9</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J55" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" t="s">
         <v>69</v>
       </c>
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
       <c r="C56" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="D56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>58.3</v>
+        <v>42.9</v>
       </c>
       <c r="F56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K56" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
@@ -2952,34 +2958,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C57" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J57" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58">
@@ -2987,34 +2993,34 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C58" t="n">
+        <v>80</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>80</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>66.7</v>
       </c>
-      <c r="D58" t="n">
-        <v>20</v>
-      </c>
-      <c r="E58" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F58" t="n">
-        <v>20</v>
-      </c>
-      <c r="G58" t="n">
-        <v>20</v>
-      </c>
-      <c r="H58" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I58" t="n">
-        <v>25</v>
-      </c>
       <c r="J58" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="59">
@@ -3022,31 +3028,31 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C59" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>5.6</v>
+        <v>46.7</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3057,22 +3063,22 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C60" t="n">
         <v>55.6</v>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E60" t="n">
-        <v>43.1</v>
+        <v>5.6</v>
       </c>
       <c r="F60" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3084,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3092,31 +3098,31 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D61" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="n">
-        <v>46.7</v>
+        <v>43.1</v>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="G61" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>100</v>
@@ -3127,34 +3133,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
         <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -3162,28 +3168,28 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>50</v>
@@ -3197,28 +3203,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C64" t="n">
-        <v>80</v>
-      </c>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
+        <v>75</v>
+      </c>
+      <c r="D64" t="n">
+        <v>50</v>
+      </c>
+      <c r="E64" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" t="n">
+        <v>50</v>
+      </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3226,34 +3238,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C65" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="F65" t="n">
-        <v>11.1</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>33.3</v>
       </c>
-      <c r="I65" t="n">
-        <v>100</v>
-      </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="66">
@@ -3261,25 +3267,25 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D66" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="F66" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
@@ -3288,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3296,22 +3302,22 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C67" t="n">
-        <v>46.7</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E67" t="n">
-        <v>26.7</v>
+        <v>75</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3323,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="68">
@@ -3331,34 +3337,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C68" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="D68" t="n">
+        <v>20</v>
+      </c>
+      <c r="E68" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" t="n">
         <v>75</v>
       </c>
-      <c r="E68" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="F68" t="n">
-        <v>75</v>
-      </c>
-      <c r="G68" t="n">
-        <v>33.3</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -3366,54 +3372,60 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C69" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="D69" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="E69" t="n">
-        <v>8.3</v>
+        <v>-8.3</v>
       </c>
       <c r="F69" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="G69" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>50</v>
+      </c>
+      <c r="J69" t="n">
         <v>25</v>
       </c>
-      <c r="H69" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I69" t="n">
-        <v>50</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s">
         <v>84</v>
       </c>
-      <c r="B70" t="s">
-        <v>83</v>
-      </c>
       <c r="C70" t="n">
-        <v>100</v>
-      </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
+        <v>53.8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>45.5</v>
+      </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I70" t="n">
         <v>50</v>
@@ -3430,34 +3442,28 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D71" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E71" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F71" t="n">
-        <v>36.4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -3465,34 +3471,34 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C72" t="n">
-        <v>76.9</v>
+        <v>78.6</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="E72" t="n">
-        <v>51.9</v>
+        <v>42.2</v>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="G72" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I72" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J72" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K72" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3500,34 +3506,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C73" t="n">
-        <v>83.3</v>
+        <v>76.9</v>
       </c>
       <c r="D73" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>25</v>
+      </c>
+      <c r="G73" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J73" t="n">
         <v>28.6</v>
       </c>
-      <c r="E73" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="F73" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>50</v>
-      </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="74">
@@ -3535,31 +3541,31 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="E74" t="n">
-        <v>32.1</v>
+        <v>54.7</v>
       </c>
       <c r="F74" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="G74" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I74" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3570,22 +3576,22 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E75" t="n">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G75" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3597,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3605,34 +3611,34 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C76" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>43.3</v>
+        <v>100</v>
       </c>
       <c r="F76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="H76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -3640,34 +3646,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E77" t="n">
-        <v>58.8</v>
+        <v>43.3</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H77" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="I77" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J77" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K77" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
@@ -3675,34 +3681,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78" t="n">
-        <v>83.3</v>
+        <v>58.8</v>
       </c>
       <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>10</v>
+      </c>
+      <c r="H78" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J78" t="n">
         <v>16.7</v>
       </c>
-      <c r="E78" t="n">
-        <v>66.6</v>
-      </c>
-      <c r="F78" t="n">
+      <c r="K78" t="n">
         <v>16.7</v>
-      </c>
-      <c r="G78" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H78" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>100</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3710,34 +3716,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79" t="n">
-        <v>81.8</v>
+        <v>83.3</v>
       </c>
       <c r="D79" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="E79" t="n">
-        <v>72.7</v>
+        <v>66.6</v>
       </c>
       <c r="F79" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="I79" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K79" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3745,101 +3751,101 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C80" t="n">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="D80" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="E80" t="n">
-        <v>58.4</v>
+        <v>72.7</v>
       </c>
       <c r="F80" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="G80" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I80" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J80" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K80" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E81" t="n">
-        <v>50</v>
+        <v>58.4</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C82" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3847,37 +3853,37 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" t="s">
         <v>97</v>
       </c>
-      <c r="B83" t="s">
-        <v>96</v>
-      </c>
       <c r="C83" t="n">
-        <v>85.7</v>
+        <v>61.5</v>
       </c>
       <c r="D83" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="n">
-        <v>63.5</v>
+        <v>50.4</v>
       </c>
       <c r="F83" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="G83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I83" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J83" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K83" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3885,34 +3891,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C84" t="n">
-        <v>88.9</v>
+        <v>85.7</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E84" t="n">
-        <v>88.9</v>
+        <v>63.5</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H84" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K84" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -3920,34 +3926,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I85" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -3955,34 +3961,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C86" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>40</v>
+        <v>85.7</v>
       </c>
       <c r="J86" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3990,34 +3996,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C87" t="n">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="D87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>55</v>
+        <v>64.3</v>
       </c>
       <c r="F87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>11.1</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I87" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="J87" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>14.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
@@ -4025,34 +4031,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C88" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D88" t="n">
         <v>25</v>
       </c>
       <c r="E88" t="n">
-        <v>60.7</v>
+        <v>55</v>
       </c>
       <c r="F88" t="n">
         <v>25</v>
       </c>
       <c r="G88" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="H88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J88" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="89">
@@ -4060,34 +4066,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C89" t="n">
-        <v>90.9</v>
+        <v>85.7</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E89" t="n">
-        <v>90.9</v>
+        <v>60.7</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I89" t="n">
         <v>50</v>
       </c>
       <c r="J89" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K89" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4095,34 +4101,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" t="n">
-        <v>77.8</v>
+        <v>90.9</v>
       </c>
       <c r="D90" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>61.1</v>
+        <v>90.9</v>
       </c>
       <c r="F90" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J90" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K90" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="91">
@@ -4130,34 +4136,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C91" t="n">
-        <v>85.7</v>
+        <v>77.8</v>
       </c>
       <c r="D91" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E91" t="n">
-        <v>66.9</v>
+        <v>61.1</v>
       </c>
       <c r="F91" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="G91" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="H91" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I91" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K91" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="92">
@@ -4165,69 +4171,69 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C92" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="D92" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E92" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H92" t="n">
         <v>14.3</v>
       </c>
-      <c r="E92" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F92" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G92" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H92" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I92" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J92" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>107</v>
+      </c>
+      <c r="B93" t="s">
         <v>108</v>
       </c>
-      <c r="B93" t="s">
-        <v>107</v>
-      </c>
       <c r="C93" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D93" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="E93" t="n">
-        <v>33.4</v>
+        <v>52.4</v>
       </c>
       <c r="F93" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="G93" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I93" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="94">
@@ -4235,34 +4241,34 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C94" t="n">
-        <v>80.8</v>
+        <v>55.6</v>
       </c>
       <c r="D94" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="E94" t="n">
-        <v>62.6</v>
+        <v>33.4</v>
       </c>
       <c r="F94" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="G94" t="n">
-        <v>36</v>
+        <v>42.9</v>
       </c>
       <c r="H94" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4270,34 +4276,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C95" t="n">
-        <v>91.7</v>
+        <v>80.8</v>
       </c>
       <c r="D95" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="E95" t="n">
-        <v>41.7</v>
+        <v>62.6</v>
       </c>
       <c r="F95" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="G95" t="n">
-        <v>21.4</v>
+        <v>36</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I95" t="n">
-        <v>28.6</v>
+        <v>62.5</v>
       </c>
       <c r="J95" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="K95" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96">
@@ -4305,34 +4311,34 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C96" t="n">
-        <v>60</v>
+        <v>91.7</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E96" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="97">
@@ -4340,28 +4346,28 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C97" t="n">
+        <v>60</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>60</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
         <v>100</v>
-      </c>
-      <c r="D97" t="n">
-        <v>20</v>
-      </c>
-      <c r="E97" t="n">
-        <v>80</v>
-      </c>
-      <c r="F97" t="n">
-        <v>20</v>
-      </c>
-      <c r="G97" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>66.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4375,34 +4381,34 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C98" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D98" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E98" t="n">
+        <v>80</v>
+      </c>
+      <c r="F98" t="n">
+        <v>20</v>
+      </c>
+      <c r="G98" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>66.7</v>
       </c>
-      <c r="F98" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>50</v>
-      </c>
       <c r="J98" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4410,19 +4416,19 @@
         <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C99" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E99" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4431,13 +4437,13 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J99" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="100">
@@ -4445,34 +4451,34 @@
         <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D100" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>54.7</v>
+        <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4480,34 +4486,34 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E101" t="n">
-        <v>57.1</v>
+        <v>54.7</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G101" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H101" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K101" t="n">
-        <v>60</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="102">
@@ -4515,34 +4521,34 @@
         <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C102" t="n">
-        <v>70</v>
+        <v>57.1</v>
       </c>
       <c r="D102" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>32.5</v>
+        <v>57.1</v>
       </c>
       <c r="F102" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I102" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="J102" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -4550,34 +4556,34 @@
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C103" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D103" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="E103" t="n">
-        <v>53.6</v>
+        <v>32.5</v>
       </c>
       <c r="F103" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="G103" t="n">
-        <v>46.7</v>
+        <v>17.6</v>
       </c>
       <c r="H103" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K103" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -4585,34 +4591,34 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C104" t="n">
-        <v>84.6</v>
+        <v>75</v>
       </c>
       <c r="D104" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E104" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F104" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H104" t="n">
         <v>14.3</v>
       </c>
-      <c r="E104" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F104" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G104" t="n">
-        <v>13</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
       <c r="I104" t="n">
-        <v>43.8</v>
+        <v>66.7</v>
       </c>
       <c r="J104" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="105">
@@ -4620,34 +4626,34 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>68.6</v>
+        <v>84.6</v>
       </c>
       <c r="D105" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="E105" t="n">
-        <v>59.5</v>
+        <v>70.3</v>
       </c>
       <c r="F105" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="G105" t="n">
-        <v>23.1</v>
+        <v>13</v>
       </c>
       <c r="H105" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="J105" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="K105" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="106">
@@ -4655,34 +4661,34 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C106" t="n">
-        <v>50</v>
+        <v>68.6</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E106" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I106" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="107">
@@ -4690,34 +4696,34 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="n">
-        <v>90.9</v>
+        <v>50</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>70.9</v>
+        <v>50</v>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J107" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4725,31 +4731,31 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C108" t="n">
-        <v>60</v>
+        <v>90.9</v>
       </c>
       <c r="D108" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="E108" t="n">
-        <v>17.1</v>
+        <v>70.9</v>
       </c>
       <c r="F108" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="G108" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J108" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H108" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>100</v>
       </c>
       <c r="K108" t="n">
         <v>50</v>
@@ -4760,34 +4766,34 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D109" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="E109" t="n">
-        <v>73.3</v>
+        <v>17.1</v>
       </c>
       <c r="F109" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="G109" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I109" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110">
@@ -4795,22 +4801,22 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C110" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E110" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4819,10 +4825,10 @@
         <v>33.3</v>
       </c>
       <c r="J110" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K110" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4830,51 +4836,57 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C111" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="F111" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K111" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>127</v>
+      </c>
+      <c r="B112" t="s">
         <v>128</v>
       </c>
-      <c r="B112" t="s">
-        <v>127</v>
-      </c>
       <c r="C112" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="n">
-        <v>42.9</v>
+        <v>5.6</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G112" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="H112" t="n">
         <v>66.7</v>
@@ -4888,25 +4900,25 @@
         <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C113" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I113"/>
       <c r="J113"/>
@@ -4917,69 +4929,63 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C114" t="n">
-        <v>61.1</v>
+        <v>33.3</v>
       </c>
       <c r="D114" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>52</v>
+        <v>33.3</v>
       </c>
       <c r="F114" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
     </row>
     <row r="115">
       <c r="A115" t="s">
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D115" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="E115" t="n">
-        <v>31.8</v>
+        <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="G115" t="n">
-        <v>42.9</v>
+        <v>8.3</v>
       </c>
       <c r="H115" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J115" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="116">
@@ -4987,34 +4993,34 @@
         <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C116" t="n">
         <v>50</v>
       </c>
       <c r="D116" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E116" t="n">
-        <v>26.9</v>
+        <v>31.8</v>
       </c>
       <c r="F116" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="G116" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="H116" t="n">
         <v>16.7</v>
       </c>
       <c r="I116" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K116" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117">
@@ -5022,34 +5028,34 @@
         <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C117" t="n">
+        <v>50</v>
+      </c>
+      <c r="D117" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F117" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H117" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I117" t="n">
         <v>66.7</v>
       </c>
-      <c r="D117" t="n">
-        <v>25</v>
-      </c>
-      <c r="E117" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F117" t="n">
-        <v>25</v>
-      </c>
-      <c r="G117" t="n">
+      <c r="J117" t="n">
         <v>33.3</v>
       </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>100</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="118">
@@ -5057,34 +5063,34 @@
         <v>134</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C118" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E118" t="n">
-        <v>61.5</v>
+        <v>41.7</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G118" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="H118" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J118" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5092,34 +5098,34 @@
         <v>135</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C119" t="n">
-        <v>45</v>
+        <v>61.5</v>
       </c>
       <c r="D119" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>28.3</v>
+        <v>61.5</v>
       </c>
       <c r="F119" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>27.3</v>
+        <v>12.5</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I119" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="120">
@@ -5127,31 +5133,31 @@
         <v>136</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C120" t="n">
-        <v>71.4</v>
+        <v>45</v>
       </c>
       <c r="D120" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E120" t="n">
-        <v>51.4</v>
+        <v>28.3</v>
       </c>
       <c r="F120" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G120" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J120" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5162,67 +5168,102 @@
         <v>137</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C121" t="n">
         <v>71.4</v>
       </c>
       <c r="D121" t="n">
+        <v>20</v>
+      </c>
+      <c r="E121" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F121" t="n">
+        <v>20</v>
+      </c>
+      <c r="G121" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>50</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>138</v>
+      </c>
+      <c r="B122" t="s">
+        <v>128</v>
+      </c>
+      <c r="C122" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D122" t="n">
         <v>7.1</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E122" t="n">
         <v>64.3</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F122" t="n">
         <v>7.1</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G122" t="n">
         <v>18.2</v>
       </c>
-      <c r="H121" t="n">
+      <c r="H122" t="n">
         <v>12.5</v>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
         <v>100</v>
       </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122"/>
-      <c r="B122" t="s">
-        <v>138</v>
-      </c>
-      <c r="C122" t="n">
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123"/>
+      <c r="B123" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" t="n">
         <v>68.3</v>
       </c>
-      <c r="D122" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E122" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="F122" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G122" t="n">
+      <c r="D123" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="G123" t="n">
         <v>20.9</v>
       </c>
-      <c r="H122" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="I122" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="J122" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="K122" t="n">
-        <v>32.4</v>
+      <c r="H123" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J123" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>31.8</v>
       </c>
     </row>
   </sheetData>
@@ -5254,22 +5295,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5278,13 +5319,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
@@ -5359,42 +5400,42 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>57.4</v>
+        <v>60.7</v>
       </c>
       <c r="D4" t="n">
-        <v>66.5</v>
+        <v>66.8</v>
       </c>
       <c r="E4" t="n">
-        <v>18.8</v>
+        <v>21.1</v>
       </c>
       <c r="F4" t="n">
-        <v>36.5</v>
+        <v>34.9</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>25.4</v>
       </c>
       <c r="K4" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5429,7 +5470,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5464,7 +5505,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5499,7 +5540,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -5604,42 +5645,42 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>58.6</v>
       </c>
       <c r="D11" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="F11" t="n">
-        <v>38.2</v>
+        <v>36.8</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="H11" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -5672,7 +5713,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -5707,42 +5748,42 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="D14" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
-        <v>53.3</v>
+        <v>58.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -5777,7 +5818,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -5812,7 +5853,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -5847,7 +5888,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -5882,7 +5923,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -5917,7 +5958,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
@@ -5952,69 +5993,69 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B21" t="s">
         <v>35</v>
       </c>
       <c r="C21" t="n">
-        <v>76.8</v>
+        <v>68.4</v>
       </c>
       <c r="D21" t="n">
-        <v>66.7</v>
+        <v>63.8</v>
       </c>
       <c r="E21" t="n">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="F21" t="n">
-        <v>44.4</v>
+        <v>47.8</v>
       </c>
       <c r="G21" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="H21" t="n">
-        <v>47.7</v>
+        <v>46.6</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="K21" t="n">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>46.7</v>
+        <v>45.2</v>
       </c>
       <c r="D22" t="n">
-        <v>54.9</v>
+        <v>54.3</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="F22" t="n">
         <v>26.7</v>
       </c>
       <c r="G22" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="K22" t="n">
         <v>-3.4</v>
@@ -6022,7 +6063,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -6057,7 +6098,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
@@ -6092,7 +6133,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -6127,7 +6168,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -6162,7 +6203,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -6197,7 +6238,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
@@ -6232,310 +6273,310 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>57.9</v>
+        <v>33.3</v>
       </c>
       <c r="D30" t="n">
         <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C31" t="n">
-        <v>62.8</v>
+        <v>57.9</v>
       </c>
       <c r="D31" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>9.3</v>
       </c>
       <c r="F31" t="n">
-        <v>41.7</v>
+        <v>12.5</v>
       </c>
       <c r="G31" t="n">
-        <v>9.3</v>
+        <v>16.7</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="K31" t="n">
-        <v>2.3</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32"/>
+        <v>7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H32" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33"/>
       <c r="G33" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="D34" t="n">
-        <v>70.2</v>
+        <v>37.5</v>
       </c>
       <c r="E34" t="n">
-        <v>23.5</v>
+        <v>9.5</v>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J34" t="n">
-        <v>34.8</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>28.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>66.7</v>
+        <v>71.4</v>
       </c>
       <c r="D35" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>23.5</v>
       </c>
       <c r="F35" t="n">
         <v>50</v>
       </c>
       <c r="G35" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>18.2</v>
+        <v>40</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>19.2</v>
+        <v>34.8</v>
       </c>
       <c r="K35" t="n">
-        <v>6.6</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D36" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36"/>
+        <v>30</v>
+      </c>
+      <c r="F36" t="n">
+        <v>50</v>
+      </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="D37" t="n">
-        <v>49.2</v>
+        <v>80</v>
       </c>
       <c r="E37" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37"/>
       <c r="G37" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -6543,34 +6584,34 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="D38" t="n">
-        <v>52.9</v>
+        <v>49.2</v>
       </c>
       <c r="E38" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G38" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H38" t="n">
-        <v>37.5</v>
+        <v>46.2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -6578,98 +6619,98 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>7.7</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39"/>
-      <c r="G39" t="n">
-        <v>100</v>
-      </c>
-      <c r="H39"/>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39"/>
       <c r="K39" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C40" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>57.6</v>
+        <v>7.7</v>
       </c>
       <c r="E40" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40"/>
       <c r="G40" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>23.1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H40"/>
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="J40"/>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41" t="n">
-        <v>55.6</v>
+        <v>35.3</v>
       </c>
       <c r="D41" t="n">
-        <v>63.2</v>
+        <v>57.6</v>
       </c>
       <c r="E41" t="n">
-        <v>7.1</v>
+        <v>17.6</v>
       </c>
       <c r="F41" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="H41" t="n">
-        <v>28.6</v>
+        <v>23.1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>10.5</v>
+        <v>23.1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -6677,34 +6718,34 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D42" t="n">
-        <v>55</v>
+        <v>63.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -6712,296 +6753,296 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>57.8</v>
+        <v>55</v>
       </c>
       <c r="E43" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C44" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D44" t="n">
-        <v>87.5</v>
+        <v>57.8</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="H44" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C45" t="n">
-        <v>69.2</v>
+        <v>100</v>
       </c>
       <c r="D45" t="n">
-        <v>74.7</v>
+        <v>87.5</v>
       </c>
       <c r="E45" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C46" t="n">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="D46" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="F46" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="H46" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>58.3</v>
+        <v>61.5</v>
       </c>
       <c r="D47" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H47" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>12.5</v>
+        <v>21.4</v>
       </c>
       <c r="K47" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="D48" t="n">
-        <v>41.2</v>
+        <v>65.3</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K48" t="n">
-        <v>-20</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="D49" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="n">
         <v>33.3</v>
       </c>
-      <c r="G49" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50</v>
-      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D50" t="n">
-        <v>38.9</v>
+        <v>44.1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G50" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>57.9</v>
+        <v>38.9</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -7010,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -7019,382 +7060,382 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>-25</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" t="n">
         <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>41.4</v>
+        <v>57.9</v>
       </c>
       <c r="E52" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C53" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>57.5</v>
+        <v>41.4</v>
       </c>
       <c r="E53" t="n">
-        <v>18.7</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="G53" t="n">
-        <v>20.8</v>
+        <v>33.3</v>
       </c>
       <c r="H53" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K53" t="n">
-        <v>8.4</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D54" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="F54" t="n">
-        <v>40</v>
+        <v>51.9</v>
       </c>
       <c r="G54" t="n">
-        <v>7.1</v>
+        <v>20.8</v>
       </c>
       <c r="H54" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C55" t="n">
         <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E55" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="G55" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H55" t="n">
         <v>40</v>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>29.4</v>
+        <v>8.3</v>
       </c>
       <c r="K55" t="n">
-        <v>16.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D56" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>29.4</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>87.5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
       <c r="G57" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>63.4</v>
+        <v>20</v>
       </c>
       <c r="E58" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F58" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F58"/>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H58" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C59" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D59" t="n">
-        <v>80</v>
+        <v>63.4</v>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D60" t="n">
-        <v>31.6</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>7.1</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C61" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D61" t="n">
-        <v>57.1</v>
+        <v>31.6</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61"/>
+        <v>7.1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>100</v>
+      </c>
       <c r="G61" t="n">
-        <v>9.1</v>
+        <v>40</v>
       </c>
       <c r="H61" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D62" t="n">
-        <v>39.1</v>
+        <v>57.1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F62"/>
       <c r="G62" t="n">
-        <v>33.3</v>
+        <v>9.1</v>
       </c>
       <c r="H62" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -7403,145 +7444,180 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-33.3</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>53.3</v>
+        <v>39.1</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="H63" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.1</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C64" t="n">
-        <v>52</v>
+        <v>66.7</v>
       </c>
       <c r="D64" t="n">
-        <v>55.2</v>
+        <v>53.3</v>
       </c>
       <c r="E64" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H64" t="n">
         <v>28.6</v>
       </c>
-      <c r="G64" t="n">
-        <v>8</v>
-      </c>
-      <c r="H64" t="n">
-        <v>47.4</v>
-      </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C65" t="n">
+        <v>52</v>
+      </c>
+      <c r="D65" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8</v>
+      </c>
+      <c r="H65" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="n">
         <v>68.8</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>59.2</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>16</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
         <v>5.9</v>
       </c>
-      <c r="H65" t="n">
-        <v>50</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" t="n">
         <v>5.9</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J66" t="n">
         <v>17.4</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66"/>
-      <c r="B66" t="s">
-        <v>138</v>
-      </c>
-      <c r="C66" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67"/>
+      <c r="B67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D67" t="n">
         <v>57.2</v>
       </c>
-      <c r="E66" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F66" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="G66" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="E67" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G67" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I67" t="n">
         <v>0.9</v>
       </c>
-      <c r="J66" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K66" t="n">
-        <v>-3.4</v>
+      <c r="J67" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-3.2</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -54,6 +54,9 @@
     <t xml:space="preserve">Brock Badgers</t>
   </si>
   <si>
+    <t xml:space="preserve">Avery Brooks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brady Campbell</t>
   </si>
   <si>
@@ -474,6 +477,9 @@
     <t xml:space="preserve">Joel Palmer</t>
   </si>
   <si>
+    <t xml:space="preserve">Maverick Lawrence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Max Burroughsford</t>
   </si>
   <si>
@@ -487,6 +493,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rowan Gelder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Atkinson</t>
   </si>
   <si>
     <t xml:space="preserve">Ryan Facchini</t>
@@ -679,8 +688,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K123" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K124" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K124"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -699,8 +708,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K67" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K69" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K69"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1091,31 +1100,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>73.6</v>
+        <v>66.7</v>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>28.6</v>
       </c>
       <c r="E3" t="n">
-        <v>59.2</v>
+        <v>38.1</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4</v>
+        <v>28.6</v>
       </c>
       <c r="G3" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>35.8</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>35.8</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1126,31 +1135,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>51.4</v>
+        <v>73.6</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="n">
-        <v>41.4</v>
+        <v>59.2</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="G4" t="n">
-        <v>36.4</v>
+        <v>18.7</v>
       </c>
       <c r="H4" t="n">
-        <v>11.8</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>57.1</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>35.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="5">
@@ -1161,31 +1170,31 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>45.5</v>
+        <v>53.8</v>
       </c>
       <c r="D5" t="n">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="n">
-        <v>36.6</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
       <c r="G5" t="n">
-        <v>21.4</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>43.8</v>
+        <v>11.1</v>
       </c>
       <c r="I5" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="K5" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1196,31 +1205,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>71.9</v>
+        <v>45.5</v>
       </c>
       <c r="D6" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="E6" t="n">
-        <v>61.8</v>
+        <v>36.6</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="G6" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="H6" t="n">
-        <v>9.6</v>
+        <v>43.8</v>
       </c>
       <c r="I6" t="n">
-        <v>45</v>
+        <v>71.4</v>
       </c>
       <c r="J6" t="n">
-        <v>35</v>
+        <v>28.6</v>
       </c>
       <c r="K6" t="n">
-        <v>32.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="7">
@@ -1231,31 +1240,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>71.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>61.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J7" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="8">
@@ -1266,31 +1275,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>79.6</v>
+        <v>73.3</v>
       </c>
       <c r="D8" t="n">
-        <v>19.7</v>
+        <v>6.2</v>
       </c>
       <c r="E8" t="n">
-        <v>59.9</v>
+        <v>67.1</v>
       </c>
       <c r="F8" t="n">
-        <v>19.7</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>24.6</v>
+        <v>30.8</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>14.3</v>
       </c>
       <c r="I8" t="n">
-        <v>48.1</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>28.8</v>
+        <v>50</v>
       </c>
       <c r="K8" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1301,31 +1310,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>73.2</v>
+        <v>79.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>19.7</v>
       </c>
       <c r="E9" t="n">
-        <v>70.8</v>
+        <v>59.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>19.7</v>
       </c>
       <c r="G9" t="n">
-        <v>19.4</v>
+        <v>24.6</v>
       </c>
       <c r="H9" t="n">
-        <v>18.8</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>42.9</v>
+        <v>48.1</v>
       </c>
       <c r="J9" t="n">
-        <v>25</v>
+        <v>28.8</v>
       </c>
       <c r="K9" t="n">
-        <v>57.1</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="10">
@@ -1336,25 +1345,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
+        <v>73.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.4</v>
+      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="11">
@@ -1365,17 +1380,11 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -1383,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1400,13 +1409,13 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1418,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -1435,31 +1444,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.7</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>48.8</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>32.2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>51.2</v>
+        <v>28.6</v>
       </c>
       <c r="J13" t="n">
-        <v>23.3</v>
+        <v>42.9</v>
       </c>
       <c r="K13" t="n">
-        <v>32.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="14">
@@ -1470,25 +1479,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
+        <v>66.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17.9</v>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
+        <v>23.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="15">
@@ -1501,29 +1516,23 @@
       <c r="C15" t="n">
         <v>100</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>100</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>100</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1534,31 +1543,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>63.9</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="H16" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>58.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -1569,31 +1578,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>64.7</v>
+        <v>76.3</v>
       </c>
       <c r="D17" t="n">
-        <v>9.5</v>
+        <v>12.7</v>
       </c>
       <c r="E17" t="n">
-        <v>55.2</v>
+        <v>63.6</v>
       </c>
       <c r="F17" t="n">
-        <v>9.5</v>
+        <v>12.7</v>
       </c>
       <c r="G17" t="n">
-        <v>13.5</v>
+        <v>29.7</v>
       </c>
       <c r="H17" t="n">
-        <v>13.8</v>
+        <v>18.5</v>
       </c>
       <c r="I17" t="n">
-        <v>31.8</v>
+        <v>55.6</v>
       </c>
       <c r="J17" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="K17" t="n">
-        <v>31.8</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="18">
@@ -1604,31 +1613,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>76.6</v>
+        <v>64.7</v>
       </c>
       <c r="D18" t="n">
-        <v>12.9</v>
+        <v>9.5</v>
       </c>
       <c r="E18" t="n">
-        <v>63.7</v>
+        <v>55.2</v>
       </c>
       <c r="F18" t="n">
-        <v>12.9</v>
+        <v>9.5</v>
       </c>
       <c r="G18" t="n">
-        <v>28.1</v>
+        <v>13.5</v>
       </c>
       <c r="H18" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="I18" t="n">
-        <v>44</v>
+        <v>31.8</v>
       </c>
       <c r="J18" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="19">
@@ -1639,31 +1648,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>68.8</v>
+        <v>74.6</v>
       </c>
       <c r="D19" t="n">
-        <v>17.8</v>
+        <v>16.2</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>58.4</v>
       </c>
       <c r="F19" t="n">
-        <v>17.8</v>
+        <v>16.2</v>
       </c>
       <c r="G19" t="n">
-        <v>26.8</v>
+        <v>29.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>12.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.8</v>
+        <v>48.1</v>
       </c>
       <c r="J19" t="n">
-        <v>26.3</v>
+        <v>33.3</v>
       </c>
       <c r="K19" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -1674,31 +1683,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>78.7</v>
+        <v>68.8</v>
       </c>
       <c r="D20" t="n">
-        <v>16.5</v>
+        <v>17.8</v>
       </c>
       <c r="E20" t="n">
-        <v>62.2</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>16.5</v>
+        <v>17.8</v>
       </c>
       <c r="G20" t="n">
-        <v>23.3</v>
+        <v>26.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>35.1</v>
+        <v>36.8</v>
       </c>
       <c r="J20" t="n">
-        <v>38.6</v>
+        <v>26.3</v>
       </c>
       <c r="K20" t="n">
-        <v>36.4</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="21">
@@ -1709,31 +1718,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>55.4</v>
+        <v>78.7</v>
       </c>
       <c r="D21" t="n">
-        <v>14.9</v>
+        <v>16.5</v>
       </c>
       <c r="E21" t="n">
-        <v>40.5</v>
+        <v>62.2</v>
       </c>
       <c r="F21" t="n">
-        <v>14.9</v>
+        <v>16.5</v>
       </c>
       <c r="G21" t="n">
-        <v>11.8</v>
+        <v>23.3</v>
       </c>
       <c r="H21" t="n">
-        <v>13.5</v>
+        <v>1.4</v>
       </c>
       <c r="I21" t="n">
-        <v>51.5</v>
+        <v>35.1</v>
       </c>
       <c r="J21" t="n">
-        <v>21.2</v>
+        <v>38.6</v>
       </c>
       <c r="K21" t="n">
-        <v>27.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="22">
@@ -1744,31 +1753,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>85.7</v>
+        <v>55.4</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="E22" t="n">
-        <v>85.7</v>
+        <v>40.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I22" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="J22" t="n">
-        <v>33.3</v>
+        <v>21.2</v>
       </c>
       <c r="K22" t="n">
-        <v>66.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="23">
@@ -1779,31 +1788,31 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>80</v>
+        <v>88.9</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>68.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>62.5</v>
       </c>
       <c r="J23" t="n">
-        <v>83.3</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>33.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="24">
@@ -1811,69 +1820,69 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>77.8</v>
+        <v>80</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K24" t="n">
         <v>33.3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>100</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
       <c r="C25" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>100</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>50</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -1881,34 +1890,34 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>42.1</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1916,34 +1925,34 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
-        <v>79.2</v>
+        <v>65</v>
       </c>
       <c r="D27" t="n">
-        <v>6.7</v>
+        <v>20.7</v>
       </c>
       <c r="E27" t="n">
-        <v>72.5</v>
+        <v>44.3</v>
       </c>
       <c r="F27" t="n">
-        <v>6.7</v>
+        <v>20.7</v>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>42.1</v>
       </c>
       <c r="H27" t="n">
-        <v>8.3</v>
+        <v>23.1</v>
       </c>
       <c r="I27" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1951,34 +1960,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>88.9</v>
+        <v>79.2</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>6.7</v>
       </c>
       <c r="E28" t="n">
-        <v>38.9</v>
+        <v>72.5</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>6.7</v>
       </c>
       <c r="G28" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -1986,34 +1995,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>61.4</v>
+        <v>88.9</v>
       </c>
       <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" t="n">
         <v>16.7</v>
       </c>
-      <c r="E29" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>28.6</v>
-      </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>26.7</v>
+        <v>75</v>
       </c>
       <c r="J29" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -2021,34 +2030,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>83.8</v>
+        <v>61.4</v>
       </c>
       <c r="D30" t="n">
-        <v>26.5</v>
+        <v>16.7</v>
       </c>
       <c r="E30" t="n">
-        <v>57.3</v>
+        <v>44.7</v>
       </c>
       <c r="F30" t="n">
-        <v>26.5</v>
+        <v>16.7</v>
       </c>
       <c r="G30" t="n">
-        <v>22.5</v>
+        <v>28.6</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I30" t="n">
-        <v>56.2</v>
+        <v>26.7</v>
       </c>
       <c r="J30" t="n">
-        <v>18.8</v>
+        <v>46.7</v>
       </c>
       <c r="K30" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -2056,34 +2065,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>68.6</v>
+        <v>83.8</v>
       </c>
       <c r="D31" t="n">
-        <v>8.8</v>
+        <v>26.5</v>
       </c>
       <c r="E31" t="n">
-        <v>59.8</v>
+        <v>57.3</v>
       </c>
       <c r="F31" t="n">
-        <v>8.8</v>
+        <v>26.5</v>
       </c>
       <c r="G31" t="n">
-        <v>29.6</v>
+        <v>22.5</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="K31" t="n">
-        <v>8.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="32">
@@ -2091,34 +2100,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>68.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>59.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I32" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J32" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="33">
@@ -2126,34 +2135,34 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>56.2</v>
+        <v>33.3</v>
       </c>
       <c r="J33" t="n">
-        <v>18.8</v>
+        <v>66.7</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2161,34 +2170,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>84</v>
+        <v>62.5</v>
       </c>
       <c r="D34" t="n">
-        <v>5.6</v>
+        <v>12.1</v>
       </c>
       <c r="E34" t="n">
-        <v>78.4</v>
+        <v>50.4</v>
       </c>
       <c r="F34" t="n">
-        <v>5.6</v>
+        <v>12.1</v>
       </c>
       <c r="G34" t="n">
-        <v>4.5</v>
+        <v>17.6</v>
       </c>
       <c r="H34" t="n">
-        <v>11.8</v>
+        <v>8.3</v>
       </c>
       <c r="I34" t="n">
-        <v>26.7</v>
+        <v>56.2</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>18.8</v>
       </c>
       <c r="K34" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2196,34 +2205,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" t="n">
-        <v>59.5</v>
+        <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>5.6</v>
       </c>
       <c r="E35" t="n">
-        <v>46.2</v>
+        <v>78.4</v>
       </c>
       <c r="F35" t="n">
-        <v>13.3</v>
+        <v>5.6</v>
       </c>
       <c r="G35" t="n">
-        <v>41.9</v>
+        <v>4.5</v>
       </c>
       <c r="H35" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="I35" t="n">
-        <v>55.6</v>
+        <v>26.7</v>
       </c>
       <c r="J35" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K35" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="36">
@@ -2231,34 +2240,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>41.9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I36" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="37">
@@ -2266,34 +2275,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>64.7</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>33.5</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2301,34 +2310,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>80</v>
+        <v>64.7</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>33.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="39">
@@ -2336,34 +2345,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" t="n">
-        <v>52.3</v>
+        <v>80</v>
       </c>
       <c r="D39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>40.2</v>
+        <v>80</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>14.8</v>
+        <v>25</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>64.3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>21.4</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2371,34 +2380,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>56.2</v>
+        <v>52.3</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>12.1</v>
       </c>
       <c r="E40" t="n">
-        <v>26.2</v>
+        <v>40.2</v>
       </c>
       <c r="F40" t="n">
-        <v>30</v>
+        <v>12.1</v>
       </c>
       <c r="G40" t="n">
-        <v>41.7</v>
+        <v>14.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="41">
@@ -2406,31 +2415,31 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>26.2</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="H41" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2438,37 +2447,37 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>42.9</v>
       </c>
       <c r="I42" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2476,34 +2485,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>27.5</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="44">
@@ -2511,34 +2520,34 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2546,34 +2555,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C45" t="n">
-        <v>66.7</v>
+        <v>47.1</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E45" t="n">
-        <v>41.7</v>
+        <v>30.4</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G45" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K45" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="46">
@@ -2581,34 +2590,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>67.5</v>
+        <v>41.7</v>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G46" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -2616,96 +2625,96 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47"/>
+        <v>20</v>
+      </c>
+      <c r="G47" t="n">
+        <v>37.5</v>
+      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
+      <c r="I47" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>57.7</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48"/>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>40.1</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="50">
@@ -2713,34 +2722,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" t="n">
         <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>25</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>66.7</v>
       </c>
     </row>
     <row r="51">
@@ -2748,19 +2757,19 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E51" t="n">
-        <v>66.7</v>
+        <v>42.3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G51" t="n">
         <v>25</v>
@@ -2769,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="52">
@@ -2783,31 +2792,31 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C52" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>41.3</v>
+        <v>66.7</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="H52" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>50</v>
@@ -2818,34 +2827,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C53" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D53" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="F53" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="G53" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="H53" t="n">
-        <v>11.1</v>
+        <v>22.2</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -2853,34 +2862,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="D54" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="n">
-        <v>-33.6</v>
+        <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I54" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -2888,34 +2897,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>62.5</v>
+        <v>36.4</v>
       </c>
       <c r="D55" t="n">
-        <v>38.5</v>
+        <v>70</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>-33.6</v>
       </c>
       <c r="F55" t="n">
-        <v>38.5</v>
+        <v>70</v>
       </c>
       <c r="G55" t="n">
-        <v>26.7</v>
+        <v>45.5</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K55" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2923,69 +2932,69 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C56" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="E56" t="n">
-        <v>42.9</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
         <v>70</v>
       </c>
-      <c r="B57" t="s">
-        <v>69</v>
-      </c>
       <c r="C57" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="D57" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>58.3</v>
+        <v>42.9</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K57" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="58">
@@ -2993,34 +3002,34 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C58" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J58" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59">
@@ -3028,34 +3037,34 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C59" t="n">
+        <v>80</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>80</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>66.7</v>
       </c>
-      <c r="D59" t="n">
-        <v>20</v>
-      </c>
-      <c r="E59" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F59" t="n">
-        <v>20</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20</v>
-      </c>
-      <c r="H59" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>25</v>
-      </c>
       <c r="J59" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="60">
@@ -3063,31 +3072,31 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C60" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E60" t="n">
-        <v>5.6</v>
+        <v>46.7</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G60" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3098,22 +3107,22 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C61" t="n">
         <v>55.6</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E61" t="n">
-        <v>43.1</v>
+        <v>5.6</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3125,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3133,31 +3142,31 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="n">
-        <v>46.7</v>
+        <v>43.1</v>
       </c>
       <c r="F62" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="G62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>100</v>
@@ -3168,34 +3177,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
         <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -3203,28 +3212,28 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>50</v>
@@ -3238,28 +3247,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C65" t="n">
-        <v>80</v>
-      </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>75</v>
+      </c>
+      <c r="D65" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50</v>
+      </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3267,34 +3282,28 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="F66" t="n">
-        <v>11.1</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
       <c r="G66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
         <v>33.3</v>
       </c>
-      <c r="I66" t="n">
-        <v>100</v>
-      </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="67">
@@ -3302,25 +3311,25 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
@@ -3329,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3337,22 +3346,22 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C68" t="n">
-        <v>46.7</v>
+        <v>100</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>26.7</v>
+        <v>75</v>
       </c>
       <c r="F68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3364,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="69">
@@ -3372,34 +3381,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C69" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="D69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E69" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="n">
         <v>75</v>
       </c>
-      <c r="E69" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="F69" t="n">
-        <v>75</v>
-      </c>
-      <c r="G69" t="n">
-        <v>33.3</v>
-      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
@@ -3407,54 +3416,60 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C70" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="D70" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="E70" t="n">
-        <v>8.3</v>
+        <v>-8.3</v>
       </c>
       <c r="F70" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="G70" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>50</v>
+      </c>
+      <c r="J70" t="n">
         <v>25</v>
       </c>
-      <c r="H70" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I70" t="n">
-        <v>50</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
       <c r="K70" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
         <v>85</v>
       </c>
-      <c r="B71" t="s">
-        <v>84</v>
-      </c>
       <c r="C71" t="n">
-        <v>100</v>
-      </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
+        <v>53.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>45.5</v>
+      </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I71" t="n">
         <v>50</v>
@@ -3471,34 +3486,28 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C72" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D72" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E72" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F72" t="n">
-        <v>36.4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
       <c r="G72" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
@@ -3506,34 +3515,34 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C73" t="n">
-        <v>76.9</v>
+        <v>78.6</v>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="E73" t="n">
-        <v>51.9</v>
+        <v>42.2</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>36.4</v>
       </c>
       <c r="G73" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I73" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3541,34 +3550,34 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C74" t="n">
-        <v>83.3</v>
+        <v>76.9</v>
       </c>
       <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>25</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J74" t="n">
         <v>28.6</v>
       </c>
-      <c r="E74" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>50</v>
-      </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="75">
@@ -3576,31 +3585,31 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C75" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="E75" t="n">
-        <v>32.1</v>
+        <v>54.7</v>
       </c>
       <c r="F75" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="G75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I75" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3611,22 +3620,22 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C76" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G76" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3638,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3646,34 +3655,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C77" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>43.3</v>
+        <v>100</v>
       </c>
       <c r="F77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78">
@@ -3681,34 +3690,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E78" t="n">
-        <v>58.8</v>
+        <v>43.3</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H78" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J78" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="K78" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -3716,34 +3725,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C79" t="n">
-        <v>83.3</v>
+        <v>58.8</v>
       </c>
       <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J79" t="n">
         <v>16.7</v>
       </c>
-      <c r="E79" t="n">
-        <v>66.6</v>
-      </c>
-      <c r="F79" t="n">
+      <c r="K79" t="n">
         <v>16.7</v>
-      </c>
-      <c r="G79" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H79" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>100</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -3751,34 +3760,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" t="n">
-        <v>81.8</v>
+        <v>83.3</v>
       </c>
       <c r="D80" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="E80" t="n">
-        <v>72.7</v>
+        <v>66.6</v>
       </c>
       <c r="F80" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H80" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="I80" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K80" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3786,101 +3795,101 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C81" t="n">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="D81" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="E81" t="n">
-        <v>58.4</v>
+        <v>72.7</v>
       </c>
       <c r="F81" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="G81" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I81" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J81" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K81" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>58.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="B83" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C83" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3888,37 +3897,37 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" t="s">
         <v>98</v>
       </c>
-      <c r="B84" t="s">
-        <v>97</v>
-      </c>
       <c r="C84" t="n">
-        <v>85.7</v>
+        <v>61.5</v>
       </c>
       <c r="D84" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="n">
-        <v>63.5</v>
+        <v>50.4</v>
       </c>
       <c r="F84" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="G84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I84" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J84" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3926,34 +3935,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C85" t="n">
-        <v>88.9</v>
+        <v>85.7</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E85" t="n">
-        <v>88.9</v>
+        <v>63.5</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H85" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K85" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86">
@@ -3961,34 +3970,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C86" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I86" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
@@ -3996,34 +4005,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C87" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>40</v>
+        <v>85.7</v>
       </c>
       <c r="J87" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4031,34 +4040,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C88" t="n">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="D88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>55</v>
+        <v>64.3</v>
       </c>
       <c r="F88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>11.1</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I88" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>14.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -4066,34 +4075,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C89" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D89" t="n">
         <v>25</v>
       </c>
       <c r="E89" t="n">
-        <v>60.7</v>
+        <v>55</v>
       </c>
       <c r="F89" t="n">
         <v>25</v>
       </c>
       <c r="G89" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="H89" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="90">
@@ -4101,34 +4110,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C90" t="n">
-        <v>90.9</v>
+        <v>85.7</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E90" t="n">
-        <v>90.9</v>
+        <v>60.7</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I90" t="n">
         <v>50</v>
       </c>
       <c r="J90" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K90" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4136,34 +4145,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" t="n">
-        <v>77.8</v>
+        <v>90.9</v>
       </c>
       <c r="D91" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>61.1</v>
+        <v>90.9</v>
       </c>
       <c r="F91" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J91" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K91" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="92">
@@ -4171,34 +4180,34 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C92" t="n">
-        <v>85.7</v>
+        <v>77.8</v>
       </c>
       <c r="D92" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E92" t="n">
-        <v>66.9</v>
+        <v>61.1</v>
       </c>
       <c r="F92" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="G92" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="H92" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I92" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K92" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="93">
@@ -4206,69 +4215,69 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C93" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="D93" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H93" t="n">
         <v>14.3</v>
       </c>
-      <c r="E93" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F93" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G93" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H93" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I93" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J93" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" t="s">
         <v>109</v>
       </c>
-      <c r="B94" t="s">
-        <v>108</v>
-      </c>
       <c r="C94" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D94" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="E94" t="n">
-        <v>33.4</v>
+        <v>52.4</v>
       </c>
       <c r="F94" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="G94" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I94" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="95">
@@ -4276,34 +4285,34 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C95" t="n">
-        <v>80.8</v>
+        <v>55.6</v>
       </c>
       <c r="D95" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="E95" t="n">
-        <v>62.6</v>
+        <v>33.4</v>
       </c>
       <c r="F95" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="G95" t="n">
-        <v>36</v>
+        <v>42.9</v>
       </c>
       <c r="H95" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4311,34 +4320,34 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="n">
-        <v>91.7</v>
+        <v>80.8</v>
       </c>
       <c r="D96" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="E96" t="n">
-        <v>41.7</v>
+        <v>62.6</v>
       </c>
       <c r="F96" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="G96" t="n">
-        <v>21.4</v>
+        <v>36</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I96" t="n">
-        <v>28.6</v>
+        <v>62.5</v>
       </c>
       <c r="J96" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="K96" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
@@ -4346,34 +4355,34 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C97" t="n">
-        <v>60</v>
+        <v>91.7</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E97" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="98">
@@ -4381,28 +4390,28 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C98" t="n">
+        <v>60</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>60</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>100</v>
-      </c>
-      <c r="D98" t="n">
-        <v>20</v>
-      </c>
-      <c r="E98" t="n">
-        <v>80</v>
-      </c>
-      <c r="F98" t="n">
-        <v>20</v>
-      </c>
-      <c r="G98" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>66.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -4416,34 +4425,34 @@
         <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C99" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E99" t="n">
+        <v>80</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
         <v>66.7</v>
       </c>
-      <c r="F99" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>50</v>
-      </c>
       <c r="J99" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4451,19 +4460,19 @@
         <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C100" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4472,13 +4481,13 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="101">
@@ -4486,34 +4495,34 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D101" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>54.7</v>
+        <v>100</v>
       </c>
       <c r="F101" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K101" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4521,34 +4530,34 @@
         <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E102" t="n">
-        <v>57.1</v>
+        <v>54.7</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G102" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H102" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J102" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="103">
@@ -4556,34 +4565,34 @@
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C103" t="n">
-        <v>70</v>
+        <v>57.1</v>
       </c>
       <c r="D103" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>32.5</v>
+        <v>57.1</v>
       </c>
       <c r="F103" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I103" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="J103" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104">
@@ -4591,34 +4600,34 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C104" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D104" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="E104" t="n">
-        <v>53.6</v>
+        <v>32.5</v>
       </c>
       <c r="F104" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="G104" t="n">
-        <v>46.7</v>
+        <v>17.6</v>
       </c>
       <c r="H104" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K104" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -4626,34 +4635,34 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C105" t="n">
-        <v>84.6</v>
+        <v>75</v>
       </c>
       <c r="D105" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F105" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G105" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H105" t="n">
         <v>14.3</v>
       </c>
-      <c r="E105" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F105" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G105" t="n">
-        <v>13</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
       <c r="I105" t="n">
-        <v>43.8</v>
+        <v>66.7</v>
       </c>
       <c r="J105" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="106">
@@ -4661,34 +4670,34 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>68.6</v>
+        <v>84.6</v>
       </c>
       <c r="D106" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="E106" t="n">
-        <v>59.5</v>
+        <v>70.3</v>
       </c>
       <c r="F106" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="G106" t="n">
-        <v>23.1</v>
+        <v>13</v>
       </c>
       <c r="H106" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="J106" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="K106" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="107">
@@ -4696,34 +4705,34 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>68.6</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E107" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I107" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="108">
@@ -4731,34 +4740,34 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C108" t="n">
-        <v>90.9</v>
+        <v>50</v>
       </c>
       <c r="D108" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>70.9</v>
+        <v>50</v>
       </c>
       <c r="F108" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J108" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -4766,31 +4775,31 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C109" t="n">
-        <v>60</v>
+        <v>90.9</v>
       </c>
       <c r="D109" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="E109" t="n">
-        <v>17.1</v>
+        <v>70.9</v>
       </c>
       <c r="F109" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="G109" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J109" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H109" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>100</v>
       </c>
       <c r="K109" t="n">
         <v>50</v>
@@ -4801,34 +4810,34 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D110" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="E110" t="n">
-        <v>73.3</v>
+        <v>17.1</v>
       </c>
       <c r="F110" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="G110" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I110" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111">
@@ -4836,22 +4845,22 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C111" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E111" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -4860,10 +4869,10 @@
         <v>33.3</v>
       </c>
       <c r="J111" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K111" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4871,51 +4880,57 @@
         <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C112" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="F112" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I112"/>
-      <c r="J112"/>
-      <c r="K112"/>
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>128</v>
+      </c>
+      <c r="B113" t="s">
         <v>129</v>
       </c>
-      <c r="B113" t="s">
-        <v>128</v>
-      </c>
       <c r="C113" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="n">
-        <v>42.9</v>
+        <v>5.6</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G113" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="H113" t="n">
         <v>66.7</v>
@@ -4929,25 +4944,25 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C114" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
@@ -4958,69 +4973,63 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C115" t="n">
-        <v>61.1</v>
+        <v>33.3</v>
       </c>
       <c r="D115" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>52</v>
+        <v>33.3</v>
       </c>
       <c r="F115" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I115" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
         <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C116" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D116" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="E116" t="n">
-        <v>31.8</v>
+        <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="G116" t="n">
-        <v>42.9</v>
+        <v>8.3</v>
       </c>
       <c r="H116" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J116" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="117">
@@ -5028,34 +5037,34 @@
         <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C117" t="n">
         <v>50</v>
       </c>
       <c r="D117" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E117" t="n">
-        <v>26.9</v>
+        <v>31.8</v>
       </c>
       <c r="F117" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="G117" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="H117" t="n">
         <v>16.7</v>
       </c>
       <c r="I117" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K117" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118">
@@ -5063,34 +5072,34 @@
         <v>134</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C118" t="n">
+        <v>50</v>
+      </c>
+      <c r="D118" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H118" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I118" t="n">
         <v>66.7</v>
       </c>
-      <c r="D118" t="n">
-        <v>25</v>
-      </c>
-      <c r="E118" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F118" t="n">
-        <v>25</v>
-      </c>
-      <c r="G118" t="n">
+      <c r="J118" t="n">
         <v>33.3</v>
       </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>100</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="119">
@@ -5098,34 +5107,34 @@
         <v>135</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C119" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E119" t="n">
-        <v>61.5</v>
+        <v>41.7</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G119" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="H119" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J119" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5133,34 +5142,34 @@
         <v>136</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C120" t="n">
-        <v>45</v>
+        <v>61.5</v>
       </c>
       <c r="D120" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>28.3</v>
+        <v>61.5</v>
       </c>
       <c r="F120" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>27.3</v>
+        <v>12.5</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I120" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="121">
@@ -5168,31 +5177,31 @@
         <v>137</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C121" t="n">
-        <v>71.4</v>
+        <v>45</v>
       </c>
       <c r="D121" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E121" t="n">
-        <v>51.4</v>
+        <v>28.3</v>
       </c>
       <c r="F121" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G121" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J121" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5203,67 +5212,102 @@
         <v>138</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C122" t="n">
         <v>71.4</v>
       </c>
       <c r="D122" t="n">
+        <v>20</v>
+      </c>
+      <c r="E122" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F122" t="n">
+        <v>20</v>
+      </c>
+      <c r="G122" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>50</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>139</v>
+      </c>
+      <c r="B123" t="s">
+        <v>129</v>
+      </c>
+      <c r="C123" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D123" t="n">
         <v>7.1</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E123" t="n">
         <v>64.3</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F123" t="n">
         <v>7.1</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G123" t="n">
         <v>18.2</v>
       </c>
-      <c r="H122" t="n">
+      <c r="H123" t="n">
         <v>12.5</v>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
         <v>100</v>
       </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123"/>
-      <c r="B123" t="s">
-        <v>139</v>
-      </c>
-      <c r="C123" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="D123" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124"/>
+      <c r="B124" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E124" t="n">
         <v>52.3</v>
       </c>
-      <c r="F123" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G123" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H123" t="n">
-        <v>9.2</v>
-      </c>
-      <c r="I123" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="J123" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="K123" t="n">
-        <v>31.8</v>
+      <c r="F124" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>9</v>
+      </c>
+      <c r="I124" t="n">
+        <v>49</v>
+      </c>
+      <c r="J124" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K124" t="n">
+        <v>31.9</v>
       </c>
     </row>
   </sheetData>
@@ -5295,22 +5339,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5319,18 +5363,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -5365,7 +5409,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -5400,7 +5444,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -5435,7 +5479,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5470,7 +5514,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5505,7 +5549,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5540,7 +5584,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -5575,7 +5619,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -5610,42 +5654,42 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>57.1</v>
+        <v>56.2</v>
       </c>
       <c r="D10" t="n">
-        <v>48.7</v>
+        <v>50.7</v>
       </c>
       <c r="E10" t="n">
-        <v>9.2</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>25.9</v>
+        <v>22.6</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>20.9</v>
+        <v>22.2</v>
       </c>
       <c r="K10" t="n">
-        <v>-18.5</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -5680,7 +5724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -5713,104 +5757,104 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.1</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>66.3</v>
+        <v>71.4</v>
       </c>
       <c r="E13" t="n">
-        <v>22.8</v>
+        <v>45.5</v>
       </c>
       <c r="F13" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="G13" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>28.2</v>
+        <v>37.5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>52.6</v>
+        <v>53.1</v>
       </c>
       <c r="D14" t="n">
-        <v>62.3</v>
+        <v>66.3</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>22.8</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>40.7</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>8.2</v>
       </c>
       <c r="H14" t="n">
-        <v>58.8</v>
+        <v>60.6</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>16.7</v>
+        <v>28.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1</v>
+        <v>62.3</v>
       </c>
       <c r="E15" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -5818,112 +5862,112 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>53.3</v>
+        <v>77.8</v>
       </c>
       <c r="D16" t="n">
-        <v>43.6</v>
+        <v>64.7</v>
       </c>
       <c r="E16" t="n">
-        <v>8.8</v>
+        <v>8.3</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>35.7</v>
+        <v>11.1</v>
       </c>
       <c r="H16" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="J16" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-28.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>37.5</v>
+        <v>53.3</v>
       </c>
       <c r="D17" t="n">
-        <v>55.8</v>
+        <v>43.6</v>
       </c>
       <c r="E17" t="n">
-        <v>9.5</v>
+        <v>8.8</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>65.3</v>
+        <v>37.5</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>55.8</v>
       </c>
       <c r="E18" t="n">
-        <v>17.8</v>
+        <v>9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>48.6</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>7.4</v>
+        <v>42.9</v>
       </c>
       <c r="H18" t="n">
-        <v>51.5</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>25.4</v>
+        <v>17.6</v>
       </c>
       <c r="K18" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -5932,392 +5976,392 @@
         <v>33.3</v>
       </c>
       <c r="D19" t="n">
-        <v>35.7</v>
+        <v>68.8</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>14.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G19" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K19" t="n">
         <v>33.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-16.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>55.6</v>
+        <v>65.3</v>
       </c>
       <c r="D20" t="n">
-        <v>49.1</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>6.7</v>
+        <v>17.8</v>
       </c>
       <c r="F20" t="n">
-        <v>66.7</v>
+        <v>48.6</v>
       </c>
       <c r="G20" t="n">
-        <v>17.6</v>
+        <v>7.4</v>
       </c>
       <c r="H20" t="n">
-        <v>18.2</v>
+        <v>51.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>23.8</v>
+        <v>25.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>68.4</v>
+        <v>33.3</v>
       </c>
       <c r="D21" t="n">
-        <v>63.8</v>
+        <v>35.7</v>
       </c>
       <c r="E21" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>7.9</v>
+        <v>16.7</v>
       </c>
       <c r="H21" t="n">
-        <v>46.6</v>
+        <v>33.3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="n">
-        <v>45.2</v>
+        <v>55.6</v>
       </c>
       <c r="D22" t="n">
-        <v>54.3</v>
+        <v>49.1</v>
       </c>
       <c r="E22" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="F22" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="G22" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H22" t="n">
-        <v>52.9</v>
+        <v>18.2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.4</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="n">
-        <v>83.3</v>
+        <v>68.4</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>63.8</v>
       </c>
       <c r="E23" t="n">
-        <v>18.2</v>
+        <v>10.3</v>
       </c>
       <c r="F23" t="n">
-        <v>33.3</v>
+        <v>47.8</v>
       </c>
       <c r="G23" t="n">
-        <v>16.7</v>
+        <v>7.9</v>
       </c>
       <c r="H23" t="n">
-        <v>25</v>
+        <v>46.6</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>22.2</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="n">
-        <v>58.3</v>
+        <v>45.2</v>
       </c>
       <c r="D24" t="n">
-        <v>52.1</v>
+        <v>54.3</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3</v>
+        <v>11.1</v>
       </c>
       <c r="F24" t="n">
-        <v>66.7</v>
+        <v>26.7</v>
       </c>
       <c r="G24" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>52.9</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>42.9</v>
+        <v>23.1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" t="n">
-        <v>37.5</v>
+        <v>83.3</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>4.5</v>
+        <v>18.2</v>
       </c>
       <c r="F25" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H25" t="n">
         <v>25</v>
       </c>
-      <c r="G25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>38.5</v>
-      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>51.4</v>
+        <v>58.3</v>
       </c>
       <c r="D26" t="n">
-        <v>59.4</v>
+        <v>52.1</v>
       </c>
       <c r="E26" t="n">
-        <v>13.2</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>42.1</v>
+        <v>66.7</v>
       </c>
       <c r="G26" t="n">
-        <v>11.4</v>
+        <v>33.3</v>
       </c>
       <c r="H26" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>27</v>
+        <v>42.9</v>
       </c>
       <c r="K26" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>28.6</v>
+        <v>4.5</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>45.5</v>
+        <v>18.2</v>
       </c>
       <c r="K27" t="n">
-        <v>40</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>66.7</v>
+        <v>51.4</v>
       </c>
       <c r="D28" t="n">
-        <v>57.1</v>
+        <v>59.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="G28" t="n">
-        <v>16.7</v>
+        <v>11.4</v>
       </c>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>14.3</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>-16.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>15.4</v>
+        <v>45.5</v>
       </c>
       <c r="K29" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -6326,327 +6370,327 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H30" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>9.3</v>
+        <v>23.1</v>
       </c>
       <c r="F31" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>60</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K31" t="n">
         <v>16.7</v>
-      </c>
-      <c r="H31" t="n">
-        <v>50</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-11.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" t="n">
-        <v>62.8</v>
+        <v>33.3</v>
       </c>
       <c r="D32" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>48.5</v>
+        <v>66.7</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="D33" t="n">
         <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33"/>
+        <v>9.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.5</v>
+      </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H33" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>28.6</v>
+        <v>62.8</v>
       </c>
       <c r="D34" t="n">
-        <v>37.5</v>
+        <v>57.5</v>
       </c>
       <c r="E34" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G34" t="n">
-        <v>28.6</v>
+        <v>9.3</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="I34" t="n">
-        <v>14.3</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-28.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>70.2</v>
+        <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35"/>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="D36" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>9.5</v>
       </c>
       <c r="F36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>6.7</v>
+        <v>28.6</v>
       </c>
       <c r="H36" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>6.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="D37" t="n">
-        <v>80</v>
+        <v>70.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37"/>
+        <v>23.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>50</v>
+      </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C38" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="D38" t="n">
-        <v>49.2</v>
+        <v>66.7</v>
       </c>
       <c r="E38" t="n">
-        <v>9.1</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="H38" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D39" t="n">
-        <v>52.9</v>
+        <v>80</v>
       </c>
       <c r="E39" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F39" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39"/>
       <c r="G39" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -6654,63 +6698,69 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="D40" t="n">
-        <v>7.7</v>
+        <v>49.2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40"/>
+        <v>9.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33.3</v>
+      </c>
       <c r="G40" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40"/>
+        <v>11.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>46.2</v>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40"/>
+      <c r="J40" t="n">
+        <v>20</v>
+      </c>
       <c r="K40" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C41" t="n">
-        <v>35.3</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>57.6</v>
+        <v>52.9</v>
       </c>
       <c r="E41" t="n">
-        <v>17.6</v>
+        <v>11.8</v>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G41" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="H41" t="n">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -6718,69 +6768,63 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C42" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>63.2</v>
+        <v>7.7</v>
       </c>
       <c r="E42" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>16.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42"/>
       <c r="G42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>28.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H42"/>
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J42"/>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>57.6</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -6788,51 +6832,51 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C44" t="n">
-        <v>63</v>
+        <v>55.6</v>
       </c>
       <c r="D44" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="E44" t="n">
-        <v>13.6</v>
+        <v>7.1</v>
       </c>
       <c r="F44" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="G44" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>23.5</v>
+        <v>10.5</v>
       </c>
       <c r="K44" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>87.5</v>
+        <v>55</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -6844,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6858,60 +6902,60 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" t="n">
-        <v>69.2</v>
+        <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>74.7</v>
+        <v>57.8</v>
       </c>
       <c r="E46" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G46" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H46" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="K46" t="n">
-        <v>19.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C47" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="D47" t="n">
-        <v>63.2</v>
+        <v>87.5</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>66.7</v>
@@ -6920,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6928,121 +6972,121 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C48" t="n">
-        <v>58.3</v>
+        <v>69.2</v>
       </c>
       <c r="D48" t="n">
-        <v>65.3</v>
+        <v>74.7</v>
       </c>
       <c r="E48" t="n">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H48" t="n">
-        <v>42.9</v>
+        <v>57.9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>12.5</v>
+        <v>24.4</v>
       </c>
       <c r="K48" t="n">
-        <v>8.3</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C49" t="n">
-        <v>40</v>
+        <v>61.5</v>
       </c>
       <c r="D49" t="n">
-        <v>41.2</v>
+        <v>63.2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="H49" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="K49" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C50" t="n">
-        <v>14.3</v>
+        <v>58.3</v>
       </c>
       <c r="D50" t="n">
-        <v>44.1</v>
+        <v>65.3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F50" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G50" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K50" t="n">
-        <v>-14.3</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D51" t="n">
-        <v>38.9</v>
+        <v>41.2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -7051,573 +7095,643 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-66.7</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="D52" t="n">
-        <v>57.9</v>
+        <v>44.1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G52" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K52" t="n">
-        <v>-25</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>41.4</v>
+        <v>38.9</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-16.6</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C54" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="E54" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>51.9</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="K54" t="n">
-        <v>8.4</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55" t="n">
         <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>59.3</v>
+        <v>41.4</v>
       </c>
       <c r="E55" t="n">
         <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="G55" t="n">
-        <v>7.1</v>
+        <v>33.3</v>
       </c>
       <c r="H55" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>8.3</v>
+        <v>14.3</v>
       </c>
       <c r="K55" t="n">
-        <v>7.2</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="E56" t="n">
-        <v>10.2</v>
+        <v>18.7</v>
       </c>
       <c r="F56" t="n">
-        <v>46.7</v>
+        <v>51.9</v>
       </c>
       <c r="G56" t="n">
-        <v>6.7</v>
+        <v>20.8</v>
       </c>
       <c r="H56" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>16.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C57" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>87.5</v>
+        <v>59.3</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H57" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>33.3</v>
+        <v>8.3</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58"/>
+        <v>10.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>46.7</v>
+      </c>
       <c r="G58" t="n">
-        <v>66.7</v>
+        <v>6.7</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-66.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C59" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>63.4</v>
+        <v>87.5</v>
       </c>
       <c r="E59" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>20</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60"/>
+      <c r="G60" t="n">
         <v>66.7</v>
       </c>
-      <c r="D60" t="n">
-        <v>80</v>
-      </c>
-      <c r="E60" t="n">
-        <v>50</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" t="n">
-        <v>40</v>
+        <v>77.8</v>
       </c>
       <c r="D61" t="n">
-        <v>31.6</v>
+        <v>63.4</v>
       </c>
       <c r="E61" t="n">
-        <v>7.1</v>
+        <v>17.6</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-20</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C62" t="n">
         <v>66.7</v>
       </c>
       <c r="D62" t="n">
-        <v>57.1</v>
+        <v>80</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62"/>
+        <v>50</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D63" t="n">
-        <v>39.1</v>
+        <v>31.6</v>
       </c>
       <c r="E63" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
+        <v>40</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>33.3</v>
       </c>
-      <c r="H63" t="n">
-        <v>50</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
       <c r="K63" t="n">
-        <v>-33.3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" t="n">
         <v>66.7</v>
       </c>
       <c r="D64" t="n">
-        <v>53.3</v>
+        <v>57.1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
+      <c r="F64"/>
       <c r="G64" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H64" t="n">
-        <v>28.6</v>
+        <v>55.6</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>-11.1</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C65" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>55.2</v>
+        <v>39.1</v>
       </c>
       <c r="E65" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="F65" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>8</v>
+        <v>33.3</v>
       </c>
       <c r="H65" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C66" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>205</v>
+      </c>
+      <c r="B67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" t="n">
+        <v>52</v>
+      </c>
+      <c r="D67" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" t="n">
         <v>68.8</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D68" t="n">
         <v>59.2</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E68" t="n">
         <v>16</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>5.9</v>
       </c>
-      <c r="H66" t="n">
-        <v>50</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" t="n">
         <v>5.9</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J68" t="n">
         <v>17.4</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67"/>
-      <c r="B67" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="D67" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="E67" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F67" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G67" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J67" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K67" t="n">
-        <v>-3.2</v>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69"/>
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -48,10 +48,16 @@
     <t xml:space="preserve">Pull %</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Awrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brock Badgers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adam Geddes</t>
   </si>
   <si>
-    <t xml:space="preserve">Brock Badgers</t>
+    <t xml:space="preserve">Adam Thuss</t>
   </si>
   <si>
     <t xml:space="preserve">Avery Brooks</t>
@@ -72,6 +78,9 @@
     <t xml:space="preserve">Colin Mockford</t>
   </si>
   <si>
+    <t xml:space="preserve">Dominic Pugliese</t>
+  </si>
+  <si>
     <t xml:space="preserve">Flynn Matheson</t>
   </si>
   <si>
@@ -105,21 +114,42 @@
     <t xml:space="preserve">Liam Riley</t>
   </si>
   <si>
+    <t xml:space="preserve">Matt Dubrick</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nate Parsons</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathaniel King</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nolan Phelan</t>
   </si>
   <si>
+    <t xml:space="preserve">Parker McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quin Steinke</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reid Lunney</t>
   </si>
   <si>
+    <t xml:space="preserve">Ryan Nuernberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Valero</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tim Somerville</t>
   </si>
   <si>
     <t xml:space="preserve">Tobey Drennan</t>
   </si>
   <si>
+    <t xml:space="preserve">Trent Sillett</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adrian Crewe</t>
   </si>
   <si>
@@ -306,9 +336,6 @@
     <t xml:space="preserve">Sam Shephard</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam Awrey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Western Mustangs</t>
   </si>
   <si>
@@ -330,13 +357,10 @@
     <t xml:space="preserve">Koby Sernick</t>
   </si>
   <si>
-    <t xml:space="preserve">Parker McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Nuernberger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Sillett</t>
+    <t xml:space="preserve">Neurnberger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rowan Rajhans</t>
   </si>
   <si>
     <t xml:space="preserve">Ash Abols</t>
@@ -459,6 +483,9 @@
     <t xml:space="preserve">Charlie Hughes</t>
   </si>
   <si>
+    <t xml:space="preserve">Connor Lynch</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daniel Lucas</t>
   </si>
   <si>
@@ -501,6 +528,12 @@
     <t xml:space="preserve">Ryan Facchini</t>
   </si>
   <si>
+    <t xml:space="preserve">Sebastian Shikatani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Ray</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wilson Michel</t>
   </si>
   <si>
@@ -580,6 +613,9 @@
   </si>
   <si>
     <t xml:space="preserve">Justin Stonkus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leo LeClair</t>
   </si>
   <si>
     <t xml:space="preserve">Lucas Shannon</t>
@@ -688,8 +724,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K124" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K149"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -708,8 +744,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K69" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K80" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K80"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1065,31 +1101,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>52.9</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>14.6</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>15.9</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -1100,31 +1136,31 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>66.7</v>
+        <v>59.4</v>
       </c>
       <c r="D3" t="n">
-        <v>28.6</v>
+        <v>7.8</v>
       </c>
       <c r="E3" t="n">
-        <v>38.1</v>
+        <v>51.6</v>
       </c>
       <c r="F3" t="n">
-        <v>28.6</v>
+        <v>7.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>21.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="4">
@@ -1135,31 +1171,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>73.6</v>
+        <v>66.7</v>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>33.3</v>
       </c>
       <c r="E4" t="n">
-        <v>59.2</v>
+        <v>33.4</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4</v>
+        <v>33.3</v>
       </c>
       <c r="G4" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>35.8</v>
+        <v>33.3</v>
       </c>
       <c r="K4" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1170,28 +1206,28 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>28.6</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>38.1</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8</v>
+        <v>28.6</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1205,31 +1241,31 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>45.5</v>
+        <v>73.7</v>
       </c>
       <c r="D6" t="n">
-        <v>8.9</v>
+        <v>14.3</v>
       </c>
       <c r="E6" t="n">
-        <v>36.6</v>
+        <v>59.4</v>
       </c>
       <c r="F6" t="n">
-        <v>8.9</v>
+        <v>14.3</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="H6" t="n">
-        <v>43.8</v>
+        <v>6.9</v>
       </c>
       <c r="I6" t="n">
-        <v>71.4</v>
+        <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K6" t="n">
-        <v>57.1</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="7">
@@ -1240,31 +1276,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>71.9</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="E7" t="n">
-        <v>61.8</v>
+        <v>43.6</v>
       </c>
       <c r="F7" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="G7" t="n">
-        <v>9.1</v>
+        <v>34.6</v>
       </c>
       <c r="H7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="I7" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
       <c r="J7" t="n">
-        <v>35</v>
+        <v>11.1</v>
       </c>
       <c r="K7" t="n">
-        <v>32.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
@@ -1275,31 +1311,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>73.3</v>
+        <v>45.5</v>
       </c>
       <c r="D8" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="E8" t="n">
-        <v>67.1</v>
+        <v>36.6</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="G8" t="n">
-        <v>30.8</v>
+        <v>21.4</v>
       </c>
       <c r="H8" t="n">
-        <v>14.3</v>
+        <v>43.8</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>71.4</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="9">
@@ -1310,31 +1346,31 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>79.6</v>
+        <v>71.9</v>
       </c>
       <c r="D9" t="n">
-        <v>19.7</v>
+        <v>10.1</v>
       </c>
       <c r="E9" t="n">
-        <v>59.9</v>
+        <v>61.8</v>
       </c>
       <c r="F9" t="n">
-        <v>19.7</v>
+        <v>10.1</v>
       </c>
       <c r="G9" t="n">
-        <v>24.6</v>
+        <v>9.1</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="I9" t="n">
-        <v>48.1</v>
+        <v>45</v>
       </c>
       <c r="J9" t="n">
-        <v>28.8</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>42.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="10">
@@ -1345,31 +1381,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="E10" t="n">
-        <v>70.8</v>
+        <v>67.1</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>19.4</v>
+        <v>30.8</v>
       </c>
       <c r="H10" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="I10" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K10" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1380,26 +1416,26 @@
         <v>12</v>
       </c>
       <c r="C11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
         <v>100</v>
       </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1409,31 +1445,31 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>60.7</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>25.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>26.3</v>
       </c>
       <c r="K12" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="13">
@@ -1444,31 +1480,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>72.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="E13" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="I13" t="n">
-        <v>28.6</v>
+        <v>43.8</v>
       </c>
       <c r="J13" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>14.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="14">
@@ -1479,31 +1515,25 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17.9</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
       <c r="G14" t="n">
-        <v>32.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>51.2</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>32.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1514,11 +1544,17 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
+        <v>75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
@@ -1532,7 +1568,7 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1543,31 +1579,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>60.9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>60.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>28.6</v>
+        <v>7.1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="17">
@@ -1578,31 +1614,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>76.3</v>
+        <v>66.9</v>
       </c>
       <c r="D17" t="n">
-        <v>12.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="n">
-        <v>63.6</v>
+        <v>49.5</v>
       </c>
       <c r="F17" t="n">
-        <v>12.7</v>
+        <v>17.4</v>
       </c>
       <c r="G17" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="H17" t="n">
-        <v>18.5</v>
+        <v>15.7</v>
       </c>
       <c r="I17" t="n">
-        <v>55.6</v>
+        <v>48.9</v>
       </c>
       <c r="J17" t="n">
-        <v>22.2</v>
+        <v>25.5</v>
       </c>
       <c r="K17" t="n">
-        <v>55.6</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="18">
@@ -1613,31 +1649,25 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>9.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
       <c r="G18" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>31.8</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>31.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1648,31 +1678,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>74.6</v>
+        <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>58.4</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>29.7</v>
+        <v>28.6</v>
       </c>
       <c r="H19" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>48.1</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -1683,31 +1713,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>68.8</v>
+        <v>75.5</v>
       </c>
       <c r="D20" t="n">
-        <v>17.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>17.8</v>
+        <v>12.5</v>
       </c>
       <c r="G20" t="n">
-        <v>26.8</v>
+        <v>28.3</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>15.2</v>
       </c>
       <c r="I20" t="n">
-        <v>36.8</v>
+        <v>43.5</v>
       </c>
       <c r="J20" t="n">
-        <v>26.3</v>
+        <v>17.4</v>
       </c>
       <c r="K20" t="n">
-        <v>44.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="21">
@@ -1718,31 +1748,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>78.7</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>16.5</v>
+        <v>10.9</v>
       </c>
       <c r="E21" t="n">
-        <v>62.2</v>
+        <v>57.1</v>
       </c>
       <c r="F21" t="n">
-        <v>16.5</v>
+        <v>10.9</v>
       </c>
       <c r="G21" t="n">
-        <v>23.3</v>
+        <v>10.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4</v>
+        <v>13.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>37.9</v>
       </c>
       <c r="J21" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="K21" t="n">
-        <v>36.4</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="22">
@@ -1753,31 +1783,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>55.4</v>
+        <v>75</v>
       </c>
       <c r="D22" t="n">
-        <v>14.9</v>
+        <v>16.2</v>
       </c>
       <c r="E22" t="n">
-        <v>40.5</v>
+        <v>58.8</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9</v>
+        <v>16.2</v>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>29.2</v>
       </c>
       <c r="H22" t="n">
-        <v>13.5</v>
+        <v>11.9</v>
       </c>
       <c r="I22" t="n">
-        <v>51.5</v>
+        <v>46.4</v>
       </c>
       <c r="J22" t="n">
-        <v>21.2</v>
+        <v>32.1</v>
       </c>
       <c r="K22" t="n">
-        <v>27.3</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="23">
@@ -1788,31 +1818,31 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>88.9</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>68.9</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1823,31 +1853,31 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>45.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>16.7</v>
+        <v>35</v>
       </c>
       <c r="J24" t="n">
-        <v>83.3</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>33.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="25">
@@ -1855,296 +1885,278 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>33.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
       <c r="G25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>100</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>35.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>37.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>65</v>
+        <v>83.3</v>
       </c>
       <c r="D27" t="n">
-        <v>20.7</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="n">
-        <v>44.3</v>
+        <v>70.8</v>
       </c>
       <c r="F27" t="n">
-        <v>20.7</v>
+        <v>12.5</v>
       </c>
       <c r="G27" t="n">
-        <v>42.1</v>
+        <v>16.7</v>
       </c>
       <c r="H27" t="n">
-        <v>23.1</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>79.2</v>
+        <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>6.7</v>
+        <v>66.7</v>
       </c>
       <c r="E28" t="n">
-        <v>72.5</v>
+        <v>-6.7</v>
       </c>
       <c r="F28" t="n">
-        <v>6.7</v>
+        <v>66.7</v>
       </c>
       <c r="G28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>88.9</v>
+        <v>55.4</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>14.9</v>
       </c>
       <c r="E29" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>14.9</v>
       </c>
       <c r="G29" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I29" t="n">
-        <v>75</v>
+        <v>51.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="n">
-        <v>61.4</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C30"/>
       <c r="D30" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>44.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30"/>
       <c r="F30" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G30" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G30"/>
       <c r="H30" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I30" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>57.3</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>56.2</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>68.6</v>
+        <v>85.7</v>
       </c>
       <c r="D32" t="n">
-        <v>8.8</v>
+        <v>16.7</v>
       </c>
       <c r="E32" t="n">
-        <v>59.8</v>
+        <v>69</v>
       </c>
       <c r="F32" t="n">
-        <v>8.8</v>
+        <v>16.7</v>
       </c>
       <c r="G32" t="n">
-        <v>29.6</v>
+        <v>7.1</v>
       </c>
       <c r="H32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
-        <v>8.3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2156,83 +2168,83 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K33" t="n">
         <v>33.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>50.4</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>56.2</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>18.8</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
         <v>46</v>
       </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
       <c r="C35" t="n">
-        <v>84</v>
+        <v>77.8</v>
       </c>
       <c r="D35" t="n">
-        <v>5.6</v>
+        <v>33.3</v>
       </c>
       <c r="E35" t="n">
-        <v>78.4</v>
+        <v>44.5</v>
       </c>
       <c r="F35" t="n">
-        <v>5.6</v>
+        <v>33.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="H35" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>26.7</v>
+        <v>100</v>
       </c>
       <c r="J35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
@@ -2240,34 +2252,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>41.9</v>
+        <v>50</v>
       </c>
       <c r="H36" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2275,34 +2287,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>44.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="I37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -2310,34 +2322,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>64.7</v>
+        <v>79.2</v>
       </c>
       <c r="D38" t="n">
-        <v>31.2</v>
+        <v>6.7</v>
       </c>
       <c r="E38" t="n">
-        <v>33.5</v>
+        <v>72.5</v>
       </c>
       <c r="F38" t="n">
-        <v>31.2</v>
+        <v>6.7</v>
       </c>
       <c r="G38" t="n">
-        <v>31.2</v>
+        <v>15</v>
       </c>
       <c r="H38" t="n">
-        <v>16.7</v>
+        <v>8.3</v>
       </c>
       <c r="I38" t="n">
-        <v>57.1</v>
+        <v>70</v>
       </c>
       <c r="J38" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -2345,34 +2357,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C39" t="n">
-        <v>80</v>
+        <v>88.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>80</v>
+        <v>38.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
@@ -2380,34 +2392,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C40" t="n">
-        <v>52.3</v>
+        <v>61.4</v>
       </c>
       <c r="D40" t="n">
-        <v>12.1</v>
+        <v>16.7</v>
       </c>
       <c r="E40" t="n">
-        <v>40.2</v>
+        <v>44.7</v>
       </c>
       <c r="F40" t="n">
-        <v>12.1</v>
+        <v>16.7</v>
       </c>
       <c r="G40" t="n">
-        <v>14.8</v>
+        <v>28.6</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="I40" t="n">
-        <v>64.3</v>
+        <v>26.7</v>
       </c>
       <c r="J40" t="n">
-        <v>21.4</v>
+        <v>46.7</v>
       </c>
       <c r="K40" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -2415,34 +2427,34 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C41" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>56.2</v>
       </c>
-      <c r="D41" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="F41" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>75</v>
-      </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="42">
@@ -2450,376 +2462,384 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>68.6</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>59.8</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>8.8</v>
       </c>
       <c r="G42" t="n">
-        <v>66.7</v>
+        <v>29.6</v>
       </c>
       <c r="H42" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="J43" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="K43" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>62.5</v>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="E44" t="n">
-        <v>27.5</v>
+        <v>50.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I44" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>47.1</v>
+        <v>84</v>
       </c>
       <c r="D45" t="n">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="E45" t="n">
-        <v>30.4</v>
+        <v>78.4</v>
       </c>
       <c r="F45" t="n">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I45" t="n">
-        <v>57.1</v>
+        <v>26.7</v>
       </c>
       <c r="J45" t="n">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="K45" t="n">
-        <v>57.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C46" t="n">
-        <v>66.7</v>
+        <v>59.5</v>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="E46" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="G46" t="n">
-        <v>25</v>
+        <v>41.9</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I46" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K46" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>67.5</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>64.7</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48"/>
+        <v>31.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>31.2</v>
+      </c>
       <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48"/>
+        <v>16.7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>28.6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C49" t="n">
-        <v>57.7</v>
+        <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>40.1</v>
+        <v>80</v>
       </c>
       <c r="F49" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>52.3</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>40.2</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>14.8</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="D51" t="n">
-        <v>7.7</v>
+        <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>42.3</v>
+        <v>26.2</v>
       </c>
       <c r="F51" t="n">
-        <v>7.7</v>
+        <v>30</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>41.7</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
         <v>64</v>
       </c>
-      <c r="B52" t="s">
-        <v>54</v>
-      </c>
       <c r="C52" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>66.7</v>
       </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>25</v>
-      </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2827,34 +2847,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C53" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>41.3</v>
+        <v>60</v>
       </c>
       <c r="F53" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>38.5</v>
+        <v>26.7</v>
       </c>
       <c r="H53" t="n">
-        <v>22.2</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="J53" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K53" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="54">
@@ -2862,34 +2882,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C54" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D54" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>27.5</v>
       </c>
       <c r="F54" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G54" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2897,34 +2917,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C55" t="n">
-        <v>36.4</v>
+        <v>47.1</v>
       </c>
       <c r="D55" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="E55" t="n">
-        <v>-33.6</v>
+        <v>30.4</v>
       </c>
       <c r="F55" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="G55" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J55" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="56">
@@ -2932,34 +2952,34 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C56" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>41.7</v>
       </c>
       <c r="F56" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -2967,311 +2987,303 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C57" t="n">
-        <v>42.9</v>
+        <v>87.5</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
-        <v>42.9</v>
+        <v>67.5</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J57" t="n">
         <v>33.3</v>
       </c>
       <c r="K57" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C58" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>58.3</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G58" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G58"/>
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="n">
-        <v>75</v>
-      </c>
-      <c r="J58" t="n">
-        <v>25</v>
-      </c>
-      <c r="K58" t="n">
-        <v>75</v>
-      </c>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C59" t="n">
-        <v>80</v>
+        <v>57.7</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E59" t="n">
-        <v>80</v>
+        <v>40.1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="J59" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="K59" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C60" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>25</v>
-      </c>
-      <c r="J60" t="n">
-        <v>75</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>7.7</v>
       </c>
       <c r="E61" t="n">
-        <v>5.6</v>
+        <v>42.3</v>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>7.7</v>
       </c>
       <c r="G61" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C62" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>43.1</v>
+        <v>66.7</v>
       </c>
       <c r="F62" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C63" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="E63" t="n">
-        <v>46.7</v>
+        <v>41.3</v>
       </c>
       <c r="F63" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G63" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I63" t="n">
         <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E64" t="n">
         <v>50</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D65" t="n">
         <v>70</v>
       </c>
-      <c r="C65" t="n">
-        <v>75</v>
-      </c>
-      <c r="D65" t="n">
-        <v>50</v>
-      </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>-33.6</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3279,66 +3291,72 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C66" t="n">
-        <v>80</v>
-      </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
+        <v>62.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>38.5</v>
+      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="J66" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K66" t="n">
-        <v>66.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" t="s">
         <v>80</v>
       </c>
-      <c r="B67" t="s">
-        <v>70</v>
-      </c>
       <c r="C67" t="n">
-        <v>78.6</v>
+        <v>42.9</v>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>67.5</v>
+        <v>42.9</v>
       </c>
       <c r="F67" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>33.3</v>
       </c>
-      <c r="I67" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="68">
@@ -3346,34 +3364,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D68" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G68" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>75</v>
+      </c>
+      <c r="J68" t="n">
         <v>25</v>
       </c>
-      <c r="E68" t="n">
+      <c r="K68" t="n">
         <v>75</v>
-      </c>
-      <c r="F68" t="n">
-        <v>25</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>100</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="69">
@@ -3381,34 +3399,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C69" t="n">
-        <v>46.7</v>
+        <v>80</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>26.7</v>
+        <v>80</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="70">
@@ -3416,34 +3434,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C70" t="n">
         <v>66.7</v>
       </c>
       <c r="D70" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" t="n">
+        <v>20</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>25</v>
+      </c>
+      <c r="J70" t="n">
         <v>75</v>
       </c>
-      <c r="E70" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="F70" t="n">
-        <v>75</v>
-      </c>
-      <c r="G70" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>50</v>
-      </c>
-      <c r="J70" t="n">
-        <v>25</v>
-      </c>
       <c r="K70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3451,162 +3469,168 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C71" t="n">
-        <v>53.8</v>
+        <v>55.6</v>
       </c>
       <c r="D71" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>8.3</v>
+        <v>5.6</v>
       </c>
       <c r="F71" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="G71" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="H71" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C72" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>50</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>100</v>
-      </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>50</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C73" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D73" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="E73" t="n">
-        <v>42.2</v>
+        <v>46.7</v>
       </c>
       <c r="F73" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
-        <v>13.3</v>
+        <v>40</v>
       </c>
       <c r="H73" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J73" t="n">
         <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C74" t="n">
-        <v>76.9</v>
+        <v>50</v>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>51.9</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C75" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="D75" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>54.7</v>
+        <v>25</v>
       </c>
       <c r="F75" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H75" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J75" t="n">
         <v>50</v>
@@ -3617,63 +3641,57 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C76" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="D76" t="n">
-        <v>25</v>
-      </c>
-      <c r="E76" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>25</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
       <c r="G76" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="n">
-        <v>100</v>
+        <v>67.5</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G77" t="n">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I77" t="n">
         <v>100</v>
@@ -3682,147 +3700,147 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C78" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D78" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E78" t="n">
-        <v>43.3</v>
+        <v>75</v>
       </c>
       <c r="F78" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C79" t="n">
-        <v>58.8</v>
+        <v>46.7</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E79" t="n">
-        <v>58.8</v>
+        <v>26.7</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G79" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="H79" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J79" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C80" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="D80" t="n">
-        <v>16.7</v>
+        <v>75</v>
       </c>
       <c r="E80" t="n">
-        <v>66.6</v>
+        <v>-8.3</v>
       </c>
       <c r="F80" t="n">
-        <v>16.7</v>
+        <v>75</v>
       </c>
       <c r="G80" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="H80" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" t="s">
         <v>95</v>
       </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
       <c r="C81" t="n">
-        <v>81.8</v>
+        <v>53.8</v>
       </c>
       <c r="D81" t="n">
-        <v>9.1</v>
+        <v>45.5</v>
       </c>
       <c r="E81" t="n">
-        <v>72.7</v>
+        <v>8.3</v>
       </c>
       <c r="F81" t="n">
-        <v>9.1</v>
+        <v>45.5</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I81" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
@@ -3830,66 +3848,60 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C82" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D82" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="E82" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="F82" t="n">
-        <v>8.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
       <c r="G82" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J82" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C83" t="n">
-        <v>50</v>
+        <v>78.6</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="E83" t="n">
-        <v>50</v>
+        <v>42.2</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3897,37 +3909,37 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C84" t="n">
-        <v>61.5</v>
+        <v>76.9</v>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="E84" t="n">
-        <v>50.4</v>
+        <v>51.9</v>
       </c>
       <c r="F84" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K84" t="n">
         <v>42.9</v>
-      </c>
-      <c r="I84" t="n">
-        <v>50</v>
-      </c>
-      <c r="J84" t="n">
-        <v>50</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3935,34 +3947,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C85" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="D85" t="n">
-        <v>22.2</v>
+        <v>28.6</v>
       </c>
       <c r="E85" t="n">
-        <v>63.5</v>
+        <v>54.7</v>
       </c>
       <c r="F85" t="n">
-        <v>22.2</v>
+        <v>28.6</v>
       </c>
       <c r="G85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I85" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3970,34 +3982,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" t="n">
-        <v>88.9</v>
+        <v>57.1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
-        <v>88.9</v>
+        <v>32.1</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H86" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4005,34 +4017,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C87" t="n">
-        <v>78.6</v>
+        <v>100</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>78.6</v>
+        <v>100</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
@@ -4040,34 +4052,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C88" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E88" t="n">
-        <v>64.3</v>
+        <v>43.3</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="H88" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I88" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -4075,34 +4087,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C89" t="n">
-        <v>80</v>
+        <v>58.8</v>
       </c>
       <c r="D89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>55</v>
+        <v>58.8</v>
       </c>
       <c r="F89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I89" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J89" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K89" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="90">
@@ -4110,31 +4122,31 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C90" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="D90" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E90" t="n">
-        <v>60.7</v>
+        <v>66.6</v>
       </c>
       <c r="F90" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G90" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="H90" t="n">
         <v>33.3</v>
       </c>
       <c r="I90" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4145,34 +4157,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C91" t="n">
-        <v>90.9</v>
+        <v>81.8</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E91" t="n">
-        <v>90.9</v>
+        <v>72.7</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I91" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J91" t="n">
         <v>25</v>
       </c>
       <c r="K91" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
@@ -4180,133 +4192,133 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="D92" t="n">
-        <v>16.7</v>
+        <v>8.3</v>
       </c>
       <c r="E92" t="n">
-        <v>61.1</v>
+        <v>58.4</v>
       </c>
       <c r="F92" t="n">
-        <v>16.7</v>
+        <v>8.3</v>
       </c>
       <c r="G92" t="n">
-        <v>4.2</v>
+        <v>9.1</v>
       </c>
       <c r="H92" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I92" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J92" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="K92" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C93" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="D93" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>66.9</v>
+        <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C94" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="D94" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="E94" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="F94" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
-        <v>35.7</v>
+        <v>8.3</v>
       </c>
       <c r="H94" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="I94" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J94" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K94" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C95" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>33.4</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4317,89 +4329,89 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C96" t="n">
-        <v>80.8</v>
+        <v>41.7</v>
       </c>
       <c r="D96" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="E96" t="n">
-        <v>62.6</v>
+        <v>16.7</v>
       </c>
       <c r="F96" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="G96" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H96" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>12.5</v>
+        <v>80</v>
       </c>
       <c r="K96" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C97" t="n">
-        <v>91.7</v>
+        <v>88.9</v>
       </c>
       <c r="D97" t="n">
-        <v>50</v>
+        <v>13.3</v>
       </c>
       <c r="E97" t="n">
-        <v>41.7</v>
+        <v>75.6</v>
       </c>
       <c r="F97" t="n">
-        <v>50</v>
+        <v>13.3</v>
       </c>
       <c r="G97" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I97" t="n">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="J97" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="K97" t="n">
-        <v>71.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>60</v>
+        <v>88.9</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>60</v>
+        <v>88.9</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -4408,363 +4420,351 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C99" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C100" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="D100" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>66.7</v>
+        <v>78.6</v>
       </c>
       <c r="F100" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="J100" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C101" t="n">
+        <v>75</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>75</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>100</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>100</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>100</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C102" t="n">
-        <v>83.3</v>
+        <v>64.3</v>
       </c>
       <c r="D102" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>54.7</v>
+        <v>64.3</v>
       </c>
       <c r="F102" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I102" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J102" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>16.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C103" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E103" t="n">
-        <v>57.1</v>
+        <v>25</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G103" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H103" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I103" t="n">
-        <v>60</v>
-      </c>
-      <c r="J103" t="n">
-        <v>20</v>
-      </c>
-      <c r="K103" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D104" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>32.5</v>
+        <v>100</v>
       </c>
       <c r="F104" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J104" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C105" t="n">
         <v>75</v>
       </c>
       <c r="D105" t="n">
-        <v>21.4</v>
+        <v>40</v>
       </c>
       <c r="E105" t="n">
-        <v>53.6</v>
+        <v>35</v>
       </c>
       <c r="F105" t="n">
-        <v>21.4</v>
+        <v>40</v>
       </c>
       <c r="G105" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="H105" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K105" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C106" t="n">
-        <v>84.6</v>
+        <v>80</v>
       </c>
       <c r="D106" t="n">
+        <v>25</v>
+      </c>
+      <c r="E106" t="n">
+        <v>55</v>
+      </c>
+      <c r="F106" t="n">
+        <v>25</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J106" t="n">
         <v>14.3</v>
       </c>
-      <c r="E106" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F106" t="n">
+      <c r="K106" t="n">
         <v>14.3</v>
-      </c>
-      <c r="G106" t="n">
-        <v>13</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J106" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K106" t="n">
-        <v>12.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C107" t="n">
-        <v>68.6</v>
-      </c>
-      <c r="D107" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E107" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="F107" t="n">
-        <v>9.1</v>
-      </c>
+        <v>33.3</v>
+      </c>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
       <c r="G107" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E108" t="n">
-        <v>50</v>
+        <v>60.7</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I108" t="n">
         <v>50</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4772,542 +4772,1399 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C109" t="n">
-        <v>90.9</v>
+        <v>100</v>
       </c>
       <c r="D109" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>70.9</v>
+        <v>100</v>
       </c>
       <c r="F109" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>27.3</v>
+        <v>66.7</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J109" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C110" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D110" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="n">
-        <v>17.1</v>
+        <v>37.5</v>
       </c>
       <c r="F110" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="G110" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>20</v>
+      </c>
+      <c r="I110" t="n">
         <v>33.3</v>
       </c>
-      <c r="H110" t="n">
+      <c r="J110" t="n">
         <v>33.3</v>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>100</v>
-      </c>
       <c r="K110" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
-      </c>
-      <c r="C111" t="n">
-        <v>90</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="C111"/>
       <c r="D111" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E111" t="n">
-        <v>73.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111"/>
       <c r="F111" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G111" t="n">
-        <v>18.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G111"/>
       <c r="H111" t="n">
         <v>0</v>
       </c>
-      <c r="I111" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J111" t="n">
-        <v>50</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C112" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I112" t="n">
-        <v>33.3</v>
+        <v>69.2</v>
       </c>
       <c r="J112" t="n">
-        <v>33.3</v>
+        <v>15.4</v>
       </c>
       <c r="K112" t="n">
-        <v>33.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="B113" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C113" t="n">
-        <v>16.7</v>
+        <v>54.5</v>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>5.6</v>
+        <v>54.5</v>
       </c>
       <c r="F113" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I113"/>
-      <c r="J113"/>
-      <c r="K113"/>
+        <v>28.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>60</v>
+      </c>
+      <c r="J113" t="n">
+        <v>20</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C114" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G114" t="n">
-        <v>66.7</v>
+        <v>23.1</v>
       </c>
       <c r="H114" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I114"/>
-      <c r="J114"/>
-      <c r="K114"/>
+        <v>14.3</v>
+      </c>
+      <c r="I114" t="n">
+        <v>40</v>
+      </c>
+      <c r="J114" t="n">
+        <v>40</v>
+      </c>
+      <c r="K114" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C115" t="n">
-        <v>33.3</v>
+        <v>71.4</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="E115" t="n">
-        <v>33.3</v>
+        <v>61.1</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115"/>
-      <c r="J115"/>
-      <c r="K115"/>
+        <v>18.8</v>
+      </c>
+      <c r="I115" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J115" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K115" t="n">
+        <v>54.5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C116" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="D116" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="E116" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="F116" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G116" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K116" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C117" t="n">
-        <v>50</v>
-      </c>
-      <c r="D117" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E117" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F117" t="n">
-        <v>18.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
       <c r="G117" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J117" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C118" t="n">
-        <v>50</v>
+        <v>67.7</v>
       </c>
       <c r="D118" t="n">
-        <v>23.1</v>
+        <v>10.7</v>
       </c>
       <c r="E118" t="n">
-        <v>26.9</v>
+        <v>57</v>
       </c>
       <c r="F118" t="n">
-        <v>23.1</v>
+        <v>10.7</v>
       </c>
       <c r="G118" t="n">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
       <c r="H118" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="I118" t="n">
-        <v>66.7</v>
+        <v>27.3</v>
       </c>
       <c r="J118" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>66.7</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C119" t="n">
         <v>66.7</v>
       </c>
       <c r="D119" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="E119" t="n">
-        <v>41.7</v>
+        <v>52.4</v>
       </c>
       <c r="F119" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="G119" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>50</v>
+      </c>
+      <c r="J119" t="n">
         <v>33.3</v>
       </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>100</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C120" t="n">
-        <v>61.5</v>
+        <v>55.6</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="E120" t="n">
-        <v>61.5</v>
+        <v>33.4</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5</v>
+        <v>42.9</v>
       </c>
       <c r="H120" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J120" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C121" t="n">
-        <v>45</v>
+        <v>80.8</v>
       </c>
       <c r="D121" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="E121" t="n">
-        <v>28.3</v>
+        <v>62.6</v>
       </c>
       <c r="F121" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="G121" t="n">
-        <v>27.3</v>
+        <v>36</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I121" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C122" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="D122" t="n">
+        <v>50</v>
+      </c>
+      <c r="E122" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F122" t="n">
+        <v>50</v>
+      </c>
+      <c r="G122" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J122" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="K122" t="n">
         <v>71.4</v>
-      </c>
-      <c r="D122" t="n">
-        <v>20</v>
-      </c>
-      <c r="E122" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="F122" t="n">
-        <v>20</v>
-      </c>
-      <c r="G122" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>50</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>117</v>
+      </c>
+      <c r="C123" t="n">
+        <v>60</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>60</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>100</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" t="n">
+        <v>100</v>
+      </c>
+      <c r="D124" t="n">
+        <v>20</v>
+      </c>
+      <c r="E124" t="n">
+        <v>80</v>
+      </c>
+      <c r="F124" t="n">
+        <v>20</v>
+      </c>
+      <c r="G124" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>117</v>
+      </c>
+      <c r="C125" t="n">
+        <v>75</v>
+      </c>
+      <c r="D125" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>50</v>
+      </c>
+      <c r="J125" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>117</v>
+      </c>
+      <c r="C126" t="n">
+        <v>100</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>100</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>117</v>
+      </c>
+      <c r="C127" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D127" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E127" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F127" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G127" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>126</v>
+      </c>
+      <c r="B128" t="s">
+        <v>117</v>
+      </c>
+      <c r="C128" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>25</v>
+      </c>
+      <c r="H128" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I128" t="n">
+        <v>60</v>
+      </c>
+      <c r="J128" t="n">
+        <v>20</v>
+      </c>
+      <c r="K128" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+      <c r="B129" t="s">
+        <v>117</v>
+      </c>
+      <c r="C129" t="n">
+        <v>70</v>
+      </c>
+      <c r="D129" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G129" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>25</v>
+      </c>
+      <c r="K129" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>128</v>
+      </c>
+      <c r="B130" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130" t="n">
+        <v>75</v>
+      </c>
+      <c r="D130" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E130" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H130" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I130" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s">
+        <v>117</v>
+      </c>
+      <c r="C131" t="n">
+        <v>84.6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F131" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>13</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J131" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K131" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" t="s">
+        <v>117</v>
+      </c>
+      <c r="C132" t="n">
+        <v>68.6</v>
+      </c>
+      <c r="D132" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I132" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K132" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>131</v>
+      </c>
+      <c r="B133" t="s">
+        <v>117</v>
+      </c>
+      <c r="C133" t="n">
+        <v>50</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>50</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>50</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" t="s">
+        <v>117</v>
+      </c>
+      <c r="C134" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D134" t="n">
+        <v>20</v>
+      </c>
+      <c r="E134" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F134" t="n">
+        <v>20</v>
+      </c>
+      <c r="G134" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J134" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>117</v>
+      </c>
+      <c r="C135" t="n">
+        <v>60</v>
+      </c>
+      <c r="D135" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G135" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>100</v>
+      </c>
+      <c r="K135" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" t="s">
+        <v>117</v>
+      </c>
+      <c r="C136" t="n">
+        <v>90</v>
+      </c>
+      <c r="D136" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E136" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G136" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J136" t="n">
+        <v>50</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" t="s">
+        <v>117</v>
+      </c>
+      <c r="C137" t="n">
+        <v>100</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>100</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K137" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" t="s">
+        <v>137</v>
+      </c>
+      <c r="C138" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>50</v>
+      </c>
+      <c r="H138" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I138"/>
+      <c r="J138"/>
+      <c r="K138"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>137</v>
+      </c>
+      <c r="C139" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H139" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I139"/>
+      <c r="J139"/>
+      <c r="K139"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
         <v>139</v>
       </c>
-      <c r="B123" t="s">
-        <v>129</v>
-      </c>
-      <c r="C123" t="n">
+      <c r="B140" t="s">
+        <v>137</v>
+      </c>
+      <c r="C140" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140"/>
+      <c r="J140"/>
+      <c r="K140"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>137</v>
+      </c>
+      <c r="C141" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>52</v>
+      </c>
+      <c r="F141" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G141" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>137</v>
+      </c>
+      <c r="C142" t="n">
+        <v>50</v>
+      </c>
+      <c r="D142" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E142" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F142" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H142" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>75</v>
+      </c>
+      <c r="K142" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>137</v>
+      </c>
+      <c r="C143" t="n">
+        <v>50</v>
+      </c>
+      <c r="D143" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G143" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I143" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J143" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K143" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>137</v>
+      </c>
+      <c r="C144" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D144" t="n">
+        <v>25</v>
+      </c>
+      <c r="E144" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F144" t="n">
+        <v>25</v>
+      </c>
+      <c r="G144" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>100</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>137</v>
+      </c>
+      <c r="C145" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I145" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K145" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>137</v>
+      </c>
+      <c r="C146" t="n">
+        <v>45</v>
+      </c>
+      <c r="D146" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E146" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F146" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G146" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>100</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>137</v>
+      </c>
+      <c r="C147" t="n">
         <v>71.4</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D147" t="n">
+        <v>20</v>
+      </c>
+      <c r="E147" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F147" t="n">
+        <v>20</v>
+      </c>
+      <c r="G147" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>50</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>137</v>
+      </c>
+      <c r="C148" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D148" t="n">
         <v>7.1</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E148" t="n">
         <v>64.3</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F148" t="n">
         <v>7.1</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G148" t="n">
         <v>18.2</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H148" t="n">
         <v>12.5</v>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
         <v>100</v>
       </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124"/>
-      <c r="B124" t="s">
-        <v>140</v>
-      </c>
-      <c r="C124" t="n">
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149" t="s">
+        <v>148</v>
+      </c>
+      <c r="C149" t="n">
         <v>68.7</v>
       </c>
-      <c r="D124" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E124" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="F124" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G124" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H124" t="n">
-        <v>9</v>
-      </c>
-      <c r="I124" t="n">
-        <v>49</v>
-      </c>
-      <c r="J124" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="K124" t="n">
-        <v>31.9</v>
+      <c r="D149" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E149" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G149" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H149" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I149" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="K149" t="n">
+        <v>34.5</v>
       </c>
     </row>
   </sheetData>
@@ -5339,22 +6196,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5363,18 +6220,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -5409,7 +6266,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -5444,7 +6301,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -5479,1061 +6336,1059 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>60.6</v>
+        <v>33.3</v>
       </c>
       <c r="D5" t="n">
-        <v>65.9</v>
+        <v>54.5</v>
       </c>
       <c r="E5" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>45.2</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10.6</v>
+        <v>33.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>47.1</v>
+        <v>60.6</v>
       </c>
       <c r="D6" t="n">
-        <v>59.5</v>
+        <v>65.9</v>
       </c>
       <c r="E6" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="F6" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>11.4</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>41.7</v>
+        <v>45.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>10.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>47.1</v>
       </c>
       <c r="D7" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9.4</v>
+        <v>16.1</v>
       </c>
       <c r="F7" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>11.4</v>
       </c>
       <c r="H7" t="n">
-        <v>38.9</v>
+        <v>41.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>19.1</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>87.8</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>79.3</v>
+        <v>58.5</v>
       </c>
       <c r="E8" t="n">
-        <v>36.4</v>
+        <v>9.4</v>
       </c>
       <c r="F8" t="n">
-        <v>41.2</v>
+        <v>27.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>43.8</v>
+        <v>38.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>24.6</v>
+        <v>19.1</v>
       </c>
       <c r="K8" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>66.7</v>
+        <v>87.8</v>
       </c>
       <c r="D9" t="n">
-        <v>70.6</v>
+        <v>79.3</v>
       </c>
       <c r="E9" t="n">
-        <v>28.6</v>
+        <v>36.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9.1</v>
+        <v>24.6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>56.2</v>
+        <v>66.7</v>
       </c>
       <c r="D10" t="n">
-        <v>50.7</v>
+        <v>70.6</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>28.6</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>38.9</v>
+        <v>33.3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>22.2</v>
+        <v>9.1</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>58.6</v>
+        <v>48.8</v>
       </c>
       <c r="D11" t="n">
-        <v>56.2</v>
+        <v>47.6</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
       <c r="F11" t="n">
-        <v>36.8</v>
+        <v>15.8</v>
       </c>
       <c r="G11" t="n">
-        <v>14.9</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>52.7</v>
+        <v>36.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>20.7</v>
+        <v>24.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>57.3</v>
       </c>
       <c r="D12" t="n">
-        <v>66.7</v>
+        <v>55.3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12"/>
+        <v>10.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>36.8</v>
+      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>71.4</v>
+        <v>66.7</v>
       </c>
       <c r="E13" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13"/>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>66.3</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>22.8</v>
+        <v>31.6</v>
       </c>
       <c r="F14" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="G14" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>60.6</v>
+        <v>40</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>28.2</v>
+        <v>22.7</v>
       </c>
       <c r="K14" t="n">
-        <v>14.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>52.6</v>
+        <v>53.1</v>
       </c>
       <c r="D15" t="n">
-        <v>62.3</v>
+        <v>66.3</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>22.8</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>40.7</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>8.2</v>
       </c>
       <c r="H15" t="n">
-        <v>58.8</v>
+        <v>60.6</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>16.7</v>
+        <v>28.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>77.8</v>
+        <v>52.6</v>
       </c>
       <c r="D16" t="n">
-        <v>64.7</v>
+        <v>62.3</v>
       </c>
       <c r="E16" t="n">
-        <v>8.3</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>11.1</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>66.7</v>
+        <v>58.8</v>
       </c>
       <c r="I16" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="K16" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>53.3</v>
+        <v>65.4</v>
       </c>
       <c r="D17" t="n">
-        <v>43.6</v>
+        <v>64.3</v>
       </c>
       <c r="E17" t="n">
-        <v>8.8</v>
+        <v>9.7</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>35.7</v>
+        <v>7.7</v>
       </c>
       <c r="H17" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-28.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>37.5</v>
+        <v>53.3</v>
       </c>
       <c r="D18" t="n">
-        <v>55.8</v>
+        <v>43.6</v>
       </c>
       <c r="E18" t="n">
-        <v>9.5</v>
+        <v>8.8</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="D19" t="n">
-        <v>68.8</v>
+        <v>56.5</v>
       </c>
       <c r="E19" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="F19" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K19" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>65.3</v>
+        <v>33.3</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>68.8</v>
       </c>
       <c r="E20" t="n">
-        <v>17.8</v>
+        <v>14.3</v>
       </c>
       <c r="F20" t="n">
-        <v>48.6</v>
+        <v>33.3</v>
       </c>
       <c r="G20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>51.5</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>25.4</v>
+        <v>14.3</v>
       </c>
       <c r="K20" t="n">
-        <v>16.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>33.3</v>
+        <v>65.1</v>
       </c>
       <c r="D21" t="n">
-        <v>35.7</v>
+        <v>62.3</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
       <c r="G21" t="n">
-        <v>16.7</v>
+        <v>8.2</v>
       </c>
       <c r="H21" t="n">
-        <v>33.3</v>
+        <v>52.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>25.1</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
       <c r="D22" t="n">
-        <v>49.1</v>
+        <v>57.1</v>
       </c>
       <c r="E22" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="F22" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>23.8</v>
+        <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>68.4</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>63.8</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>47.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F23"/>
       <c r="G23" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>46.6</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>45.2</v>
+        <v>33.3</v>
       </c>
       <c r="D24" t="n">
-        <v>54.3</v>
+        <v>35.7</v>
       </c>
       <c r="E24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>16.7</v>
       </c>
       <c r="H24" t="n">
-        <v>52.9</v>
+        <v>33.3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.4</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C25" t="n">
-        <v>83.3</v>
+        <v>55.6</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>49.1</v>
       </c>
       <c r="E25" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H25" t="n">
         <v>18.2</v>
       </c>
-      <c r="F25" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>25</v>
-      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>22.2</v>
+        <v>23.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C26" t="n">
-        <v>58.3</v>
+        <v>68.4</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>63.8</v>
       </c>
       <c r="E26" t="n">
-        <v>4.3</v>
+        <v>10.3</v>
       </c>
       <c r="F26" t="n">
-        <v>66.7</v>
+        <v>47.8</v>
       </c>
       <c r="G26" t="n">
-        <v>33.3</v>
+        <v>7.9</v>
       </c>
       <c r="H26" t="n">
-        <v>75</v>
+        <v>46.6</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>42.9</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C27" t="n">
-        <v>37.5</v>
+        <v>45.2</v>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="G27" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="H27" t="n">
-        <v>38.5</v>
+        <v>52.9</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>18.2</v>
+        <v>23.1</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C28" t="n">
-        <v>51.4</v>
+        <v>83.3</v>
       </c>
       <c r="D28" t="n">
-        <v>59.4</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>13.2</v>
+        <v>18.2</v>
       </c>
       <c r="F28" t="n">
-        <v>42.1</v>
+        <v>33.3</v>
       </c>
       <c r="G28" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>27</v>
+        <v>22.2</v>
       </c>
       <c r="K28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C29" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>52.1</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>4.3</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>45.5</v>
+        <v>42.9</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C30" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="D30" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.7</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C31" t="n">
-        <v>66.7</v>
+        <v>51.4</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>59.4</v>
       </c>
       <c r="E31" t="n">
-        <v>23.1</v>
+        <v>13.2</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>42.1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>45.5</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.4</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>16.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C32" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C33" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E33" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>23.3</v>
+        <v>14.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.1</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C34" t="n">
-        <v>62.8</v>
+        <v>66.7</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5</v>
+        <v>63</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>23.1</v>
       </c>
       <c r="F34" t="n">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="G34" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>48.5</v>
+        <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>21.7</v>
+        <v>15.4</v>
       </c>
       <c r="K34" t="n">
-        <v>2.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D35" t="n">
         <v>50</v>
@@ -6541,12 +7396,14 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -6560,271 +7417,275 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C36" t="n">
-        <v>28.6</v>
+        <v>57.9</v>
       </c>
       <c r="D36" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E36" t="n">
-        <v>9.5</v>
+        <v>9.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G36" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="H36" t="n">
         <v>50</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C37" t="n">
-        <v>71.4</v>
+        <v>62.8</v>
       </c>
       <c r="D37" t="n">
-        <v>70.2</v>
+        <v>57.5</v>
       </c>
       <c r="E37" t="n">
-        <v>23.5</v>
+        <v>7</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H37" t="n">
-        <v>40</v>
+        <v>48.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
-        <v>34.8</v>
+        <v>21.7</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C38" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
-      </c>
-      <c r="F38" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38"/>
       <c r="G38" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39"/>
+        <v>9.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H39" t="n">
         <v>50</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C40" t="n">
-        <v>44.4</v>
+        <v>71.4</v>
       </c>
       <c r="D40" t="n">
-        <v>49.2</v>
+        <v>70.2</v>
       </c>
       <c r="E40" t="n">
-        <v>9.1</v>
+        <v>23.5</v>
       </c>
       <c r="F40" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>34.8</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D41" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="E41" t="n">
-        <v>11.8</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
         <v>50</v>
       </c>
       <c r="G41" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="H41" t="n">
-        <v>37.5</v>
+        <v>18.2</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7.7</v>
+        <v>19.2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42" t="n">
-        <v>7.7</v>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42"/>
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42"/>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
       <c r="K42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C43" t="n">
-        <v>35.3</v>
+        <v>44.4</v>
       </c>
       <c r="D43" t="n">
-        <v>57.6</v>
+        <v>49.2</v>
       </c>
       <c r="E43" t="n">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="F43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>20</v>
-      </c>
-      <c r="G43" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>23.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -6832,34 +7693,34 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C44" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>63.2</v>
+        <v>52.9</v>
       </c>
       <c r="E44" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H44" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -6867,104 +7728,98 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>7.7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45"/>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H45"/>
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
+      <c r="J45"/>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C46" t="n">
-        <v>63</v>
+        <v>35.3</v>
       </c>
       <c r="D46" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="E46" t="n">
-        <v>13.6</v>
+        <v>17.6</v>
       </c>
       <c r="F46" t="n">
-        <v>41.7</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>23.1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="K46" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C47" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D47" t="n">
-        <v>87.5</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H47" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -6972,165 +7827,163 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C48" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>74.7</v>
+        <v>55</v>
       </c>
       <c r="E48" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>57.9</v>
+        <v>20</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C49" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>63.2</v>
+        <v>57.8</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>13.6</v>
       </c>
       <c r="F49" t="n">
-        <v>30.8</v>
+        <v>41.7</v>
       </c>
       <c r="G49" t="n">
-        <v>15.4</v>
+        <v>11.5</v>
       </c>
       <c r="H49" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>21.4</v>
+        <v>23.5</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C50" t="n">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="D50" t="n">
-        <v>65.3</v>
+        <v>87.5</v>
       </c>
       <c r="E50" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C51" t="n">
-        <v>40</v>
+        <v>69.2</v>
       </c>
       <c r="D51" t="n">
-        <v>41.2</v>
+        <v>74.7</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="H51" t="n">
-        <v>33.3</v>
+        <v>57.9</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="K51" t="n">
-        <v>-20</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C52" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="D52" t="n">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="F52"/>
       <c r="G52" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>50</v>
@@ -7139,384 +7992,382 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D53" t="n">
-        <v>38.9</v>
+        <v>90</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="D54" t="n">
-        <v>57.9</v>
+        <v>63.2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G54" t="n">
-        <v>25</v>
+        <v>15.4</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="K54" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D55" t="n">
-        <v>41.4</v>
+        <v>70.4</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="F55" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="G55" t="n">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>34.8</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>14.3</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>-16.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C56" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="D56" t="n">
-        <v>57.5</v>
+        <v>65.3</v>
       </c>
       <c r="E56" t="n">
-        <v>18.7</v>
+        <v>31.4</v>
       </c>
       <c r="F56" t="n">
-        <v>51.9</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>47.8</v>
+        <v>42.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K56" t="n">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D57" t="n">
-        <v>59.3</v>
+        <v>55.6</v>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
-      </c>
-      <c r="F57" t="n">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F57"/>
       <c r="G57" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D58" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" t="n">
         <v>60</v>
       </c>
-      <c r="E58" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="G58" t="n">
-        <v>6.7</v>
-      </c>
       <c r="H58" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>29.4</v>
+        <v>16.7</v>
       </c>
       <c r="K58" t="n">
-        <v>16.6</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D59" t="n">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60"/>
+        <v>50</v>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60"/>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
         <v>66.7</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
       <c r="K60" t="n">
-        <v>-66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C61" t="n">
-        <v>77.8</v>
+        <v>46.2</v>
       </c>
       <c r="D61" t="n">
-        <v>63.4</v>
+        <v>53.1</v>
       </c>
       <c r="E61" t="n">
-        <v>17.6</v>
+        <v>11.8</v>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H61" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>27.8</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>41.2</v>
       </c>
       <c r="E62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="D63" t="n">
-        <v>31.6</v>
+        <v>44.1</v>
       </c>
       <c r="E63" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="G63" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -7525,31 +8376,33 @@
         <v>33.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-20</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>66.7</v>
       </c>
-      <c r="D64" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64"/>
-      <c r="G64" t="n">
-        <v>9.1</v>
-      </c>
       <c r="H64" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -7558,180 +8411,561 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>-9.1</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C65" t="n">
         <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>39.1</v>
+        <v>57.9</v>
       </c>
       <c r="E65" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K65" t="n">
-        <v>-33.3</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>53.3</v>
+        <v>41.4</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G66" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="H66" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-11.1</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C67" t="n">
-        <v>52</v>
+        <v>57.1</v>
       </c>
       <c r="D67" t="n">
-        <v>55.2</v>
+        <v>57.5</v>
       </c>
       <c r="E67" t="n">
-        <v>9.1</v>
+        <v>18.7</v>
       </c>
       <c r="F67" t="n">
-        <v>28.6</v>
+        <v>51.9</v>
       </c>
       <c r="G67" t="n">
-        <v>8</v>
+        <v>20.8</v>
       </c>
       <c r="H67" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C68" t="n">
+        <v>50</v>
+      </c>
+      <c r="D68" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" t="n">
+        <v>40</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>40</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" t="n">
+        <v>50</v>
+      </c>
+      <c r="D69" t="n">
+        <v>60</v>
+      </c>
+      <c r="E69" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H69" t="n">
+        <v>40</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K69" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" t="s">
+        <v>117</v>
+      </c>
+      <c r="C70" t="n">
+        <v>100</v>
+      </c>
+      <c r="D70" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50</v>
+      </c>
+      <c r="I70" t="n">
+        <v>25</v>
+      </c>
+      <c r="J70" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>210</v>
+      </c>
+      <c r="B71" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71"/>
+      <c r="G71" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>211</v>
+      </c>
+      <c r="B72" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D72" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>50</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>212</v>
+      </c>
+      <c r="B73" t="s">
+        <v>117</v>
+      </c>
+      <c r="C73" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D73" t="n">
+        <v>80</v>
+      </c>
+      <c r="E73" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>50</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74" t="n">
+        <v>40</v>
+      </c>
+      <c r="D74" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>100</v>
+      </c>
+      <c r="G74" t="n">
+        <v>40</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75"/>
+      <c r="G75" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>215</v>
+      </c>
+      <c r="B76" t="s">
+        <v>137</v>
+      </c>
+      <c r="C76" t="n">
+        <v>50</v>
+      </c>
+      <c r="D76" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>216</v>
+      </c>
+      <c r="B77" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>217</v>
+      </c>
+      <c r="B78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" t="n">
+        <v>52</v>
+      </c>
+      <c r="D78" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>218</v>
+      </c>
+      <c r="B79" t="s">
+        <v>137</v>
+      </c>
+      <c r="C79" t="n">
         <v>68.8</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D79" t="n">
         <v>59.2</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E79" t="n">
         <v>16</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
         <v>5.9</v>
       </c>
-      <c r="H68" t="n">
-        <v>50</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="H79" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" t="n">
         <v>5.9</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J79" t="n">
         <v>17.4</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69"/>
-      <c r="B69" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="D69" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="E69" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F69" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="G69" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H69" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K69" t="n">
-        <v>-2</v>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80" t="s">
+        <v>148</v>
+      </c>
+      <c r="C80" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D80" t="n">
+        <v>58</v>
+      </c>
+      <c r="E80" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F80" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H80" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J80" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jaxon Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxson Price</t>
   </si>
   <si>
     <t xml:space="preserve">Josh Frazer</t>
@@ -724,8 +721,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K149"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K148" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K148"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1651,23 +1648,29 @@
       <c r="C18" t="n">
         <v>100</v>
       </c>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1678,31 +1681,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>100</v>
+        <v>75.5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G19" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I19" t="n">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="20">
@@ -1713,31 +1716,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>75.5</v>
+        <v>68</v>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>57.1</v>
       </c>
       <c r="F20" t="n">
-        <v>12.5</v>
+        <v>10.9</v>
       </c>
       <c r="G20" t="n">
-        <v>28.3</v>
+        <v>10.5</v>
       </c>
       <c r="H20" t="n">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="I20" t="n">
-        <v>43.5</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>17.4</v>
+        <v>37.9</v>
       </c>
       <c r="K20" t="n">
-        <v>43.5</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="21">
@@ -1748,31 +1751,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>10.9</v>
+        <v>16.2</v>
       </c>
       <c r="E21" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="F21" t="n">
-        <v>10.9</v>
+        <v>16.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10.5</v>
+        <v>29.2</v>
       </c>
       <c r="H21" t="n">
-        <v>13.5</v>
+        <v>11.9</v>
       </c>
       <c r="I21" t="n">
-        <v>37.9</v>
+        <v>46.4</v>
       </c>
       <c r="J21" t="n">
-        <v>37.9</v>
+        <v>32.1</v>
       </c>
       <c r="K21" t="n">
-        <v>32.1</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="22">
@@ -1783,31 +1786,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58.8</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>32.1</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>51.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1818,31 +1821,31 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>35</v>
+      </c>
+      <c r="J23" t="n">
         <v>25</v>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>100</v>
-      </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="24">
@@ -1853,31 +1856,25 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D24" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>21.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
       <c r="G24" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1888,25 +1885,31 @@
         <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>100</v>
-      </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
+        <v>77.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.5</v>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>35.6</v>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>37.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="26">
@@ -1917,31 +1920,31 @@
         <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>77.5</v>
+        <v>83.3</v>
       </c>
       <c r="D26" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="n">
-        <v>62</v>
+        <v>70.8</v>
       </c>
       <c r="F26" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>16.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>37.3</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>36.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1952,31 +1955,31 @@
         <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
       <c r="E27" t="n">
-        <v>70.8</v>
+        <v>-6.7</v>
       </c>
       <c r="F27" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
       <c r="G27" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1987,31 +1990,31 @@
         <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>55.4</v>
       </c>
       <c r="D28" t="n">
-        <v>66.7</v>
+        <v>14.9</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.7</v>
+        <v>40.5</v>
       </c>
       <c r="F28" t="n">
-        <v>66.7</v>
+        <v>14.9</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="29">
@@ -2021,33 +2024,21 @@
       <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="n">
-        <v>55.4</v>
-      </c>
+      <c r="C29"/>
       <c r="D29" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>40.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29"/>
       <c r="F29" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G29" t="n">
-        <v>11.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G29"/>
       <c r="H29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>27.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -2056,21 +2047,33 @@
       <c r="B30" t="s">
         <v>12</v>
       </c>
-      <c r="C30"/>
+      <c r="C30" t="n">
+        <v>100</v>
+      </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30"/>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30"/>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
@@ -2080,31 +2083,31 @@
         <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
@@ -2115,31 +2118,31 @@
         <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>80</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>16.7</v>
       </c>
-      <c r="E32" t="n">
-        <v>69</v>
-      </c>
-      <c r="F32" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>60</v>
-      </c>
       <c r="J32" t="n">
-        <v>30</v>
+        <v>83.3</v>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="33">
@@ -2150,13 +2153,13 @@
         <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2168,13 +2171,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2182,69 +2185,69 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C34" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
         <v>100</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>100</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
         <v>45</v>
       </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
       <c r="C35" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="D35" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>44.5</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2252,34 +2255,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>44.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -2287,34 +2290,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="n">
-        <v>65</v>
+        <v>79.2</v>
       </c>
       <c r="D37" t="n">
-        <v>20.7</v>
+        <v>6.7</v>
       </c>
       <c r="E37" t="n">
-        <v>44.3</v>
+        <v>72.5</v>
       </c>
       <c r="F37" t="n">
-        <v>20.7</v>
+        <v>6.7</v>
       </c>
       <c r="G37" t="n">
-        <v>42.1</v>
+        <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>23.1</v>
+        <v>8.3</v>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -2322,34 +2325,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" t="n">
-        <v>79.2</v>
+        <v>88.9</v>
       </c>
       <c r="D38" t="n">
-        <v>6.7</v>
+        <v>50</v>
       </c>
       <c r="E38" t="n">
-        <v>72.5</v>
+        <v>38.9</v>
       </c>
       <c r="F38" t="n">
-        <v>6.7</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="H38" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -2357,34 +2360,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" t="n">
-        <v>88.9</v>
+        <v>61.4</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="E39" t="n">
-        <v>38.9</v>
+        <v>44.7</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="G39" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H39" t="n">
         <v>16.7</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" t="n">
-        <v>75</v>
+        <v>26.7</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2392,34 +2395,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="n">
-        <v>61.4</v>
+        <v>83.8</v>
       </c>
       <c r="D40" t="n">
-        <v>16.7</v>
+        <v>26.5</v>
       </c>
       <c r="E40" t="n">
-        <v>44.7</v>
+        <v>57.3</v>
       </c>
       <c r="F40" t="n">
-        <v>16.7</v>
+        <v>26.5</v>
       </c>
       <c r="G40" t="n">
-        <v>28.6</v>
+        <v>22.5</v>
       </c>
       <c r="H40" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>26.7</v>
+        <v>56.2</v>
       </c>
       <c r="J40" t="n">
-        <v>46.7</v>
+        <v>18.8</v>
       </c>
       <c r="K40" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="41">
@@ -2427,34 +2430,34 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" t="n">
-        <v>83.8</v>
+        <v>68.6</v>
       </c>
       <c r="D41" t="n">
-        <v>26.5</v>
+        <v>8.8</v>
       </c>
       <c r="E41" t="n">
-        <v>57.3</v>
+        <v>59.8</v>
       </c>
       <c r="F41" t="n">
-        <v>26.5</v>
+        <v>8.8</v>
       </c>
       <c r="G41" t="n">
-        <v>22.5</v>
+        <v>29.6</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I41" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="J41" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>66.7</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="42">
@@ -2462,34 +2465,34 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>68.6</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
-        <v>8.8</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>59.8</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>8.8</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J42" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="K42" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2497,34 +2500,34 @@
         <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I43" t="n">
-        <v>33.3</v>
+        <v>56.2</v>
       </c>
       <c r="J43" t="n">
-        <v>66.7</v>
+        <v>18.8</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -2532,34 +2535,34 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" t="n">
-        <v>62.5</v>
+        <v>84</v>
       </c>
       <c r="D44" t="n">
-        <v>12.1</v>
+        <v>5.6</v>
       </c>
       <c r="E44" t="n">
-        <v>50.4</v>
+        <v>78.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12.1</v>
+        <v>5.6</v>
       </c>
       <c r="G44" t="n">
-        <v>17.6</v>
+        <v>4.5</v>
       </c>
       <c r="H44" t="n">
-        <v>8.3</v>
+        <v>11.8</v>
       </c>
       <c r="I44" t="n">
-        <v>56.2</v>
+        <v>26.7</v>
       </c>
       <c r="J44" t="n">
-        <v>18.8</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="45">
@@ -2567,34 +2570,34 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" t="n">
-        <v>84</v>
+        <v>59.5</v>
       </c>
       <c r="D45" t="n">
-        <v>5.6</v>
+        <v>13.3</v>
       </c>
       <c r="E45" t="n">
-        <v>78.4</v>
+        <v>46.2</v>
       </c>
       <c r="F45" t="n">
-        <v>5.6</v>
+        <v>13.3</v>
       </c>
       <c r="G45" t="n">
-        <v>4.5</v>
+        <v>41.9</v>
       </c>
       <c r="H45" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="I45" t="n">
-        <v>26.7</v>
+        <v>55.6</v>
       </c>
       <c r="J45" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="K45" t="n">
-        <v>46.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="46">
@@ -2602,34 +2605,34 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>59.5</v>
+        <v>50</v>
       </c>
       <c r="D46" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>41.9</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2637,34 +2640,34 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>33.5</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I47" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="48">
@@ -2672,34 +2675,34 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" t="n">
-        <v>64.7</v>
+        <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>33.5</v>
+        <v>80</v>
       </c>
       <c r="F48" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="H48" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="K48" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2707,34 +2710,34 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" t="n">
-        <v>80</v>
+        <v>52.3</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>40.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G49" t="n">
-        <v>25</v>
+        <v>14.8</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>21.4</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="50">
@@ -2742,34 +2745,34 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" t="n">
-        <v>52.3</v>
+        <v>56.2</v>
       </c>
       <c r="D50" t="n">
-        <v>12.1</v>
+        <v>30</v>
       </c>
       <c r="E50" t="n">
-        <v>40.2</v>
+        <v>26.2</v>
       </c>
       <c r="F50" t="n">
-        <v>12.1</v>
+        <v>30</v>
       </c>
       <c r="G50" t="n">
-        <v>14.8</v>
+        <v>41.7</v>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>64.3</v>
+        <v>75</v>
       </c>
       <c r="J50" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2777,31 +2780,31 @@
         <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C51" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>26.2</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I51" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2809,37 +2812,37 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>64</v>
+      </c>
+      <c r="B52" t="s">
         <v>63</v>
       </c>
-      <c r="B52" t="s">
-        <v>64</v>
-      </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K52" t="n">
         <v>66.7</v>
-      </c>
-      <c r="H52" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>50</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2847,34 +2850,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>27.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G53" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2882,34 +2885,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" t="n">
-        <v>40</v>
+        <v>47.1</v>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="n">
-        <v>27.5</v>
+        <v>30.4</v>
       </c>
       <c r="F54" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="55">
@@ -2917,34 +2920,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" t="n">
-        <v>47.1</v>
+        <v>66.7</v>
       </c>
       <c r="D55" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E55" t="n">
-        <v>30.4</v>
+        <v>41.7</v>
       </c>
       <c r="F55" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>57.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -2952,34 +2955,34 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G56" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K56" t="n">
         <v>66.7</v>
-      </c>
-      <c r="D56" t="n">
-        <v>25</v>
-      </c>
-      <c r="E56" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F56" t="n">
-        <v>25</v>
-      </c>
-      <c r="G56" t="n">
-        <v>25</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>100</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -2987,96 +2990,96 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
-      </c>
-      <c r="G57" t="n">
-        <v>37.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G57"/>
       <c r="H57" t="n">
         <v>0</v>
       </c>
-      <c r="I57" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J57" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K57" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>57.7</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58"/>
+        <v>17.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
+      <c r="I58" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" t="n">
-        <v>57.7</v>
+        <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
@@ -3084,34 +3087,34 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" t="n">
         <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="61">
@@ -3119,19 +3122,19 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D61" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>42.3</v>
+        <v>66.7</v>
       </c>
       <c r="F61" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>25</v>
@@ -3140,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -3154,31 +3157,31 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E62" t="n">
-        <v>66.7</v>
+        <v>41.3</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G62" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>50</v>
+      </c>
+      <c r="J62" t="n">
         <v>25</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>50</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>50</v>
@@ -3189,34 +3192,34 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C63" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D63" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E63" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G63" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="H63" t="n">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="I63" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K63" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
@@ -3224,34 +3227,34 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>70</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>70</v>
+      </c>
+      <c r="G64" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>66.7</v>
       </c>
-      <c r="D64" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E64" t="n">
-        <v>50</v>
-      </c>
-      <c r="F64" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="J64" t="n">
         <v>33.3</v>
       </c>
-      <c r="H64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>20</v>
-      </c>
-      <c r="J64" t="n">
-        <v>40</v>
-      </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3259,34 +3262,34 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C65" t="n">
-        <v>36.4</v>
+        <v>62.5</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>38.5</v>
       </c>
       <c r="E65" t="n">
-        <v>-33.6</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
-        <v>70</v>
+        <v>38.5</v>
       </c>
       <c r="G65" t="n">
-        <v>45.5</v>
+        <v>26.7</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J65" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="66">
@@ -3294,69 +3297,69 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C66" t="n">
-        <v>62.5</v>
+        <v>42.9</v>
       </c>
       <c r="D66" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>42.9</v>
       </c>
       <c r="F66" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K66" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" t="s">
         <v>79</v>
       </c>
-      <c r="B67" t="s">
-        <v>80</v>
-      </c>
       <c r="C67" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E67" t="n">
-        <v>42.9</v>
+        <v>58.3</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J67" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
@@ -3364,34 +3367,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" t="n">
         <v>80</v>
       </c>
-      <c r="C68" t="n">
-        <v>75</v>
-      </c>
       <c r="D68" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>58.3</v>
+        <v>80</v>
       </c>
       <c r="F68" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="J68" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K68" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69">
@@ -3399,34 +3402,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E69" t="n">
-        <v>80</v>
+        <v>46.7</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I69" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K69" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3434,31 +3437,31 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C70" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E70" t="n">
-        <v>46.7</v>
+        <v>5.6</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="H70" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3469,22 +3472,22 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C71" t="n">
         <v>55.6</v>
       </c>
       <c r="D71" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="n">
-        <v>5.6</v>
+        <v>43.1</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="G71" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3496,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -3504,31 +3507,31 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C72" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E72" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
       <c r="F72" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K72" t="n">
         <v>100</v>
@@ -3539,34 +3542,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C73" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3574,28 +3577,28 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C74" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
         <v>50</v>
@@ -3609,34 +3612,28 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="n">
         <v>80</v>
       </c>
-      <c r="C75" t="n">
-        <v>75</v>
-      </c>
-      <c r="D75" t="n">
-        <v>50</v>
-      </c>
-      <c r="E75" t="n">
-        <v>25</v>
-      </c>
-      <c r="F75" t="n">
-        <v>50</v>
-      </c>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J75" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="76">
@@ -3644,28 +3641,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>80</v>
-      </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
+        <v>78.6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>11.1</v>
+      </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I76" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3673,25 +3676,25 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C77" t="n">
-        <v>78.6</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="F77" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="G77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>100</v>
@@ -3700,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="78">
@@ -3708,22 +3711,22 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78" t="n">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="D78" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
         <v>75</v>
-      </c>
-      <c r="F78" t="n">
-        <v>25</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3735,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -3743,34 +3746,34 @@
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="D79" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E79" t="n">
-        <v>26.7</v>
+        <v>-8.3</v>
       </c>
       <c r="F79" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="G79" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K79" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -3778,60 +3781,54 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C80" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="D80" t="n">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="E80" t="n">
-        <v>-8.3</v>
+        <v>8.3</v>
       </c>
       <c r="F80" t="n">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="G80" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I80" t="n">
         <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" t="s">
         <v>94</v>
       </c>
-      <c r="B81" t="s">
-        <v>95</v>
-      </c>
       <c r="C81" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="D81" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E81" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>45.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>50</v>
@@ -3848,28 +3845,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C82" t="n">
-        <v>100</v>
-      </c>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
+        <v>78.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>36.4</v>
+      </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I82" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K82" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3877,34 +3880,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C83" t="n">
-        <v>78.6</v>
+        <v>76.9</v>
       </c>
       <c r="D83" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="E83" t="n">
-        <v>42.2</v>
+        <v>51.9</v>
       </c>
       <c r="F83" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="G83" t="n">
-        <v>13.3</v>
+        <v>9.1</v>
       </c>
       <c r="H83" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J83" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="84">
@@ -3912,34 +3915,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C84" t="n">
-        <v>76.9</v>
+        <v>83.3</v>
       </c>
       <c r="D84" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="E84" t="n">
-        <v>51.9</v>
+        <v>54.7</v>
       </c>
       <c r="F84" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="G84" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I84" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3947,31 +3950,31 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="D85" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="E85" t="n">
-        <v>54.7</v>
+        <v>32.1</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H85" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J85" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3982,22 +3985,22 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C86" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>32.1</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4009,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
@@ -4017,34 +4020,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C87" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E87" t="n">
-        <v>100</v>
+        <v>43.3</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G87" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I87" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K87" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
@@ -4052,34 +4055,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C88" t="n">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J88" t="n">
         <v>16.7</v>
       </c>
-      <c r="E88" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="F88" t="n">
+      <c r="K88" t="n">
         <v>16.7</v>
-      </c>
-      <c r="G88" t="n">
-        <v>20</v>
-      </c>
-      <c r="H88" t="n">
-        <v>50</v>
-      </c>
-      <c r="I88" t="n">
-        <v>50</v>
-      </c>
-      <c r="J88" t="n">
-        <v>50</v>
-      </c>
-      <c r="K88" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="89">
@@ -4087,34 +4090,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C89" t="n">
-        <v>58.8</v>
+        <v>83.3</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E89" t="n">
-        <v>58.8</v>
+        <v>66.6</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>42.9</v>
       </c>
       <c r="H89" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="I89" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="K89" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4122,34 +4125,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C90" t="n">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="D90" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="E90" t="n">
-        <v>66.6</v>
+        <v>72.7</v>
       </c>
       <c r="F90" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="G90" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J90" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91">
@@ -4157,162 +4160,162 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>81.8</v>
+        <v>66.7</v>
       </c>
       <c r="D91" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G91" t="n">
         <v>9.1</v>
       </c>
-      <c r="E91" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="F91" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
       <c r="H91" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="I91" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J91" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K91" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C92" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D92" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>58.4</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C93" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C94" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>52.5</v>
+        <v>100</v>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4321,45 +4324,45 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C96" t="n">
-        <v>41.7</v>
+        <v>88.9</v>
       </c>
       <c r="D96" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="E96" t="n">
-        <v>16.7</v>
+        <v>75.6</v>
       </c>
       <c r="F96" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="G96" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J96" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K96" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -4367,51 +4370,51 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C97" t="n">
         <v>88.9</v>
       </c>
       <c r="D97" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>75.6</v>
+        <v>88.9</v>
       </c>
       <c r="F97" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>14.3</v>
       </c>
       <c r="I97" t="n">
+        <v>80</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>20</v>
-      </c>
-      <c r="J97" t="n">
-        <v>60</v>
-      </c>
-      <c r="K97" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C98" t="n">
-        <v>88.9</v>
+        <v>75</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>88.9</v>
+        <v>75</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -4420,217 +4423,217 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C99" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C100" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>33.3</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C101" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>33.3</v>
+        <v>11.1</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C102" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E102" t="n">
-        <v>64.3</v>
+        <v>25</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G102" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="H102" t="n">
-        <v>25</v>
-      </c>
-      <c r="I102" t="n">
-        <v>40</v>
-      </c>
-      <c r="J102" t="n">
-        <v>20</v>
-      </c>
-      <c r="K102" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D103" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
-      <c r="I103"/>
-      <c r="J103"/>
-      <c r="K103"/>
+      <c r="I103" t="n">
+        <v>50</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C104" t="n">
+        <v>75</v>
+      </c>
+      <c r="D104" t="n">
+        <v>40</v>
+      </c>
+      <c r="E104" t="n">
+        <v>35</v>
+      </c>
+      <c r="F104" t="n">
+        <v>40</v>
+      </c>
+      <c r="G104" t="n">
+        <v>40</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
         <v>100</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>100</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>50</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>100</v>
@@ -4638,136 +4641,136 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C105" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D105" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E105" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F105" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G105" t="n">
-        <v>40</v>
+        <v>11.1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="K105" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="B106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" t="n">
-        <v>80</v>
-      </c>
-      <c r="D106" t="n">
-        <v>25</v>
-      </c>
-      <c r="E106" t="n">
-        <v>55</v>
-      </c>
-      <c r="F106" t="n">
-        <v>25</v>
-      </c>
+        <v>33.3</v>
+      </c>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
       <c r="G106" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J106" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>25</v>
+      </c>
+      <c r="E107" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F107" t="n">
+        <v>25</v>
+      </c>
+      <c r="G107" t="n">
+        <v>25</v>
+      </c>
+      <c r="H107" t="n">
         <v>33.3</v>
       </c>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
       <c r="I107" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K107" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C108" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="D108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>60.7</v>
+        <v>100</v>
       </c>
       <c r="F108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H108" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J108" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109">
@@ -4775,197 +4778,197 @@
         <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C109" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G109" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H109" t="n">
+        <v>20</v>
+      </c>
+      <c r="I109" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K109" t="n">
         <v>66.7</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>100</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
-      </c>
-      <c r="C110" t="n">
-        <v>50</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C110"/>
       <c r="D110" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>37.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E110"/>
       <c r="F110" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G110" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G110"/>
       <c r="H110" t="n">
-        <v>20</v>
-      </c>
-      <c r="I110" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J110" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K110" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
-      </c>
-      <c r="C111"/>
+        <v>106</v>
+      </c>
+      <c r="C111" t="n">
+        <v>95.2</v>
+      </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
-      <c r="E111"/>
+      <c r="E111" t="n">
+        <v>95.2</v>
+      </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
-      <c r="G111"/>
+      <c r="G111" t="n">
+        <v>5</v>
+      </c>
       <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
+        <v>7.1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K111" t="n">
+        <v>53.8</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
         <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" t="n">
-        <v>95.2</v>
+        <v>54.5</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>95.2</v>
+        <v>54.5</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>7.1</v>
+        <v>28.6</v>
       </c>
       <c r="I112" t="n">
-        <v>69.2</v>
+        <v>60</v>
       </c>
       <c r="J112" t="n">
-        <v>15.4</v>
+        <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C113" t="n">
-        <v>54.5</v>
+        <v>75</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="n">
-        <v>54.5</v>
+        <v>62.5</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H113" t="n">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I113" t="n">
+        <v>40</v>
+      </c>
+      <c r="J113" t="n">
+        <v>40</v>
+      </c>
+      <c r="K113" t="n">
         <v>60</v>
-      </c>
-      <c r="J113" t="n">
-        <v>20</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C114" t="n">
-        <v>75</v>
+        <v>71.4</v>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>10.3</v>
       </c>
       <c r="E114" t="n">
-        <v>62.5</v>
+        <v>61.1</v>
       </c>
       <c r="F114" t="n">
-        <v>12.5</v>
+        <v>10.3</v>
       </c>
       <c r="G114" t="n">
-        <v>23.1</v>
+        <v>3</v>
       </c>
       <c r="H114" t="n">
-        <v>14.3</v>
+        <v>18.8</v>
       </c>
       <c r="I114" t="n">
-        <v>40</v>
+        <v>72.7</v>
       </c>
       <c r="J114" t="n">
-        <v>40</v>
+        <v>18.2</v>
       </c>
       <c r="K114" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="115">
@@ -4973,34 +4976,34 @@
         <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C115" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
       <c r="D115" t="n">
-        <v>10.3</v>
+        <v>25</v>
       </c>
       <c r="E115" t="n">
-        <v>61.1</v>
+        <v>25</v>
       </c>
       <c r="F115" t="n">
-        <v>10.3</v>
+        <v>25</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>33.3</v>
       </c>
       <c r="H115" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>72.7</v>
+        <v>33.3</v>
       </c>
       <c r="J115" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="K115" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5008,31 +5011,25 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C116" t="n">
-        <v>50</v>
-      </c>
-      <c r="D116" t="n">
-        <v>25</v>
-      </c>
-      <c r="E116" t="n">
-        <v>25</v>
-      </c>
-      <c r="F116" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
       <c r="G116" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J116" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5040,101 +5037,107 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C117" t="n">
-        <v>100</v>
-      </c>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
+        <v>67.7</v>
+      </c>
+      <c r="D117" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E117" t="n">
+        <v>57</v>
+      </c>
+      <c r="F117" t="n">
+        <v>10.7</v>
+      </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I117" t="n">
-        <v>100</v>
+        <v>27.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C118" t="n">
-        <v>67.7</v>
+        <v>66.7</v>
       </c>
       <c r="D118" t="n">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="E118" t="n">
-        <v>57</v>
+        <v>52.4</v>
       </c>
       <c r="F118" t="n">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="G118" t="n">
-        <v>12.5</v>
+        <v>35.7</v>
       </c>
       <c r="H118" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="I118" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K118" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
         <v>116</v>
       </c>
-      <c r="B119" t="s">
-        <v>117</v>
-      </c>
       <c r="C119" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D119" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="E119" t="n">
-        <v>52.4</v>
+        <v>33.4</v>
       </c>
       <c r="F119" t="n">
-        <v>14.3</v>
+        <v>22.2</v>
       </c>
       <c r="G119" t="n">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="H119" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J119" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5142,34 +5145,34 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C120" t="n">
-        <v>55.6</v>
+        <v>80.8</v>
       </c>
       <c r="D120" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="E120" t="n">
-        <v>33.4</v>
+        <v>62.6</v>
       </c>
       <c r="F120" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="G120" t="n">
-        <v>42.9</v>
+        <v>36</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I120" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121">
@@ -5177,34 +5180,34 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C121" t="n">
-        <v>80.8</v>
+        <v>91.7</v>
       </c>
       <c r="D121" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="E121" t="n">
-        <v>62.6</v>
+        <v>41.7</v>
       </c>
       <c r="F121" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="G121" t="n">
-        <v>36</v>
+        <v>21.4</v>
       </c>
       <c r="H121" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>62.5</v>
+        <v>28.6</v>
       </c>
       <c r="J121" t="n">
-        <v>12.5</v>
+        <v>42.9</v>
       </c>
       <c r="K121" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="122">
@@ -5212,34 +5215,34 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C122" t="n">
-        <v>91.7</v>
+        <v>60</v>
       </c>
       <c r="D122" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="J122" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5247,28 +5250,28 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C123" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E123" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5282,34 +5285,34 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C124" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D124" t="n">
-        <v>20</v>
+        <v>8.3</v>
       </c>
       <c r="E124" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="F124" t="n">
-        <v>20</v>
+        <v>8.3</v>
       </c>
       <c r="G124" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="125">
@@ -5317,19 +5320,19 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D125" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="F125" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -5338,13 +5341,13 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="K125" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5352,34 +5355,34 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C126" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E126" t="n">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J126" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="127">
@@ -5387,34 +5390,34 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C127" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="D127" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>54.7</v>
+        <v>57.1</v>
       </c>
       <c r="F127" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I127" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J127" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K127" t="n">
-        <v>16.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128">
@@ -5422,34 +5425,34 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C128" t="n">
-        <v>57.1</v>
+        <v>70</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E128" t="n">
-        <v>57.1</v>
+        <v>32.5</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G128" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J128" t="n">
         <v>25</v>
       </c>
-      <c r="H128" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I128" t="n">
-        <v>60</v>
-      </c>
-      <c r="J128" t="n">
-        <v>20</v>
-      </c>
       <c r="K128" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129">
@@ -5457,34 +5460,34 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C129" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D129" t="n">
-        <v>37.5</v>
+        <v>21.4</v>
       </c>
       <c r="E129" t="n">
-        <v>32.5</v>
+        <v>53.6</v>
       </c>
       <c r="F129" t="n">
-        <v>37.5</v>
+        <v>21.4</v>
       </c>
       <c r="G129" t="n">
-        <v>17.6</v>
+        <v>46.7</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I129" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J129" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="130">
@@ -5492,34 +5495,34 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C130" t="n">
-        <v>75</v>
+        <v>84.6</v>
       </c>
       <c r="D130" t="n">
-        <v>21.4</v>
+        <v>14.3</v>
       </c>
       <c r="E130" t="n">
-        <v>53.6</v>
+        <v>70.3</v>
       </c>
       <c r="F130" t="n">
-        <v>21.4</v>
+        <v>14.3</v>
       </c>
       <c r="G130" t="n">
-        <v>46.7</v>
+        <v>13</v>
       </c>
       <c r="H130" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K130" t="n">
-        <v>66.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="131">
@@ -5527,34 +5530,34 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C131" t="n">
-        <v>84.6</v>
+        <v>68.6</v>
       </c>
       <c r="D131" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>59.5</v>
       </c>
       <c r="F131" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="G131" t="n">
-        <v>13</v>
+        <v>23.1</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I131" t="n">
-        <v>43.8</v>
+        <v>33.3</v>
       </c>
       <c r="J131" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="K131" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="132">
@@ -5562,34 +5565,34 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C132" t="n">
-        <v>68.6</v>
+        <v>50</v>
       </c>
       <c r="D132" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>59.5</v>
+        <v>50</v>
       </c>
       <c r="F132" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J132" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5597,34 +5600,34 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C133" t="n">
-        <v>50</v>
+        <v>90.9</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E133" t="n">
-        <v>50</v>
+        <v>70.9</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="134">
@@ -5632,31 +5635,31 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C134" t="n">
-        <v>90.9</v>
+        <v>60</v>
       </c>
       <c r="D134" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="E134" t="n">
-        <v>70.9</v>
+        <v>17.1</v>
       </c>
       <c r="F134" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="G134" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I134" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K134" t="n">
         <v>50</v>
@@ -5667,34 +5670,34 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C135" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D135" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="E135" t="n">
-        <v>17.1</v>
+        <v>73.3</v>
       </c>
       <c r="F135" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="G135" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
         <v>33.3</v>
       </c>
-      <c r="H135" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
       <c r="J135" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K135" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5702,22 +5705,22 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C136" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D136" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>73.3</v>
+        <v>100</v>
       </c>
       <c r="F136" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -5726,10 +5729,10 @@
         <v>33.3</v>
       </c>
       <c r="J136" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="137">
@@ -5737,57 +5740,51 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C137" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="n">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J137" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K137" t="n">
-        <v>33.3</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
         <v>136</v>
       </c>
-      <c r="B138" t="s">
-        <v>137</v>
-      </c>
       <c r="C138" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>5.6</v>
+        <v>42.9</v>
       </c>
       <c r="F138" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H138" t="n">
         <v>66.7</v>
@@ -5801,25 +5798,25 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C139" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
@@ -5830,63 +5827,69 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C140" t="n">
-        <v>33.3</v>
+        <v>61.1</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E140" t="n">
-        <v>33.3</v>
+        <v>52</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140"/>
-      <c r="J140"/>
-      <c r="K140"/>
+      <c r="I140" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C141" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="D141" t="n">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="E141" t="n">
-        <v>52</v>
+        <v>31.8</v>
       </c>
       <c r="F141" t="n">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="G141" t="n">
-        <v>8.3</v>
+        <v>42.9</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I141" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K141" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -5894,34 +5897,34 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C142" t="n">
         <v>50</v>
       </c>
       <c r="D142" t="n">
-        <v>18.2</v>
+        <v>23.1</v>
       </c>
       <c r="E142" t="n">
-        <v>31.8</v>
+        <v>26.9</v>
       </c>
       <c r="F142" t="n">
-        <v>18.2</v>
+        <v>23.1</v>
       </c>
       <c r="G142" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="H142" t="n">
         <v>16.7</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J142" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="143">
@@ -5929,34 +5932,34 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C143" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D143" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="E143" t="n">
-        <v>26.9</v>
+        <v>41.7</v>
       </c>
       <c r="F143" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="G143" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="H143" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J143" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5964,34 +5967,34 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C144" t="n">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="D144" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>41.7</v>
+        <v>61.5</v>
       </c>
       <c r="F144" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I144" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="145">
@@ -5999,34 +6002,34 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C145" t="n">
-        <v>61.5</v>
+        <v>45</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E145" t="n">
-        <v>61.5</v>
+        <v>28.3</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G145" t="n">
-        <v>12.5</v>
+        <v>27.3</v>
       </c>
       <c r="H145" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J145" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6034,31 +6037,31 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C146" t="n">
-        <v>45</v>
+        <v>71.4</v>
       </c>
       <c r="D146" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E146" t="n">
-        <v>28.3</v>
+        <v>51.4</v>
       </c>
       <c r="F146" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G146" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6069,102 +6072,67 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C147" t="n">
         <v>71.4</v>
       </c>
       <c r="D147" t="n">
-        <v>20</v>
+        <v>7.1</v>
       </c>
       <c r="E147" t="n">
-        <v>51.4</v>
+        <v>64.3</v>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>7.1</v>
       </c>
       <c r="G147" t="n">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="s">
+      <c r="A148"/>
+      <c r="B148" t="s">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
-        <v>137</v>
-      </c>
       <c r="C148" t="n">
-        <v>71.4</v>
+        <v>68.4</v>
       </c>
       <c r="D148" t="n">
-        <v>7.1</v>
+        <v>14.8</v>
       </c>
       <c r="E148" t="n">
-        <v>64.3</v>
+        <v>52.7</v>
       </c>
       <c r="F148" t="n">
-        <v>7.1</v>
+        <v>14.8</v>
       </c>
       <c r="G148" t="n">
-        <v>18.2</v>
+        <v>20.9</v>
       </c>
       <c r="H148" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="J148" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149"/>
-      <c r="B149" t="s">
-        <v>148</v>
-      </c>
-      <c r="C149" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="D149" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E149" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="F149" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G149" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H149" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I149" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="J149" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="K149" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
     </row>
   </sheetData>
@@ -6196,22 +6164,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6220,13 +6188,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2">
@@ -6301,7 +6269,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6336,7 +6304,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6371,7 +6339,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6406,7 +6374,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6441,7 +6409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6476,7 +6444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -6581,7 +6549,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6616,7 +6584,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6649,7 +6617,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -6684,7 +6652,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -6719,7 +6687,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -6754,7 +6722,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -6789,7 +6757,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -6824,7 +6792,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -6859,7 +6827,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -6894,7 +6862,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -6929,7 +6897,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -6964,7 +6932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -6997,7 +6965,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -7032,10 +7000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="n">
         <v>55.6</v>
@@ -7067,10 +7035,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" t="n">
         <v>68.4</v>
@@ -7102,10 +7070,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" t="n">
         <v>45.2</v>
@@ -7137,10 +7105,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="n">
         <v>83.3</v>
@@ -7172,10 +7140,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" t="n">
         <v>58.3</v>
@@ -7207,10 +7175,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" t="n">
         <v>37.5</v>
@@ -7242,10 +7210,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" t="n">
         <v>51.4</v>
@@ -7277,10 +7245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" t="n">
         <v>80</v>
@@ -7312,10 +7280,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" t="n">
         <v>66.7</v>
@@ -7347,10 +7315,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" t="n">
         <v>66.7</v>
@@ -7382,10 +7350,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" t="n">
         <v>33.3</v>
@@ -7417,10 +7385,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" t="n">
         <v>57.9</v>
@@ -7452,10 +7420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C37" t="n">
         <v>62.8</v>
@@ -7487,10 +7455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -7520,10 +7488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C39" t="n">
         <v>28.6</v>
@@ -7555,10 +7523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" t="n">
         <v>71.4</v>
@@ -7590,10 +7558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C41" t="n">
         <v>66.7</v>
@@ -7625,10 +7593,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" t="n">
         <v>100</v>
@@ -7658,10 +7626,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43" t="n">
         <v>44.4</v>
@@ -7693,10 +7661,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C44" t="n">
         <v>50</v>
@@ -7728,10 +7696,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -7757,10 +7725,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C46" t="n">
         <v>35.3</v>
@@ -7792,10 +7760,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" t="n">
         <v>55.6</v>
@@ -7827,10 +7795,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7862,10 +7830,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" t="n">
         <v>63</v>
@@ -7897,10 +7865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" t="n">
         <v>100</v>
@@ -7932,10 +7900,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C51" t="n">
         <v>69.2</v>
@@ -7967,10 +7935,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C52" t="n">
         <v>100</v>
@@ -8000,10 +7968,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" t="n">
         <v>100</v>
@@ -8035,10 +8003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C54" t="n">
         <v>61.5</v>
@@ -8070,10 +8038,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" t="n">
         <v>70</v>
@@ -8105,10 +8073,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C56" t="n">
         <v>58.3</v>
@@ -8140,10 +8108,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" t="n">
         <v>40</v>
@@ -8173,10 +8141,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C58" t="n">
         <v>60</v>
@@ -8208,10 +8176,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C59" t="n">
         <v>33.3</v>
@@ -8243,10 +8211,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C60" t="n">
         <v>100</v>
@@ -8276,10 +8244,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C61" t="n">
         <v>46.2</v>
@@ -8311,10 +8279,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62" t="n">
         <v>40</v>
@@ -8346,10 +8314,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63" t="n">
         <v>14.3</v>
@@ -8381,10 +8349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -8416,10 +8384,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C65" t="n">
         <v>50</v>
@@ -8451,10 +8419,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C66" t="n">
         <v>50</v>
@@ -8486,10 +8454,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C67" t="n">
         <v>57.1</v>
@@ -8521,10 +8489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" t="n">
         <v>50</v>
@@ -8556,10 +8524,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C69" t="n">
         <v>50</v>
@@ -8591,10 +8559,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C70" t="n">
         <v>100</v>
@@ -8626,10 +8594,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -8659,10 +8627,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" t="n">
         <v>77.8</v>
@@ -8694,10 +8662,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" t="n">
         <v>66.7</v>
@@ -8729,10 +8697,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C74" t="n">
         <v>40</v>
@@ -8764,10 +8732,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C75" t="n">
         <v>66.7</v>
@@ -8797,10 +8765,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C76" t="n">
         <v>50</v>
@@ -8832,10 +8800,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" t="n">
         <v>66.7</v>
@@ -8867,10 +8835,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C78" t="n">
         <v>52</v>
@@ -8902,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C79" t="n">
         <v>68.8</v>
@@ -8938,7 +8906,7 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C80" t="n">
         <v>54.9</v>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -96,6 +96,9 @@
     <t xml:space="preserve">Josh Frazer</t>
   </si>
   <si>
+    <t xml:space="preserve">Junichi Yuki</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kade Falardeau</t>
   </si>
   <si>
@@ -111,12 +114,18 @@
     <t xml:space="preserve">Reid Lunney</t>
   </si>
   <si>
+    <t xml:space="preserve">Rhys Jenkyn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tim Somerville</t>
   </si>
   <si>
     <t xml:space="preserve">Tobey Drennan</t>
   </si>
   <si>
+    <t xml:space="preserve">Ty Tinnish</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adrian Crewe</t>
   </si>
   <si>
@@ -264,25 +273,34 @@
     <t xml:space="preserve">Woochan Nam</t>
   </si>
   <si>
+    <t xml:space="preserve">Waterloo Warriors</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adam Leatherland</t>
   </si>
   <si>
-    <t xml:space="preserve">Waterloo Warriors</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adam Rusch</t>
   </si>
   <si>
     <t xml:space="preserve">Arthur Kowara</t>
   </si>
   <si>
+    <t xml:space="preserve">Ben Waddell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Carter Kipp</t>
   </si>
   <si>
+    <t xml:space="preserve">Cole Smart</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jai Pawa</t>
   </si>
   <si>
-    <t xml:space="preserve">Junichi Yuki</t>
+    <t xml:space="preserve">Jonah Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalan Maharaj</t>
   </si>
   <si>
     <t xml:space="preserve">Max Greaves</t>
@@ -294,9 +312,6 @@
     <t xml:space="preserve">Nico Valvo</t>
   </si>
   <si>
-    <t xml:space="preserve">Rhys Jenkyn</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sam Grant</t>
   </si>
   <si>
@@ -507,9 +522,15 @@
     <t xml:space="preserve">Max Van Dam</t>
   </si>
   <si>
+    <t xml:space="preserve">Myles Robinson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nolan McFarlane</t>
   </si>
   <si>
+    <t xml:space="preserve">Owen Toon</t>
+  </si>
+  <si>
     <t xml:space="preserve">RJ Moniz</t>
   </si>
   <si>
@@ -597,7 +618,13 @@
     <t xml:space="preserve">Aidan Armitage</t>
   </si>
   <si>
+    <t xml:space="preserve">Justin Mende</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luca Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Newman</t>
   </si>
   <si>
     <t xml:space="preserve">Connor Lynch</t>
@@ -721,8 +748,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K131" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K146" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K146"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -741,8 +768,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K73" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K81" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K81"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1098,31 +1125,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7</v>
+        <v>60.7</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="E2" t="n">
-        <v>52.1</v>
+        <v>53.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="I2" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="J2" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="K2" t="n">
-        <v>43.4</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="3">
@@ -1168,31 +1195,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="D4" t="n">
         <v>13.8</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="F4" t="n">
         <v>13.8</v>
       </c>
       <c r="G4" t="n">
-        <v>19.2</v>
+        <v>18.6</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="I4" t="n">
-        <v>37.3</v>
+        <v>35.9</v>
       </c>
       <c r="J4" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="K4" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="5">
@@ -1343,22 +1370,22 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>79.6</v>
+        <v>78.8</v>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="F9" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>27.4</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="I9" t="n">
         <v>45.6</v>
@@ -1378,31 +1405,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>68.9</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
       </c>
       <c r="H10" t="n">
-        <v>18.2</v>
+        <v>16.9</v>
       </c>
       <c r="I10" t="n">
-        <v>43.8</v>
+        <v>45.7</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>22.9</v>
       </c>
       <c r="K10" t="n">
-        <v>56.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="11">
@@ -1477,31 +1504,31 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>60.9</v>
+        <v>59.3</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>60.9</v>
+        <v>59.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="K13" t="n">
-        <v>22.2</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="14">
@@ -1512,31 +1539,31 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>67.6</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>17.2</v>
+        <v>18.6</v>
       </c>
       <c r="E14" t="n">
         <v>50.4</v>
       </c>
       <c r="F14" t="n">
-        <v>17.2</v>
+        <v>18.6</v>
       </c>
       <c r="G14" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="H14" t="n">
-        <v>15.3</v>
+        <v>14.1</v>
       </c>
       <c r="I14" t="n">
-        <v>49</v>
+        <v>48.1</v>
       </c>
       <c r="J14" t="n">
-        <v>24.5</v>
+        <v>27.8</v>
       </c>
       <c r="K14" t="n">
-        <v>32.7</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="15">
@@ -1582,31 +1609,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>75.5</v>
+        <v>76.7</v>
       </c>
       <c r="D16" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>62.8</v>
       </c>
       <c r="F16" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="G16" t="n">
-        <v>29.4</v>
+        <v>28.1</v>
       </c>
       <c r="H16" t="n">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="I16" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="J16" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1617,31 +1644,25 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10.9</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>36.7</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1652,31 +1673,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>76</v>
+        <v>67.4</v>
       </c>
       <c r="D18" t="n">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>60.3</v>
+        <v>57.4</v>
       </c>
       <c r="F18" t="n">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>30.9</v>
+        <v>12.1</v>
       </c>
       <c r="H18" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="I18" t="n">
-        <v>48.3</v>
+        <v>42.9</v>
       </c>
       <c r="J18" t="n">
-        <v>31</v>
+        <v>34.3</v>
       </c>
       <c r="K18" t="n">
-        <v>53.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="19">
@@ -1687,31 +1708,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>66.7</v>
+        <v>76.9</v>
       </c>
       <c r="D19" t="n">
-        <v>21.2</v>
+        <v>15.5</v>
       </c>
       <c r="E19" t="n">
-        <v>45.5</v>
+        <v>61.4</v>
       </c>
       <c r="F19" t="n">
-        <v>21.2</v>
+        <v>15.5</v>
       </c>
       <c r="G19" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35</v>
+        <v>48.4</v>
       </c>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>32.3</v>
       </c>
       <c r="K19" t="n">
-        <v>47.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="20">
@@ -1722,31 +1743,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>77.5</v>
+        <v>67.7</v>
       </c>
       <c r="D20" t="n">
-        <v>15.5</v>
+        <v>20.8</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>46.9</v>
       </c>
       <c r="F20" t="n">
-        <v>15.5</v>
+        <v>20.8</v>
       </c>
       <c r="G20" t="n">
-        <v>23</v>
+        <v>32.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="I20" t="n">
-        <v>35.6</v>
+        <v>40.9</v>
       </c>
       <c r="J20" t="n">
-        <v>37.3</v>
+        <v>22.7</v>
       </c>
       <c r="K20" t="n">
-        <v>36.8</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="21">
@@ -1757,31 +1778,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>55.4</v>
+        <v>77.6</v>
       </c>
       <c r="D21" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="n">
-        <v>40.5</v>
+        <v>62.3</v>
       </c>
       <c r="F21" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="G21" t="n">
-        <v>11.8</v>
+        <v>22.9</v>
       </c>
       <c r="H21" t="n">
-        <v>13.5</v>
+        <v>2.4</v>
       </c>
       <c r="I21" t="n">
-        <v>51.5</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>21.2</v>
+        <v>37.1</v>
       </c>
       <c r="K21" t="n">
-        <v>27.3</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="22">
@@ -1792,31 +1813,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>86.7</v>
+        <v>55.4</v>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>40.5</v>
       </c>
       <c r="F22" t="n">
-        <v>16.7</v>
+        <v>14.9</v>
       </c>
       <c r="G22" t="n">
-        <v>6.7</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="I22" t="n">
-        <v>63.6</v>
+        <v>51.5</v>
       </c>
       <c r="J22" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K22" t="n">
         <v>27.3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>63.6</v>
       </c>
     </row>
     <row r="23">
@@ -1827,17 +1848,11 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>80</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>80</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
       <c r="G23" t="n">
         <v>0</v>
       </c>
@@ -1845,13 +1860,13 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="J23" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1859,139 +1874,139 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="D24" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="n">
-        <v>44.5</v>
+        <v>70</v>
       </c>
       <c r="F24" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>44.3</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
         <v>38</v>
       </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
       <c r="C27" t="n">
-        <v>79.2</v>
+        <v>77.8</v>
       </c>
       <c r="D27" t="n">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="E27" t="n">
-        <v>72.5</v>
+        <v>44.5</v>
       </c>
       <c r="F27" t="n">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1999,34 +2014,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>88.9</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>38.9</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2034,34 +2049,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>61.4</v>
+        <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>20.7</v>
       </c>
       <c r="E29" t="n">
-        <v>44.7</v>
+        <v>44.3</v>
       </c>
       <c r="F29" t="n">
-        <v>16.7</v>
+        <v>20.7</v>
       </c>
       <c r="G29" t="n">
-        <v>28.6</v>
+        <v>42.1</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="I29" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="J29" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -2069,34 +2084,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>83.8</v>
+        <v>79.2</v>
       </c>
       <c r="D30" t="n">
-        <v>26.5</v>
+        <v>6.7</v>
       </c>
       <c r="E30" t="n">
-        <v>57.3</v>
+        <v>72.5</v>
       </c>
       <c r="F30" t="n">
-        <v>26.5</v>
+        <v>6.7</v>
       </c>
       <c r="G30" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I30" t="n">
-        <v>56.2</v>
+        <v>70</v>
       </c>
       <c r="J30" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>66.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2104,34 +2119,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>68.6</v>
+        <v>88.9</v>
       </c>
       <c r="D31" t="n">
-        <v>8.8</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
-        <v>59.8</v>
+        <v>38.9</v>
       </c>
       <c r="F31" t="n">
-        <v>8.8</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>29.6</v>
+        <v>16.7</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>8.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -2139,34 +2154,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>61.4</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>44.7</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I32" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="J32" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -2174,25 +2189,25 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>62.5</v>
+        <v>83.8</v>
       </c>
       <c r="D33" t="n">
-        <v>12.1</v>
+        <v>26.5</v>
       </c>
       <c r="E33" t="n">
-        <v>50.4</v>
+        <v>57.3</v>
       </c>
       <c r="F33" t="n">
-        <v>12.1</v>
+        <v>26.5</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6</v>
+        <v>22.5</v>
       </c>
       <c r="H33" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>56.2</v>
@@ -2201,7 +2216,7 @@
         <v>18.8</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="34">
@@ -2209,34 +2224,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>84</v>
+        <v>68.6</v>
       </c>
       <c r="D34" t="n">
-        <v>5.6</v>
+        <v>8.8</v>
       </c>
       <c r="E34" t="n">
-        <v>78.4</v>
+        <v>59.8</v>
       </c>
       <c r="F34" t="n">
-        <v>5.6</v>
+        <v>8.8</v>
       </c>
       <c r="G34" t="n">
-        <v>4.5</v>
+        <v>29.6</v>
       </c>
       <c r="H34" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K34" t="n">
-        <v>46.7</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="35">
@@ -2244,34 +2259,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>59.5</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>41.9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
       <c r="J35" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="K35" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2279,34 +2294,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I36" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -2314,34 +2329,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C37" t="n">
-        <v>64.7</v>
+        <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>31.2</v>
+        <v>5.6</v>
       </c>
       <c r="E37" t="n">
-        <v>33.5</v>
+        <v>78.4</v>
       </c>
       <c r="F37" t="n">
-        <v>31.2</v>
+        <v>5.6</v>
       </c>
       <c r="G37" t="n">
-        <v>31.2</v>
+        <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="I37" t="n">
-        <v>57.1</v>
+        <v>26.7</v>
       </c>
       <c r="J37" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="38">
@@ -2349,34 +2364,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C38" t="n">
-        <v>80</v>
+        <v>59.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>46.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>41.9</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="39">
@@ -2384,34 +2399,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>52.3</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>40.2</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2419,34 +2434,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>56.2</v>
+        <v>64.7</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="E40" t="n">
-        <v>26.2</v>
+        <v>33.5</v>
       </c>
       <c r="F40" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G40" t="n">
-        <v>41.7</v>
+        <v>31.2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I40" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="41">
@@ -2454,25 +2469,25 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2486,66 +2501,66 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>52.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>40.2</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G42" t="n">
-        <v>26.7</v>
+        <v>14.8</v>
       </c>
       <c r="H42" t="n">
         <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>83.3</v>
+        <v>64.3</v>
       </c>
       <c r="J42" t="n">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="K42" t="n">
-        <v>66.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>56.2</v>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>27.5</v>
+        <v>26.2</v>
       </c>
       <c r="F43" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2556,37 +2571,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
         <v>56</v>
       </c>
-      <c r="B44" t="s">
-        <v>53</v>
-      </c>
       <c r="C44" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>30.4</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I44" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2594,34 +2609,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C45" t="n">
+        <v>60</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>60</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K45" t="n">
         <v>66.7</v>
-      </c>
-      <c r="D45" t="n">
-        <v>25</v>
-      </c>
-      <c r="E45" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F45" t="n">
-        <v>25</v>
-      </c>
-      <c r="G45" t="n">
-        <v>25</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>100</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -2629,34 +2644,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C46" t="n">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="D46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G46" t="n">
         <v>20</v>
       </c>
-      <c r="E46" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="F46" t="n">
-        <v>20</v>
-      </c>
-      <c r="G46" t="n">
-        <v>37.5</v>
-      </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2664,61 +2679,69 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47"/>
+        <v>16.7</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
+      <c r="I47" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>57.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" t="n">
-        <v>57.7</v>
+        <v>66.7</v>
       </c>
       <c r="D48" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>40.1</v>
+        <v>41.7</v>
       </c>
       <c r="F48" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -2726,34 +2749,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="50">
@@ -2761,69 +2784,61 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50"/>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C51" t="n">
-        <v>66.7</v>
+        <v>57.7</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E51" t="n">
-        <v>66.7</v>
+        <v>40.1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K51" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="52">
@@ -2831,34 +2846,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C52" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2866,34 +2881,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C53" t="n">
+        <v>50</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>66.7</v>
       </c>
-      <c r="D53" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>50</v>
-      </c>
-      <c r="F53" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G53" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>20</v>
-      </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="54">
@@ -2901,34 +2916,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C54" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="D54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>-33.6</v>
+        <v>66.7</v>
       </c>
       <c r="F54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -2936,34 +2951,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C55" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="D55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G55" t="n">
         <v>38.5</v>
       </c>
-      <c r="E55" t="n">
-        <v>24</v>
-      </c>
-      <c r="F55" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>26.7</v>
-      </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I55" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -2971,139 +2986,139 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C56" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D57" t="n">
         <v>70</v>
       </c>
-      <c r="B57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" t="n">
-        <v>75</v>
-      </c>
-      <c r="D57" t="n">
-        <v>16.7</v>
-      </c>
       <c r="E57" t="n">
-        <v>58.3</v>
+        <v>-33.6</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7</v>
+        <v>70</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>45.5</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K57" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C58" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J58" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>66.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" t="s">
         <v>72</v>
       </c>
-      <c r="B59" t="s">
-        <v>69</v>
-      </c>
       <c r="C59" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="60">
@@ -3111,34 +3126,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C60" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="E60" t="n">
-        <v>5.6</v>
+        <v>58.3</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="G60" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61">
@@ -3146,34 +3161,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C61" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>43.1</v>
+        <v>80</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="62">
@@ -3181,7 +3196,7 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C62" t="n">
         <v>66.7</v>
@@ -3196,19 +3211,19 @@
         <v>20</v>
       </c>
       <c r="G62" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3216,22 +3231,22 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3240,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3251,34 +3266,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="D64" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>43.1</v>
       </c>
       <c r="F64" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="G64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3286,28 +3301,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C65" t="n">
-        <v>80</v>
-      </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>66.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>20</v>
+      </c>
+      <c r="E65" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>20</v>
+      </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -3315,31 +3336,31 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C66" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>67.5</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3350,34 +3371,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C67" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D67" t="n">
+        <v>50</v>
+      </c>
+      <c r="E67" t="n">
         <v>25</v>
       </c>
-      <c r="E67" t="n">
-        <v>75</v>
-      </c>
       <c r="F67" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" t="n">
         <v>25</v>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K67" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3385,34 +3406,28 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C68" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="D68" t="n">
-        <v>20</v>
-      </c>
-      <c r="E68" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F68" t="n">
-        <v>20</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
       <c r="G68" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69">
@@ -3420,34 +3435,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>66.7</v>
+        <v>78.6</v>
       </c>
       <c r="D69" t="n">
-        <v>75</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="n">
-        <v>-8.3</v>
+        <v>67.5</v>
       </c>
       <c r="F69" t="n">
-        <v>75</v>
+        <v>11.1</v>
       </c>
       <c r="G69" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H69" t="n">
         <v>33.3</v>
       </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3455,57 +3470,63 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C70" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="D70" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="E70" t="n">
-        <v>8.3</v>
+        <v>75</v>
       </c>
       <c r="F70" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="G70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C71" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E71" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" t="n">
+        <v>75</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
         <v>100</v>
-      </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>50</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3516,314 +3537,308 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C72" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D72" t="n">
-        <v>36.4</v>
+        <v>75</v>
       </c>
       <c r="E72" t="n">
-        <v>42.2</v>
+        <v>-8.3</v>
       </c>
       <c r="F72" t="n">
-        <v>36.4</v>
+        <v>75</v>
       </c>
       <c r="G72" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="H72" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J72" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C73" t="n">
-        <v>76.9</v>
+        <v>75</v>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>51.9</v>
+        <v>75</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C74" t="n">
-        <v>83.3</v>
+        <v>52.9</v>
       </c>
       <c r="D74" t="n">
-        <v>28.6</v>
+        <v>38.5</v>
       </c>
       <c r="E74" t="n">
-        <v>54.7</v>
+        <v>14.4</v>
       </c>
       <c r="F74" t="n">
-        <v>28.6</v>
+        <v>38.5</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H74" t="n">
-        <v>33.3</v>
+        <v>11.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C75" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>25</v>
-      </c>
-      <c r="E75" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F75" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C76" t="n">
-        <v>100</v>
+        <v>72.2</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="E76" t="n">
-        <v>100</v>
+        <v>36.5</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="G76" t="n">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K76" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C77" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>43.3</v>
+        <v>75</v>
       </c>
       <c r="F77" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C78" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C79" t="n">
-        <v>83.3</v>
+        <v>80.8</v>
       </c>
       <c r="D79" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="n">
-        <v>66.6</v>
+        <v>68.3</v>
       </c>
       <c r="F79" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G79" t="n">
-        <v>42.9</v>
+        <v>9.1</v>
       </c>
       <c r="H79" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
+        <v>23.1</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C80" t="n">
-        <v>81.8</v>
+        <v>58.3</v>
       </c>
       <c r="D80" t="n">
         <v>9.1</v>
       </c>
       <c r="E80" t="n">
-        <v>72.7</v>
+        <v>49.2</v>
       </c>
       <c r="F80" t="n">
         <v>9.1</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H80" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="I80" t="n">
         <v>75</v>
       </c>
       <c r="J80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>75</v>
@@ -3831,69 +3846,69 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C81" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D81" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>58.4</v>
+        <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K81" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C82" t="n">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>31.6</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3901,174 +3916,162 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>57.1</v>
+        <v>71.4</v>
       </c>
       <c r="D83" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>48.4</v>
+        <v>71.4</v>
       </c>
       <c r="F83" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="H83" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J83" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
-      </c>
-      <c r="C84" t="n">
-        <v>46.7</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C84"/>
       <c r="D84" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E84" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E84"/>
       <c r="F84" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G84" t="n">
-        <v>18.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G84"/>
       <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K84" t="n">
-        <v>37.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C85" t="n">
-        <v>88.9</v>
+        <v>45</v>
       </c>
       <c r="D85" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E85" t="n">
-        <v>75.6</v>
+        <v>25</v>
       </c>
       <c r="F85" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="G85" t="n">
-        <v>20</v>
+        <v>45.5</v>
       </c>
       <c r="H85" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J85" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="n">
+        <v>50</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>100</v>
       </c>
-      <c r="B86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" t="n">
-        <v>88.9</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>88.9</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I86" t="n">
-        <v>80</v>
-      </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>78.6</v>
+        <v>37.5</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>78.6</v>
+        <v>37.5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4076,28 +4079,28 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C88" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D88" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="F88" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4106,266 +4109,278 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C89" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>11.1</v>
+        <v>66.7</v>
       </c>
       <c r="H89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J89" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C90" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D90" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E90" t="n">
-        <v>55</v>
+        <v>43.3</v>
       </c>
       <c r="F90" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G90" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I90" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J90" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="K90" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C91" t="n">
-        <v>85.7</v>
+        <v>59.1</v>
       </c>
       <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>50</v>
+      </c>
+      <c r="J91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K91" t="n">
         <v>25</v>
-      </c>
-      <c r="E91" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F91" t="n">
-        <v>25</v>
-      </c>
-      <c r="G91" t="n">
-        <v>25</v>
-      </c>
-      <c r="H91" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I91" t="n">
-        <v>50</v>
-      </c>
-      <c r="J91" t="n">
-        <v>50</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C92" t="n">
-        <v>43.8</v>
+        <v>76.5</v>
       </c>
       <c r="D92" t="n">
-        <v>9.1</v>
+        <v>26.3</v>
       </c>
       <c r="E92" t="n">
-        <v>34.7</v>
+        <v>50.2</v>
       </c>
       <c r="F92" t="n">
-        <v>9.1</v>
+        <v>26.3</v>
       </c>
       <c r="G92" t="n">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="H92" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="I92" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J92" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C93" t="n">
-        <v>100</v>
-      </c>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
+        <v>81.8</v>
+      </c>
+      <c r="D93" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>9.1</v>
+      </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J93" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
-      </c>
-      <c r="C94"/>
+        <v>86</v>
+      </c>
+      <c r="C94" t="n">
+        <v>64</v>
+      </c>
       <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94"/>
+        <v>9.1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>54.9</v>
+      </c>
       <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94"/>
+        <v>9.1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>11.1</v>
+      </c>
       <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94"/>
-      <c r="J94"/>
-      <c r="K94"/>
+        <v>15.4</v>
+      </c>
+      <c r="I94" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J94" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K94" t="n">
+        <v>77.8</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C95" t="n">
-        <v>92.6</v>
-      </c>
-      <c r="D95" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E95" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="F95" t="n">
-        <v>5.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
       <c r="G95" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="J95" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="B96" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C96" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>43.7</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4373,28 +4388,28 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C97" t="n">
-        <v>75</v>
+        <v>77.8</v>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="F97" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="H97" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
         <v>40</v>
@@ -4403,176 +4418,176 @@
         <v>40</v>
       </c>
       <c r="K97" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C98" t="n">
-        <v>71.4</v>
+        <v>57.1</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
+        <v>8.7</v>
       </c>
       <c r="E98" t="n">
-        <v>61.4</v>
+        <v>48.4</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>8.7</v>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>14.3</v>
       </c>
       <c r="H98" t="n">
-        <v>17.6</v>
+        <v>27.3</v>
       </c>
       <c r="I98" t="n">
-        <v>72.7</v>
+        <v>80</v>
       </c>
       <c r="J98" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>55.6</v>
+        <v>46.7</v>
       </c>
       <c r="D99" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="E99" t="n">
-        <v>38.9</v>
+        <v>20</v>
       </c>
       <c r="F99" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="G99" t="n">
-        <v>28.6</v>
+        <v>18.2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C100" t="n">
-        <v>68.8</v>
+        <v>88.9</v>
       </c>
       <c r="D100" t="n">
-        <v>10.3</v>
+        <v>13.3</v>
       </c>
       <c r="E100" t="n">
-        <v>58.5</v>
+        <v>75.6</v>
       </c>
       <c r="F100" t="n">
-        <v>10.3</v>
+        <v>13.3</v>
       </c>
       <c r="G100" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H100" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="I100" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J100" t="n">
-        <v>8.3</v>
+        <v>60</v>
       </c>
       <c r="K100" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C101" t="n">
-        <v>66.7</v>
+        <v>88.9</v>
       </c>
       <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>88.9</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
         <v>14.3</v>
       </c>
-      <c r="E101" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F101" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G101" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H101" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I101" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J101" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B102" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C102" t="n">
-        <v>55.6</v>
+        <v>78.6</v>
       </c>
       <c r="D102" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>33.4</v>
+        <v>78.6</v>
       </c>
       <c r="F102" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>42.9</v>
+        <v>9.1</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -4583,139 +4598,139 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B103" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>80.8</v>
+        <v>57.1</v>
       </c>
       <c r="D103" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="E103" t="n">
-        <v>62.6</v>
+        <v>48</v>
       </c>
       <c r="F103" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="G103" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H103" t="n">
-        <v>15.4</v>
+        <v>50</v>
       </c>
       <c r="I103" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C104" t="n">
-        <v>91.7</v>
+        <v>64.3</v>
       </c>
       <c r="D104" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>41.7</v>
+        <v>64.3</v>
       </c>
       <c r="F104" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>21.4</v>
+        <v>11.1</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I104" t="n">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="J104" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>71.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C105" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C106" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="D106" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E106" t="n">
-        <v>80</v>
+        <v>60.7</v>
       </c>
       <c r="F106" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G106" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I106" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4723,58 +4738,52 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C107" t="n">
-        <v>75</v>
+        <v>43.8</v>
       </c>
       <c r="D107" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="E107" t="n">
-        <v>66.7</v>
+        <v>34.7</v>
       </c>
       <c r="F107" t="n">
-        <v>8.3</v>
+        <v>9.1</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I107" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J107" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="K107" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C108" t="n">
         <v>100</v>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>100</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="n">
         <v>0</v>
       </c>
@@ -4793,465 +4802,465 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
-      </c>
-      <c r="C109" t="n">
-        <v>83.3</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C109"/>
       <c r="D109" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E109" t="n">
-        <v>54.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E109"/>
       <c r="F109" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G109" t="n">
-        <v>16.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G109"/>
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J109" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K109" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C110" t="n">
+        <v>92.6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H110" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I110" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K110" t="n">
         <v>57.1</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>25</v>
-      </c>
-      <c r="H110" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I110" t="n">
-        <v>60</v>
-      </c>
-      <c r="J110" t="n">
-        <v>20</v>
-      </c>
-      <c r="K110" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C111" t="n">
-        <v>70</v>
+        <v>56.2</v>
       </c>
       <c r="D111" t="n">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="n">
-        <v>32.5</v>
+        <v>43.7</v>
       </c>
       <c r="F111" t="n">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
       <c r="G111" t="n">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I111" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="J111" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K111" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C112" t="n">
         <v>75</v>
       </c>
       <c r="D112" t="n">
-        <v>21.4</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="n">
-        <v>53.6</v>
+        <v>62.5</v>
       </c>
       <c r="F112" t="n">
-        <v>21.4</v>
+        <v>12.5</v>
       </c>
       <c r="G112" t="n">
-        <v>46.7</v>
+        <v>23.1</v>
       </c>
       <c r="H112" t="n">
         <v>14.3</v>
       </c>
       <c r="I112" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K112" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B113" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C113" t="n">
-        <v>84.6</v>
+        <v>71.4</v>
       </c>
       <c r="D113" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="E113" t="n">
-        <v>70.3</v>
+        <v>61.4</v>
       </c>
       <c r="F113" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I113" t="n">
-        <v>43.8</v>
+        <v>72.7</v>
       </c>
       <c r="J113" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="K113" t="n">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B114" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C114" t="n">
-        <v>68.6</v>
+        <v>55.6</v>
       </c>
       <c r="D114" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="E114" t="n">
-        <v>59.5</v>
+        <v>38.9</v>
       </c>
       <c r="F114" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="G114" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="H114" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J114" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="K114" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C115" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="E115" t="n">
-        <v>50</v>
+        <v>58.5</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C116" t="n">
-        <v>90.9</v>
+        <v>66.7</v>
       </c>
       <c r="D116" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="E116" t="n">
-        <v>70.9</v>
+        <v>52.4</v>
       </c>
       <c r="F116" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G116" t="n">
-        <v>27.3</v>
+        <v>35.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I116" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J116" t="n">
         <v>33.3</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C117" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="D117" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F117" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G117" t="n">
         <v>42.9</v>
       </c>
-      <c r="E117" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F117" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G117" t="n">
-        <v>33.3</v>
-      </c>
       <c r="H117" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>90</v>
+        <v>80.8</v>
       </c>
       <c r="D118" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="E118" t="n">
-        <v>73.3</v>
+        <v>62.6</v>
       </c>
       <c r="F118" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="G118" t="n">
-        <v>18.2</v>
+        <v>36</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I118" t="n">
-        <v>33.3</v>
+        <v>62.5</v>
       </c>
       <c r="J118" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C119" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="J119" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="K119" t="n">
-        <v>33.3</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C120" t="n">
-        <v>16.7</v>
+        <v>60</v>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>5.6</v>
+        <v>60</v>
       </c>
       <c r="F120" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120"/>
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>100</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C121" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E121" t="n">
-        <v>42.9</v>
+        <v>80</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G121" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
         <v>66.7</v>
       </c>
-      <c r="H121" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121"/>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E122" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -5259,321 +5268,834 @@
       <c r="H122" t="n">
         <v>0</v>
       </c>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122"/>
+      <c r="I122" t="n">
+        <v>50</v>
+      </c>
+      <c r="J122" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C123" t="n">
-        <v>61.1</v>
+        <v>100</v>
       </c>
       <c r="D123" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K123" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C124" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="D124" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="E124" t="n">
-        <v>31.8</v>
+        <v>54.7</v>
       </c>
       <c r="F124" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="G124" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K124" t="n">
         <v>16.7</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>75</v>
-      </c>
-      <c r="K124" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C125" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D125" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>26.9</v>
+        <v>57.1</v>
       </c>
       <c r="F125" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H125" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I125" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J125" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C126" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="D126" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J126" t="n">
         <v>25</v>
       </c>
-      <c r="E126" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F126" t="n">
+      <c r="K126" t="n">
         <v>25</v>
-      </c>
-      <c r="G126" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>100</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C127" t="n">
-        <v>61.5</v>
+        <v>75</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="E127" t="n">
-        <v>61.5</v>
+        <v>53.6</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="G127" t="n">
-        <v>12.5</v>
+        <v>46.7</v>
       </c>
       <c r="H127" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="I127" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J127" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C128" t="n">
-        <v>45</v>
+        <v>84.6</v>
       </c>
       <c r="D128" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E128" t="n">
-        <v>28.3</v>
+        <v>70.3</v>
       </c>
       <c r="F128" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="G128" t="n">
-        <v>27.3</v>
+        <v>13</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C129" t="n">
-        <v>71.4</v>
+        <v>68.6</v>
       </c>
       <c r="D129" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="E129" t="n">
-        <v>51.4</v>
+        <v>59.5</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="G129" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I129" t="n">
         <v>33.3</v>
       </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
       <c r="J129" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C130" t="n">
+        <v>50</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>50</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>121</v>
+      </c>
+      <c r="C131" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D131" t="n">
+        <v>20</v>
+      </c>
+      <c r="E131" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>20</v>
+      </c>
+      <c r="G131" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J131" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K131" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s">
+        <v>121</v>
+      </c>
+      <c r="C132" t="n">
+        <v>60</v>
+      </c>
+      <c r="D132" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E132" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G132" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>100</v>
+      </c>
+      <c r="K132" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" t="s">
+        <v>121</v>
+      </c>
+      <c r="C133" t="n">
+        <v>90</v>
+      </c>
+      <c r="D133" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E133" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F133" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G133" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>50</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" t="s">
+        <v>121</v>
+      </c>
+      <c r="C134" t="n">
+        <v>100</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>100</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" t="s">
+        <v>141</v>
+      </c>
+      <c r="C135" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>50</v>
+      </c>
+      <c r="H135" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I135"/>
+      <c r="J135"/>
+      <c r="K135"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" t="s">
+        <v>141</v>
+      </c>
+      <c r="C136" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H136" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I136"/>
+      <c r="J136"/>
+      <c r="K136"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" t="s">
+        <v>141</v>
+      </c>
+      <c r="C137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" t="s">
+        <v>141</v>
+      </c>
+      <c r="C138" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>52</v>
+      </c>
+      <c r="F138" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" t="s">
+        <v>141</v>
+      </c>
+      <c r="C139" t="n">
+        <v>50</v>
+      </c>
+      <c r="D139" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F139" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G139" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H139" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>75</v>
+      </c>
+      <c r="K139" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
         <v>146</v>
       </c>
-      <c r="B130" t="s">
-        <v>136</v>
-      </c>
-      <c r="C130" t="n">
+      <c r="B140" t="s">
+        <v>141</v>
+      </c>
+      <c r="C140" t="n">
+        <v>50</v>
+      </c>
+      <c r="D140" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G140" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H140" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I140" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J140" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K140" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" t="s">
+        <v>141</v>
+      </c>
+      <c r="C141" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D141" t="n">
+        <v>25</v>
+      </c>
+      <c r="E141" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F141" t="n">
+        <v>25</v>
+      </c>
+      <c r="G141" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>100</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" t="s">
+        <v>141</v>
+      </c>
+      <c r="C142" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I142" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K142" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" t="s">
+        <v>141</v>
+      </c>
+      <c r="C143" t="n">
+        <v>45</v>
+      </c>
+      <c r="D143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E143" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G143" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>100</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" t="s">
+        <v>141</v>
+      </c>
+      <c r="C144" t="n">
         <v>71.4</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D144" t="n">
+        <v>20</v>
+      </c>
+      <c r="E144" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F144" t="n">
+        <v>20</v>
+      </c>
+      <c r="G144" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>50</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" t="s">
+        <v>141</v>
+      </c>
+      <c r="C145" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D145" t="n">
         <v>7.1</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E145" t="n">
         <v>64.3</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F145" t="n">
         <v>7.1</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G145" t="n">
         <v>18.2</v>
       </c>
-      <c r="H130" t="n">
+      <c r="H145" t="n">
         <v>12.5</v>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
         <v>100</v>
       </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131"/>
-      <c r="B131" t="s">
-        <v>147</v>
-      </c>
-      <c r="C131" t="n">
-        <v>67.9</v>
-      </c>
-      <c r="D131" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="F131" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="G131" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H131" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I131" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J131" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="K131" t="n">
-        <v>32.9</v>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146" t="s">
+        <v>152</v>
+      </c>
+      <c r="C146" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="E146" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F146" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G146" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H146" t="n">
+        <v>9</v>
+      </c>
+      <c r="I146" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K146" t="n">
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>
@@ -5605,22 +6127,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5629,13 +6151,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
@@ -5710,7 +6232,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -5745,7 +6267,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5780,7 +6302,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5815,7 +6337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5850,37 +6372,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>87.8</v>
+        <v>83.3</v>
       </c>
       <c r="D8" t="n">
-        <v>79.3</v>
+        <v>75.4</v>
       </c>
       <c r="E8" t="n">
-        <v>36.4</v>
+        <v>30.9</v>
       </c>
       <c r="F8" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>43.8</v>
+        <v>46.9</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>24.6</v>
+        <v>26.2</v>
       </c>
       <c r="K8" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="9">
@@ -5955,7 +6477,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -5990,7 +6512,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6023,7 +6545,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6058,69 +6580,69 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>53.1</v>
+        <v>55.4</v>
       </c>
       <c r="D14" t="n">
-        <v>66.3</v>
+        <v>65.1</v>
       </c>
       <c r="E14" t="n">
-        <v>22.8</v>
+        <v>19.7</v>
       </c>
       <c r="F14" t="n">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>8.2</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>60.6</v>
+        <v>59.6</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="K14" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="D15" t="n">
-        <v>61.4</v>
+        <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>47.6</v>
+        <v>52.2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -6128,182 +6650,182 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>65.4</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>9.7</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>53.3</v>
+        <v>65.4</v>
       </c>
       <c r="D17" t="n">
-        <v>43.6</v>
+        <v>64.3</v>
       </c>
       <c r="E17" t="n">
-        <v>8.8</v>
+        <v>9.7</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>35.7</v>
+        <v>7.7</v>
       </c>
       <c r="H17" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-28.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>46.2</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>46.2</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="D19" t="n">
-        <v>68.8</v>
+        <v>43.6</v>
       </c>
       <c r="E19" t="n">
-        <v>14.3</v>
+        <v>8.8</v>
       </c>
       <c r="F19" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K19" t="n">
-        <v>33.3</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>64.6</v>
+        <v>46.2</v>
       </c>
       <c r="D20" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>16.4</v>
+        <v>5.9</v>
       </c>
       <c r="F20" t="n">
-        <v>45.9</v>
+        <v>66.7</v>
       </c>
       <c r="G20" t="n">
-        <v>8.6</v>
+        <v>46.2</v>
       </c>
       <c r="H20" t="n">
-        <v>51.8</v>
+        <v>66.7</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>25.4</v>
+        <v>16.7</v>
       </c>
       <c r="K20" t="n">
-        <v>13.8</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -6312,392 +6834,392 @@
         <v>33.3</v>
       </c>
       <c r="D21" t="n">
-        <v>35.7</v>
+        <v>68.8</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>14.3</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G21" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K21" t="n">
         <v>33.3</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-16.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>55.6</v>
+        <v>64.6</v>
       </c>
       <c r="D22" t="n">
-        <v>49.1</v>
+        <v>61.8</v>
       </c>
       <c r="E22" t="n">
-        <v>6.7</v>
+        <v>16.4</v>
       </c>
       <c r="F22" t="n">
-        <v>66.7</v>
+        <v>45.9</v>
       </c>
       <c r="G22" t="n">
-        <v>17.6</v>
+        <v>8.6</v>
       </c>
       <c r="H22" t="n">
-        <v>18.2</v>
+        <v>51.8</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
-        <v>23.8</v>
+        <v>25.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>68.4</v>
+        <v>33.3</v>
       </c>
       <c r="D23" t="n">
-        <v>63.8</v>
+        <v>35.7</v>
       </c>
       <c r="E23" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>7.9</v>
+        <v>16.7</v>
       </c>
       <c r="H23" t="n">
-        <v>46.6</v>
+        <v>33.3</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>6.6</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C24" t="n">
-        <v>45.2</v>
+        <v>55.6</v>
       </c>
       <c r="D24" t="n">
-        <v>54.3</v>
+        <v>49.1</v>
       </c>
       <c r="E24" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="F24" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="G24" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H24" t="n">
-        <v>52.9</v>
+        <v>18.2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.4</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C25" t="n">
-        <v>83.3</v>
+        <v>68.4</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>63.8</v>
       </c>
       <c r="E25" t="n">
-        <v>18.2</v>
+        <v>10.3</v>
       </c>
       <c r="F25" t="n">
-        <v>33.3</v>
+        <v>47.8</v>
       </c>
       <c r="G25" t="n">
-        <v>16.7</v>
+        <v>7.9</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>46.6</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>22.2</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>58.3</v>
+        <v>45.2</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>54.3</v>
       </c>
       <c r="E26" t="n">
-        <v>4.3</v>
+        <v>11.1</v>
       </c>
       <c r="F26" t="n">
-        <v>66.7</v>
+        <v>26.7</v>
       </c>
       <c r="G26" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H26" t="n">
-        <v>75</v>
+        <v>52.9</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>42.9</v>
+        <v>23.1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>37.5</v>
+        <v>83.3</v>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>18.2</v>
       </c>
       <c r="F27" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H27" t="n">
         <v>25</v>
       </c>
-      <c r="G27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>38.5</v>
-      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>51.4</v>
+        <v>58.3</v>
       </c>
       <c r="D28" t="n">
-        <v>59.4</v>
+        <v>52.1</v>
       </c>
       <c r="E28" t="n">
-        <v>13.2</v>
+        <v>4.3</v>
       </c>
       <c r="F28" t="n">
-        <v>42.1</v>
+        <v>66.7</v>
       </c>
       <c r="G28" t="n">
-        <v>11.4</v>
+        <v>33.3</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>27</v>
+        <v>42.9</v>
       </c>
       <c r="K28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>45.5</v>
+        <v>18.2</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>66.7</v>
+        <v>51.4</v>
       </c>
       <c r="D30" t="n">
-        <v>57.1</v>
+        <v>59.4</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7</v>
+        <v>11.4</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>14.3</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.4</v>
+        <v>45.5</v>
       </c>
       <c r="K31" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6706,327 +7228,327 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H32" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E33" t="n">
-        <v>9.3</v>
+        <v>23.1</v>
       </c>
       <c r="F33" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>60</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K33" t="n">
         <v>16.7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>-11.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C34" t="n">
-        <v>62.8</v>
+        <v>33.3</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>48.5</v>
+        <v>66.7</v>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="D35" t="n">
         <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35"/>
+        <v>9.3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>12.5</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H35" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C36" t="n">
-        <v>28.6</v>
+        <v>62.8</v>
       </c>
       <c r="D36" t="n">
-        <v>37.5</v>
+        <v>57.5</v>
       </c>
       <c r="E36" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G36" t="n">
-        <v>28.6</v>
+        <v>9.3</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C37" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>70.2</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37"/>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="D38" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>9.5</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>6.7</v>
+        <v>28.6</v>
       </c>
       <c r="H38" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J38" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>6.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>70.2</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39"/>
+        <v>23.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50</v>
+      </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C40" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="D40" t="n">
-        <v>49.2</v>
+        <v>66.7</v>
       </c>
       <c r="E40" t="n">
-        <v>9.1</v>
+        <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="H40" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D41" t="n">
-        <v>52.9</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41"/>
       <c r="G41" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -7034,63 +7556,69 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="D42" t="n">
-        <v>7.7</v>
+        <v>49.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42"/>
+        <v>9.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>33.3</v>
+      </c>
       <c r="G42" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42"/>
+        <v>11.1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>46.2</v>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42"/>
+      <c r="J42" t="n">
+        <v>20</v>
+      </c>
       <c r="K42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C43" t="n">
-        <v>35.3</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>57.6</v>
+        <v>52.9</v>
       </c>
       <c r="E43" t="n">
-        <v>17.6</v>
+        <v>11.8</v>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="H43" t="n">
-        <v>23.1</v>
+        <v>37.5</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -7098,69 +7626,63 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C44" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>63.2</v>
+        <v>7.7</v>
       </c>
       <c r="E44" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>16.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44"/>
       <c r="G44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>28.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H44"/>
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J44"/>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>57.6</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -7168,51 +7690,51 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C46" t="n">
-        <v>63</v>
+        <v>55.6</v>
       </c>
       <c r="D46" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="E46" t="n">
-        <v>13.6</v>
+        <v>7.1</v>
       </c>
       <c r="F46" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="G46" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>23.5</v>
+        <v>10.5</v>
       </c>
       <c r="K46" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>87.5</v>
+        <v>55</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -7224,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -7238,95 +7760,93 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>69.2</v>
+        <v>63</v>
       </c>
       <c r="D48" t="n">
-        <v>74.7</v>
+        <v>57.8</v>
       </c>
       <c r="E48" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H48" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="K48" t="n">
-        <v>19.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D49" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="E49" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E49"/>
       <c r="F49" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="D50" t="n">
-        <v>63.2</v>
+        <v>87.5</v>
       </c>
       <c r="E50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>66.7</v>
@@ -7335,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -7343,436 +7863,432 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C51" t="n">
-        <v>70</v>
+        <v>52.9</v>
       </c>
       <c r="D51" t="n">
-        <v>70.4</v>
+        <v>60.8</v>
       </c>
       <c r="E51" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
       </c>
       <c r="F51" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="G51" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="H51" t="n">
-        <v>34.8</v>
+        <v>42.9</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>22</v>
+        <v>32.1</v>
       </c>
       <c r="K51" t="n">
-        <v>16.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C52" t="n">
-        <v>58.3</v>
+        <v>69.2</v>
       </c>
       <c r="D52" t="n">
-        <v>65.3</v>
+        <v>74.7</v>
       </c>
       <c r="E52" t="n">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H52" t="n">
-        <v>42.9</v>
+        <v>57.9</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>12.5</v>
+        <v>24.4</v>
       </c>
       <c r="K52" t="n">
-        <v>8.3</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>63.2</v>
+        <v>50</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
-      </c>
-      <c r="F53" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F53"/>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C54" t="n">
-        <v>46.4</v>
+        <v>55</v>
       </c>
       <c r="D54" t="n">
-        <v>53.9</v>
+        <v>62</v>
       </c>
       <c r="E54" t="n">
         <v>11.5</v>
       </c>
       <c r="F54" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="G54" t="n">
-        <v>17.9</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>35.3</v>
+        <v>40</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>23.7</v>
+        <v>21.9</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C55" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D55" t="n">
-        <v>41.2</v>
+        <v>66.7</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C56" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>44.1</v>
+        <v>40</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="F56"/>
       <c r="G56" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>-14.3</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>38.9</v>
+        <v>53.6</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-66.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="D58" t="n">
-        <v>57.9</v>
+        <v>63.2</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G58" t="n">
-        <v>25</v>
+        <v>15.4</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C59" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>41.4</v>
+        <v>70.4</v>
       </c>
       <c r="E59" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="F59" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="G59" t="n">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>34.8</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>14.3</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>-16.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C60" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="D60" t="n">
-        <v>57.5</v>
+        <v>65.3</v>
       </c>
       <c r="E60" t="n">
-        <v>18.7</v>
+        <v>31.4</v>
       </c>
       <c r="F60" t="n">
-        <v>51.9</v>
+        <v>25</v>
       </c>
       <c r="G60" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>47.8</v>
+        <v>42.9</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K60" t="n">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C61" t="n">
         <v>50</v>
       </c>
       <c r="D61" t="n">
-        <v>59.3</v>
+        <v>63.2</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F61" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="G61" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>8.3</v>
+        <v>37.5</v>
       </c>
       <c r="K61" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>53.9</v>
       </c>
       <c r="E62" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="F62" t="n">
-        <v>46.7</v>
+        <v>36.4</v>
       </c>
       <c r="G62" t="n">
-        <v>6.7</v>
+        <v>17.9</v>
       </c>
       <c r="H62" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>29.4</v>
+        <v>23.7</v>
       </c>
       <c r="K62" t="n">
-        <v>16.6</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C63" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D63" t="n">
-        <v>87.5</v>
+        <v>41.2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -7781,292 +8297,296 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H63" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>25</v>
       </c>
-      <c r="J63" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>44.1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
-      <c r="F64"/>
+      <c r="F64" t="n">
+        <v>33.3</v>
+      </c>
       <c r="G64" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C65" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>63.4</v>
+        <v>38.9</v>
       </c>
       <c r="E65" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H65" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>80</v>
+        <v>57.9</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C67" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
-        <v>31.6</v>
+        <v>41.4</v>
       </c>
       <c r="E67" t="n">
-        <v>7.1</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="G67" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K67" t="n">
-        <v>-20</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C68" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="D68" t="n">
-        <v>57.1</v>
+        <v>57.5</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68"/>
+        <v>18.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>51.9</v>
+      </c>
       <c r="G68" t="n">
-        <v>9.1</v>
+        <v>20.8</v>
       </c>
       <c r="H68" t="n">
-        <v>55.6</v>
+        <v>47.8</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>-9.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C69" t="n">
         <v>50</v>
       </c>
       <c r="D69" t="n">
-        <v>39.1</v>
+        <v>59.3</v>
       </c>
       <c r="E69" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G69" t="n">
-        <v>33.3</v>
+        <v>7.1</v>
       </c>
       <c r="H69" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K69" t="n">
-        <v>-33.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C70" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G70" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="H70" t="n">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
-        <v>7.1</v>
+        <v>29.4</v>
       </c>
       <c r="K70" t="n">
-        <v>-11.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C71" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D71" t="n">
-        <v>55.2</v>
+        <v>87.5</v>
       </c>
       <c r="E71" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -8074,70 +8594,346 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72"/>
+      <c r="G72" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-66.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>50</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>220</v>
+      </c>
+      <c r="B74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>80</v>
+      </c>
+      <c r="E74" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>50</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>50</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" t="n">
+        <v>40</v>
+      </c>
+      <c r="D75" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>40</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>222</v>
+      </c>
+      <c r="B76" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76"/>
+      <c r="G76" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>223</v>
+      </c>
+      <c r="B77" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" t="n">
+        <v>50</v>
+      </c>
+      <c r="D77" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>224</v>
+      </c>
+      <c r="B78" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" t="n">
+        <v>52</v>
+      </c>
+      <c r="D79" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8</v>
+      </c>
+      <c r="H79" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>226</v>
+      </c>
+      <c r="B80" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" t="n">
         <v>68.8</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D80" t="n">
         <v>59.2</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E80" t="n">
         <v>16</v>
       </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
         <v>5.9</v>
       </c>
-      <c r="H72" t="n">
-        <v>50</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="H80" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" t="n">
         <v>5.9</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J80" t="n">
         <v>17.4</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73"/>
-      <c r="B73" t="s">
-        <v>147</v>
-      </c>
-      <c r="C73" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="D73" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E73" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F73" t="n">
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E81" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F81" t="n">
         <v>30</v>
       </c>
-      <c r="G73" t="n">
-        <v>14</v>
-      </c>
-      <c r="H73" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J73" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>-1.4</v>
+      <c r="G81" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J81" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-1.7</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -96,228 +96,228 @@
     <t xml:space="preserve">Josh Frazer</t>
   </si>
   <si>
+    <t xml:space="preserve">Kade Falardeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nate Parsons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Phelan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reid Lunney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Somerville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tobey Drennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Crewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guelph Gryphons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Peiper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Westfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Ogston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gillis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylen Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian Fabrizio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Da Gama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Cantwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Chang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Boyle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Scicluna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Gloria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sawyer Whitaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Cullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anden Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon McMurray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declan Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eli Oughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson McQuade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Kim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Dykyj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayan Alazem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Underwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Velocci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinten Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Stonehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Vivaldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U of T Varsity Blues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elias Rubio Reyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haven Tai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Barber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Gannett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Worthen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Verman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Zidros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Hsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spenser Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomoki Yamamoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woochan Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Leatherland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterloo Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Rusch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Kowara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter Kipp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Smart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Pawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonah Allen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junichi Yuki</t>
   </si>
   <si>
-    <t xml:space="preserve">Kade Falardeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nate Parsons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Phelan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reid Lunney</t>
+    <t xml:space="preserve">Kalan Maharaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Greaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Todd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Valvo</t>
   </si>
   <si>
     <t xml:space="preserve">Rhys Jenkyn</t>
   </si>
   <si>
-    <t xml:space="preserve">Tim Somerville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tobey Drennan</t>
+    <t xml:space="preserve">Sam Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shephard</t>
   </si>
   <si>
     <t xml:space="preserve">Ty Tinnish</t>
   </si>
   <si>
-    <t xml:space="preserve">Adrian Crewe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guelph Gryphons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Peiper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Westfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Ogston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gillis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylen Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian Fabrizio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marco Da Gama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Cantwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Chang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Boyle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Scicluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Gloria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sawyer Whitaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Cullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anden Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McMaster Marauders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon McMurray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declan Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eli Oughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson McQuade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Kim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Dykyj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayan Alazem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Underwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolas Velocci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinten Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sydney Stonehouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidan Vivaldi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U of T Varsity Blues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elias Rubio Reyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elis Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haven Tai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Barber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Gannett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Worthen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirk Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Verman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Zidros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Hsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spenser Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomoki Yamamoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woochan Nam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterloo Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Leatherland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Rusch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Kowara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carter Kipp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Smart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Pawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonah Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalan Maharaj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Greaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Todd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Shephard</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adam Awrey</t>
   </si>
   <si>
@@ -522,109 +522,109 @@
     <t xml:space="preserve">Max Van Dam</t>
   </si>
   <si>
+    <t xml:space="preserve">Nolan McFarlane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RJ Moniz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rowan Gelder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Facchini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson Michel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Picard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Meron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.C. Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JJ Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landon Hutar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Miziolek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Rutherford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhys Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinny Bouchard Wright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex VanRaay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaden Fonseca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcello Colucci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Cabezas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taio Fotiou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenny Leung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kojiro Hirata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ravin Yuvarajan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taisei Hihara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Armitage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Mende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Valvo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Myles Robinson</t>
   </si>
   <si>
-    <t xml:space="preserve">Nolan McFarlane</t>
+    <t xml:space="preserve">Owen Newman</t>
   </si>
   <si>
     <t xml:space="preserve">Owen Toon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RJ Moniz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowan Gelder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Facchini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson Michel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Picard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Meron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.C. Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JJ Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landon Hutar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Miziolek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Rutherford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhys Montgomery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinny Bouchard Wright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex VanRaay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erik Lopez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaden Fonseca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcello Colucci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McMillan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Cabezas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taio Fotiou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kenny Leung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kojiro Hirata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ravin Yuvarajan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taisei Hihara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidan Armitage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Mende</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Newman</t>
   </si>
   <si>
     <t xml:space="preserve">Connor Lynch</t>
@@ -748,8 +748,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K146" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K136" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K136"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -768,8 +768,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K81" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K77" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K77"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1125,31 +1125,31 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>60.7</v>
+        <v>61</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="E2" t="n">
-        <v>53.5</v>
+        <v>53.9</v>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="G2" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="H2" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="I2" t="n">
-        <v>52.6</v>
+        <v>51.7</v>
       </c>
       <c r="J2" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="K2" t="n">
-        <v>40.4</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="3">
@@ -1195,31 +1195,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>74.2</v>
+        <v>73.9</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="E4" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="F4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="G4" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>35.9</v>
+        <v>36.9</v>
       </c>
       <c r="J4" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="K4" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="5">
@@ -1405,31 +1405,31 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>72.7</v>
       </c>
       <c r="D10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>68.9</v>
+        <v>69.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="H10" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="I10" t="n">
-        <v>45.7</v>
+        <v>44.4</v>
       </c>
       <c r="J10" t="n">
-        <v>22.9</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1612,19 +1612,19 @@
         <v>76.7</v>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="E16" t="n">
-        <v>62.8</v>
+        <v>63.9</v>
       </c>
       <c r="F16" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="G16" t="n">
         <v>28.1</v>
       </c>
       <c r="H16" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="I16" t="n">
         <v>42.9</v>
@@ -1644,25 +1644,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
+        <v>67</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.8</v>
+      </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="18">
@@ -1673,31 +1679,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>67.4</v>
+        <v>77.2</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="n">
-        <v>57.4</v>
+        <v>61.9</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="G18" t="n">
-        <v>12.1</v>
+        <v>29.2</v>
       </c>
       <c r="H18" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="I18" t="n">
-        <v>42.9</v>
+        <v>46.9</v>
       </c>
       <c r="J18" t="n">
-        <v>34.3</v>
+        <v>31.2</v>
       </c>
       <c r="K18" t="n">
-        <v>35.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="19">
@@ -1708,31 +1714,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>76.9</v>
+        <v>67.7</v>
       </c>
       <c r="D19" t="n">
-        <v>15.5</v>
+        <v>20.8</v>
       </c>
       <c r="E19" t="n">
-        <v>61.4</v>
+        <v>46.9</v>
       </c>
       <c r="F19" t="n">
-        <v>15.5</v>
+        <v>20.8</v>
       </c>
       <c r="G19" t="n">
-        <v>29.6</v>
+        <v>32.1</v>
       </c>
       <c r="H19" t="n">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="I19" t="n">
-        <v>48.4</v>
+        <v>40.9</v>
       </c>
       <c r="J19" t="n">
-        <v>32.3</v>
+        <v>22.7</v>
       </c>
       <c r="K19" t="n">
-        <v>53.3</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="20">
@@ -1743,31 +1749,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>67.7</v>
+        <v>77.6</v>
       </c>
       <c r="D20" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="n">
-        <v>46.9</v>
+        <v>62.3</v>
       </c>
       <c r="F20" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="G20" t="n">
-        <v>32.1</v>
+        <v>22.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>40.9</v>
+        <v>35.5</v>
       </c>
       <c r="J20" t="n">
-        <v>22.7</v>
+        <v>37.1</v>
       </c>
       <c r="K20" t="n">
-        <v>52.4</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="21">
@@ -1778,31 +1784,31 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>77.6</v>
+        <v>55.4</v>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="E21" t="n">
-        <v>62.3</v>
+        <v>40.5</v>
       </c>
       <c r="F21" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="G21" t="n">
-        <v>22.9</v>
+        <v>11.8</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>51.5</v>
       </c>
       <c r="J21" t="n">
-        <v>37.1</v>
+        <v>21.2</v>
       </c>
       <c r="K21" t="n">
-        <v>38.3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="22">
@@ -1813,31 +1819,31 @@
         <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>55.4</v>
+        <v>87.5</v>
       </c>
       <c r="D22" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="n">
-        <v>40.5</v>
+        <v>70.8</v>
       </c>
       <c r="F22" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>51.5</v>
+        <v>66.7</v>
       </c>
       <c r="J22" t="n">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
-        <v>27.3</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23">
@@ -1848,11 +1854,17 @@
         <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
+        <v>80</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
@@ -1860,13 +1872,13 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
@@ -1874,139 +1886,139 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>86.7</v>
+        <v>77.8</v>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>44.5</v>
       </c>
       <c r="F24" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
         <v>35</v>
       </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
       <c r="C25" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>44.3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>77.8</v>
+        <v>79.2</v>
       </c>
       <c r="D27" t="n">
-        <v>33.3</v>
+        <v>6.7</v>
       </c>
       <c r="E27" t="n">
-        <v>44.5</v>
+        <v>72.5</v>
       </c>
       <c r="F27" t="n">
-        <v>33.3</v>
+        <v>6.7</v>
       </c>
       <c r="G27" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -2014,34 +2026,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>88.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>38.9</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -2049,34 +2061,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>65</v>
+        <v>61.4</v>
       </c>
       <c r="D29" t="n">
-        <v>20.7</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="n">
-        <v>44.3</v>
+        <v>44.7</v>
       </c>
       <c r="F29" t="n">
-        <v>20.7</v>
+        <v>16.7</v>
       </c>
       <c r="G29" t="n">
-        <v>42.1</v>
+        <v>28.6</v>
       </c>
       <c r="H29" t="n">
-        <v>23.1</v>
+        <v>16.7</v>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2084,34 +2096,34 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>79.2</v>
+        <v>83.8</v>
       </c>
       <c r="D30" t="n">
-        <v>6.7</v>
+        <v>26.5</v>
       </c>
       <c r="E30" t="n">
-        <v>72.5</v>
+        <v>57.3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.7</v>
+        <v>26.5</v>
       </c>
       <c r="G30" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="H30" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>70</v>
+        <v>56.2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="31">
@@ -2119,34 +2131,34 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>88.9</v>
+        <v>68.6</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>8.8</v>
       </c>
       <c r="E31" t="n">
-        <v>38.9</v>
+        <v>59.8</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>8.8</v>
       </c>
       <c r="G31" t="n">
-        <v>16.7</v>
+        <v>29.6</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="32">
@@ -2154,34 +2166,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>61.4</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>44.7</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="J32" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="K32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2189,25 +2201,25 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>83.8</v>
+        <v>62.5</v>
       </c>
       <c r="D33" t="n">
-        <v>26.5</v>
+        <v>12.1</v>
       </c>
       <c r="E33" t="n">
-        <v>57.3</v>
+        <v>50.4</v>
       </c>
       <c r="F33" t="n">
-        <v>26.5</v>
+        <v>12.1</v>
       </c>
       <c r="G33" t="n">
-        <v>22.5</v>
+        <v>17.6</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I33" t="n">
         <v>56.2</v>
@@ -2216,7 +2228,7 @@
         <v>18.8</v>
       </c>
       <c r="K33" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -2224,34 +2236,34 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>68.6</v>
+        <v>84</v>
       </c>
       <c r="D34" t="n">
-        <v>8.8</v>
+        <v>5.6</v>
       </c>
       <c r="E34" t="n">
-        <v>59.8</v>
+        <v>78.4</v>
       </c>
       <c r="F34" t="n">
-        <v>8.8</v>
+        <v>5.6</v>
       </c>
       <c r="G34" t="n">
-        <v>29.6</v>
+        <v>4.5</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="I34" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="J34" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>8.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="35">
@@ -2259,34 +2271,34 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>41.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I35" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J35" t="n">
         <v>33.3</v>
       </c>
-      <c r="J35" t="n">
-        <v>66.7</v>
-      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="36">
@@ -2294,34 +2306,34 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>56.2</v>
+        <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2329,34 +2341,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>84</v>
+        <v>64.7</v>
       </c>
       <c r="D37" t="n">
-        <v>5.6</v>
+        <v>31.2</v>
       </c>
       <c r="E37" t="n">
-        <v>78.4</v>
+        <v>33.5</v>
       </c>
       <c r="F37" t="n">
-        <v>5.6</v>
+        <v>31.2</v>
       </c>
       <c r="G37" t="n">
-        <v>4.5</v>
+        <v>31.2</v>
       </c>
       <c r="H37" t="n">
-        <v>11.8</v>
+        <v>16.7</v>
       </c>
       <c r="I37" t="n">
-        <v>26.7</v>
+        <v>57.1</v>
       </c>
       <c r="J37" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="K37" t="n">
-        <v>46.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="38">
@@ -2364,34 +2376,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>59.5</v>
+        <v>80</v>
       </c>
       <c r="D38" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>46.2</v>
+        <v>80</v>
       </c>
       <c r="F38" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>41.9</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2399,34 +2411,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>52.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>40.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="40">
@@ -2434,34 +2446,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>64.7</v>
+        <v>56.2</v>
       </c>
       <c r="D40" t="n">
-        <v>31.2</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>33.5</v>
+        <v>26.2</v>
       </c>
       <c r="F40" t="n">
-        <v>31.2</v>
+        <v>30</v>
       </c>
       <c r="G40" t="n">
-        <v>31.2</v>
+        <v>41.7</v>
       </c>
       <c r="H40" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="J40" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2469,25 +2481,25 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2501,66 +2513,66 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
         <v>53</v>
       </c>
-      <c r="B42" t="s">
-        <v>38</v>
-      </c>
       <c r="C42" t="n">
-        <v>52.3</v>
+        <v>60</v>
       </c>
       <c r="D42" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>40.2</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8</v>
+        <v>26.7</v>
       </c>
       <c r="H42" t="n">
         <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>64.3</v>
+        <v>83.3</v>
       </c>
       <c r="J42" t="n">
-        <v>21.4</v>
+        <v>16.7</v>
       </c>
       <c r="K42" t="n">
-        <v>14.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>56.2</v>
+        <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="n">
-        <v>26.2</v>
+        <v>27.5</v>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="G43" t="n">
-        <v>41.7</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2571,37 +2583,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>30.4</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G44" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="45">
@@ -2609,34 +2621,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G45" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -2644,34 +2656,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>40</v>
+        <v>87.5</v>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>27.5</v>
+        <v>67.5</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="47">
@@ -2679,69 +2691,61 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>47.1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47"/>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>57.1</v>
-      </c>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>66.7</v>
+        <v>57.7</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>17.6</v>
       </c>
       <c r="E48" t="n">
-        <v>41.7</v>
+        <v>40.1</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>17.6</v>
       </c>
       <c r="G48" t="n">
-        <v>25</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="49">
@@ -2749,34 +2753,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="E49" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="F49" t="n">
-        <v>20</v>
-      </c>
-      <c r="G49" t="n">
-        <v>37.5</v>
-      </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2784,61 +2788,69 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50"/>
+        <v>7.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>25</v>
+      </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
+      <c r="I50" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>57.7</v>
+        <v>66.7</v>
       </c>
       <c r="D51" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>40.1</v>
+        <v>66.7</v>
       </c>
       <c r="F51" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2846,34 +2858,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>38.5</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2881,34 +2893,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>7.7</v>
+        <v>16.7</v>
       </c>
       <c r="E53" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
-        <v>7.7</v>
+        <v>16.7</v>
       </c>
       <c r="G53" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I53" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K53" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -2916,34 +2928,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>70</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-33.6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>70</v>
+      </c>
+      <c r="G54" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>66.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>25</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>50</v>
-      </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2951,34 +2963,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C55" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="D55" t="n">
-        <v>14.3</v>
+        <v>38.5</v>
       </c>
       <c r="E55" t="n">
-        <v>41.3</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
-        <v>14.3</v>
+        <v>38.5</v>
       </c>
       <c r="G55" t="n">
-        <v>38.5</v>
+        <v>26.7</v>
       </c>
       <c r="H55" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J55" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="56">
@@ -2986,139 +2998,139 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="D56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="F56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
         <v>33.3</v>
       </c>
-      <c r="H56" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>20</v>
-      </c>
-      <c r="J56" t="n">
-        <v>40</v>
-      </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" t="s">
         <v>69</v>
       </c>
-      <c r="B57" t="s">
-        <v>56</v>
-      </c>
       <c r="C57" t="n">
-        <v>36.4</v>
+        <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="n">
-        <v>-33.6</v>
+        <v>58.3</v>
       </c>
       <c r="F57" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="G57" t="n">
-        <v>45.5</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J57" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C58" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="D58" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K58" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C59" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K59" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3126,34 +3138,34 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C60" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="D60" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="E60" t="n">
-        <v>58.3</v>
+        <v>5.6</v>
       </c>
       <c r="F60" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3161,34 +3173,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="n">
-        <v>80</v>
+        <v>43.1</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -3196,7 +3208,7 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C62" t="n">
         <v>66.7</v>
@@ -3211,19 +3223,19 @@
         <v>20</v>
       </c>
       <c r="G62" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H62" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -3231,22 +3243,22 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3255,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3266,34 +3278,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C64" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E64" t="n">
-        <v>43.1</v>
+        <v>25</v>
       </c>
       <c r="F64" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3301,34 +3313,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C65" t="n">
+        <v>80</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J65" t="n">
         <v>66.7</v>
       </c>
-      <c r="D65" t="n">
-        <v>20</v>
-      </c>
-      <c r="E65" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F65" t="n">
-        <v>20</v>
-      </c>
-      <c r="G65" t="n">
-        <v>40</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>50</v>
-      </c>
-      <c r="J65" t="n">
-        <v>50</v>
-      </c>
       <c r="K65" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="66">
@@ -3336,31 +3342,31 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
+        <v>78.6</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3371,34 +3377,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C67" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" t="n">
+        <v>25</v>
+      </c>
+      <c r="E67" t="n">
         <v>75</v>
       </c>
-      <c r="D67" t="n">
-        <v>50</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>25</v>
       </c>
-      <c r="F67" t="n">
-        <v>50</v>
-      </c>
       <c r="G67" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="68">
@@ -3406,28 +3412,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C68" t="n">
-        <v>80</v>
-      </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
+        <v>46.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>20</v>
+      </c>
+      <c r="E68" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20</v>
+      </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J68" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -3435,34 +3447,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C69" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>75</v>
       </c>
       <c r="E69" t="n">
-        <v>67.5</v>
+        <v>-8.3</v>
       </c>
       <c r="F69" t="n">
-        <v>11.1</v>
+        <v>75</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="H69" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -3470,63 +3482,57 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C70" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="D70" t="n">
-        <v>25</v>
+        <v>38.5</v>
       </c>
       <c r="E70" t="n">
-        <v>75</v>
+        <v>14.4</v>
       </c>
       <c r="F70" t="n">
-        <v>25</v>
+        <v>38.5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I70" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" t="s">
         <v>84</v>
       </c>
-      <c r="B71" t="s">
-        <v>72</v>
-      </c>
       <c r="C71" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="D71" t="n">
-        <v>20</v>
-      </c>
-      <c r="E71" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F71" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3537,45 +3543,45 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C72" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="D72" t="n">
-        <v>75</v>
+        <v>35.7</v>
       </c>
       <c r="E72" t="n">
-        <v>-8.3</v>
+        <v>36.5</v>
       </c>
       <c r="F72" t="n">
-        <v>75</v>
+        <v>35.7</v>
       </c>
       <c r="G72" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J72" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="K72" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" t="n">
         <v>75</v>
@@ -3596,179 +3602,185 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C74" t="n">
-        <v>52.9</v>
+        <v>80.8</v>
       </c>
       <c r="D74" t="n">
-        <v>38.5</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="n">
-        <v>14.4</v>
+        <v>68.3</v>
       </c>
       <c r="F74" t="n">
-        <v>38.5</v>
+        <v>12.5</v>
       </c>
       <c r="G74" t="n">
-        <v>21.4</v>
+        <v>9.1</v>
       </c>
       <c r="H74" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K74" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C75" t="n">
-        <v>100</v>
-      </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
+        <v>58.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.1</v>
+      </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I75" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C76" t="n">
-        <v>72.2</v>
+        <v>73.3</v>
       </c>
       <c r="D76" t="n">
-        <v>35.7</v>
+        <v>41.7</v>
       </c>
       <c r="E76" t="n">
-        <v>36.5</v>
+        <v>31.6</v>
       </c>
       <c r="F76" t="n">
-        <v>35.7</v>
+        <v>41.7</v>
       </c>
       <c r="G76" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="H76" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I76" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="K76" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C77" t="n">
-        <v>75</v>
+        <v>71.4</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>75</v>
+        <v>71.4</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
-        <v>50</v>
+        <v>27.6</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3776,243 +3788,255 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C79" t="n">
-        <v>80.8</v>
+        <v>37.5</v>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>68.3</v>
+        <v>37.5</v>
       </c>
       <c r="F79" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>61.5</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>23.1</v>
+        <v>100</v>
       </c>
       <c r="K79" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C80" t="n">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>49.2</v>
+        <v>100</v>
       </c>
       <c r="F80" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H80" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" t="n">
+        <v>60</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E81" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G81" t="n">
         <v>20</v>
       </c>
-      <c r="B81" t="s">
-        <v>86</v>
-      </c>
-      <c r="C81" t="n">
-        <v>100</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>100</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J81" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C82" t="n">
-        <v>73.3</v>
+        <v>59.1</v>
       </c>
       <c r="D82" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>31.6</v>
+        <v>59.1</v>
       </c>
       <c r="F82" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>18.8</v>
+        <v>15.4</v>
       </c>
       <c r="H82" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J82" t="n">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C83" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="E83" t="n">
-        <v>71.4</v>
+        <v>48.7</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="G83" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I83" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K83" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84"/>
+        <v>84</v>
+      </c>
+      <c r="C84" t="n">
+        <v>81.8</v>
+      </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84"/>
+        <v>9.1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>72.7</v>
+      </c>
       <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84"/>
+        <v>9.1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
       <c r="H84" t="n">
-        <v>100</v>
-      </c>
-      <c r="I84"/>
-      <c r="J84"/>
-      <c r="K84"/>
+        <v>20</v>
+      </c>
+      <c r="I84" t="n">
+        <v>75</v>
+      </c>
+      <c r="J84" t="n">
+        <v>25</v>
+      </c>
+      <c r="K84" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>54.9</v>
       </c>
       <c r="F85" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="G85" t="n">
-        <v>45.5</v>
+        <v>11.1</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I85" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="J85" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C86" t="n">
         <v>50</v>
@@ -4033,354 +4057,360 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C87" t="n">
-        <v>37.5</v>
+        <v>72.7</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>37.5</v>
+        <v>72.7</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>66.7</v>
+        <v>12.5</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J87" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C88" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>8.7</v>
       </c>
       <c r="E88" t="n">
-        <v>100</v>
+        <v>48.4</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>8.7</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C89" t="n">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="E89" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="G89" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="K89" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C90" t="n">
-        <v>60</v>
+        <v>88.9</v>
       </c>
       <c r="D90" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E90" t="n">
-        <v>43.3</v>
+        <v>75.6</v>
       </c>
       <c r="F90" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="G90" t="n">
         <v>20</v>
       </c>
       <c r="H90" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="I90" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J90" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C91" t="n">
-        <v>59.1</v>
+        <v>88.9</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>59.1</v>
+        <v>88.9</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I91" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J91" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C92" t="n">
-        <v>76.5</v>
+        <v>78.6</v>
       </c>
       <c r="D92" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>50.2</v>
+        <v>78.6</v>
       </c>
       <c r="F92" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>27.8</v>
+        <v>9.1</v>
       </c>
       <c r="H92" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>60</v>
+        <v>85.7</v>
       </c>
       <c r="J92" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C93" t="n">
-        <v>81.8</v>
+        <v>57.1</v>
       </c>
       <c r="D93" t="n">
         <v>9.1</v>
       </c>
       <c r="E93" t="n">
-        <v>72.7</v>
+        <v>48</v>
       </c>
       <c r="F93" t="n">
         <v>9.1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H93" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C94" t="n">
-        <v>64</v>
+        <v>64.3</v>
       </c>
       <c r="D94" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>54.9</v>
+        <v>64.3</v>
       </c>
       <c r="F94" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>11.1</v>
       </c>
       <c r="H94" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="I94" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="J94" t="n">
-        <v>44.4</v>
+        <v>20</v>
       </c>
       <c r="K94" t="n">
-        <v>77.8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C95" t="n">
-        <v>100</v>
-      </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
+        <v>80</v>
+      </c>
+      <c r="D95" t="n">
+        <v>25</v>
+      </c>
+      <c r="E95" t="n">
+        <v>55</v>
+      </c>
+      <c r="F95" t="n">
+        <v>25</v>
+      </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C96" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>60.7</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4388,506 +4418,506 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C97" t="n">
-        <v>77.8</v>
+        <v>43.8</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E97" t="n">
-        <v>77.8</v>
+        <v>34.7</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G97" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I97" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J97" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K97" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
         <v>102</v>
       </c>
       <c r="C98" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="D98" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="E98" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
       <c r="G98" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
       </c>
-      <c r="C99" t="n">
-        <v>46.7</v>
-      </c>
+      <c r="C99"/>
       <c r="D99" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E99" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E99"/>
       <c r="F99" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G99" t="n">
-        <v>18.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G99"/>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K99" t="n">
-        <v>37.5</v>
-      </c>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
         <v>102</v>
       </c>
       <c r="C100" t="n">
-        <v>88.9</v>
+        <v>92.6</v>
       </c>
       <c r="D100" t="n">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="E100" t="n">
-        <v>75.6</v>
+        <v>87.3</v>
       </c>
       <c r="F100" t="n">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="G100" t="n">
-        <v>20</v>
+        <v>7.7</v>
       </c>
       <c r="H100" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I100" t="n">
-        <v>20</v>
+        <v>64.3</v>
       </c>
       <c r="J100" t="n">
-        <v>60</v>
+        <v>21.4</v>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
         <v>102</v>
       </c>
       <c r="C101" t="n">
-        <v>88.9</v>
+        <v>56.2</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="n">
-        <v>88.9</v>
+        <v>43.7</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H101" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J101" t="n">
         <v>14.3</v>
       </c>
-      <c r="I101" t="n">
-        <v>80</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
       <c r="K101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B102" t="s">
         <v>102</v>
       </c>
       <c r="C102" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="n">
-        <v>78.6</v>
+        <v>62.5</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G102" t="n">
-        <v>9.1</v>
+        <v>23.1</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I102" t="n">
-        <v>85.7</v>
+        <v>40</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
         <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>57.1</v>
+        <v>71.4</v>
       </c>
       <c r="D103" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>48</v>
+        <v>61.4</v>
       </c>
       <c r="F103" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="K103" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
         <v>102</v>
       </c>
       <c r="C104" t="n">
-        <v>64.3</v>
+        <v>55.6</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E104" t="n">
-        <v>64.3</v>
+        <v>38.9</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G104" t="n">
-        <v>11.1</v>
+        <v>28.6</v>
       </c>
       <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>50</v>
+      </c>
+      <c r="J104" t="n">
         <v>25</v>
       </c>
-      <c r="I104" t="n">
-        <v>40</v>
-      </c>
-      <c r="J104" t="n">
-        <v>20</v>
-      </c>
       <c r="K104" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B105" t="s">
         <v>102</v>
       </c>
       <c r="C105" t="n">
-        <v>80</v>
+        <v>68.8</v>
       </c>
       <c r="D105" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>12</v>
+      </c>
+      <c r="H105" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I105" t="n">
         <v>25</v>
       </c>
-      <c r="E105" t="n">
-        <v>55</v>
-      </c>
-      <c r="F105" t="n">
-        <v>25</v>
-      </c>
-      <c r="G105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>57.1</v>
-      </c>
       <c r="J105" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="K105" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C106" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="D106" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="E106" t="n">
-        <v>60.7</v>
+        <v>52.4</v>
       </c>
       <c r="F106" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="G106" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="H106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>50</v>
+      </c>
+      <c r="J106" t="n">
         <v>33.3</v>
       </c>
-      <c r="I106" t="n">
-        <v>50</v>
-      </c>
-      <c r="J106" t="n">
-        <v>50</v>
-      </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C107" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
       <c r="D107" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="E107" t="n">
-        <v>34.7</v>
+        <v>33.4</v>
       </c>
       <c r="F107" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="G107" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="H107" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C108" t="n">
-        <v>100</v>
-      </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
+        <v>80.8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F108" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="J108" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
-      </c>
-      <c r="C109"/>
+        <v>121</v>
+      </c>
+      <c r="C109" t="n">
+        <v>91.7</v>
+      </c>
       <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109"/>
+        <v>50</v>
+      </c>
+      <c r="E109" t="n">
+        <v>41.7</v>
+      </c>
       <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109"/>
+        <v>50</v>
+      </c>
+      <c r="G109" t="n">
+        <v>21.4</v>
+      </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109"/>
-      <c r="J109"/>
-      <c r="K109"/>
+      <c r="I109" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J109" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="K109" t="n">
+        <v>71.4</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C110" t="n">
-        <v>92.6</v>
+        <v>60</v>
       </c>
       <c r="D110" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>87.3</v>
+        <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="J110" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C111" t="n">
-        <v>56.2</v>
+        <v>100</v>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E111" t="n">
-        <v>43.7</v>
+        <v>80</v>
       </c>
       <c r="F111" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G111" t="n">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="H111" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="J111" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4895,299 +4925,299 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C112" t="n">
         <v>75</v>
       </c>
       <c r="D112" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F112" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>50</v>
+      </c>
+      <c r="J112" t="n">
         <v>12.5</v>
       </c>
-      <c r="E112" t="n">
+      <c r="K112" t="n">
         <v>62.5</v>
-      </c>
-      <c r="F112" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G112" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H112" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I112" t="n">
-        <v>40</v>
-      </c>
-      <c r="J112" t="n">
-        <v>40</v>
-      </c>
-      <c r="K112" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C113" t="n">
-        <v>71.4</v>
+        <v>100</v>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>61.4</v>
+        <v>100</v>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>72.7</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>18.2</v>
+        <v>100</v>
       </c>
       <c r="K113" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C114" t="n">
-        <v>55.6</v>
+        <v>83.3</v>
       </c>
       <c r="D114" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E114" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G114" t="n">
         <v>16.7</v>
       </c>
-      <c r="E114" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F114" t="n">
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J114" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K114" t="n">
         <v>16.7</v>
-      </c>
-      <c r="G114" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>50</v>
-      </c>
-      <c r="J114" t="n">
-        <v>25</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C115" t="n">
-        <v>68.8</v>
+        <v>57.1</v>
       </c>
       <c r="D115" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>58.5</v>
+        <v>57.1</v>
       </c>
       <c r="F115" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>18.8</v>
+        <v>14.3</v>
       </c>
       <c r="I115" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J115" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
         <v>121</v>
       </c>
       <c r="C116" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="D116" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="E116" t="n">
-        <v>52.4</v>
+        <v>32.5</v>
       </c>
       <c r="F116" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="G116" t="n">
-        <v>35.7</v>
+        <v>17.6</v>
       </c>
       <c r="H116" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J116" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K116" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B117" t="s">
         <v>121</v>
       </c>
       <c r="C117" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D117" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="E117" t="n">
-        <v>33.4</v>
+        <v>53.6</v>
       </c>
       <c r="F117" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="G117" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I117" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B118" t="s">
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>80.8</v>
+        <v>84.6</v>
       </c>
       <c r="D118" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="E118" t="n">
-        <v>62.6</v>
+        <v>70.3</v>
       </c>
       <c r="F118" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="G118" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H118" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>62.5</v>
+        <v>43.8</v>
       </c>
       <c r="J118" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K118" t="n">
         <v>12.5</v>
-      </c>
-      <c r="K118" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B119" t="s">
         <v>121</v>
       </c>
       <c r="C119" t="n">
-        <v>91.7</v>
+        <v>68.6</v>
       </c>
       <c r="D119" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="E119" t="n">
-        <v>41.7</v>
+        <v>59.5</v>
       </c>
       <c r="F119" t="n">
-        <v>50</v>
+        <v>9.1</v>
       </c>
       <c r="G119" t="n">
-        <v>21.4</v>
+        <v>23.1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I119" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="J119" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="K119" t="n">
-        <v>71.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B120" t="s">
         <v>121</v>
       </c>
       <c r="C120" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -5199,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5210,25 +5240,25 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B121" t="s">
         <v>121</v>
       </c>
       <c r="C121" t="n">
-        <v>100</v>
+        <v>90.9</v>
       </c>
       <c r="D121" t="n">
         <v>20</v>
       </c>
       <c r="E121" t="n">
-        <v>80</v>
+        <v>70.9</v>
       </c>
       <c r="F121" t="n">
         <v>20</v>
       </c>
       <c r="G121" t="n">
-        <v>28.6</v>
+        <v>27.3</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5237,77 +5267,77 @@
         <v>66.7</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B122" t="s">
         <v>121</v>
       </c>
       <c r="C122" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D122" t="n">
-        <v>8.3</v>
+        <v>42.9</v>
       </c>
       <c r="E122" t="n">
-        <v>66.7</v>
+        <v>17.1</v>
       </c>
       <c r="F122" t="n">
-        <v>8.3</v>
+        <v>42.9</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I122" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="K122" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B123" t="s">
         <v>121</v>
       </c>
       <c r="C123" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E123" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J123" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5315,25 +5345,25 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
         <v>121</v>
       </c>
       <c r="C124" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D124" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>54.7</v>
+        <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5345,319 +5375,301 @@
         <v>33.3</v>
       </c>
       <c r="K124" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C125" t="n">
-        <v>57.1</v>
+        <v>16.7</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="n">
-        <v>57.1</v>
+        <v>5.6</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G125" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H125" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I125" t="n">
-        <v>60</v>
-      </c>
-      <c r="J125" t="n">
-        <v>20</v>
-      </c>
-      <c r="K125" t="n">
-        <v>60</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I125"/>
+      <c r="J125"/>
+      <c r="K125"/>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C126" t="n">
-        <v>70</v>
+        <v>42.9</v>
       </c>
       <c r="D126" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>32.5</v>
+        <v>42.9</v>
       </c>
       <c r="F126" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>17.6</v>
+        <v>66.7</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J126" t="n">
-        <v>25</v>
-      </c>
-      <c r="K126" t="n">
-        <v>25</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I126"/>
+      <c r="J126"/>
+      <c r="K126"/>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C127" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="D127" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>53.6</v>
+        <v>33.3</v>
       </c>
       <c r="F127" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I127" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I127"/>
+      <c r="J127"/>
+      <c r="K127"/>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C128" t="n">
-        <v>84.6</v>
+        <v>61.1</v>
       </c>
       <c r="D128" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>52</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
         <v>14.3</v>
-      </c>
-      <c r="E128" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F128" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G128" t="n">
-        <v>13</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J128" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K128" t="n">
-        <v>12.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C129" t="n">
-        <v>68.6</v>
+        <v>50</v>
       </c>
       <c r="D129" t="n">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="E129" t="n">
-        <v>59.5</v>
+        <v>31.8</v>
       </c>
       <c r="F129" t="n">
-        <v>9.1</v>
+        <v>18.2</v>
       </c>
       <c r="G129" t="n">
-        <v>23.1</v>
+        <v>42.9</v>
       </c>
       <c r="H129" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="I129" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>16.7</v>
+        <v>75</v>
       </c>
       <c r="K129" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C130" t="n">
         <v>50</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>26.9</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I130" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C131" t="n">
-        <v>90.9</v>
+        <v>66.7</v>
       </c>
       <c r="D131" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E131" t="n">
-        <v>70.9</v>
+        <v>41.7</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G131" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J131" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C132" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H132" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I132" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K132" t="n">
         <v>42.9</v>
-      </c>
-      <c r="E132" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F132" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G132" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H132" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>100</v>
-      </c>
-      <c r="K132" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C133" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D133" t="n">
         <v>16.7</v>
       </c>
       <c r="E133" t="n">
-        <v>73.3</v>
+        <v>28.3</v>
       </c>
       <c r="F133" t="n">
         <v>16.7</v>
       </c>
       <c r="G133" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J133" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5665,437 +5677,105 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C134" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E134" t="n">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K134" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B135" t="s">
         <v>141</v>
       </c>
       <c r="C135" t="n">
-        <v>16.7</v>
+        <v>71.4</v>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="E135" t="n">
-        <v>5.6</v>
+        <v>64.3</v>
       </c>
       <c r="F135" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="G135" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="H135" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135"/>
+        <v>12.5</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>100</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
-        <v>142</v>
-      </c>
+      <c r="A136"/>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C136" t="n">
-        <v>42.9</v>
+        <v>67.5</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="E136" t="n">
-        <v>42.9</v>
+        <v>52</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="G136" t="n">
-        <v>66.7</v>
+        <v>21.7</v>
       </c>
       <c r="H136" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I136"/>
-      <c r="J136"/>
-      <c r="K136"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>143</v>
-      </c>
-      <c r="B137" t="s">
-        <v>141</v>
-      </c>
-      <c r="C137" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137"/>
-      <c r="J137"/>
-      <c r="K137"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>144</v>
-      </c>
-      <c r="B138" t="s">
-        <v>141</v>
-      </c>
-      <c r="C138" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="D138" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>52</v>
-      </c>
-      <c r="F138" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G138" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>145</v>
-      </c>
-      <c r="B139" t="s">
-        <v>141</v>
-      </c>
-      <c r="C139" t="n">
-        <v>50</v>
-      </c>
-      <c r="D139" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E139" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F139" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G139" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H139" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>75</v>
-      </c>
-      <c r="K139" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>146</v>
-      </c>
-      <c r="B140" t="s">
-        <v>141</v>
-      </c>
-      <c r="C140" t="n">
-        <v>50</v>
-      </c>
-      <c r="D140" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="F140" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G140" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H140" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I140" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J140" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K140" t="n">
-        <v>66.7</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>147</v>
-      </c>
-      <c r="B141" t="s">
-        <v>141</v>
-      </c>
-      <c r="C141" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D141" t="n">
-        <v>25</v>
-      </c>
-      <c r="E141" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F141" t="n">
-        <v>25</v>
-      </c>
-      <c r="G141" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>100</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>148</v>
-      </c>
-      <c r="B142" t="s">
-        <v>141</v>
-      </c>
-      <c r="C142" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H142" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I142" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J142" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K142" t="n">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>149</v>
-      </c>
-      <c r="B143" t="s">
-        <v>141</v>
-      </c>
-      <c r="C143" t="n">
-        <v>45</v>
-      </c>
-      <c r="D143" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E143" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="F143" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G143" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>100</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>150</v>
-      </c>
-      <c r="B144" t="s">
-        <v>141</v>
-      </c>
-      <c r="C144" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="D144" t="n">
-        <v>20</v>
-      </c>
-      <c r="E144" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="F144" t="n">
-        <v>20</v>
-      </c>
-      <c r="G144" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>50</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>151</v>
-      </c>
-      <c r="B145" t="s">
-        <v>141</v>
-      </c>
-      <c r="C145" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="D145" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F145" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G145" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H145" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n">
-        <v>100</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146"/>
-      <c r="B146" t="s">
-        <v>152</v>
-      </c>
-      <c r="C146" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="D146" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="E146" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F146" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G146" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H146" t="n">
-        <v>9</v>
-      </c>
-      <c r="I146" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="K146" t="n">
-        <v>32.2</v>
+        <v>8.9</v>
+      </c>
+      <c r="I136" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K136" t="n">
+        <v>33.5</v>
       </c>
     </row>
   </sheetData>
@@ -6378,31 +6058,31 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="D8" t="n">
-        <v>75.4</v>
+        <v>75.9</v>
       </c>
       <c r="E8" t="n">
         <v>30.9</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="G8" t="n">
         <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>46.9</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>26.2</v>
+        <v>25.5</v>
       </c>
       <c r="K8" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="9">
@@ -6621,28 +6301,28 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -6656,31 +6336,31 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>65.4</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>64.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
@@ -6691,31 +6371,31 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>65.4</v>
+        <v>53.3</v>
       </c>
       <c r="D17" t="n">
-        <v>64.3</v>
+        <v>43.6</v>
       </c>
       <c r="E17" t="n">
-        <v>9.7</v>
+        <v>8.8</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>7.7</v>
+        <v>35.7</v>
       </c>
       <c r="H17" t="n">
-        <v>52.4</v>
+        <v>57.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="18">
@@ -6726,31 +6406,31 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>46.2</v>
       </c>
       <c r="D18" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>46.2</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K18" t="n">
-        <v>-20</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="19">
@@ -6761,31 +6441,31 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="D19" t="n">
-        <v>43.6</v>
+        <v>68.8</v>
       </c>
       <c r="E19" t="n">
-        <v>8.8</v>
+        <v>14.3</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G19" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-28.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="20">
@@ -6796,31 +6476,31 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>46.2</v>
+        <v>64.6</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>61.8</v>
       </c>
       <c r="E20" t="n">
-        <v>5.9</v>
+        <v>16.4</v>
       </c>
       <c r="F20" t="n">
-        <v>66.7</v>
+        <v>45.9</v>
       </c>
       <c r="G20" t="n">
-        <v>46.2</v>
+        <v>8.6</v>
       </c>
       <c r="H20" t="n">
-        <v>66.7</v>
+        <v>51.8</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
-        <v>16.7</v>
+        <v>25.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-15.4</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="21">
@@ -6834,28 +6514,28 @@
         <v>33.3</v>
       </c>
       <c r="D21" t="n">
-        <v>68.8</v>
+        <v>35.7</v>
       </c>
       <c r="E21" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H21" t="n">
         <v>33.3</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>100</v>
-      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>33.3</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="22">
@@ -6863,34 +6543,34 @@
         <v>175</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C22" t="n">
-        <v>64.6</v>
+        <v>55.6</v>
       </c>
       <c r="D22" t="n">
-        <v>61.8</v>
+        <v>49.1</v>
       </c>
       <c r="E22" t="n">
-        <v>16.4</v>
+        <v>6.7</v>
       </c>
       <c r="F22" t="n">
-        <v>45.9</v>
+        <v>66.7</v>
       </c>
       <c r="G22" t="n">
-        <v>8.6</v>
+        <v>17.6</v>
       </c>
       <c r="H22" t="n">
-        <v>51.8</v>
+        <v>18.2</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
       <c r="K22" t="n">
-        <v>13.8</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="23">
@@ -6898,34 +6578,34 @@
         <v>176</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>33.3</v>
+        <v>68.4</v>
       </c>
       <c r="D23" t="n">
-        <v>35.7</v>
+        <v>63.8</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>47.8</v>
       </c>
       <c r="G23" t="n">
-        <v>16.7</v>
+        <v>7.9</v>
       </c>
       <c r="H23" t="n">
-        <v>33.3</v>
+        <v>46.6</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>-16.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="24">
@@ -6933,34 +6613,34 @@
         <v>177</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>55.6</v>
+        <v>45.2</v>
       </c>
       <c r="D24" t="n">
-        <v>49.1</v>
+        <v>54.3</v>
       </c>
       <c r="E24" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="F24" t="n">
-        <v>66.7</v>
+        <v>26.7</v>
       </c>
       <c r="G24" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H24" t="n">
-        <v>18.2</v>
+        <v>52.9</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.8</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="25">
@@ -6968,34 +6648,34 @@
         <v>178</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
-        <v>68.4</v>
+        <v>83.3</v>
       </c>
       <c r="D25" t="n">
-        <v>63.8</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>10.3</v>
+        <v>18.2</v>
       </c>
       <c r="F25" t="n">
-        <v>47.8</v>
+        <v>33.3</v>
       </c>
       <c r="G25" t="n">
-        <v>7.9</v>
+        <v>16.7</v>
       </c>
       <c r="H25" t="n">
-        <v>46.6</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>22.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -7003,34 +6683,34 @@
         <v>179</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>45.2</v>
+        <v>58.3</v>
       </c>
       <c r="D26" t="n">
-        <v>54.3</v>
+        <v>52.1</v>
       </c>
       <c r="E26" t="n">
-        <v>11.1</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="G26" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="H26" t="n">
-        <v>52.9</v>
+        <v>75</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>23.1</v>
+        <v>42.9</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -7038,34 +6718,34 @@
         <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>83.3</v>
+        <v>37.5</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>18.2</v>
       </c>
-      <c r="F27" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H27" t="n">
-        <v>25</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>22.2</v>
-      </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="28">
@@ -7073,34 +6753,34 @@
         <v>181</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>58.3</v>
+        <v>51.4</v>
       </c>
       <c r="D28" t="n">
-        <v>52.1</v>
+        <v>59.4</v>
       </c>
       <c r="E28" t="n">
-        <v>4.3</v>
+        <v>13.2</v>
       </c>
       <c r="F28" t="n">
-        <v>66.7</v>
+        <v>42.1</v>
       </c>
       <c r="G28" t="n">
-        <v>33.3</v>
+        <v>11.4</v>
       </c>
       <c r="H28" t="n">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>42.9</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="29">
@@ -7108,34 +6788,34 @@
         <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>37.5</v>
+        <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
-        <v>4.5</v>
+        <v>28.6</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>18.2</v>
+        <v>45.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -7143,34 +6823,34 @@
         <v>183</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>51.4</v>
+        <v>66.7</v>
       </c>
       <c r="D30" t="n">
-        <v>59.4</v>
+        <v>57.1</v>
       </c>
       <c r="E30" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>11.4</v>
+        <v>16.7</v>
       </c>
       <c r="H30" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>27</v>
+        <v>14.3</v>
       </c>
       <c r="K30" t="n">
-        <v>11.5</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="31">
@@ -7178,34 +6858,34 @@
         <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="n">
-        <v>28.6</v>
+        <v>23.1</v>
       </c>
       <c r="F31" t="n">
+        <v>25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>60</v>
       </c>
-      <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>45.5</v>
+        <v>15.4</v>
       </c>
       <c r="K31" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -7213,34 +6893,34 @@
         <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C32" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>66.7</v>
       </c>
-      <c r="D32" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>40</v>
-      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -7248,34 +6928,34 @@
         <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>23.1</v>
+        <v>9.3</v>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>15.4</v>
+        <v>23.3</v>
       </c>
       <c r="K33" t="n">
-        <v>16.7</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="34">
@@ -7283,34 +6963,34 @@
         <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>33.3</v>
+        <v>62.8</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H34" t="n">
-        <v>66.7</v>
+        <v>48.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="35">
@@ -7318,34 +6998,32 @@
         <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>57.9</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>12.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35"/>
       <c r="G35" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -7353,34 +7031,34 @@
         <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>62.8</v>
+        <v>28.6</v>
       </c>
       <c r="D36" t="n">
-        <v>57.5</v>
+        <v>37.5</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="F36" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>9.3</v>
+        <v>28.6</v>
       </c>
       <c r="H36" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>14.3</v>
       </c>
       <c r="J36" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>2.3</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="37">
@@ -7388,32 +7066,34 @@
         <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>70.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37"/>
+        <v>23.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>50</v>
+      </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="38">
@@ -7421,34 +7101,34 @@
         <v>191</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="D38" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="E38" t="n">
-        <v>9.5</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>28.6</v>
+        <v>6.7</v>
       </c>
       <c r="H38" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="I38" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-28.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="39">
@@ -7456,34 +7136,32 @@
         <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>71.4</v>
+        <v>100</v>
       </c>
       <c r="D39" t="n">
-        <v>70.2</v>
+        <v>80</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F39"/>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -7491,34 +7169,34 @@
         <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C40" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="D40" t="n">
-        <v>66.7</v>
+        <v>49.2</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G40" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="H40" t="n">
-        <v>18.2</v>
+        <v>46.2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7526,29 +7204,31 @@
         <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C41" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>52.9</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41"/>
+        <v>11.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>50</v>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -7559,34 +7239,28 @@
         <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C42" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>49.2</v>
+        <v>7.7</v>
       </c>
       <c r="E42" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42"/>
       <c r="G42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>46.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H42"/>
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="n">
-        <v>20</v>
-      </c>
+      <c r="J42"/>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="43">
@@ -7594,31 +7268,31 @@
         <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="D43" t="n">
-        <v>52.9</v>
+        <v>57.6</v>
       </c>
       <c r="E43" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" t="n">
         <v>11.8</v>
       </c>
-      <c r="F43" t="n">
-        <v>50</v>
-      </c>
-      <c r="G43" t="n">
-        <v>9.1</v>
-      </c>
       <c r="H43" t="n">
-        <v>37.5</v>
+        <v>23.1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>7.7</v>
+        <v>23.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -7629,60 +7303,66 @@
         <v>197</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D44" t="n">
-        <v>7.7</v>
+        <v>63.2</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44"/>
+        <v>7.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16.7</v>
+      </c>
       <c r="G44" t="n">
-        <v>100</v>
-      </c>
-      <c r="H44"/>
+        <v>11.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28.6</v>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44"/>
+      <c r="J44" t="n">
+        <v>10.5</v>
+      </c>
       <c r="K44" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C45" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>57.6</v>
+        <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
         <v>20</v>
       </c>
-      <c r="G45" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>23.1</v>
-      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -7690,51 +7370,51 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C46" t="n">
-        <v>55.6</v>
+        <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>63.2</v>
+        <v>57.8</v>
       </c>
       <c r="E46" t="n">
-        <v>7.1</v>
+        <v>13.6</v>
       </c>
       <c r="F46" t="n">
-        <v>16.7</v>
+        <v>41.7</v>
       </c>
       <c r="G46" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="H46" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B47" t="s">
         <v>84</v>
       </c>
-      <c r="B47" t="s">
-        <v>72</v>
-      </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>87.5</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -7746,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -7760,275 +7440,279 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C48" t="n">
-        <v>63</v>
+        <v>52.9</v>
       </c>
       <c r="D48" t="n">
-        <v>57.8</v>
+        <v>60.8</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6</v>
+        <v>16.7</v>
       </c>
       <c r="F48" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="G48" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="H48" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>23.5</v>
+        <v>32.1</v>
       </c>
       <c r="K48" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="B49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C49" t="n">
-        <v>100</v>
+        <v>69.2</v>
       </c>
       <c r="D49" t="n">
-        <v>100</v>
-      </c>
-      <c r="E49"/>
+        <v>74.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>28.6</v>
+      </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>57.9</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>87.5</v>
+        <v>61.7</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>66.7</v>
+        <v>41.2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C51" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="D51" t="n">
-        <v>60.8</v>
+        <v>66.7</v>
       </c>
       <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>80</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K51" t="n">
         <v>16.7</v>
-      </c>
-      <c r="F51" t="n">
-        <v>40</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H51" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C52" t="n">
-        <v>69.2</v>
+        <v>14.3</v>
       </c>
       <c r="D52" t="n">
-        <v>74.7</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>28.6</v>
       </c>
-      <c r="F52" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H52" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>19.3</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53"/>
+        <v>13.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>50</v>
+      </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C54" t="n">
-        <v>55</v>
+        <v>61.5</v>
       </c>
       <c r="D54" t="n">
-        <v>62</v>
+        <v>63.2</v>
       </c>
       <c r="E54" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>15.4</v>
       </c>
       <c r="H54" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C55" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="D55" t="n">
-        <v>66.7</v>
+        <v>70.4</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H55" t="n">
-        <v>80</v>
+        <v>34.8</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
         <v>16.7</v>
@@ -8036,40 +7720,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="D56" t="n">
-        <v>40</v>
+        <v>65.3</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56"/>
+        <v>31.4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>25</v>
+      </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-50</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B57" t="s">
         <v>102</v>
@@ -8078,313 +7764,313 @@
         <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>53.6</v>
+        <v>63.2</v>
       </c>
       <c r="E57" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="F57" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>26.7</v>
+        <v>37.5</v>
       </c>
       <c r="K57" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B58" t="s">
         <v>102</v>
       </c>
       <c r="C58" t="n">
-        <v>61.5</v>
+        <v>46.4</v>
       </c>
       <c r="D58" t="n">
-        <v>63.2</v>
+        <v>53.9</v>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="F58" t="n">
-        <v>30.8</v>
+        <v>36.4</v>
       </c>
       <c r="G58" t="n">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="H58" t="n">
-        <v>66.7</v>
+        <v>35.3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B59" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C59" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D59" t="n">
-        <v>70.4</v>
+        <v>41.2</v>
       </c>
       <c r="E59" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="H59" t="n">
-        <v>34.8</v>
+        <v>33.3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K59" t="n">
-        <v>16.7</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C60" t="n">
-        <v>58.3</v>
+        <v>14.3</v>
       </c>
       <c r="D60" t="n">
-        <v>65.3</v>
+        <v>44.1</v>
       </c>
       <c r="E60" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H60" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K60" t="n">
-        <v>8.3</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>63.2</v>
+        <v>38.9</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
         <v>66.7</v>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>50</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C62" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="D62" t="n">
-        <v>53.9</v>
+        <v>57.9</v>
       </c>
       <c r="E62" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="H62" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>23.7</v>
+        <v>28.6</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
         <v>121</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G63" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="H63" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-20</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
         <v>121</v>
       </c>
       <c r="C64" t="n">
-        <v>14.3</v>
+        <v>57.1</v>
       </c>
       <c r="D64" t="n">
-        <v>44.1</v>
+        <v>57.5</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="F64" t="n">
-        <v>33.3</v>
+        <v>51.9</v>
       </c>
       <c r="G64" t="n">
-        <v>28.6</v>
+        <v>20.8</v>
       </c>
       <c r="H64" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B65" t="s">
         <v>121</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>38.9</v>
+        <v>59.3</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G65" t="n">
-        <v>66.7</v>
+        <v>7.1</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
         <v>121</v>
@@ -8393,227 +8079,225 @@
         <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G66" t="n">
-        <v>25</v>
+        <v>6.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="K66" t="n">
-        <v>-25</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>121</v>
       </c>
       <c r="C67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>41.4</v>
+        <v>87.5</v>
       </c>
       <c r="E67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" t="n">
+        <v>25</v>
+      </c>
+      <c r="J67" t="n">
         <v>33.3</v>
       </c>
-      <c r="G67" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H67" t="n">
-        <v>50</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>14.3</v>
-      </c>
       <c r="K67" t="n">
-        <v>-16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
         <v>121</v>
       </c>
       <c r="C68" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>57.5</v>
+        <v>20</v>
       </c>
       <c r="E68" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F68" t="n">
-        <v>51.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F68"/>
       <c r="G68" t="n">
-        <v>20.8</v>
+        <v>66.7</v>
       </c>
       <c r="H68" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>8.4</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B69" t="s">
         <v>121</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="D69" t="n">
-        <v>59.3</v>
+        <v>63.4</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>40</v>
+        <v>27.3</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>8.3</v>
+        <v>27.3</v>
       </c>
       <c r="K69" t="n">
-        <v>7.2</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B70" t="s">
         <v>121</v>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D70" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E70" t="n">
-        <v>10.2</v>
+        <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>29.4</v>
+        <v>50</v>
       </c>
       <c r="K70" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
         <v>121</v>
       </c>
       <c r="C71" t="n">
+        <v>40</v>
+      </c>
+      <c r="D71" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F71" t="n">
         <v>100</v>
       </c>
-      <c r="D71" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>33.3</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>66.7</v>
+        <v>9.1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -8622,318 +8306,180 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>-66.7</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B73" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C73" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>63.4</v>
+        <v>39.1</v>
       </c>
       <c r="E73" t="n">
-        <v>17.6</v>
+        <v>6.7</v>
       </c>
       <c r="F73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H73" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>27.8</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C74" t="n">
         <v>66.7</v>
       </c>
       <c r="D74" t="n">
-        <v>80</v>
+        <v>53.3</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>7.1</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C75" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D75" t="n">
-        <v>31.6</v>
+        <v>55.2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F75" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="G75" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K75" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B76" t="s">
         <v>141</v>
       </c>
       <c r="C76" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="D76" t="n">
-        <v>57.1</v>
+        <v>59.2</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76"/>
+        <v>16</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
       <c r="G76" t="n">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="H76" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
-        <v>223</v>
-      </c>
+      <c r="A77"/>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C77" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="D77" t="n">
-        <v>39.1</v>
+        <v>57.7</v>
       </c>
       <c r="E77" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G77" t="n">
-        <v>33.3</v>
+        <v>13.8</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>43.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.3</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>224</v>
-      </c>
-      <c r="B78" t="s">
-        <v>141</v>
-      </c>
-      <c r="C78" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D78" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H78" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K78" t="n">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>225</v>
-      </c>
-      <c r="B79" t="s">
-        <v>141</v>
-      </c>
-      <c r="C79" t="n">
-        <v>52</v>
-      </c>
-      <c r="D79" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8</v>
-      </c>
-      <c r="H79" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I79" t="n">
-        <v>4</v>
-      </c>
-      <c r="J79" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>226</v>
-      </c>
-      <c r="B80" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="D80" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="E80" t="n">
-        <v>16</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H80" t="n">
-        <v>50</v>
-      </c>
-      <c r="I80" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J80" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81"/>
-      <c r="B81" t="s">
-        <v>152</v>
-      </c>
-      <c r="C81" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="D81" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E81" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F81" t="n">
-        <v>30</v>
-      </c>
-      <c r="G81" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H81" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J81" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K81" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -180,6 +180,9 @@
     <t xml:space="preserve">Brandon McMurray</t>
   </si>
   <si>
+    <t xml:space="preserve">Brody Nguyen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Declan Shannon</t>
   </si>
   <si>
@@ -198,6 +201,12 @@
     <t xml:space="preserve">John Dykyj</t>
   </si>
   <si>
+    <t xml:space="preserve">Jueun Chung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Meade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Justin White</t>
   </si>
   <si>
@@ -210,9 +219,15 @@
     <t xml:space="preserve">Matt Underwood</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathan Smid</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nicolas Velocci</t>
   </si>
   <si>
+    <t xml:space="preserve">Nikolas Proksel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quinten Shannon</t>
   </si>
   <si>
@@ -285,6 +300,9 @@
     <t xml:space="preserve">Cole Smart</t>
   </si>
   <si>
+    <t xml:space="preserve">Declan Uniac</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jai Pawa</t>
   </si>
   <si>
@@ -303,6 +321,9 @@
     <t xml:space="preserve">Max Todd</t>
   </si>
   <si>
+    <t xml:space="preserve">Myles Hazen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nico Valvo</t>
   </si>
   <si>
@@ -354,9 +375,6 @@
     <t xml:space="preserve">Nathaniel King</t>
   </si>
   <si>
-    <t xml:space="preserve">Neurnberger</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parker McLean</t>
   </si>
   <si>
@@ -573,6 +591,9 @@
     <t xml:space="preserve">Alex VanRaay</t>
   </si>
   <si>
+    <t xml:space="preserve">Devan Fenwick</t>
+  </si>
+  <si>
     <t xml:space="preserve">Erik Lopez</t>
   </si>
   <si>
@@ -585,6 +606,9 @@
     <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
   </si>
   <si>
+    <t xml:space="preserve">Premnath Nayak</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sam McMillan</t>
   </si>
   <si>
@@ -592,6 +616,9 @@
   </si>
   <si>
     <t xml:space="preserve">Taio Fotiou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Nguyen</t>
   </si>
   <si>
     <t xml:space="preserve">Kenny Leung</t>
@@ -748,8 +775,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K136" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K142" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K142"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -768,8 +795,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K77" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K80" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K80"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2484,25 +2511,25 @@
         <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>66.7</v>
+        <v>36.4</v>
       </c>
       <c r="H41" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
         <v>50</v>
@@ -2554,22 +2581,22 @@
         <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>27.5</v>
+        <v>50</v>
       </c>
       <c r="F43" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
         <v>100</v>
@@ -2589,31 +2616,31 @@
         <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2624,31 +2651,31 @@
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>66.7</v>
+        <v>47.1</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E45" t="n">
-        <v>41.7</v>
+        <v>30.4</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G45" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K45" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="46">
@@ -2659,31 +2686,31 @@
         <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>67.5</v>
+        <v>41.7</v>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G46" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -2694,24 +2721,32 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>76.9</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47"/>
+        <v>16.7</v>
+      </c>
+      <c r="G47" t="n">
+        <v>36.4</v>
+      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
+      <c r="I47" t="n">
+        <v>50</v>
+      </c>
+      <c r="J47" t="n">
+        <v>25</v>
+      </c>
+      <c r="K47" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
@@ -2721,32 +2756,24 @@
         <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>57.7</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48"/>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>45.5</v>
-      </c>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
@@ -2756,31 +2783,31 @@
         <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>54.8</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>39.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -2791,31 +2818,31 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D50" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>42.3</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="G50" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
@@ -2826,31 +2853,31 @@
         <v>53</v>
       </c>
       <c r="C51" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G51" t="n">
         <v>66.7</v>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>25</v>
-      </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2861,31 +2888,31 @@
         <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2896,31 +2923,31 @@
         <v>53</v>
       </c>
       <c r="C53" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I53" t="n">
         <v>66.7</v>
       </c>
-      <c r="D53" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E53" t="n">
-        <v>50</v>
-      </c>
-      <c r="F53" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G53" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>20</v>
-      </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="54">
@@ -2931,31 +2958,31 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="D54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>-33.6</v>
+        <v>66.7</v>
       </c>
       <c r="F54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -2966,31 +2993,31 @@
         <v>53</v>
       </c>
       <c r="C55" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="D55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G55" t="n">
         <v>38.5</v>
       </c>
-      <c r="E55" t="n">
-        <v>24</v>
-      </c>
-      <c r="F55" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>26.7</v>
-      </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I55" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -2998,16 +3025,16 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C56" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3019,115 +3046,115 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C57" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D57" t="n">
         <v>16.7</v>
       </c>
       <c r="E57" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
         <v>16.7</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I57" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C58" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C59" t="n">
-        <v>66.7</v>
+        <v>41.2</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E59" t="n">
+        <v>-8.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>50</v>
+      </c>
+      <c r="G59" t="n">
         <v>46.7</v>
       </c>
-      <c r="F59" t="n">
-        <v>20</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20</v>
-      </c>
       <c r="H59" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J59" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3135,60 +3162,60 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C60" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="E60" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="G60" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>37.5</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" t="s">
         <v>74</v>
       </c>
-      <c r="B61" t="s">
-        <v>69</v>
-      </c>
       <c r="C61" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3197,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="62">
@@ -3208,34 +3235,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E62" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="F62" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G62" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63">
@@ -3243,16 +3270,16 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3264,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J63" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="64">
@@ -3278,31 +3305,31 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C64" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>20</v>
+      </c>
+      <c r="E64" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>20</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>25</v>
+      </c>
+      <c r="J64" t="n">
         <v>75</v>
-      </c>
-      <c r="D64" t="n">
-        <v>50</v>
-      </c>
-      <c r="E64" t="n">
-        <v>25</v>
-      </c>
-      <c r="F64" t="n">
-        <v>50</v>
-      </c>
-      <c r="G64" t="n">
-        <v>25</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>50</v>
-      </c>
-      <c r="J64" t="n">
-        <v>50</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3313,28 +3340,34 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C65" t="n">
-        <v>80</v>
-      </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>55.6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50</v>
+      </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3342,34 +3375,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C66" t="n">
-        <v>78.6</v>
+        <v>55.6</v>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="n">
-        <v>67.5</v>
+        <v>43.1</v>
       </c>
       <c r="F66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="G66" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="H66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>100</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3377,34 +3410,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C67" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F67" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" t="n">
+        <v>40</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>50</v>
+      </c>
+      <c r="J67" t="n">
+        <v>50</v>
+      </c>
+      <c r="K67" t="n">
         <v>100</v>
-      </c>
-      <c r="D67" t="n">
-        <v>25</v>
-      </c>
-      <c r="E67" t="n">
-        <v>75</v>
-      </c>
-      <c r="F67" t="n">
-        <v>25</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>100</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="68">
@@ -3412,34 +3445,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C68" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="F68" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3447,22 +3480,22 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C69" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D69" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E69" t="n">
-        <v>-8.3</v>
+        <v>25</v>
       </c>
       <c r="F69" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3471,10 +3504,10 @@
         <v>50</v>
       </c>
       <c r="J69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3482,203 +3515,203 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C70" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="D70" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>38.5</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
       <c r="G70" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K70" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C71" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H71" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I71" t="n">
         <v>100</v>
       </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>50</v>
-      </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C72" t="n">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="D72" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="E72" t="n">
-        <v>36.5</v>
+        <v>75</v>
       </c>
       <c r="F72" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="G72" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="J72" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C73" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D73" t="n">
+        <v>20</v>
+      </c>
+      <c r="E73" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F73" t="n">
+        <v>20</v>
+      </c>
+      <c r="G73" t="n">
         <v>75</v>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>75</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C74" t="n">
-        <v>80.8</v>
+        <v>66.7</v>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="E74" t="n">
-        <v>68.3</v>
+        <v>-8.3</v>
       </c>
       <c r="F74" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="G74" t="n">
-        <v>9.1</v>
+        <v>33.3</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" t="s">
         <v>89</v>
       </c>
-      <c r="B75" t="s">
-        <v>84</v>
-      </c>
       <c r="C75" t="n">
-        <v>58.3</v>
+        <v>64</v>
       </c>
       <c r="D75" t="n">
-        <v>9.1</v>
+        <v>31.2</v>
       </c>
       <c r="E75" t="n">
-        <v>49.2</v>
+        <v>32.8</v>
       </c>
       <c r="F75" t="n">
-        <v>9.1</v>
+        <v>31.2</v>
       </c>
       <c r="G75" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="H75" t="n">
-        <v>16.7</v>
+        <v>7.7</v>
       </c>
       <c r="I75" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
@@ -3686,34 +3719,28 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C76" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="D76" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E76" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F76" t="n">
-        <v>41.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
       <c r="G76" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J76" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -3721,34 +3748,34 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C77" t="n">
-        <v>71.4</v>
+        <v>70.8</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>71.4</v>
+        <v>45.8</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G77" t="n">
-        <v>40</v>
+        <v>18.2</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="78">
@@ -3756,34 +3783,34 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C78" t="n">
-        <v>47.6</v>
+        <v>75</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>27.6</v>
+        <v>75</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J78" t="n">
         <v>33.3</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="79">
@@ -3791,34 +3818,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C79" t="n">
-        <v>37.5</v>
+        <v>82.1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E79" t="n">
-        <v>37.5</v>
+        <v>73</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G79" t="n">
-        <v>66.7</v>
+        <v>8.3</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J79" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="80">
@@ -3826,34 +3853,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C80" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E80" t="n">
-        <v>100</v>
+        <v>49.2</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G80" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I80" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81">
@@ -3861,31 +3888,31 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C81" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>43.3</v>
+        <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>50</v>
       </c>
       <c r="J81" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>50</v>
@@ -3896,34 +3923,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C82" t="n">
-        <v>59.1</v>
+        <v>73.3</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="E82" t="n">
-        <v>59.1</v>
+        <v>31.6</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G82" t="n">
-        <v>15.4</v>
+        <v>18.8</v>
       </c>
       <c r="H82" t="n">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="I82" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3931,34 +3958,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>71.4</v>
       </c>
       <c r="D83" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>48.7</v>
+        <v>71.4</v>
       </c>
       <c r="F83" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H83" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J83" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84">
@@ -3966,34 +3993,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C84" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="D84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E84" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H84" t="n">
         <v>9.1</v>
       </c>
-      <c r="E84" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="F84" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>20</v>
-      </c>
       <c r="I84" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J84" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K84" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4001,139 +4028,139 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C85" t="n">
-        <v>64</v>
+        <v>37.5</v>
       </c>
       <c r="D85" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>54.9</v>
+        <v>37.5</v>
       </c>
       <c r="F85" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1</v>
+        <v>66.7</v>
       </c>
       <c r="H85" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="K85" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C87" t="n">
-        <v>72.7</v>
+        <v>60</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E87" t="n">
-        <v>72.7</v>
+        <v>43.3</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G87" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I87" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J87" t="n">
         <v>50</v>
       </c>
       <c r="K87" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C88" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D88" t="n">
-        <v>8.7</v>
+        <v>33.3</v>
       </c>
       <c r="E88" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="F88" t="n">
-        <v>8.7</v>
+        <v>33.3</v>
       </c>
       <c r="G88" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="H88" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
@@ -4141,34 +4168,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C89" t="n">
-        <v>46.7</v>
+        <v>59.1</v>
       </c>
       <c r="D89" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>59.1</v>
       </c>
       <c r="F89" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J89" t="n">
-        <v>62.5</v>
+        <v>12.5</v>
       </c>
       <c r="K89" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -4176,34 +4203,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>88.9</v>
+        <v>73.3</v>
       </c>
       <c r="D90" t="n">
-        <v>13.3</v>
+        <v>24</v>
       </c>
       <c r="E90" t="n">
-        <v>75.6</v>
+        <v>49.3</v>
       </c>
       <c r="F90" t="n">
-        <v>13.3</v>
+        <v>24</v>
       </c>
       <c r="G90" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="H90" t="n">
-        <v>14.3</v>
+        <v>7.7</v>
       </c>
       <c r="I90" t="n">
-        <v>20</v>
+        <v>55.6</v>
       </c>
       <c r="J90" t="n">
-        <v>60</v>
+        <v>22.2</v>
       </c>
       <c r="K90" t="n">
-        <v>100</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="91">
@@ -4211,34 +4238,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C91" t="n">
-        <v>88.9</v>
+        <v>81.8</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E91" t="n">
-        <v>88.9</v>
+        <v>72.7</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I91" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K91" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
@@ -4246,60 +4273,60 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C92" t="n">
-        <v>78.6</v>
+        <v>65.6</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E92" t="n">
-        <v>78.6</v>
+        <v>57.9</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G92" t="n">
-        <v>9.1</v>
+        <v>8.7</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I92" t="n">
-        <v>85.7</v>
+        <v>53.8</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C93" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D93" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F93" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4308,77 +4335,77 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C94" t="n">
-        <v>64.3</v>
+        <v>62.5</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>64.3</v>
+        <v>62.5</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>11.1</v>
+        <v>18.2</v>
       </c>
       <c r="H94" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="I94" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="J94" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="K94" t="n">
-        <v>60</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" t="s">
         <v>109</v>
       </c>
-      <c r="B95" t="s">
-        <v>102</v>
-      </c>
       <c r="C95" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="G95" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I95" t="n">
         <v>80</v>
       </c>
-      <c r="D95" t="n">
-        <v>25</v>
-      </c>
-      <c r="E95" t="n">
-        <v>55</v>
-      </c>
-      <c r="F95" t="n">
-        <v>25</v>
-      </c>
-      <c r="G95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>57.1</v>
-      </c>
       <c r="J95" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>14.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -4386,34 +4413,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C96" t="n">
-        <v>85.7</v>
+        <v>46.7</v>
       </c>
       <c r="D96" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="E96" t="n">
-        <v>60.7</v>
+        <v>20</v>
       </c>
       <c r="F96" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="G96" t="n">
-        <v>25</v>
+        <v>18.2</v>
       </c>
       <c r="H96" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="97">
@@ -4421,34 +4448,34 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C97" t="n">
-        <v>43.8</v>
+        <v>88.9</v>
       </c>
       <c r="D97" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="E97" t="n">
-        <v>34.7</v>
+        <v>75.6</v>
       </c>
       <c r="F97" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="G97" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H97" t="n">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I97" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J97" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98">
@@ -4456,28 +4483,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C98" t="n">
-        <v>100</v>
-      </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
+        <v>88.9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>88.9</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99">
@@ -4485,57 +4518,69 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
-      </c>
-      <c r="C99"/>
+        <v>109</v>
+      </c>
+      <c r="C99" t="n">
+        <v>78.6</v>
+      </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
-      <c r="E99"/>
+      <c r="E99" t="n">
+        <v>78.6</v>
+      </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
-      <c r="G99"/>
+      <c r="G99" t="n">
+        <v>9.1</v>
+      </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99"/>
-      <c r="J99"/>
-      <c r="K99"/>
+      <c r="I99" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C100" t="n">
-        <v>92.6</v>
+        <v>57.1</v>
       </c>
       <c r="D100" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="E100" t="n">
-        <v>87.3</v>
+        <v>48</v>
       </c>
       <c r="F100" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="G100" t="n">
-        <v>7.7</v>
+        <v>40</v>
       </c>
       <c r="H100" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I100" t="n">
-        <v>64.3</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -4543,34 +4588,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C101" t="n">
-        <v>56.2</v>
+        <v>64.3</v>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>43.7</v>
+        <v>64.3</v>
       </c>
       <c r="F101" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H101" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="I101" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J101" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
@@ -4578,34 +4623,34 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C102" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="E102" t="n">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="F102" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="G102" t="n">
-        <v>23.1</v>
+        <v>11.1</v>
       </c>
       <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J102" t="n">
         <v>14.3</v>
       </c>
-      <c r="I102" t="n">
-        <v>40</v>
-      </c>
-      <c r="J102" t="n">
-        <v>40</v>
-      </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="103">
@@ -4613,34 +4658,34 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C103" t="n">
-        <v>71.4</v>
+        <v>85.7</v>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E103" t="n">
-        <v>61.4</v>
+        <v>60.7</v>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H103" t="n">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="I103" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="J103" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="K103" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4648,34 +4693,34 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C104" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
       <c r="D104" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="E104" t="n">
-        <v>38.9</v>
+        <v>34.7</v>
       </c>
       <c r="F104" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="G104" t="n">
+        <v>25</v>
+      </c>
+      <c r="H104" t="n">
         <v>28.6</v>
       </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
       <c r="I104" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J104" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -4683,34 +4728,28 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C105" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="D105" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="E105" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="F105" t="n">
-        <v>10.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
       <c r="G105" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>8.3</v>
+        <v>100</v>
       </c>
       <c r="K105" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4718,66 +4757,66 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>66.7</v>
+        <v>92.6</v>
       </c>
       <c r="D106" t="n">
-        <v>14.3</v>
+        <v>5.3</v>
       </c>
       <c r="E106" t="n">
-        <v>52.4</v>
+        <v>87.3</v>
       </c>
       <c r="F106" t="n">
-        <v>14.3</v>
+        <v>5.3</v>
       </c>
       <c r="G106" t="n">
-        <v>35.7</v>
+        <v>7.7</v>
       </c>
       <c r="H106" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="I106" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="J106" t="n">
-        <v>33.3</v>
+        <v>21.4</v>
       </c>
       <c r="K106" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C107" t="n">
-        <v>55.6</v>
+        <v>56.2</v>
       </c>
       <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="F107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H107" t="n">
         <v>22.2</v>
       </c>
-      <c r="E107" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F107" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G107" t="n">
+      <c r="I107" t="n">
         <v>42.9</v>
       </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>100</v>
-      </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4785,104 +4824,104 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C108" t="n">
-        <v>80.8</v>
+        <v>75</v>
       </c>
       <c r="D108" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="F108" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>36</v>
+        <v>23.1</v>
       </c>
       <c r="H108" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="I108" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="J108" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C109" t="n">
-        <v>91.7</v>
+        <v>71.4</v>
       </c>
       <c r="D109" t="n">
-        <v>50</v>
+        <v>9.7</v>
       </c>
       <c r="E109" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="F109" t="n">
-        <v>50</v>
+        <v>9.7</v>
       </c>
       <c r="G109" t="n">
-        <v>21.4</v>
+        <v>3</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I109" t="n">
-        <v>28.6</v>
+        <v>72.7</v>
       </c>
       <c r="J109" t="n">
-        <v>42.9</v>
+        <v>18.2</v>
       </c>
       <c r="K109" t="n">
-        <v>71.4</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E110" t="n">
-        <v>60</v>
+        <v>38.9</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4890,72 +4929,72 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C111" t="n">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="D111" t="n">
-        <v>20</v>
+        <v>10.3</v>
       </c>
       <c r="E111" t="n">
-        <v>80</v>
+        <v>58.5</v>
       </c>
       <c r="F111" t="n">
-        <v>20</v>
+        <v>10.3</v>
       </c>
       <c r="G111" t="n">
-        <v>28.6</v>
+        <v>12</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I111" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>126</v>
+      </c>
+      <c r="B112" t="s">
         <v>127</v>
       </c>
-      <c r="B112" t="s">
-        <v>121</v>
-      </c>
       <c r="C112" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D112" t="n">
-        <v>8.3</v>
+        <v>14.3</v>
       </c>
       <c r="E112" t="n">
-        <v>66.7</v>
+        <v>52.4</v>
       </c>
       <c r="F112" t="n">
-        <v>8.3</v>
+        <v>14.3</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I112" t="n">
         <v>50</v>
       </c>
       <c r="J112" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K112" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="113">
@@ -4963,31 +5002,31 @@
         <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C113" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F113" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
         <v>100</v>
       </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>100</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
       <c r="J113" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4998,34 +5037,34 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C114" t="n">
-        <v>83.3</v>
+        <v>80.8</v>
       </c>
       <c r="D114" t="n">
-        <v>28.6</v>
+        <v>18.2</v>
       </c>
       <c r="E114" t="n">
-        <v>54.7</v>
+        <v>62.6</v>
       </c>
       <c r="F114" t="n">
-        <v>28.6</v>
+        <v>18.2</v>
       </c>
       <c r="G114" t="n">
-        <v>16.7</v>
+        <v>36</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I114" t="n">
-        <v>33.3</v>
+        <v>62.5</v>
       </c>
       <c r="J114" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K114" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115">
@@ -5033,34 +5072,34 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C115" t="n">
-        <v>57.1</v>
+        <v>91.7</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E115" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G115" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="H115" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>60</v>
+        <v>28.6</v>
       </c>
       <c r="J115" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="K115" t="n">
-        <v>60</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="116">
@@ -5068,34 +5107,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C116" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D116" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>32.5</v>
+        <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J116" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5103,25 +5142,25 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C117" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D117" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="E117" t="n">
-        <v>53.6</v>
+        <v>80</v>
       </c>
       <c r="F117" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="G117" t="n">
-        <v>46.7</v>
+        <v>28.6</v>
       </c>
       <c r="H117" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>66.7</v>
@@ -5130,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5138,34 +5177,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C118" t="n">
-        <v>84.6</v>
+        <v>75</v>
       </c>
       <c r="D118" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="E118" t="n">
-        <v>70.3</v>
+        <v>66.7</v>
       </c>
       <c r="F118" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="G118" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="K118" t="n">
-        <v>12.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="119">
@@ -5173,34 +5212,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C119" t="n">
-        <v>68.6</v>
+        <v>100</v>
       </c>
       <c r="D119" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="F119" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="K119" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5208,34 +5247,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C120" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E120" t="n">
-        <v>50</v>
+        <v>54.7</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="121">
@@ -5243,34 +5282,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C121" t="n">
-        <v>90.9</v>
+        <v>57.1</v>
       </c>
       <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>25</v>
+      </c>
+      <c r="H121" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>60</v>
+      </c>
+      <c r="J121" t="n">
         <v>20</v>
       </c>
-      <c r="E121" t="n">
-        <v>70.9</v>
-      </c>
-      <c r="F121" t="n">
-        <v>20</v>
-      </c>
-      <c r="G121" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J121" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K121" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122">
@@ -5278,34 +5317,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C122" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D122" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="E122" t="n">
-        <v>17.1</v>
+        <v>32.5</v>
       </c>
       <c r="F122" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="G122" t="n">
-        <v>33.3</v>
+        <v>17.6</v>
       </c>
       <c r="H122" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J122" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K122" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123">
@@ -5313,34 +5352,34 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C123" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D123" t="n">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="E123" t="n">
-        <v>73.3</v>
+        <v>53.6</v>
       </c>
       <c r="F123" t="n">
-        <v>16.7</v>
+        <v>21.4</v>
       </c>
       <c r="G123" t="n">
-        <v>18.2</v>
+        <v>46.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I123" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="J123" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="124">
@@ -5348,34 +5387,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>100</v>
+        <v>84.6</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E124" t="n">
-        <v>100</v>
+        <v>70.3</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="J124" t="n">
-        <v>33.3</v>
+        <v>18.8</v>
       </c>
       <c r="K124" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="125">
@@ -5383,331 +5422,331 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C125" t="n">
+        <v>68.6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G125" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I125" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J125" t="n">
         <v>16.7</v>
       </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G125" t="n">
-        <v>50</v>
-      </c>
-      <c r="H125" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I125"/>
-      <c r="J125"/>
-      <c r="K125"/>
+      <c r="K125" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C126" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I126"/>
-      <c r="J126"/>
-      <c r="K126"/>
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>50</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C127" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="D127" t="n">
+        <v>20</v>
+      </c>
+      <c r="E127" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>20</v>
+      </c>
+      <c r="G127" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J127" t="n">
         <v>33.3</v>
       </c>
-      <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127"/>
-      <c r="J127"/>
-      <c r="K127"/>
+      <c r="K127" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C128" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="D128" t="n">
-        <v>9.1</v>
+        <v>42.9</v>
       </c>
       <c r="E128" t="n">
-        <v>52</v>
+        <v>17.1</v>
       </c>
       <c r="F128" t="n">
-        <v>9.1</v>
+        <v>42.9</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I128" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K128" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C129" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D129" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E129" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G129" t="n">
         <v>18.2</v>
       </c>
-      <c r="E129" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F129" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G129" t="n">
-        <v>42.9</v>
-      </c>
       <c r="H129" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K129" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C130" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D130" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>26.9</v>
+        <v>100</v>
       </c>
       <c r="F130" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J130" t="n">
         <v>33.3</v>
       </c>
       <c r="K130" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
+        <v>146</v>
+      </c>
+      <c r="B131" t="s">
         <v>147</v>
       </c>
-      <c r="B131" t="s">
-        <v>141</v>
-      </c>
       <c r="C131" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G131" t="n">
+        <v>50</v>
+      </c>
+      <c r="H131" t="n">
         <v>66.7</v>
       </c>
-      <c r="D131" t="n">
-        <v>25</v>
-      </c>
-      <c r="E131" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F131" t="n">
-        <v>25</v>
-      </c>
-      <c r="G131" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>100</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
+      <c r="I131"/>
+      <c r="J131"/>
+      <c r="K131"/>
     </row>
     <row r="132">
       <c r="A132" t="s">
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C132" t="n">
-        <v>61.5</v>
+        <v>42.9</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>61.5</v>
+        <v>42.9</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
       <c r="H132" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I132" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J132" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K132" t="n">
-        <v>42.9</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I132"/>
+      <c r="J132"/>
+      <c r="K132"/>
     </row>
     <row r="133">
       <c r="A133" t="s">
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C133" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="D133" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="F133" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
-      <c r="I133" t="n">
-        <v>100</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
+      <c r="I133"/>
+      <c r="J133"/>
+      <c r="K133"/>
     </row>
     <row r="134">
       <c r="A134" t="s">
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C134" t="n">
-        <v>71.4</v>
+        <v>61.1</v>
       </c>
       <c r="D134" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="E134" t="n">
-        <v>51.4</v>
+        <v>52</v>
       </c>
       <c r="F134" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="G134" t="n">
-        <v>33.3</v>
+        <v>8.3</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J134" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="135">
@@ -5715,67 +5754,277 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C135" t="n">
+        <v>50</v>
+      </c>
+      <c r="D135" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F135" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H135" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>75</v>
+      </c>
+      <c r="K135" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>152</v>
+      </c>
+      <c r="B136" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136" t="n">
+        <v>50</v>
+      </c>
+      <c r="D136" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F136" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I136" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J136" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>153</v>
+      </c>
+      <c r="B137" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D137" t="n">
+        <v>25</v>
+      </c>
+      <c r="E137" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F137" t="n">
+        <v>25</v>
+      </c>
+      <c r="G137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>100</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>154</v>
+      </c>
+      <c r="B138" t="s">
+        <v>147</v>
+      </c>
+      <c r="C138" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I138" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K138" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>155</v>
+      </c>
+      <c r="B139" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" t="n">
+        <v>45</v>
+      </c>
+      <c r="D139" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E139" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G139" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>100</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>156</v>
+      </c>
+      <c r="B140" t="s">
+        <v>147</v>
+      </c>
+      <c r="C140" t="n">
         <v>71.4</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D140" t="n">
+        <v>20</v>
+      </c>
+      <c r="E140" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>20</v>
+      </c>
+      <c r="G140" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>50</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>157</v>
+      </c>
+      <c r="B141" t="s">
+        <v>147</v>
+      </c>
+      <c r="C141" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D141" t="n">
         <v>7.1</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E141" t="n">
         <v>64.3</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F141" t="n">
         <v>7.1</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G141" t="n">
         <v>18.2</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H141" t="n">
         <v>12.5</v>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
         <v>100</v>
       </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136"/>
-      <c r="B136" t="s">
-        <v>152</v>
-      </c>
-      <c r="C136" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="D136" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="E136" t="n">
-        <v>52</v>
-      </c>
-      <c r="F136" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="G136" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H136" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I136" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="J136" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="K136" t="n">
-        <v>33.5</v>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142"/>
+      <c r="B142" t="s">
+        <v>158</v>
+      </c>
+      <c r="C142" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F142" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G142" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H142" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="I142" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="J142" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>34.5</v>
       </c>
     </row>
   </sheetData>
@@ -5807,22 +6056,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -5831,13 +6080,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
@@ -5912,7 +6161,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -5947,7 +6196,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5982,7 +6231,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6017,7 +6266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6052,7 +6301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6157,7 +6406,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6192,7 +6441,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6225,7 +6474,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6260,7 +6509,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -6295,7 +6544,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -6330,7 +6579,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -6365,7 +6614,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -6400,7 +6649,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -6435,7 +6684,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -6470,7 +6719,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -6505,7 +6754,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -6540,7 +6789,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
@@ -6575,7 +6824,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -6610,7 +6859,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
@@ -6645,7 +6894,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -6680,7 +6929,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -6715,7 +6964,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -6750,7 +6999,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
@@ -6785,7 +7034,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -6820,7 +7069,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
@@ -6855,7 +7104,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
@@ -6890,7 +7139,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
@@ -6925,310 +7174,310 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
       <c r="C33" t="n">
-        <v>57.9</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="E33" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s">
         <v>53</v>
       </c>
       <c r="C34" t="n">
-        <v>62.8</v>
+        <v>57.9</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>9.3</v>
       </c>
       <c r="F34" t="n">
-        <v>41.7</v>
+        <v>12.5</v>
       </c>
       <c r="G34" t="n">
-        <v>9.3</v>
+        <v>16.7</v>
       </c>
       <c r="H34" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
       <c r="K34" t="n">
-        <v>2.3</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>57.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35"/>
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41.7</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="H35" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36"/>
       <c r="G36" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I36" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="D37" t="n">
-        <v>70.2</v>
+        <v>37.5</v>
       </c>
       <c r="E37" t="n">
-        <v>23.5</v>
+        <v>9.5</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H37" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
-        <v>34.8</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D38" t="n">
-        <v>66.7</v>
+        <v>52.2</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G38" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="H38" t="n">
-        <v>18.2</v>
+        <v>91.7</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>19.2</v>
+        <v>23.1</v>
       </c>
       <c r="K38" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>70.2</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39"/>
+        <v>23.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50</v>
+      </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C40" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="D40" t="n">
-        <v>49.2</v>
+        <v>66.7</v>
       </c>
       <c r="E40" t="n">
-        <v>9.1</v>
+        <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="H40" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D41" t="n">
-        <v>52.9</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41"/>
       <c r="G41" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -7236,63 +7485,69 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D42" t="n">
-        <v>7.7</v>
+        <v>46.2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42"/>
+        <v>22.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.3</v>
+      </c>
       <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42"/>
+        <v>11.1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
       <c r="K42" t="n">
-        <v>-100</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C43" t="n">
-        <v>35.3</v>
+        <v>44.4</v>
       </c>
       <c r="D43" t="n">
-        <v>57.6</v>
+        <v>49.2</v>
       </c>
       <c r="E43" t="n">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="F43" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>20</v>
-      </c>
-      <c r="G43" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>23.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -7300,34 +7555,34 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C44" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>63.2</v>
+        <v>52.9</v>
       </c>
       <c r="E44" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H44" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -7335,104 +7590,98 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>7.7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45"/>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H45"/>
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
+      <c r="J45"/>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C46" t="n">
-        <v>63</v>
+        <v>35.3</v>
       </c>
       <c r="D46" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="E46" t="n">
-        <v>13.6</v>
+        <v>17.6</v>
       </c>
       <c r="F46" t="n">
-        <v>41.7</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>23.1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="K46" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C47" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D47" t="n">
-        <v>87.5</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H47" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -7440,445 +7689,445 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C48" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>60.8</v>
+        <v>55</v>
       </c>
       <c r="E48" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C49" t="n">
-        <v>69.2</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>74.7</v>
+        <v>57.8</v>
       </c>
       <c r="E49" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="F49" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G49" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H49" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="K49" t="n">
-        <v>19.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D50" t="n">
-        <v>61.7</v>
+        <v>87.5</v>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>41.2</v>
+        <v>66.7</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C51" t="n">
-        <v>66.7</v>
+        <v>52.9</v>
       </c>
       <c r="D51" t="n">
-        <v>66.7</v>
+        <v>60.8</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H51" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>22.2</v>
+        <v>32.1</v>
       </c>
       <c r="K51" t="n">
-        <v>16.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C52" t="n">
-        <v>14.3</v>
+        <v>69.2</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>74.7</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>28.6</v>
+        <v>3.8</v>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-28.6</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C53" t="n">
         <v>50</v>
       </c>
       <c r="D53" t="n">
-        <v>53.6</v>
+        <v>56.4</v>
       </c>
       <c r="E53" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="F53" t="n">
-        <v>50</v>
+        <v>29.4</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H53" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="K53" t="n">
-        <v>12.5</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C54" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G54" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>66.7</v>
+        <v>88.9</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>21.4</v>
+        <v>23.5</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C55" t="n">
-        <v>70</v>
+        <v>36.4</v>
       </c>
       <c r="D55" t="n">
-        <v>70.4</v>
+        <v>60.5</v>
       </c>
       <c r="E55" t="n">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="F55" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="G55" t="n">
-        <v>3.3</v>
+        <v>27.3</v>
       </c>
       <c r="H55" t="n">
-        <v>34.8</v>
+        <v>60</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>22</v>
+        <v>11.1</v>
       </c>
       <c r="K55" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C56" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="D56" t="n">
-        <v>65.3</v>
+        <v>53.6</v>
       </c>
       <c r="E56" t="n">
-        <v>31.4</v>
+        <v>13.3</v>
       </c>
       <c r="F56" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K56" t="n">
         <v>12.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>8.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="D57" t="n">
         <v>63.2</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F57" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H57" t="n">
         <v>66.7</v>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>50</v>
-      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>37.5</v>
+        <v>21.4</v>
       </c>
       <c r="K57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C58" t="n">
-        <v>46.4</v>
+        <v>70</v>
       </c>
       <c r="D58" t="n">
-        <v>53.9</v>
+        <v>70.4</v>
       </c>
       <c r="E58" t="n">
-        <v>11.5</v>
+        <v>15.8</v>
       </c>
       <c r="F58" t="n">
-        <v>36.4</v>
+        <v>37.5</v>
       </c>
       <c r="G58" t="n">
-        <v>17.9</v>
+        <v>3.3</v>
       </c>
       <c r="H58" t="n">
-        <v>35.3</v>
+        <v>34.8</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="D59" t="n">
-        <v>41.2</v>
+        <v>65.3</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="K59" t="n">
-        <v>-20</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C60" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>44.1</v>
+        <v>63.2</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F60" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="G60" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>50</v>
@@ -7887,59 +8136,59 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
       <c r="D61" t="n">
-        <v>38.9</v>
+        <v>53.9</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G61" t="n">
-        <v>66.7</v>
+        <v>17.9</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.7</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C62" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D62" t="n">
-        <v>57.9</v>
+        <v>41.2</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -7948,279 +8197,281 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
+        <v>20</v>
+      </c>
+      <c r="H62" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>25</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>28.6</v>
-      </c>
       <c r="K62" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C63" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="D63" t="n">
-        <v>41.4</v>
+        <v>44.1</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>33.3</v>
       </c>
       <c r="G63" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>33.3</v>
       </c>
-      <c r="H63" t="n">
-        <v>50</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>14.3</v>
-      </c>
       <c r="K63" t="n">
-        <v>-16.6</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C64" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>57.5</v>
+        <v>38.9</v>
       </c>
       <c r="E64" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>51.9</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>20.8</v>
+        <v>66.7</v>
       </c>
       <c r="H64" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>8.4</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C65" t="n">
         <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>7.1</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>8.3</v>
+        <v>28.6</v>
       </c>
       <c r="K65" t="n">
-        <v>7.2</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C66" t="n">
         <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>60</v>
+        <v>41.4</v>
       </c>
       <c r="E66" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>46.7</v>
+        <v>33.3</v>
       </c>
       <c r="G66" t="n">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="H66" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>29.4</v>
+        <v>14.3</v>
       </c>
       <c r="K66" t="n">
-        <v>16.6</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C67" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="D67" t="n">
-        <v>87.5</v>
+        <v>57.5</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>51.9</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>25</v>
       </c>
-      <c r="J67" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>59.3</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68"/>
+        <v>15</v>
+      </c>
+      <c r="F68" t="n">
+        <v>40</v>
+      </c>
       <c r="G68" t="n">
-        <v>66.7</v>
+        <v>7.1</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K68" t="n">
-        <v>-66.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C69" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D69" t="n">
-        <v>63.4</v>
+        <v>60</v>
       </c>
       <c r="E69" t="n">
-        <v>17.6</v>
+        <v>10.2</v>
       </c>
       <c r="F69" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H69" t="n">
-        <v>27.3</v>
+        <v>40</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
-        <v>27.3</v>
+        <v>29.4</v>
       </c>
       <c r="K69" t="n">
-        <v>27.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C70" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D70" t="n">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -8232,10 +8483,10 @@
         <v>50</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -8243,25 +8494,23 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="E71" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -8270,66 +8519,68 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>-20</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C72" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D72" t="n">
-        <v>57.1</v>
+        <v>63.4</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72"/>
+        <v>17.6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>50</v>
+      </c>
       <c r="G72" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>55.6</v>
+        <v>27.3</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-9.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B73" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D73" t="n">
-        <v>39.1</v>
+        <v>80</v>
       </c>
       <c r="E73" t="n">
-        <v>6.7</v>
+        <v>50</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>50</v>
@@ -8338,148 +8589,251 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>-33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C74" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D74" t="n">
-        <v>53.3</v>
+        <v>31.6</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H74" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>7.1</v>
+        <v>33.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-11.1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C75" t="n">
-        <v>52</v>
+        <v>66.7</v>
       </c>
       <c r="D75" t="n">
-        <v>55.2</v>
+        <v>57.1</v>
       </c>
       <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75"/>
+      <c r="G75" t="n">
         <v>9.1</v>
       </c>
-      <c r="F75" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G75" t="n">
-        <v>8</v>
-      </c>
       <c r="H75" t="n">
-        <v>47.4</v>
+        <v>55.6</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C76" t="n">
+        <v>50</v>
+      </c>
+      <c r="D76" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>234</v>
+      </c>
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" t="n">
+        <v>52</v>
+      </c>
+      <c r="D78" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>235</v>
+      </c>
+      <c r="B79" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" t="n">
         <v>68.8</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D79" t="n">
         <v>59.2</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E79" t="n">
         <v>16</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
         <v>5.9</v>
       </c>
-      <c r="H76" t="n">
-        <v>50</v>
-      </c>
-      <c r="I76" t="n">
+      <c r="H79" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" t="n">
         <v>5.9</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J79" t="n">
         <v>17.4</v>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77"/>
-      <c r="B77" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="D77" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="E77" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F77" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G77" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J77" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K77" t="n">
-        <v>-1.3</v>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H80" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>19</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-1.4</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -171,21 +171,30 @@
     <t xml:space="preserve">Tommy Cullen</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Leatherland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anden Cooper</t>
   </si>
   <si>
-    <t xml:space="preserve">McMaster Marauders</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brandon McMurray</t>
   </si>
   <si>
     <t xml:space="preserve">Brody Nguyen</t>
   </si>
   <si>
+    <t xml:space="preserve">Coy Gordon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Declan Shannon</t>
   </si>
   <si>
+    <t xml:space="preserve">Devan Fenwick</t>
+  </si>
+  <si>
     <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
   </si>
   <si>
@@ -231,6 +240,12 @@
     <t xml:space="preserve">Quinten Shannon</t>
   </si>
   <si>
+    <t xml:space="preserve">Rhys Jenkyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shephard</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sydney Stonehouse</t>
   </si>
   <si>
@@ -279,9 +294,6 @@
     <t xml:space="preserve">Woochan Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam Leatherland</t>
-  </si>
-  <si>
     <t xml:space="preserve">Waterloo Warriors</t>
   </si>
   <si>
@@ -327,15 +339,12 @@
     <t xml:space="preserve">Nico Valvo</t>
   </si>
   <si>
-    <t xml:space="preserve">Rhys Jenkyn</t>
+    <t xml:space="preserve">Raywat Bajracharya</t>
   </si>
   <si>
     <t xml:space="preserve">Sam Grant</t>
   </si>
   <si>
-    <t xml:space="preserve">Sam Shephard</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ty Tinnish</t>
   </si>
   <si>
@@ -591,15 +600,18 @@
     <t xml:space="preserve">Alex VanRaay</t>
   </si>
   <si>
-    <t xml:space="preserve">Devan Fenwick</t>
-  </si>
-  <si>
     <t xml:space="preserve">Erik Lopez</t>
   </si>
   <si>
     <t xml:space="preserve">Jaden Fonseca</t>
   </si>
   <si>
+    <t xml:space="preserve">Jaxx Carthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maddox Yee</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marcello Colucci</t>
   </si>
   <si>
@@ -607,6 +619,9 @@
   </si>
   <si>
     <t xml:space="preserve">Premnath Nayak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risden Dimayuga</t>
   </si>
   <si>
     <t xml:space="preserve">Sam McMillan</t>
@@ -775,8 +790,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K142" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K142"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K154" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K154"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -795,8 +810,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K80" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K87" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K87"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2510,33 +2525,23 @@
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
       <c r="G41" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>50</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -2546,31 +2551,31 @@
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>36.4</v>
       </c>
       <c r="I42" t="n">
-        <v>83.3</v>
+        <v>40</v>
       </c>
       <c r="J42" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2581,31 +2586,31 @@
         <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="44">
@@ -2616,22 +2621,22 @@
         <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>27.5</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
@@ -2651,16 +2656,16 @@
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>30.4</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2669,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -2686,19 +2691,19 @@
         <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="n">
-        <v>41.7</v>
+        <v>27.5</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="G46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2710,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2721,19 +2726,19 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>76.9</v>
+        <v>100</v>
       </c>
       <c r="D47" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>60.2</v>
+        <v>100</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2742,10 +2747,10 @@
         <v>50</v>
       </c>
       <c r="J47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2756,24 +2761,32 @@
         <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48"/>
+        <v>16.7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48"/>
+      <c r="I48" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K48" t="n">
+        <v>57.1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
@@ -2783,31 +2796,31 @@
         <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>54.8</v>
+        <v>66.7</v>
       </c>
       <c r="D49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E49" t="n">
-        <v>39.8</v>
+        <v>41.7</v>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>25</v>
-      </c>
-      <c r="K49" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -2818,31 +2831,31 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="D50" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>60</v>
+      </c>
+      <c r="J50" t="n">
         <v>20</v>
       </c>
-      <c r="E50" t="n">
-        <v>55</v>
-      </c>
-      <c r="F50" t="n">
-        <v>20</v>
-      </c>
-      <c r="G50" t="n">
-        <v>75</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
@@ -2853,32 +2866,24 @@
         <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G51"/>
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="n">
-        <v>100</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -2888,31 +2893,31 @@
         <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>38.2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="G52" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2923,31 +2928,31 @@
         <v>53</v>
       </c>
       <c r="C53" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="D53" t="n">
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
-        <v>47.6</v>
+        <v>42.5</v>
       </c>
       <c r="F53" t="n">
-        <v>9.5</v>
+        <v>20</v>
       </c>
       <c r="G53" t="n">
-        <v>28.6</v>
+        <v>42.9</v>
       </c>
       <c r="H53" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
@@ -2958,31 +2963,31 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G54" t="n">
         <v>66.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>25</v>
-      </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2993,31 +2998,31 @@
         <v>53</v>
       </c>
       <c r="C55" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>38.5</v>
+        <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>25</v>
-      </c>
-      <c r="K55" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -3028,31 +3033,31 @@
         <v>53</v>
       </c>
       <c r="C56" t="n">
-        <v>100</v>
+        <v>57.7</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>49.4</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I56" t="n">
-        <v>100</v>
+        <v>71.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>66.7</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="57">
@@ -3066,28 +3071,28 @@
         <v>66.7</v>
       </c>
       <c r="D57" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="F57" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H57" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
@@ -3098,28 +3103,28 @@
         <v>53</v>
       </c>
       <c r="C58" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E58" t="n">
-        <v>75</v>
+        <v>41.3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G58" t="n">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I58" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
         <v>50</v>
@@ -3133,31 +3138,31 @@
         <v>53</v>
       </c>
       <c r="C59" t="n">
-        <v>41.2</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>-8.8</v>
+        <v>100</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="60">
@@ -3168,31 +3173,31 @@
         <v>53</v>
       </c>
       <c r="C60" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="D60" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="G60" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I60" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K60" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3200,90 +3205,82 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C61" t="n">
-        <v>42.9</v>
+        <v>85.7</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
-        <v>42.9</v>
+        <v>65.7</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C62" t="n">
-        <v>75</v>
+        <v>38.1</v>
       </c>
       <c r="D62" t="n">
-        <v>16.7</v>
+        <v>52.6</v>
       </c>
       <c r="E62" t="n">
-        <v>58.3</v>
+        <v>-14.5</v>
       </c>
       <c r="F62" t="n">
-        <v>16.7</v>
+        <v>52.6</v>
       </c>
       <c r="G62" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I62" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
-      </c>
-      <c r="C63" t="n">
-        <v>80</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>80</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
       <c r="G63" t="n">
         <v>0</v>
       </c>
@@ -3291,45 +3288,37 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D64" t="n">
-        <v>20</v>
-      </c>
-      <c r="E64" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F64" t="n">
-        <v>20</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
       <c r="G64" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3337,60 +3326,60 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C65" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="D65" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="E65" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>38.5</v>
       </c>
       <c r="G65" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>37.5</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" t="s">
         <v>79</v>
       </c>
-      <c r="B66" t="s">
-        <v>74</v>
-      </c>
       <c r="C66" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="F66" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3399,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K66" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="67">
@@ -3410,34 +3399,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C67" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D67" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E67" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G67" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J67" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
@@ -3445,16 +3434,16 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3466,13 +3455,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69">
@@ -3480,31 +3469,31 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C69" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E69" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I69" t="n">
+        <v>25</v>
+      </c>
+      <c r="J69" t="n">
         <v>75</v>
-      </c>
-      <c r="D69" t="n">
-        <v>50</v>
-      </c>
-      <c r="E69" t="n">
-        <v>25</v>
-      </c>
-      <c r="F69" t="n">
-        <v>50</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>50</v>
-      </c>
-      <c r="J69" t="n">
-        <v>50</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3515,28 +3504,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C70" t="n">
-        <v>80</v>
-      </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
+        <v>55.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>50</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>50</v>
+      </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3544,34 +3539,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C71" t="n">
-        <v>78.6</v>
+        <v>55.6</v>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="n">
-        <v>67.5</v>
+        <v>43.1</v>
       </c>
       <c r="F71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="G71" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
         <v>100</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3579,34 +3574,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C72" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>20</v>
+      </c>
+      <c r="G72" t="n">
+        <v>40</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>50</v>
+      </c>
+      <c r="J72" t="n">
+        <v>50</v>
+      </c>
+      <c r="K72" t="n">
         <v>100</v>
-      </c>
-      <c r="D72" t="n">
-        <v>25</v>
-      </c>
-      <c r="E72" t="n">
-        <v>75</v>
-      </c>
-      <c r="F72" t="n">
-        <v>25</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>100</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="73">
@@ -3614,34 +3609,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C73" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3649,22 +3644,22 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C74" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E74" t="n">
-        <v>-8.3</v>
+        <v>25</v>
       </c>
       <c r="F74" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G74" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3673,10 +3668,10 @@
         <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3684,224 +3679,218 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C75" t="n">
-        <v>64</v>
-      </c>
-      <c r="D75" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E75" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="F75" t="n">
-        <v>31.2</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>70</v>
+        <v>33.3</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C76" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H76" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I76" t="n">
         <v>100</v>
       </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>50</v>
-      </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C77" t="n">
-        <v>70.8</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
         <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>45.8</v>
+        <v>75</v>
       </c>
       <c r="F77" t="n">
         <v>25</v>
       </c>
       <c r="G77" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C78" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
         <v>75</v>
       </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
-        <v>75</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J78" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C79" t="n">
-        <v>82.1</v>
+        <v>66.7</v>
       </c>
       <c r="D79" t="n">
-        <v>9.1</v>
+        <v>75</v>
       </c>
       <c r="E79" t="n">
-        <v>73</v>
+        <v>-8.3</v>
       </c>
       <c r="F79" t="n">
-        <v>9.1</v>
+        <v>75</v>
       </c>
       <c r="G79" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K79" t="n">
-        <v>53.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C80" t="n">
-        <v>58.3</v>
+        <v>67.7</v>
       </c>
       <c r="D80" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H80" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I80" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J80" t="n">
         <v>9.1</v>
       </c>
-      <c r="E80" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="F80" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>25</v>
-      </c>
-      <c r="H80" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I80" t="n">
-        <v>75</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
       <c r="K80" t="n">
-        <v>75</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C81" t="n">
-        <v>80</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>80</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
       <c r="G81" t="n">
         <v>0</v>
       </c>
@@ -3920,419 +3909,389 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" t="n">
-        <v>73.3</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C82"/>
       <c r="D82" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E82" t="n">
-        <v>31.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E82"/>
       <c r="F82" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I82" t="n">
-        <v>20</v>
-      </c>
-      <c r="J82" t="n">
-        <v>60</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C83" t="n">
-        <v>71.4</v>
+        <v>73.1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E83" t="n">
-        <v>71.4</v>
+        <v>48.1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G83" t="n">
-        <v>40</v>
+        <v>17.9</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I83" t="n">
-        <v>100</v>
+        <v>27.3</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="K83" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C84" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>38.2</v>
+        <v>75</v>
       </c>
       <c r="F84" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>33.3</v>
       </c>
-      <c r="H84" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>60</v>
-      </c>
       <c r="J84" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C85" t="n">
-        <v>37.5</v>
+        <v>83.9</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E85" t="n">
-        <v>37.5</v>
+        <v>76.2</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G85" t="n">
-        <v>66.7</v>
+        <v>7.1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="J85" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C86" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>49.2</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G86" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I86" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C87" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D87" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="E87" t="n">
-        <v>43.3</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G87" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
-      </c>
-      <c r="I87" t="n">
-        <v>50</v>
-      </c>
-      <c r="J87" t="n">
-        <v>50</v>
-      </c>
-      <c r="K87" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C88" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="D88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I88" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J88" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C89" t="n">
-        <v>59.1</v>
+        <v>50</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>59.1</v>
+        <v>50</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I89" t="n">
-        <v>50</v>
-      </c>
-      <c r="J89" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K89" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C90" t="n">
         <v>73.3</v>
       </c>
       <c r="D90" t="n">
-        <v>24</v>
+        <v>41.7</v>
       </c>
       <c r="E90" t="n">
-        <v>49.3</v>
+        <v>31.6</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>41.7</v>
       </c>
       <c r="G90" t="n">
-        <v>21.4</v>
+        <v>17.6</v>
       </c>
       <c r="H90" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="I90" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
       <c r="J90" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
       <c r="K90" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C91" t="n">
-        <v>81.8</v>
+        <v>71.4</v>
       </c>
       <c r="D91" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>72.7</v>
+        <v>71.4</v>
       </c>
       <c r="F91" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H91" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J91" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" t="n">
-        <v>65.6</v>
-      </c>
-      <c r="D92" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E92" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="F92" t="n">
-        <v>7.7</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
       <c r="G92" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="J92" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>76.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C93" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4340,139 +4299,139 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>18.2</v>
+        <v>66.7</v>
       </c>
       <c r="H94" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="K94" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B95" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C95" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D95" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>48.4</v>
+        <v>100</v>
       </c>
       <c r="F95" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="H95" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J95" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C96" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="D96" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E96" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G96" t="n">
         <v>20</v>
       </c>
-      <c r="F96" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G96" t="n">
-        <v>18.2</v>
-      </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J96" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="K96" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C97" t="n">
-        <v>88.9</v>
+        <v>83.3</v>
       </c>
       <c r="D97" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="E97" t="n">
-        <v>75.6</v>
+        <v>50</v>
       </c>
       <c r="F97" t="n">
-        <v>13.3</v>
+        <v>33.3</v>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="H97" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J97" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K97" t="n">
         <v>100</v>
@@ -4480,262 +4439,242 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C98" t="n">
-        <v>88.9</v>
+        <v>59.1</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>88.9</v>
+        <v>59.1</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H98" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="I98" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K98" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
-      </c>
-      <c r="C99" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
       <c r="G99" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
-      </c>
-      <c r="C100" t="n">
-        <v>57.1</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C100"/>
       <c r="D100" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E100" t="n">
-        <v>48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E100"/>
       <c r="F100" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G100" t="n">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G100"/>
       <c r="H100" t="n">
-        <v>50</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
         <v>100</v>
       </c>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C101" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="H101" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C102" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="E102" t="n">
-        <v>55</v>
+        <v>51.9</v>
       </c>
       <c r="F102" t="n">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="G102" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I102" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="J102" t="n">
-        <v>14.3</v>
+        <v>27.3</v>
       </c>
       <c r="K102" t="n">
-        <v>14.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C103" t="n">
-        <v>85.7</v>
+        <v>81.8</v>
       </c>
       <c r="D103" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F103" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>20</v>
+      </c>
+      <c r="I103" t="n">
+        <v>75</v>
+      </c>
+      <c r="J103" t="n">
         <v>25</v>
       </c>
-      <c r="E103" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F103" t="n">
-        <v>25</v>
-      </c>
-      <c r="G103" t="n">
-        <v>25</v>
-      </c>
-      <c r="H103" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I103" t="n">
-        <v>50</v>
-      </c>
-      <c r="J103" t="n">
-        <v>50</v>
-      </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C104" t="n">
-        <v>43.8</v>
+        <v>67.6</v>
       </c>
       <c r="D104" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="E104" t="n">
-        <v>34.7</v>
+        <v>60.5</v>
       </c>
       <c r="F104" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="G104" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H104" t="n">
-        <v>28.6</v>
+        <v>10.5</v>
       </c>
       <c r="I104" t="n">
-        <v>25</v>
+        <v>46.7</v>
       </c>
       <c r="J104" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="K104" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C105" t="n">
-        <v>100</v>
-      </c>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
+        <v>50</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>50</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
@@ -4746,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4754,419 +4693,413 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B106" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C106" t="n">
-        <v>92.6</v>
+        <v>66.7</v>
       </c>
       <c r="D106" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>87.3</v>
+        <v>66.7</v>
       </c>
       <c r="F106" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="H106" t="n">
-        <v>12.5</v>
+        <v>26.7</v>
       </c>
       <c r="I106" t="n">
-        <v>64.3</v>
+        <v>30</v>
       </c>
       <c r="J106" t="n">
-        <v>21.4</v>
+        <v>30</v>
       </c>
       <c r="K106" t="n">
-        <v>57.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C107" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>8.7</v>
       </c>
       <c r="E107" t="n">
-        <v>43.7</v>
+        <v>48.4</v>
       </c>
       <c r="F107" t="n">
-        <v>12.5</v>
+        <v>8.7</v>
       </c>
       <c r="G107" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="H107" t="n">
-        <v>22.2</v>
+        <v>27.3</v>
       </c>
       <c r="I107" t="n">
-        <v>42.9</v>
+        <v>80</v>
       </c>
       <c r="J107" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C108" t="n">
-        <v>75</v>
+        <v>46.7</v>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>26.7</v>
       </c>
       <c r="E108" t="n">
+        <v>20</v>
+      </c>
+      <c r="F108" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G108" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
         <v>62.5</v>
       </c>
-      <c r="F108" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G108" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H108" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I108" t="n">
-        <v>40</v>
-      </c>
-      <c r="J108" t="n">
-        <v>40</v>
-      </c>
       <c r="K108" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>71.4</v>
+        <v>88.9</v>
       </c>
       <c r="D109" t="n">
-        <v>9.7</v>
+        <v>13.3</v>
       </c>
       <c r="E109" t="n">
-        <v>61.7</v>
+        <v>75.6</v>
       </c>
       <c r="F109" t="n">
-        <v>9.7</v>
+        <v>13.3</v>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H109" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I109" t="n">
-        <v>72.7</v>
+        <v>20</v>
       </c>
       <c r="J109" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="K109" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C110" t="n">
-        <v>55.6</v>
+        <v>88.9</v>
       </c>
       <c r="D110" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>38.9</v>
+        <v>88.9</v>
       </c>
       <c r="F110" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I110" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J110" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C111" t="n">
-        <v>68.8</v>
+        <v>78.6</v>
       </c>
       <c r="D111" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>58.5</v>
+        <v>78.6</v>
       </c>
       <c r="F111" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="H111" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>25</v>
+        <v>85.7</v>
       </c>
       <c r="J111" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C112" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="D112" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="E112" t="n">
-        <v>52.4</v>
+        <v>48</v>
       </c>
       <c r="F112" t="n">
-        <v>14.3</v>
+        <v>9.1</v>
       </c>
       <c r="G112" t="n">
-        <v>35.7</v>
+        <v>40</v>
       </c>
       <c r="H112" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="I112" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C113" t="n">
-        <v>55.6</v>
+        <v>64.3</v>
       </c>
       <c r="D113" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>33.4</v>
+        <v>64.3</v>
       </c>
       <c r="F113" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>42.9</v>
+        <v>11.1</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I113" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C114" t="n">
-        <v>80.8</v>
+        <v>80</v>
       </c>
       <c r="D114" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="E114" t="n">
-        <v>62.6</v>
+        <v>55</v>
       </c>
       <c r="F114" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="G114" t="n">
-        <v>36</v>
+        <v>11.1</v>
       </c>
       <c r="H114" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="J114" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="K114" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C115" t="n">
-        <v>91.7</v>
+        <v>85.7</v>
       </c>
       <c r="D115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E115" t="n">
-        <v>41.7</v>
+        <v>60.7</v>
       </c>
       <c r="F115" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G115" t="n">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I115" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="J115" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="K115" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C116" t="n">
-        <v>60</v>
+        <v>43.8</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E116" t="n">
-        <v>60</v>
+        <v>34.7</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I116" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C117" t="n">
         <v>100</v>
       </c>
-      <c r="D117" t="n">
-        <v>20</v>
-      </c>
-      <c r="E117" t="n">
-        <v>80</v>
-      </c>
-      <c r="F117" t="n">
-        <v>20</v>
-      </c>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
       <c r="G117" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5174,69 +5107,69 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C118" t="n">
-        <v>75</v>
+        <v>92.6</v>
       </c>
       <c r="D118" t="n">
-        <v>8.3</v>
+        <v>5.3</v>
       </c>
       <c r="E118" t="n">
-        <v>66.7</v>
+        <v>87.3</v>
       </c>
       <c r="F118" t="n">
-        <v>8.3</v>
+        <v>5.3</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I118" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="J118" t="n">
-        <v>12.5</v>
+        <v>21.4</v>
       </c>
       <c r="K118" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C119" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
+        <v>43.7</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="J119" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5244,349 +5177,349 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C120" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="D120" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="E120" t="n">
-        <v>54.7</v>
+        <v>62.5</v>
       </c>
       <c r="F120" t="n">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
       <c r="G120" t="n">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I120" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J120" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K120" t="n">
-        <v>16.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C121" t="n">
-        <v>57.1</v>
+        <v>71.4</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="E121" t="n">
-        <v>57.1</v>
+        <v>61.7</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="G121" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H121" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="I121" t="n">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="J121" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="K121" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C122" t="n">
-        <v>70</v>
+        <v>55.6</v>
       </c>
       <c r="D122" t="n">
-        <v>37.5</v>
+        <v>16.7</v>
       </c>
       <c r="E122" t="n">
-        <v>32.5</v>
+        <v>38.9</v>
       </c>
       <c r="F122" t="n">
-        <v>37.5</v>
+        <v>16.7</v>
       </c>
       <c r="G122" t="n">
-        <v>17.6</v>
+        <v>28.6</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J122" t="n">
         <v>25</v>
       </c>
       <c r="K122" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C123" t="n">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="D123" t="n">
-        <v>21.4</v>
+        <v>10.3</v>
       </c>
       <c r="E123" t="n">
-        <v>53.6</v>
+        <v>58.5</v>
       </c>
       <c r="F123" t="n">
-        <v>21.4</v>
+        <v>10.3</v>
       </c>
       <c r="G123" t="n">
-        <v>46.7</v>
+        <v>12</v>
       </c>
       <c r="H123" t="n">
-        <v>14.3</v>
+        <v>18.8</v>
       </c>
       <c r="I123" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K123" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C124" t="n">
-        <v>84.6</v>
+        <v>66.7</v>
       </c>
       <c r="D124" t="n">
         <v>14.3</v>
       </c>
       <c r="E124" t="n">
-        <v>70.3</v>
+        <v>52.4</v>
       </c>
       <c r="F124" t="n">
         <v>14.3</v>
       </c>
       <c r="G124" t="n">
-        <v>13</v>
+        <v>35.7</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I124" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="J124" t="n">
-        <v>18.8</v>
+        <v>33.3</v>
       </c>
       <c r="K124" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C125" t="n">
-        <v>68.6</v>
+        <v>55.6</v>
       </c>
       <c r="D125" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="E125" t="n">
-        <v>59.5</v>
+        <v>33.4</v>
       </c>
       <c r="F125" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="G125" t="n">
-        <v>23.1</v>
+        <v>42.9</v>
       </c>
       <c r="H125" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J125" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C126" t="n">
-        <v>50</v>
+        <v>80.8</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E126" t="n">
-        <v>50</v>
+        <v>62.6</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I126" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>90.9</v>
+        <v>91.7</v>
       </c>
       <c r="D127" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E127" t="n">
-        <v>70.9</v>
+        <v>41.7</v>
       </c>
       <c r="F127" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G127" t="n">
-        <v>27.3</v>
+        <v>21.4</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="J127" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="K127" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C128" t="n">
         <v>60</v>
       </c>
       <c r="D128" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>17.1</v>
+        <v>60</v>
       </c>
       <c r="F128" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J128" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C129" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D129" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E129" t="n">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="F129" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G129" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="J129" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5594,22 +5527,22 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C130" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E130" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5618,295 +5551,313 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J130" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K130" t="n">
-        <v>33.3</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C131" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="F131" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I131"/>
-      <c r="J131"/>
-      <c r="K131"/>
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>100</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C132" t="n">
-        <v>42.9</v>
+        <v>83.3</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E132" t="n">
-        <v>42.9</v>
+        <v>54.7</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G132" t="n">
-        <v>66.7</v>
+        <v>16.7</v>
       </c>
       <c r="H132" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I132"/>
-      <c r="J132"/>
-      <c r="K132"/>
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K132" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C133" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133"/>
-      <c r="J133"/>
-      <c r="K133"/>
+        <v>14.3</v>
+      </c>
+      <c r="I133" t="n">
+        <v>60</v>
+      </c>
+      <c r="J133" t="n">
+        <v>20</v>
+      </c>
+      <c r="K133" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C134" t="n">
-        <v>61.1</v>
+        <v>70</v>
       </c>
       <c r="D134" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="E134" t="n">
-        <v>52</v>
+        <v>32.5</v>
       </c>
       <c r="F134" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="G134" t="n">
-        <v>8.3</v>
+        <v>17.6</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>85.7</v>
+        <v>37.5</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K134" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C135" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D135" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="E135" t="n">
-        <v>31.8</v>
+        <v>53.6</v>
       </c>
       <c r="F135" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="G135" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="H135" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J135" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C136" t="n">
-        <v>50</v>
+        <v>84.6</v>
       </c>
       <c r="D136" t="n">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="E136" t="n">
-        <v>26.9</v>
+        <v>70.3</v>
       </c>
       <c r="F136" t="n">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="G136" t="n">
-        <v>37.5</v>
+        <v>13</v>
       </c>
       <c r="H136" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="J136" t="n">
-        <v>33.3</v>
+        <v>18.8</v>
       </c>
       <c r="K136" t="n">
-        <v>66.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C137" t="n">
-        <v>66.7</v>
+        <v>68.6</v>
       </c>
       <c r="D137" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="E137" t="n">
-        <v>41.7</v>
+        <v>59.5</v>
       </c>
       <c r="F137" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="G137" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I137" t="n">
         <v>33.3</v>
       </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>100</v>
-      </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C138" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J138" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C139" t="n">
-        <v>45</v>
+        <v>90.9</v>
       </c>
       <c r="D139" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E139" t="n">
-        <v>28.3</v>
+        <v>70.9</v>
       </c>
       <c r="F139" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G139" t="n">
         <v>27.3</v>
@@ -5915,116 +5866,518 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C140" t="n">
-        <v>71.4</v>
+        <v>60</v>
       </c>
       <c r="D140" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="E140" t="n">
-        <v>51.4</v>
+        <v>17.1</v>
       </c>
       <c r="F140" t="n">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="G140" t="n">
         <v>33.3</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C141" t="n">
-        <v>71.4</v>
+        <v>90</v>
       </c>
       <c r="D141" t="n">
-        <v>7.1</v>
+        <v>16.7</v>
       </c>
       <c r="E141" t="n">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="F141" t="n">
-        <v>7.1</v>
+        <v>16.7</v>
       </c>
       <c r="G141" t="n">
         <v>18.2</v>
       </c>
       <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>50</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" t="s">
+        <v>130</v>
+      </c>
+      <c r="C142" t="n">
+        <v>100</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>100</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J142" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K142" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" t="s">
+        <v>150</v>
+      </c>
+      <c r="C143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G143" t="n">
+        <v>50</v>
+      </c>
+      <c r="H143" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I143"/>
+      <c r="J143"/>
+      <c r="K143"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H144" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I144"/>
+      <c r="J144"/>
+      <c r="K144"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" t="s">
+        <v>150</v>
+      </c>
+      <c r="C145" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145"/>
+      <c r="J145"/>
+      <c r="K145"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" t="s">
+        <v>150</v>
+      </c>
+      <c r="C146" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>52</v>
+      </c>
+      <c r="F146" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" t="s">
+        <v>150</v>
+      </c>
+      <c r="C147" t="n">
+        <v>50</v>
+      </c>
+      <c r="D147" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E147" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F147" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G147" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H147" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>75</v>
+      </c>
+      <c r="K147" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" t="s">
+        <v>150</v>
+      </c>
+      <c r="C148" t="n">
+        <v>50</v>
+      </c>
+      <c r="D148" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I148" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K148" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D149" t="n">
+        <v>25</v>
+      </c>
+      <c r="E149" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>25</v>
+      </c>
+      <c r="G149" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>100</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
         <v>12.5</v>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
+      <c r="H150" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K150" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" t="s">
+        <v>150</v>
+      </c>
+      <c r="C151" t="n">
+        <v>45</v>
+      </c>
+      <c r="D151" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G151" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
         <v>100</v>
       </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142"/>
-      <c r="B142" t="s">
-        <v>158</v>
-      </c>
-      <c r="C142" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="D142" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F142" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G142" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="H142" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="I142" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="J142" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="K142" t="n">
-        <v>34.5</v>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" t="s">
+        <v>150</v>
+      </c>
+      <c r="C152" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D152" t="n">
+        <v>20</v>
+      </c>
+      <c r="E152" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>50</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" t="s">
+        <v>150</v>
+      </c>
+      <c r="C153" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D153" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>100</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154"/>
+      <c r="B154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C154" t="n">
+        <v>67.9</v>
+      </c>
+      <c r="D154" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E154" t="n">
+        <v>53</v>
+      </c>
+      <c r="F154" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G154" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>10</v>
+      </c>
+      <c r="I154" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>27</v>
+      </c>
+      <c r="K154" t="n">
+        <v>35.7</v>
       </c>
     </row>
   </sheetData>
@@ -6056,22 +6409,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6080,13 +6433,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
@@ -6161,7 +6514,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6196,7 +6549,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6231,7 +6584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6266,7 +6619,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6301,7 +6654,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6406,7 +6759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6441,7 +6794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6474,7 +6827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6509,7 +6862,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -6544,7 +6897,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -6579,7 +6932,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -6614,7 +6967,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -6649,7 +7002,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -6684,7 +7037,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -6719,7 +7072,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -6754,7 +7107,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -6789,7 +7142,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
@@ -6824,7 +7177,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -6859,7 +7212,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
@@ -6894,7 +7247,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -6929,7 +7282,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
@@ -6964,7 +7317,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -6999,7 +7352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
@@ -7034,7 +7387,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
@@ -7069,7 +7422,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
@@ -7104,7 +7457,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
@@ -7139,42 +7492,42 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>33.3</v>
+        <v>48.3</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>56.4</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H32" t="n">
-        <v>66.7</v>
+        <v>36</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
@@ -7209,7 +7562,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s">
         <v>53</v>
@@ -7244,7 +7597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
@@ -7279,27 +7632,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36"/>
+        <v>100</v>
+      </c>
+      <c r="E36"/>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="H36"/>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7307,74 +7658,70 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="E37" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>50</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H37"/>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-28.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>42.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38"/>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>91.7</v>
+        <v>33.3</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -7382,207 +7729,205 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>71.4</v>
+        <v>28.6</v>
       </c>
       <c r="D39" t="n">
-        <v>70.2</v>
+        <v>37.5</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5</v>
+        <v>9.5</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H39" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J39" t="n">
-        <v>34.8</v>
+        <v>25</v>
       </c>
       <c r="K39" t="n">
-        <v>28.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
       <c r="C40" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>66.7</v>
+        <v>52.2</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G40" t="n">
-        <v>6.7</v>
+        <v>15</v>
       </c>
       <c r="H40" t="n">
-        <v>18.2</v>
+        <v>91.7</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>19.2</v>
+        <v>23.1</v>
       </c>
       <c r="K40" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
       </c>
       <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41" t="n">
         <v>100</v>
       </c>
-      <c r="D41" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41"/>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>55.6</v>
+        <v>71.4</v>
       </c>
       <c r="D42" t="n">
-        <v>46.2</v>
+        <v>70.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="I42" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="K42" t="n">
-        <v>-22.2</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="D43" t="n">
-        <v>49.2</v>
+        <v>66.7</v>
       </c>
       <c r="E43" t="n">
-        <v>9.1</v>
+        <v>30</v>
       </c>
       <c r="F43" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="H43" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
-        <v>52.9</v>
+        <v>80</v>
       </c>
       <c r="E44" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F44" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44"/>
       <c r="G44" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -7590,63 +7935,69 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D45" t="n">
-        <v>7.7</v>
+        <v>46.2</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
       <c r="G45" t="n">
-        <v>100</v>
-      </c>
-      <c r="H45"/>
+        <v>22.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>14.3</v>
+      </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45"/>
+        <v>11.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>-100</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C46" t="n">
-        <v>35.3</v>
+        <v>44.4</v>
       </c>
       <c r="D46" t="n">
-        <v>57.6</v>
+        <v>49.2</v>
       </c>
       <c r="E46" t="n">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="F46" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>20</v>
-      </c>
-      <c r="G46" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>23.1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -7654,34 +8005,34 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C47" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>63.2</v>
+        <v>52.9</v>
       </c>
       <c r="E47" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H47" t="n">
-        <v>28.6</v>
+        <v>37.5</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -7689,104 +8040,98 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>7.7</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
+      <c r="F48"/>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H48"/>
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
+      <c r="J48"/>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C49" t="n">
-        <v>63</v>
+        <v>35.3</v>
       </c>
       <c r="D49" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="E49" t="n">
-        <v>13.6</v>
+        <v>17.6</v>
       </c>
       <c r="F49" t="n">
-        <v>41.7</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>23.1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="K49" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D50" t="n">
-        <v>87.5</v>
+        <v>63.2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H50" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -7794,174 +8139,172 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>60.8</v>
+        <v>55</v>
       </c>
       <c r="E51" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C52" t="n">
-        <v>69.2</v>
+        <v>63</v>
       </c>
       <c r="D52" t="n">
-        <v>74.7</v>
+        <v>57.8</v>
       </c>
       <c r="E52" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G52" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H52" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="K52" t="n">
-        <v>19.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C53" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="E53" t="n">
-        <v>10.3</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E53"/>
       <c r="F53" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C54" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="D54" t="n">
-        <v>63.3</v>
+        <v>70.8</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="F54" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>88.9</v>
+        <v>77.8</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>23.5</v>
+        <v>30.4</v>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C55" t="n">
-        <v>36.4</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>60.5</v>
+        <v>87.5</v>
       </c>
       <c r="E55" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -7972,34 +8315,34 @@
         <v>213</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="D56" t="n">
-        <v>53.6</v>
+        <v>60.8</v>
       </c>
       <c r="E56" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="F56" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>26.7</v>
+        <v>32.1</v>
       </c>
       <c r="K56" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="57">
@@ -8007,508 +8350,508 @@
         <v>214</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C57" t="n">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="D57" t="n">
-        <v>63.2</v>
+        <v>74.7</v>
       </c>
       <c r="E57" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="F57" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="H57" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C58" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D58" t="n">
-        <v>70.4</v>
+        <v>83.3</v>
       </c>
       <c r="E58" t="n">
-        <v>15.8</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C59" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>65.3</v>
+        <v>56.4</v>
       </c>
       <c r="E59" t="n">
-        <v>31.4</v>
+        <v>10.3</v>
       </c>
       <c r="F59" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H59" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
-        <v>12.5</v>
+        <v>27.8</v>
       </c>
       <c r="K59" t="n">
-        <v>8.3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>88.9</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>37.5</v>
+        <v>23.5</v>
       </c>
       <c r="K60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C61" t="n">
-        <v>46.4</v>
+        <v>36.4</v>
       </c>
       <c r="D61" t="n">
-        <v>53.9</v>
+        <v>60.5</v>
       </c>
       <c r="E61" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="F61" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>17.9</v>
+        <v>27.3</v>
       </c>
       <c r="H61" t="n">
-        <v>35.3</v>
+        <v>60</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>23.7</v>
+        <v>11.1</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D62" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="E62"/>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
+        <v>100</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>50</v>
+      </c>
+      <c r="K62" t="n">
         <v>33.3</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>25</v>
-      </c>
-      <c r="K62" t="n">
-        <v>-20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C63" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>44.1</v>
+        <v>53.6</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="F63" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="D64" t="n">
-        <v>38.9</v>
+        <v>63.2</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="G64" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H64" t="n">
         <v>66.7</v>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D65" t="n">
-        <v>57.9</v>
+        <v>70.4</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>28.6</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>-25</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C66" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="D66" t="n">
-        <v>41.4</v>
+        <v>65.3</v>
       </c>
       <c r="E66" t="n">
-        <v>15</v>
+        <v>31.4</v>
       </c>
       <c r="F66" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="K66" t="n">
-        <v>-16.6</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B67" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C67" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
-        <v>57.5</v>
+        <v>63.2</v>
       </c>
       <c r="E67" t="n">
-        <v>18.7</v>
+        <v>25</v>
       </c>
       <c r="F67" t="n">
-        <v>51.9</v>
+        <v>66.7</v>
       </c>
       <c r="G67" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="K67" t="n">
-        <v>8.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="D68" t="n">
-        <v>59.3</v>
+        <v>53.9</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="F68" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="G68" t="n">
-        <v>7.1</v>
+        <v>17.9</v>
       </c>
       <c r="H68" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>8.3</v>
+        <v>23.7</v>
       </c>
       <c r="K68" t="n">
-        <v>7.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D69" t="n">
-        <v>60</v>
+        <v>41.2</v>
       </c>
       <c r="E69" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>6.7</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>16.6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C70" t="n">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="D70" t="n">
-        <v>87.5</v>
+        <v>44.1</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H70" t="n">
         <v>50</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>33.3</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>38.9</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" t="n">
         <v>66.7</v>
       </c>
@@ -8527,60 +8870,60 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C72" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D72" t="n">
-        <v>63.4</v>
+        <v>57.9</v>
       </c>
       <c r="E72" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H72" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>27.8</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C73" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>41.4</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H73" t="n">
         <v>50</v>
@@ -8589,127 +8932,129 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C74" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="D74" t="n">
-        <v>31.6</v>
+        <v>57.5</v>
       </c>
       <c r="E74" t="n">
-        <v>7.1</v>
+        <v>18.7</v>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="G74" t="n">
-        <v>40</v>
+        <v>20.8</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>47.8</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>-20</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C75" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D75" t="n">
-        <v>57.1</v>
+        <v>59.3</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75"/>
+        <v>15</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40</v>
+      </c>
       <c r="G75" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="H75" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K75" t="n">
-        <v>-9.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C76" t="n">
         <v>50</v>
       </c>
       <c r="D76" t="n">
-        <v>39.1</v>
+        <v>60</v>
       </c>
       <c r="E76" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G76" t="n">
         <v>6.7</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>33.3</v>
-      </c>
       <c r="H76" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.3</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C77" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>53.3</v>
+        <v>87.5</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -8718,122 +9063,363 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>7.1</v>
+        <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C78" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>55.2</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F78"/>
       <c r="G78" t="n">
-        <v>8</v>
+        <v>66.7</v>
       </c>
       <c r="H78" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>50</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>80</v>
+      </c>
+      <c r="E80" t="n">
+        <v>50</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>50</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
         <v>235</v>
       </c>
-      <c r="B79" t="s">
-        <v>147</v>
-      </c>
-      <c r="C79" t="n">
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" t="n">
+        <v>40</v>
+      </c>
+      <c r="D81" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>100</v>
+      </c>
+      <c r="G81" t="n">
+        <v>40</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>236</v>
+      </c>
+      <c r="B82" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D82" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82"/>
+      <c r="G82" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" t="n">
+        <v>50</v>
+      </c>
+      <c r="D83" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>238</v>
+      </c>
+      <c r="B84" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>239</v>
+      </c>
+      <c r="B85" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85" t="n">
+        <v>52</v>
+      </c>
+      <c r="D85" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>4</v>
+      </c>
+      <c r="J85" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>240</v>
+      </c>
+      <c r="B86" t="s">
+        <v>150</v>
+      </c>
+      <c r="C86" t="n">
         <v>68.8</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D86" t="n">
         <v>59.2</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E86" t="n">
         <v>16</v>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
         <v>5.9</v>
       </c>
-      <c r="H79" t="n">
-        <v>50</v>
-      </c>
-      <c r="I79" t="n">
+      <c r="H86" t="n">
+        <v>50</v>
+      </c>
+      <c r="I86" t="n">
         <v>5.9</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J86" t="n">
         <v>17.4</v>
       </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80"/>
-      <c r="B80" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="D80" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E80" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F80" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H80" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="I80" t="n">
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="D87" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I87" t="n">
         <v>1.2</v>
       </c>
-      <c r="J80" t="n">
-        <v>19</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-1.4</v>
+      <c r="J87" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -171,180 +171,180 @@
     <t xml:space="preserve">Tommy Cullen</t>
   </si>
   <si>
+    <t xml:space="preserve">Anden Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McMaster Marauders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon McMurray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brody Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coy Gordon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declan Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devan Fenwick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eli Oughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson McQuade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Kim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Dykyj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jueun Chung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Meade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayan Alazem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Underwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Smid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Velocci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikolas Proksel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinten Shannon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Stonehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Vivaldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U of T Varsity Blues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elias Rubio Reyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elis Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haven Tai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Barber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Gannett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Worthen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Verman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Zidros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Hsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spenser Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomoki Yamamoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woochan Nam</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adam Leatherland</t>
   </si>
   <si>
-    <t xml:space="preserve">McMaster Marauders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anden Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon McMurray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brody Nguyen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coy Gordon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declan Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devan Fenwick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward (Hong Yu) Cheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eli Oughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson McQuade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Kim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Dykyj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jueun Chung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Meade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayan Alazem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Underwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Smid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolas Velocci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikolas Proksel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinten Shannon</t>
+    <t xml:space="preserve">Waterloo Warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Rusch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Kowara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter Kipp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Smart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declan Uniac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Pawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonah Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junichi Yuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalan Maharaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Greaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Todd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myles Hazen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Valvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raywat Bajracharya</t>
   </si>
   <si>
     <t xml:space="preserve">Rhys Jenkyn</t>
   </si>
   <si>
+    <t xml:space="preserve">Sam Grant</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sam Shephard</t>
   </si>
   <si>
-    <t xml:space="preserve">Sydney Stonehouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidan Vivaldi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U of T Varsity Blues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elias Rubio Reyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elis Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haven Tai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Barber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Gannett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Worthen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirk Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Verman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Zidros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Hsu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spenser Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomoki Yamamoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woochan Nam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterloo Warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Rusch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Kowara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carter Kipp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Smart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declan Uniac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Pawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonah Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junichi Yuki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalan Maharaj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Greaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Todd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myles Hazen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raywat Bajracharya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Grant</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ty Tinnish</t>
   </si>
   <si>
@@ -606,67 +606,67 @@
     <t xml:space="preserve">Jaden Fonseca</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcello Colucci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premnath Nayak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Cabezas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taio Fotiou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Nguyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenny Leung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kojiro Hirata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ravin Yuvarajan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taisei Hihara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidan Armitage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaxx Carthy</t>
   </si>
   <si>
+    <t xml:space="preserve">Justin Mende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Valvo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maddox Yee</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcello Colucci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premnath Nayak</t>
+    <t xml:space="preserve">Myles Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Newman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Toon</t>
   </si>
   <si>
     <t xml:space="preserve">Risden Dimayuga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McMillan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Cabezas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taio Fotiou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Nguyen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kenny Leung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kojiro Hirata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ravin Yuvarajan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taisei Hihara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidan Armitage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Mende</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Valvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myles Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Newman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Toon</t>
   </si>
   <si>
     <t xml:space="preserve">Connor Lynch</t>
@@ -790,8 +790,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K154" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K145" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K145"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -810,8 +810,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K87" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K87"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K83" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K83"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2525,23 +2525,33 @@
       <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
+      <c r="C41" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41"/>
+        <v>40</v>
+      </c>
+      <c r="K41" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -2551,31 +2561,31 @@
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="H42" t="n">
-        <v>36.4</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>40</v>
+        <v>83.3</v>
       </c>
       <c r="J42" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="43">
@@ -2586,31 +2596,31 @@
         <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2624,19 +2634,19 @@
         <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
@@ -2645,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -2656,19 +2666,19 @@
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="n">
-        <v>50</v>
+        <v>27.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2680,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2691,28 +2701,28 @@
         <v>53</v>
       </c>
       <c r="C46" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>27.5</v>
+        <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2726,31 +2736,31 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>100</v>
+        <v>47.1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>30.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G47" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J47" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="48">
@@ -2761,31 +2771,31 @@
         <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>47.1</v>
+        <v>66.7</v>
       </c>
       <c r="D48" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>30.4</v>
+        <v>41.7</v>
       </c>
       <c r="F48" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>57.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -2796,31 +2806,31 @@
         <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>66.7</v>
+        <v>70.6</v>
       </c>
       <c r="D49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>41.7</v>
+        <v>60.6</v>
       </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I49" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -2831,32 +2841,24 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>73.3</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>56.6</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>33.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50"/>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="n">
-        <v>60</v>
-      </c>
-      <c r="J50" t="n">
-        <v>20</v>
-      </c>
-      <c r="K50" t="n">
-        <v>80</v>
-      </c>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
@@ -2866,24 +2868,32 @@
         <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>38.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51"/>
+        <v>17.4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>16</v>
+      </c>
       <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
+        <v>5.9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>50</v>
+      </c>
+      <c r="J51" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -2893,31 +2903,31 @@
         <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="D52" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>38.2</v>
+        <v>42.5</v>
       </c>
       <c r="F52" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="H52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -2928,31 +2938,31 @@
         <v>53</v>
       </c>
       <c r="C53" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E53" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G53" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2963,31 +2973,31 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55">
@@ -2998,31 +3008,31 @@
         <v>53</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G55" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>25</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="56">
@@ -3033,31 +3043,31 @@
         <v>53</v>
       </c>
       <c r="C56" t="n">
-        <v>57.7</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>49.4</v>
+        <v>66.7</v>
       </c>
       <c r="F56" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H56" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -3068,28 +3078,28 @@
         <v>53</v>
       </c>
       <c r="C57" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E57" t="n">
-        <v>66.7</v>
+        <v>41.3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G57" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>50</v>
+      </c>
+      <c r="J57" t="n">
         <v>25</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>50</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>50</v>
@@ -3103,31 +3113,31 @@
         <v>53</v>
       </c>
       <c r="C58" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="D58" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>41.3</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="59">
@@ -3138,31 +3148,31 @@
         <v>53</v>
       </c>
       <c r="C59" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I59" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K59" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -3173,31 +3183,31 @@
         <v>53</v>
       </c>
       <c r="C60" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>20</v>
+      </c>
+      <c r="E60" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>66.7</v>
-      </c>
-      <c r="D60" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E60" t="n">
-        <v>50</v>
-      </c>
-      <c r="F60" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G60" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>20</v>
-      </c>
-      <c r="J60" t="n">
-        <v>40</v>
-      </c>
-      <c r="K60" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3208,31 +3218,31 @@
         <v>53</v>
       </c>
       <c r="C61" t="n">
-        <v>85.7</v>
+        <v>38.1</v>
       </c>
       <c r="D61" t="n">
-        <v>20</v>
+        <v>45.5</v>
       </c>
       <c r="E61" t="n">
-        <v>65.7</v>
+        <v>-7.4</v>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>45.5</v>
       </c>
       <c r="G61" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I61" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3243,31 +3253,31 @@
         <v>53</v>
       </c>
       <c r="C62" t="n">
-        <v>38.1</v>
+        <v>62.5</v>
       </c>
       <c r="D62" t="n">
-        <v>52.6</v>
+        <v>38.5</v>
       </c>
       <c r="E62" t="n">
-        <v>-14.5</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
-        <v>52.6</v>
+        <v>38.5</v>
       </c>
       <c r="G62" t="n">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="H62" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="J62" t="n">
         <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="63">
@@ -3275,12 +3285,20 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
-      </c>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
+        <v>76</v>
+      </c>
+      <c r="C63" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
@@ -3288,110 +3306,118 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" t="s">
         <v>76</v>
       </c>
-      <c r="B64" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
+      <c r="C64" t="n">
+        <v>75</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E64" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>16.7</v>
+      </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C65" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="D65" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K65" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C66" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E66" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3399,34 +3425,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C67" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="D67" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="E67" t="n">
-        <v>58.3</v>
+        <v>5.6</v>
       </c>
       <c r="F67" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3434,34 +3460,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C68" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="n">
-        <v>80</v>
+        <v>43.1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -3469,7 +3495,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C69" t="n">
         <v>66.7</v>
@@ -3484,19 +3510,19 @@
         <v>20</v>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H69" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J69" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -3504,22 +3530,22 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C70" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3528,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3539,34 +3565,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C71" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>43.1</v>
+        <v>25</v>
       </c>
       <c r="F71" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3574,34 +3600,28 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C72" t="n">
+        <v>80</v>
+      </c>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J72" t="n">
         <v>66.7</v>
       </c>
-      <c r="D72" t="n">
-        <v>20</v>
-      </c>
-      <c r="E72" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F72" t="n">
-        <v>20</v>
-      </c>
-      <c r="G72" t="n">
-        <v>40</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>50</v>
-      </c>
-      <c r="J72" t="n">
-        <v>50</v>
-      </c>
       <c r="K72" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="73">
@@ -3609,31 +3629,31 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>78.6</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3644,34 +3664,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C74" t="n">
+        <v>100</v>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="n">
         <v>75</v>
       </c>
-      <c r="D74" t="n">
-        <v>50</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>25</v>
       </c>
-      <c r="F74" t="n">
-        <v>50</v>
-      </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="75">
@@ -3679,28 +3699,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C75" t="n">
-        <v>80</v>
-      </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
+        <v>46.7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20</v>
+      </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J75" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
@@ -3708,34 +3734,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C76" t="n">
-        <v>78.6</v>
+        <v>66.7</v>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>75</v>
       </c>
       <c r="E76" t="n">
-        <v>67.5</v>
+        <v>-8.3</v>
       </c>
       <c r="F76" t="n">
-        <v>11.1</v>
+        <v>75</v>
       </c>
       <c r="G76" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="H76" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -3743,63 +3769,57 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="E77" t="n">
-        <v>75</v>
+        <v>36.1</v>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K77" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
         <v>91</v>
       </c>
-      <c r="B78" t="s">
-        <v>79</v>
-      </c>
       <c r="C78" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="D78" t="n">
-        <v>20</v>
-      </c>
-      <c r="E78" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F78" t="n">
-        <v>20</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
       <c r="G78" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -3810,444 +3830,480 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>66.7</v>
+        <v>73.1</v>
       </c>
       <c r="D79" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E79" t="n">
-        <v>-8.3</v>
+        <v>48.1</v>
       </c>
       <c r="F79" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G79" t="n">
-        <v>33.3</v>
+        <v>17.9</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I79" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="J79" t="n">
-        <v>25</v>
+        <v>54.5</v>
       </c>
       <c r="K79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>67.7</v>
+        <v>75</v>
       </c>
       <c r="D80" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>36.1</v>
+        <v>75</v>
       </c>
       <c r="F80" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>63.6</v>
+        <v>33.3</v>
       </c>
       <c r="J80" t="n">
-        <v>9.1</v>
+        <v>33.3</v>
       </c>
       <c r="K80" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>100</v>
-      </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
+        <v>83.9</v>
+      </c>
+      <c r="D81" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E81" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7.7</v>
+      </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K81" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82"/>
+        <v>91</v>
+      </c>
+      <c r="C82" t="n">
+        <v>58.3</v>
+      </c>
       <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82"/>
+        <v>9.1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>49.2</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82"/>
-      <c r="J82"/>
-      <c r="K82"/>
+        <v>16.7</v>
+      </c>
+      <c r="I82" t="n">
+        <v>75</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C83" t="n">
-        <v>73.1</v>
+        <v>75</v>
       </c>
       <c r="D83" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>48.1</v>
+        <v>75</v>
       </c>
       <c r="F83" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>12.5</v>
+        <v>28.6</v>
       </c>
       <c r="I83" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="J83" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="E84" t="n">
-        <v>75</v>
+        <v>31.6</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I84" t="n">
         <v>33.3</v>
       </c>
       <c r="J84" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K84" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>83.9</v>
+        <v>71.4</v>
       </c>
       <c r="D85" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>76.2</v>
+        <v>71.4</v>
       </c>
       <c r="F85" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>7.1</v>
+        <v>40</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="J85" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C86" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="D86" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="E86" t="n">
-        <v>49.2</v>
+        <v>43.3</v>
       </c>
       <c r="F86" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="G86" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H86" t="n">
-        <v>16.7</v>
+        <v>7.1</v>
       </c>
       <c r="I86" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K86" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="D87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
-      <c r="I87"/>
-      <c r="J87"/>
-      <c r="K87"/>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>100</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H88" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E89" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H89" t="n">
-        <v>100</v>
-      </c>
-      <c r="I89"/>
-      <c r="J89"/>
-      <c r="K89"/>
+        <v>50</v>
+      </c>
+      <c r="I89" t="n">
+        <v>50</v>
+      </c>
+      <c r="J89" t="n">
+        <v>50</v>
+      </c>
+      <c r="K89" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>104</v>
+      </c>
+      <c r="B90" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D90" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>50</v>
+      </c>
+      <c r="F90" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>50</v>
+      </c>
+      <c r="J90" t="n">
+        <v>50</v>
+      </c>
+      <c r="K90" t="n">
         <v>100</v>
-      </c>
-      <c r="B90" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="D90" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E90" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F90" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G90" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H90" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I90" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>50</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C91" t="n">
-        <v>71.4</v>
+        <v>59.1</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>71.4</v>
+        <v>59.1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>40</v>
+        <v>15.4</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I91" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K91" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
+        <v>91</v>
+      </c>
+      <c r="C92" t="n">
+        <v>100</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>100</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4264,524 +4320,544 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C93" t="n">
-        <v>53.3</v>
+        <v>75</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>23.1</v>
       </c>
       <c r="E93" t="n">
-        <v>43.3</v>
+        <v>51.9</v>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>23.1</v>
       </c>
       <c r="G93" t="n">
-        <v>35</v>
+        <v>19.4</v>
       </c>
       <c r="H93" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="I93" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="J93" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C94" t="n">
-        <v>37.5</v>
+        <v>81.8</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E94" t="n">
-        <v>37.5</v>
+        <v>72.7</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G94" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J94" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C95" t="n">
-        <v>100</v>
+        <v>67.6</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>60.5</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="G95" t="n">
-        <v>50</v>
+        <v>7.1</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C96" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D96" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>43.3</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C97" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="D97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="F97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="I97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J97" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K97" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C98" t="n">
-        <v>59.1</v>
+        <v>57.1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>8.7</v>
       </c>
       <c r="E98" t="n">
-        <v>59.1</v>
+        <v>48.4</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>8.7</v>
       </c>
       <c r="G98" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="H98" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="I98" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J98" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
-      </c>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
+        <v>112</v>
+      </c>
+      <c r="C99" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E99" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G99" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99"/>
-      <c r="J99"/>
-      <c r="K99"/>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
-      </c>
-      <c r="C100"/>
+        <v>112</v>
+      </c>
+      <c r="C100" t="n">
+        <v>88.9</v>
+      </c>
       <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100"/>
+        <v>13.3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>75.6</v>
+      </c>
       <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100"/>
+        <v>13.3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>20</v>
+      </c>
       <c r="H100" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>20</v>
+      </c>
+      <c r="J100" t="n">
+        <v>60</v>
+      </c>
+      <c r="K100" t="n">
         <v>100</v>
       </c>
-      <c r="I100"/>
-      <c r="J100"/>
-      <c r="K100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>88.9</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>100</v>
+        <v>88.9</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I101" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C102" t="n">
-        <v>75</v>
+        <v>78.6</v>
       </c>
       <c r="D102" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>51.9</v>
+        <v>78.6</v>
       </c>
       <c r="F102" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="H102" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>54.5</v>
+        <v>85.7</v>
       </c>
       <c r="J102" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C103" t="n">
-        <v>81.8</v>
+        <v>57.1</v>
       </c>
       <c r="D103" t="n">
         <v>9.1</v>
       </c>
       <c r="E103" t="n">
-        <v>72.7</v>
+        <v>48</v>
       </c>
       <c r="F103" t="n">
         <v>9.1</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H103" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I103" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C104" t="n">
-        <v>67.6</v>
+        <v>64.3</v>
       </c>
       <c r="D104" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>60.5</v>
+        <v>64.3</v>
       </c>
       <c r="F104" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>8</v>
+        <v>11.1</v>
       </c>
       <c r="H104" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="I104" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J104" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C105" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E105" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C106" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E106" t="n">
-        <v>66.7</v>
+        <v>60.7</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G106" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="H106" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="I106" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J106" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K106" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
         <v>112</v>
       </c>
       <c r="C107" t="n">
-        <v>57.1</v>
+        <v>43.8</v>
       </c>
       <c r="D107" t="n">
-        <v>8.7</v>
+        <v>9.1</v>
       </c>
       <c r="E107" t="n">
-        <v>48.4</v>
+        <v>34.7</v>
       </c>
       <c r="F107" t="n">
-        <v>8.7</v>
+        <v>9.1</v>
       </c>
       <c r="G107" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="H107" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
       <c r="I107" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J107" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K107" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B108" t="s">
         <v>112</v>
       </c>
       <c r="C108" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="D108" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E108" t="n">
-        <v>20</v>
-      </c>
-      <c r="F108" t="n">
-        <v>26.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -4790,386 +4866,392 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="K108" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>88.9</v>
+        <v>92.6</v>
       </c>
       <c r="D109" t="n">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="E109" t="n">
-        <v>75.6</v>
+        <v>87.3</v>
       </c>
       <c r="F109" t="n">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="G109" t="n">
-        <v>20</v>
+        <v>7.7</v>
       </c>
       <c r="H109" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I109" t="n">
-        <v>20</v>
+        <v>64.3</v>
       </c>
       <c r="J109" t="n">
-        <v>60</v>
+        <v>21.4</v>
       </c>
       <c r="K109" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B110" t="s">
         <v>112</v>
       </c>
       <c r="C110" t="n">
-        <v>88.9</v>
+        <v>56.2</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="n">
-        <v>88.9</v>
+        <v>43.7</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H110" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J110" t="n">
         <v>14.3</v>
       </c>
-      <c r="I110" t="n">
-        <v>80</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
       <c r="K110" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
         <v>112</v>
       </c>
       <c r="C111" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="n">
-        <v>78.6</v>
+        <v>62.5</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G111" t="n">
-        <v>9.1</v>
+        <v>23.1</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I111" t="n">
-        <v>85.7</v>
+        <v>40</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
         <v>112</v>
       </c>
       <c r="C112" t="n">
-        <v>57.1</v>
+        <v>71.4</v>
       </c>
       <c r="D112" t="n">
-        <v>9.1</v>
+        <v>9.7</v>
       </c>
       <c r="E112" t="n">
-        <v>48</v>
+        <v>61.7</v>
       </c>
       <c r="F112" t="n">
-        <v>9.1</v>
+        <v>9.7</v>
       </c>
       <c r="G112" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H112" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="K112" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B113" t="s">
         <v>112</v>
       </c>
       <c r="C113" t="n">
-        <v>64.3</v>
+        <v>55.6</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E113" t="n">
-        <v>64.3</v>
+        <v>38.9</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G113" t="n">
-        <v>11.1</v>
+        <v>28.6</v>
       </c>
       <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>50</v>
+      </c>
+      <c r="J113" t="n">
         <v>25</v>
       </c>
-      <c r="I113" t="n">
-        <v>40</v>
-      </c>
-      <c r="J113" t="n">
-        <v>20</v>
-      </c>
       <c r="K113" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B114" t="s">
         <v>112</v>
       </c>
       <c r="C114" t="n">
-        <v>80</v>
+        <v>68.8</v>
       </c>
       <c r="D114" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I114" t="n">
         <v>25</v>
       </c>
-      <c r="E114" t="n">
-        <v>55</v>
-      </c>
-      <c r="F114" t="n">
-        <v>25</v>
-      </c>
-      <c r="G114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>57.1</v>
-      </c>
       <c r="J114" t="n">
-        <v>14.3</v>
+        <v>8.3</v>
       </c>
       <c r="K114" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C115" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="D115" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="E115" t="n">
-        <v>60.7</v>
+        <v>52.4</v>
       </c>
       <c r="F115" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="G115" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="H115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>50</v>
+      </c>
+      <c r="J115" t="n">
         <v>33.3</v>
       </c>
-      <c r="I115" t="n">
-        <v>50</v>
-      </c>
-      <c r="J115" t="n">
-        <v>50</v>
-      </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C116" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
       <c r="D116" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="E116" t="n">
-        <v>34.7</v>
+        <v>33.4</v>
       </c>
       <c r="F116" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="G116" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="H116" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="J116" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C117" t="n">
-        <v>100</v>
-      </c>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
+        <v>80.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F117" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C118" t="n">
-        <v>92.6</v>
+        <v>91.7</v>
       </c>
       <c r="D118" t="n">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="E118" t="n">
-        <v>87.3</v>
+        <v>41.7</v>
       </c>
       <c r="F118" t="n">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="G118" t="n">
-        <v>7.7</v>
+        <v>21.4</v>
       </c>
       <c r="H118" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>64.3</v>
+        <v>28.6</v>
       </c>
       <c r="J118" t="n">
-        <v>21.4</v>
+        <v>42.9</v>
       </c>
       <c r="K118" t="n">
-        <v>57.1</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C119" t="n">
-        <v>56.2</v>
+        <v>60</v>
       </c>
       <c r="D119" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>43.7</v>
+        <v>60</v>
       </c>
       <c r="F119" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="J119" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5177,104 +5259,104 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C120" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D120" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E120" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="F120" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G120" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="H120" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="J120" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C121" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D121" t="n">
-        <v>9.7</v>
+        <v>8.3</v>
       </c>
       <c r="E121" t="n">
-        <v>61.7</v>
+        <v>66.7</v>
       </c>
       <c r="F121" t="n">
-        <v>9.7</v>
+        <v>8.3</v>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="J121" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="K121" t="n">
-        <v>54.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C122" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="D122" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>38.9</v>
+        <v>100</v>
       </c>
       <c r="F122" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5282,241 +5364,241 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C123" t="n">
-        <v>68.8</v>
+        <v>83.3</v>
       </c>
       <c r="D123" t="n">
-        <v>10.3</v>
+        <v>28.6</v>
       </c>
       <c r="E123" t="n">
-        <v>58.5</v>
+        <v>54.7</v>
       </c>
       <c r="F123" t="n">
-        <v>10.3</v>
+        <v>28.6</v>
       </c>
       <c r="G123" t="n">
-        <v>12</v>
+        <v>16.7</v>
       </c>
       <c r="H123" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="J123" t="n">
-        <v>8.3</v>
+        <v>33.3</v>
       </c>
       <c r="K123" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
         <v>130</v>
       </c>
       <c r="C124" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>25</v>
+      </c>
+      <c r="H124" t="n">
         <v>14.3</v>
       </c>
-      <c r="E124" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F124" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G124" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="H124" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I124" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J124" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B125" t="s">
         <v>130</v>
       </c>
       <c r="C125" t="n">
-        <v>55.6</v>
+        <v>70</v>
       </c>
       <c r="D125" t="n">
-        <v>22.2</v>
+        <v>37.5</v>
       </c>
       <c r="E125" t="n">
-        <v>33.4</v>
+        <v>32.5</v>
       </c>
       <c r="F125" t="n">
-        <v>22.2</v>
+        <v>37.5</v>
       </c>
       <c r="G125" t="n">
-        <v>42.9</v>
+        <v>17.6</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B126" t="s">
         <v>130</v>
       </c>
       <c r="C126" t="n">
-        <v>80.8</v>
+        <v>75</v>
       </c>
       <c r="D126" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="E126" t="n">
-        <v>62.6</v>
+        <v>53.6</v>
       </c>
       <c r="F126" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="G126" t="n">
-        <v>36</v>
+        <v>46.7</v>
       </c>
       <c r="H126" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="I126" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="J126" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B127" t="s">
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>91.7</v>
+        <v>84.6</v>
       </c>
       <c r="D127" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="E127" t="n">
-        <v>41.7</v>
+        <v>70.3</v>
       </c>
       <c r="F127" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="G127" t="n">
-        <v>21.4</v>
+        <v>13</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>28.6</v>
+        <v>43.8</v>
       </c>
       <c r="J127" t="n">
-        <v>42.9</v>
+        <v>18.8</v>
       </c>
       <c r="K127" t="n">
-        <v>71.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B128" t="s">
         <v>130</v>
       </c>
       <c r="C128" t="n">
-        <v>60</v>
+        <v>68.6</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E128" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I128" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B129" t="s">
         <v>130</v>
       </c>
       <c r="C129" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D129" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5527,63 +5609,63 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B130" t="s">
         <v>130</v>
       </c>
       <c r="C130" t="n">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="D130" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E130" t="n">
+        <v>70.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>20</v>
+      </c>
+      <c r="G130" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
         <v>66.7</v>
       </c>
-      <c r="F130" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>50</v>
-      </c>
       <c r="J130" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K130" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B131" t="s">
         <v>130</v>
       </c>
       <c r="C131" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="E131" t="n">
-        <v>100</v>
+        <v>17.1</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5592,30 +5674,30 @@
         <v>100</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B132" t="s">
         <v>130</v>
       </c>
       <c r="C132" t="n">
-        <v>83.3</v>
+        <v>90</v>
       </c>
       <c r="D132" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="E132" t="n">
-        <v>54.7</v>
+        <v>73.3</v>
       </c>
       <c r="F132" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="G132" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -5624,246 +5706,228 @@
         <v>33.3</v>
       </c>
       <c r="J132" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K132" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B133" t="s">
         <v>130</v>
       </c>
       <c r="C133" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J133" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K133" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C134" t="n">
-        <v>70</v>
+        <v>16.7</v>
       </c>
       <c r="D134" t="n">
-        <v>37.5</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="n">
-        <v>32.5</v>
+        <v>5.6</v>
       </c>
       <c r="F134" t="n">
-        <v>37.5</v>
+        <v>11.1</v>
       </c>
       <c r="G134" t="n">
-        <v>17.6</v>
+        <v>50</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J134" t="n">
-        <v>25</v>
-      </c>
-      <c r="K134" t="n">
-        <v>25</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I134"/>
+      <c r="J134"/>
+      <c r="K134"/>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C135" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="D135" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>53.6</v>
+        <v>42.9</v>
       </c>
       <c r="F135" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="H135" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I135" t="n">
         <v>66.7</v>
       </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="I135"/>
+      <c r="J135"/>
+      <c r="K135"/>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C136" t="n">
-        <v>84.6</v>
+        <v>33.3</v>
       </c>
       <c r="D136" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>70.3</v>
+        <v>33.3</v>
       </c>
       <c r="F136" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
-      <c r="I136" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J136" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K136" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="I136"/>
+      <c r="J136"/>
+      <c r="K136"/>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C137" t="n">
-        <v>68.6</v>
+        <v>61.1</v>
       </c>
       <c r="D137" t="n">
         <v>9.1</v>
       </c>
       <c r="E137" t="n">
-        <v>59.5</v>
+        <v>52</v>
       </c>
       <c r="F137" t="n">
         <v>9.1</v>
       </c>
       <c r="G137" t="n">
-        <v>23.1</v>
+        <v>8.3</v>
       </c>
       <c r="H137" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>33.3</v>
+        <v>85.7</v>
       </c>
       <c r="J137" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C138" t="n">
         <v>50</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E138" t="n">
-        <v>50</v>
+        <v>31.8</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I138" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C139" t="n">
-        <v>90.9</v>
+        <v>50</v>
       </c>
       <c r="D139" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="E139" t="n">
-        <v>70.9</v>
+        <v>26.9</v>
       </c>
       <c r="F139" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="G139" t="n">
-        <v>27.3</v>
+        <v>37.5</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I139" t="n">
         <v>66.7</v>
@@ -5872,511 +5936,214 @@
         <v>33.3</v>
       </c>
       <c r="K139" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C140" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="D140" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="E140" t="n">
-        <v>17.1</v>
+        <v>41.7</v>
       </c>
       <c r="F140" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="G140" t="n">
         <v>33.3</v>
       </c>
       <c r="H140" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J140" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C141" t="n">
-        <v>90</v>
+        <v>61.5</v>
       </c>
       <c r="D141" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>73.3</v>
+        <v>61.5</v>
       </c>
       <c r="F141" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I141" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J141" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C142" t="n">
+        <v>45</v>
+      </c>
+      <c r="D142" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E142" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G142" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
         <v>100</v>
       </c>
-      <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="n">
-        <v>100</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>33.3</v>
-      </c>
       <c r="J142" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B143" t="s">
         <v>150</v>
       </c>
       <c r="C143" t="n">
-        <v>16.7</v>
+        <v>71.4</v>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E143" t="n">
-        <v>5.6</v>
+        <v>51.4</v>
       </c>
       <c r="F143" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="G143" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H143" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I143"/>
-      <c r="J143"/>
-      <c r="K143"/>
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>50</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B144" t="s">
         <v>150</v>
       </c>
       <c r="C144" t="n">
-        <v>42.9</v>
+        <v>71.4</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E144" t="n">
-        <v>42.9</v>
+        <v>64.3</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="G144" t="n">
-        <v>66.7</v>
+        <v>18.2</v>
       </c>
       <c r="H144" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I144"/>
-      <c r="J144"/>
-      <c r="K144"/>
+        <v>12.5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>100</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
-        <v>152</v>
-      </c>
+      <c r="A145"/>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C145" t="n">
-        <v>33.3</v>
+        <v>68.1</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="E145" t="n">
-        <v>33.3</v>
+        <v>53.2</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145"/>
-      <c r="J145"/>
-      <c r="K145"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>153</v>
-      </c>
-      <c r="B146" t="s">
-        <v>150</v>
-      </c>
-      <c r="C146" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="D146" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>52</v>
-      </c>
-      <c r="F146" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>154</v>
-      </c>
-      <c r="B147" t="s">
-        <v>150</v>
-      </c>
-      <c r="C147" t="n">
-        <v>50</v>
-      </c>
-      <c r="D147" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="E147" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="F147" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G147" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H147" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
-        <v>75</v>
-      </c>
-      <c r="K147" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>155</v>
-      </c>
-      <c r="B148" t="s">
-        <v>150</v>
-      </c>
-      <c r="C148" t="n">
-        <v>50</v>
-      </c>
-      <c r="D148" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="F148" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H148" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I148" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K148" t="n">
-        <v>66.7</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>156</v>
-      </c>
-      <c r="B149" t="s">
-        <v>150</v>
-      </c>
-      <c r="C149" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D149" t="n">
-        <v>25</v>
-      </c>
-      <c r="E149" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F149" t="n">
-        <v>25</v>
-      </c>
-      <c r="G149" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" t="n">
-        <v>100</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>157</v>
-      </c>
-      <c r="B150" t="s">
-        <v>150</v>
-      </c>
-      <c r="C150" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H150" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I150" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="J150" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K150" t="n">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>158</v>
-      </c>
-      <c r="B151" t="s">
-        <v>150</v>
-      </c>
-      <c r="C151" t="n">
-        <v>45</v>
-      </c>
-      <c r="D151" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E151" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="F151" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G151" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>100</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>159</v>
-      </c>
-      <c r="B152" t="s">
-        <v>150</v>
-      </c>
-      <c r="C152" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="D152" t="n">
-        <v>20</v>
-      </c>
-      <c r="E152" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="F152" t="n">
-        <v>20</v>
-      </c>
-      <c r="G152" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="n">
-        <v>50</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>160</v>
-      </c>
-      <c r="B153" t="s">
-        <v>150</v>
-      </c>
-      <c r="C153" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="D153" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F153" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H153" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>100</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154"/>
-      <c r="B154" t="s">
-        <v>161</v>
-      </c>
-      <c r="C154" t="n">
-        <v>67.9</v>
-      </c>
-      <c r="D154" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E154" t="n">
-        <v>53</v>
-      </c>
-      <c r="F154" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="G154" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H154" t="n">
-        <v>10</v>
-      </c>
-      <c r="I154" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="J154" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="I145" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J145" t="n">
         <v>27</v>
       </c>
-      <c r="K154" t="n">
+      <c r="K145" t="n">
         <v>35.7</v>
       </c>
     </row>
@@ -7498,36 +7265,36 @@
         <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="D32" t="n">
-        <v>56.4</v>
+        <v>57.3</v>
       </c>
       <c r="E32" t="n">
         <v>6.9</v>
       </c>
       <c r="F32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="G32" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="H32" t="n">
-        <v>36</v>
+        <v>37.9</v>
       </c>
       <c r="I32" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J32" t="n">
-        <v>11.9</v>
+        <v>10.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
@@ -7638,19 +7405,21 @@
         <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
-      </c>
-      <c r="E36"/>
-      <c r="F36" t="n">
-        <v>100</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36"/>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36"/>
+      <c r="H36" t="n">
+        <v>33.3</v>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7658,7 +7427,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -7669,29 +7438,31 @@
         <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="D37" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
-      </c>
-      <c r="H37"/>
+        <v>28.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>-25</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="38">
@@ -7702,26 +7473,28 @@
         <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38"/>
+        <v>5.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>42.9</v>
+      </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H38" t="n">
-        <v>33.3</v>
+        <v>91.7</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -7735,31 +7508,31 @@
         <v>53</v>
       </c>
       <c r="C39" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>40</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K39" t="n">
         <v>28.6</v>
-      </c>
-      <c r="D39" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-28.6</v>
       </c>
     </row>
     <row r="40">
@@ -7770,31 +7543,31 @@
         <v>53</v>
       </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D40" t="n">
-        <v>52.2</v>
+        <v>66.7</v>
       </c>
       <c r="E40" t="n">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>6.7</v>
       </c>
       <c r="H40" t="n">
-        <v>91.7</v>
+        <v>18.2</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>23.1</v>
+        <v>19.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="41">
@@ -7805,29 +7578,29 @@
         <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="E41"/>
-      <c r="F41" t="n">
-        <v>100</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41"/>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -7838,31 +7611,31 @@
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>71.4</v>
+        <v>55.6</v>
       </c>
       <c r="D42" t="n">
-        <v>70.2</v>
+        <v>46.2</v>
       </c>
       <c r="E42" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="H42" t="n">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="J42" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>28.6</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="43">
@@ -7870,34 +7643,34 @@
         <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C43" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="D43" t="n">
-        <v>66.7</v>
+        <v>49.2</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G43" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="H43" t="n">
-        <v>18.2</v>
+        <v>46.2</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -7905,29 +7678,31 @@
         <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C44" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
+        <v>52.9</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44"/>
+        <v>11.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>50</v>
+      </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -7938,34 +7713,28 @@
         <v>206</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C45" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>46.2</v>
+        <v>7.7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45"/>
       <c r="G45" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>14.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H45"/>
       <c r="I45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J45"/>
       <c r="K45" t="n">
-        <v>-22.2</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="46">
@@ -7973,31 +7742,31 @@
         <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C46" t="n">
-        <v>44.4</v>
+        <v>35.3</v>
       </c>
       <c r="D46" t="n">
-        <v>49.2</v>
+        <v>57.6</v>
       </c>
       <c r="E46" t="n">
-        <v>9.1</v>
+        <v>17.6</v>
       </c>
       <c r="F46" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="H46" t="n">
-        <v>46.2</v>
+        <v>23.1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -8008,31 +7777,31 @@
         <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D47" t="n">
-        <v>52.9</v>
+        <v>63.2</v>
       </c>
       <c r="E47" t="n">
-        <v>11.8</v>
+        <v>7.1</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
       <c r="G47" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H47" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>7.7</v>
+        <v>10.5</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -8040,115 +7809,121 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>7.7</v>
+        <v>55</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
       <c r="G48" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48"/>
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>20</v>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48"/>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
       <c r="K48" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C49" t="n">
-        <v>35.3</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="E49" t="n">
-        <v>17.6</v>
+        <v>13.6</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="H49" t="n">
-        <v>23.1</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C50" t="n">
-        <v>55.6</v>
+        <v>68.8</v>
       </c>
       <c r="D50" t="n">
-        <v>63.2</v>
+        <v>72.5</v>
       </c>
       <c r="E50" t="n">
-        <v>7.1</v>
+        <v>23.1</v>
       </c>
       <c r="F50" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="G50" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>28.6</v>
+        <v>77.8</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>10.5</v>
+        <v>29.2</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" t="s">
         <v>91</v>
       </c>
-      <c r="B51" t="s">
-        <v>79</v>
-      </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D51" t="n">
-        <v>55</v>
+        <v>87.5</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -8160,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -8174,228 +7949,228 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C52" t="n">
-        <v>63</v>
+        <v>52.9</v>
       </c>
       <c r="D52" t="n">
-        <v>57.8</v>
+        <v>60.8</v>
       </c>
       <c r="E52" t="n">
-        <v>13.6</v>
+        <v>16.7</v>
       </c>
       <c r="F52" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="G52" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>23.5</v>
+        <v>32.1</v>
       </c>
       <c r="K52" t="n">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C53" t="n">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="D53" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E53"/>
+        <v>74.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>28.6</v>
+      </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H53" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C54" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F54" t="n">
         <v>66.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="E54" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>62.5</v>
-      </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H54" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>30.4</v>
+        <v>28.6</v>
       </c>
       <c r="K54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C55" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>87.5</v>
+        <v>56.4</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H55" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C56" t="n">
-        <v>52.9</v>
+        <v>60</v>
       </c>
       <c r="D56" t="n">
-        <v>60.8</v>
+        <v>63.3</v>
       </c>
       <c r="E56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G56" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>42.9</v>
+        <v>88.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>32.1</v>
+        <v>23.5</v>
       </c>
       <c r="K56" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C57" t="n">
-        <v>69.2</v>
+        <v>36.4</v>
       </c>
       <c r="D57" t="n">
-        <v>74.7</v>
+        <v>60.5</v>
       </c>
       <c r="E57" t="n">
-        <v>28.6</v>
+        <v>5.3</v>
       </c>
       <c r="F57" t="n">
         <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>3.8</v>
+        <v>27.3</v>
       </c>
       <c r="H57" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>24.4</v>
+        <v>11.1</v>
       </c>
       <c r="K57" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D58" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>50</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="E58"/>
       <c r="F58" t="n">
         <v>100</v>
       </c>
@@ -8403,159 +8178,161 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C59" t="n">
         <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>56.4</v>
+        <v>53.6</v>
       </c>
       <c r="E59" t="n">
-        <v>10.3</v>
+        <v>13.3</v>
       </c>
       <c r="F59" t="n">
-        <v>29.4</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>27.8</v>
+        <v>26.7</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C60" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="D60" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>30.8</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H60" t="n">
-        <v>88.9</v>
+        <v>66.7</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>23.5</v>
+        <v>21.4</v>
       </c>
       <c r="K60" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C61" t="n">
-        <v>36.4</v>
+        <v>70</v>
       </c>
       <c r="D61" t="n">
-        <v>60.5</v>
+        <v>70.4</v>
       </c>
       <c r="E61" t="n">
-        <v>5.3</v>
+        <v>15.8</v>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="G61" t="n">
-        <v>27.3</v>
+        <v>3.3</v>
       </c>
       <c r="H61" t="n">
-        <v>60</v>
+        <v>34.8</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>11.1</v>
+        <v>22</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C62" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="D62" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="E62"/>
+        <v>65.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>31.4</v>
+      </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="K62" t="n">
-        <v>33.3</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B63" t="s">
         <v>112</v>
@@ -8564,313 +8341,313 @@
         <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>53.6</v>
+        <v>63.2</v>
       </c>
       <c r="E63" t="n">
-        <v>13.3</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>26.7</v>
+        <v>37.5</v>
       </c>
       <c r="K63" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B64" t="s">
         <v>112</v>
       </c>
       <c r="C64" t="n">
-        <v>61.5</v>
+        <v>46.4</v>
       </c>
       <c r="D64" t="n">
-        <v>63.2</v>
+        <v>53.9</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="F64" t="n">
-        <v>30.8</v>
+        <v>36.4</v>
       </c>
       <c r="G64" t="n">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="H64" t="n">
-        <v>66.7</v>
+        <v>35.3</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C65" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D65" t="n">
-        <v>70.4</v>
+        <v>41.2</v>
       </c>
       <c r="E65" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="H65" t="n">
-        <v>34.8</v>
+        <v>33.3</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K65" t="n">
-        <v>16.7</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C66" t="n">
-        <v>58.3</v>
+        <v>14.3</v>
       </c>
       <c r="D66" t="n">
-        <v>65.3</v>
+        <v>44.1</v>
       </c>
       <c r="E66" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H66" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K66" t="n">
-        <v>8.3</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>63.2</v>
+        <v>38.9</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
         <v>66.7</v>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>50</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C68" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>53.9</v>
+        <v>57.9</v>
       </c>
       <c r="E68" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="H68" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>23.7</v>
+        <v>28.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
         <v>130</v>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D69" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="H69" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K69" t="n">
-        <v>-20</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
         <v>130</v>
       </c>
       <c r="C70" t="n">
-        <v>14.3</v>
+        <v>57.1</v>
       </c>
       <c r="D70" t="n">
-        <v>44.1</v>
+        <v>57.5</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="F70" t="n">
-        <v>33.3</v>
+        <v>51.9</v>
       </c>
       <c r="G70" t="n">
-        <v>28.6</v>
+        <v>20.8</v>
       </c>
       <c r="H70" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K70" t="n">
-        <v>-14.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
         <v>130</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D71" t="n">
-        <v>38.9</v>
+        <v>59.3</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G71" t="n">
-        <v>66.7</v>
+        <v>7.1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-66.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B72" t="s">
         <v>130</v>
@@ -8879,227 +8656,225 @@
         <v>50</v>
       </c>
       <c r="D72" t="n">
-        <v>57.9</v>
+        <v>60</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G72" t="n">
-        <v>25</v>
+        <v>6.7</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
-        <v>28.6</v>
+        <v>29.4</v>
       </c>
       <c r="K72" t="n">
-        <v>-25</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="B73" t="s">
         <v>130</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D73" t="n">
-        <v>41.4</v>
+        <v>87.5</v>
       </c>
       <c r="E73" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="n">
+        <v>25</v>
+      </c>
+      <c r="J73" t="n">
         <v>33.3</v>
       </c>
-      <c r="G73" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H73" t="n">
-        <v>50</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>14.3</v>
-      </c>
       <c r="K73" t="n">
-        <v>-16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B74" t="s">
         <v>130</v>
       </c>
       <c r="C74" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>57.5</v>
+        <v>20</v>
       </c>
       <c r="E74" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>51.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F74"/>
       <c r="G74" t="n">
-        <v>20.8</v>
+        <v>66.7</v>
       </c>
       <c r="H74" t="n">
-        <v>47.8</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>8.4</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s">
         <v>130</v>
       </c>
       <c r="C75" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="D75" t="n">
-        <v>59.3</v>
+        <v>63.4</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>17.6</v>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G75" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>40</v>
+        <v>27.3</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>8.3</v>
+        <v>27.3</v>
       </c>
       <c r="K75" t="n">
-        <v>7.2</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B76" t="s">
         <v>130</v>
       </c>
       <c r="C76" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D76" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E76" t="n">
-        <v>10.2</v>
+        <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>29.4</v>
+        <v>50</v>
       </c>
       <c r="K76" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B77" t="s">
         <v>130</v>
       </c>
       <c r="C77" t="n">
+        <v>40</v>
+      </c>
+      <c r="D77" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F77" t="n">
         <v>100</v>
       </c>
-      <c r="D77" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B78" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>57.1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>66.7</v>
+        <v>9.1</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -9108,318 +8883,180 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>-66.7</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B79" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C79" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
-        <v>63.4</v>
+        <v>39.1</v>
       </c>
       <c r="E79" t="n">
-        <v>17.6</v>
+        <v>6.7</v>
       </c>
       <c r="F79" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H79" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>27.8</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C80" t="n">
         <v>66.7</v>
       </c>
       <c r="D80" t="n">
-        <v>80</v>
+        <v>53.3</v>
       </c>
       <c r="E80" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H80" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>50</v>
+        <v>7.1</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B81" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C81" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D81" t="n">
-        <v>31.6</v>
+        <v>55.2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="G81" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B82" t="s">
         <v>150</v>
       </c>
       <c r="C82" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="D82" t="n">
-        <v>57.1</v>
+        <v>59.2</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82"/>
+        <v>16</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
       <c r="G82" t="n">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="H82" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="K82" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
-        <v>237</v>
-      </c>
+      <c r="A83"/>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C83" t="n">
-        <v>50</v>
+        <v>53.2</v>
       </c>
       <c r="D83" t="n">
-        <v>39.1</v>
+        <v>57.8</v>
       </c>
       <c r="E83" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="G83" t="n">
-        <v>33.3</v>
+        <v>13.9</v>
       </c>
       <c r="H83" t="n">
-        <v>50</v>
+        <v>43.9</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="K83" t="n">
-        <v>-33.3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>238</v>
-      </c>
-      <c r="B84" t="s">
-        <v>150</v>
-      </c>
-      <c r="C84" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D84" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>239</v>
-      </c>
-      <c r="B85" t="s">
-        <v>150</v>
-      </c>
-      <c r="C85" t="n">
-        <v>52</v>
-      </c>
-      <c r="D85" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F85" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G85" t="n">
-        <v>8</v>
-      </c>
-      <c r="H85" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I85" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>240</v>
-      </c>
-      <c r="B86" t="s">
-        <v>150</v>
-      </c>
-      <c r="C86" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="D86" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="E86" t="n">
-        <v>16</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H86" t="n">
-        <v>50</v>
-      </c>
-      <c r="I86" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J86" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87"/>
-      <c r="B87" t="s">
-        <v>161</v>
-      </c>
-      <c r="C87" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="D87" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="E87" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F87" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="G87" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H87" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J87" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -138,6 +138,9 @@
     <t xml:space="preserve">Evan Ogston</t>
   </si>
   <si>
+    <t xml:space="preserve">Fabrizio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack Gillis</t>
   </si>
   <si>
@@ -225,6 +228,9 @@
     <t xml:space="preserve">Matt Underwood</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathan Markle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nathan Smid</t>
   </si>
   <si>
@@ -582,6 +588,9 @@
     <t xml:space="preserve">JJ Reynolds</t>
   </si>
   <si>
+    <t xml:space="preserve">Joe Pelow</t>
+  </si>
+  <si>
     <t xml:space="preserve">Landon Hutar</t>
   </si>
   <si>
@@ -597,9 +606,15 @@
     <t xml:space="preserve">Vinny Bouchard Wright</t>
   </si>
   <si>
+    <t xml:space="preserve">Aidan Webb</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alex VanRaay</t>
   </si>
   <si>
+    <t xml:space="preserve">David Young</t>
+  </si>
+  <si>
     <t xml:space="preserve">Erik Lopez</t>
   </si>
   <si>
@@ -610,6 +625,9 @@
   </si>
   <si>
     <t xml:space="preserve">Neal (Amar) Bhattacharya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Law</t>
   </si>
   <si>
     <t xml:space="preserve">Premnath Nayak</t>
@@ -790,8 +808,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K145" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K147" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K147"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -810,8 +828,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K83" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K87" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K87"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2001,25 +2019,25 @@
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="D26" t="n">
-        <v>20.7</v>
+        <v>18.4</v>
       </c>
       <c r="E26" t="n">
-        <v>44.3</v>
+        <v>48.3</v>
       </c>
       <c r="F26" t="n">
-        <v>20.7</v>
+        <v>18.4</v>
       </c>
       <c r="G26" t="n">
-        <v>42.1</v>
+        <v>40.9</v>
       </c>
       <c r="H26" t="n">
-        <v>23.1</v>
+        <v>27.8</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2106,31 +2124,31 @@
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>61.4</v>
+        <v>66</v>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="E29" t="n">
-        <v>44.7</v>
+        <v>52.3</v>
       </c>
       <c r="F29" t="n">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="G29" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="H29" t="n">
-        <v>16.7</v>
+        <v>13.8</v>
       </c>
       <c r="I29" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="30">
@@ -2141,32 +2159,26 @@
         <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>83.8</v>
+        <v>33.3</v>
       </c>
       <c r="D30" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>57.3</v>
+        <v>33.3</v>
       </c>
       <c r="F30" t="n">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>66.7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
@@ -2176,31 +2188,31 @@
         <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>68.6</v>
+        <v>82.9</v>
       </c>
       <c r="D31" t="n">
-        <v>8.8</v>
+        <v>27.5</v>
       </c>
       <c r="E31" t="n">
-        <v>59.8</v>
+        <v>55.4</v>
       </c>
       <c r="F31" t="n">
-        <v>8.8</v>
+        <v>27.5</v>
       </c>
       <c r="G31" t="n">
-        <v>29.6</v>
+        <v>21.7</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>50</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>8.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="32">
@@ -2211,31 +2223,31 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>68.3</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>59.2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I32" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="J32" t="n">
-        <v>66.7</v>
+        <v>21.4</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="33">
@@ -2246,31 +2258,31 @@
         <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>50.4</v>
+        <v>60</v>
       </c>
       <c r="F33" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H33" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
       <c r="I33" t="n">
-        <v>56.2</v>
+        <v>40</v>
       </c>
       <c r="J33" t="n">
-        <v>18.8</v>
+        <v>60</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -2281,31 +2293,31 @@
         <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>84</v>
+        <v>61.1</v>
       </c>
       <c r="D34" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="E34" t="n">
-        <v>78.4</v>
+        <v>49.5</v>
       </c>
       <c r="F34" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="G34" t="n">
-        <v>4.5</v>
+        <v>20.5</v>
       </c>
       <c r="H34" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="I34" t="n">
-        <v>26.7</v>
+        <v>61.1</v>
       </c>
       <c r="J34" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="K34" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2316,31 +2328,31 @@
         <v>35</v>
       </c>
       <c r="C35" t="n">
-        <v>59.5</v>
+        <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>5.6</v>
       </c>
       <c r="E35" t="n">
-        <v>46.2</v>
+        <v>78.4</v>
       </c>
       <c r="F35" t="n">
-        <v>13.3</v>
+        <v>5.6</v>
       </c>
       <c r="G35" t="n">
-        <v>41.9</v>
+        <v>4.5</v>
       </c>
       <c r="H35" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="I35" t="n">
-        <v>55.6</v>
+        <v>26.7</v>
       </c>
       <c r="J35" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="K35" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="36">
@@ -2351,31 +2363,31 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>62.7</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -2386,31 +2398,31 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>64.7</v>
+        <v>50</v>
       </c>
       <c r="D37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>33.5</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2421,31 +2433,31 @@
         <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>80</v>
+        <v>60.7</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>31.8</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="39">
@@ -2456,31 +2468,31 @@
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>52.3</v>
+        <v>80</v>
       </c>
       <c r="D39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>40.2</v>
+        <v>80</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>14.8</v>
+        <v>25</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>64.3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>21.4</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2491,31 +2503,31 @@
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>56.2</v>
+        <v>52</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="E40" t="n">
-        <v>26.2</v>
+        <v>42.9</v>
       </c>
       <c r="F40" t="n">
-        <v>30</v>
+        <v>9.1</v>
       </c>
       <c r="G40" t="n">
-        <v>41.7</v>
+        <v>12.9</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="41">
@@ -2523,69 +2535,69 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>57.9</v>
+        <v>56.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E41" t="n">
-        <v>57.9</v>
+        <v>26.2</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>30.8</v>
+        <v>41.7</v>
       </c>
       <c r="H41" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
         <v>54</v>
       </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>53.4</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="G42" t="n">
-        <v>26.7</v>
+        <v>29.4</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>35.3</v>
       </c>
       <c r="I42" t="n">
-        <v>83.3</v>
+        <v>42.9</v>
       </c>
       <c r="J42" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="K42" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="43">
@@ -2593,34 +2605,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="44">
@@ -2628,25 +2640,25 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
         <v>50</v>
       </c>
       <c r="D44" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>100</v>
@@ -2655,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2663,25 +2675,25 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C45" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>27.5</v>
+        <v>35.6</v>
       </c>
       <c r="F45" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I45" t="n">
         <v>100</v>
@@ -2690,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -2698,31 +2710,31 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" t="n">
+        <v>40</v>
+      </c>
+      <c r="D46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>100</v>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>100</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>25</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>50</v>
-      </c>
       <c r="J46" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2733,34 +2745,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" t="n">
-        <v>47.1</v>
+        <v>81.8</v>
       </c>
       <c r="D47" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E47" t="n">
-        <v>30.4</v>
+        <v>61.8</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J47" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K47" t="n">
-        <v>57.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -2768,34 +2780,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>66.7</v>
+        <v>47.1</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="E48" t="n">
-        <v>41.7</v>
+        <v>30.4</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="G48" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="49">
@@ -2803,34 +2815,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C49" t="n">
-        <v>70.6</v>
+        <v>66.7</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E49" t="n">
-        <v>60.6</v>
+        <v>41.7</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G49" t="n">
-        <v>30.8</v>
+        <v>25</v>
       </c>
       <c r="H49" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2838,96 +2850,96 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>68.4</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>60.7</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50"/>
+        <v>7.7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>28.6</v>
+      </c>
       <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
+        <v>11.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>60</v>
+      </c>
+      <c r="J50" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>16</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G51"/>
       <c r="H51" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I51" t="n">
-        <v>50</v>
-      </c>
-      <c r="J51" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K51" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C52" t="n">
-        <v>62.5</v>
+        <v>59</v>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="E52" t="n">
-        <v>42.5</v>
+        <v>43.6</v>
       </c>
       <c r="F52" t="n">
-        <v>20</v>
+        <v>15.4</v>
       </c>
       <c r="G52" t="n">
-        <v>37.5</v>
+        <v>13.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="53">
@@ -2935,34 +2947,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C53" t="n">
+        <v>60</v>
+      </c>
+      <c r="D53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>33.3</v>
       </c>
-      <c r="D53" t="n">
+      <c r="J53" t="n">
         <v>33.3</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G53" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>100</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2970,34 +2982,34 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3005,34 +3017,34 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>57.7</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>71.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
@@ -3040,34 +3052,34 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>57.7</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E56" t="n">
-        <v>66.7</v>
+        <v>49.4</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G56" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I56" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="57">
@@ -3075,34 +3087,34 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C57" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="D57" t="n">
         <v>14.3</v>
       </c>
       <c r="E57" t="n">
-        <v>41.3</v>
+        <v>45.7</v>
       </c>
       <c r="F57" t="n">
         <v>14.3</v>
       </c>
       <c r="G57" t="n">
-        <v>38.5</v>
+        <v>27.3</v>
       </c>
       <c r="H57" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="I57" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58">
@@ -3110,34 +3122,34 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C58" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="I58" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -3145,34 +3157,34 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C59" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
       <c r="D59" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F59" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>33.3</v>
       </c>
       <c r="H59" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3180,22 +3192,22 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C60" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>65.7</v>
+        <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3215,34 +3227,34 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C61" t="n">
-        <v>38.1</v>
+        <v>66.7</v>
       </c>
       <c r="D61" t="n">
-        <v>45.5</v>
+        <v>16.7</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.4</v>
+        <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>45.5</v>
+        <v>16.7</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H61" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="I61" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -3250,34 +3262,34 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C62" t="n">
-        <v>62.5</v>
+        <v>83.3</v>
       </c>
       <c r="D62" t="n">
-        <v>38.5</v>
+        <v>18.2</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>65.1</v>
       </c>
       <c r="F62" t="n">
-        <v>38.5</v>
+        <v>18.2</v>
       </c>
       <c r="G62" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I62" t="n">
-        <v>37.5</v>
+        <v>80</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -3285,86 +3297,86 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C63" t="n">
-        <v>42.9</v>
+        <v>48.1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="E63" t="n">
-        <v>42.9</v>
+        <v>12.6</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J63" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="K63" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="D64" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="E64" t="n">
-        <v>58.3</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="G64" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="J64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" t="s">
         <v>78</v>
       </c>
-      <c r="B65" t="s">
-        <v>76</v>
-      </c>
       <c r="C65" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3376,13 +3388,13 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>33.3</v>
       </c>
       <c r="K65" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="66">
@@ -3390,34 +3402,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E66" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="F66" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G66" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>75</v>
+      </c>
+      <c r="J66" t="n">
         <v>25</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>75</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3425,34 +3437,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C67" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="D67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>5.6</v>
+        <v>80</v>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="68">
@@ -3460,34 +3472,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C68" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E68" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
       <c r="F68" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="G68" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3495,34 +3507,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C69" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E69" t="n">
-        <v>46.7</v>
+        <v>5.6</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3530,22 +3542,22 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>43.1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3554,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -3565,22 +3577,22 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C71" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="D71" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>46.7</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3592,7 +3604,7 @@
         <v>50</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -3600,14 +3612,20 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C72" t="n">
-        <v>80</v>
-      </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
+        <v>50</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
@@ -3615,13 +3633,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K72" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3629,31 +3647,31 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C73" t="n">
-        <v>78.6</v>
+        <v>75</v>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="E73" t="n">
-        <v>67.5</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="G73" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H73" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3664,20 +3682,14 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C74" t="n">
-        <v>100</v>
-      </c>
-      <c r="D74" t="n">
-        <v>25</v>
-      </c>
-      <c r="E74" t="n">
-        <v>75</v>
-      </c>
-      <c r="F74" t="n">
-        <v>25</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
       <c r="G74" t="n">
         <v>0</v>
       </c>
@@ -3685,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K74" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="75">
@@ -3699,25 +3711,25 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>46.7</v>
+        <v>78.6</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="n">
-        <v>26.7</v>
+        <v>67.5</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="G75" t="n">
-        <v>75</v>
+        <v>16.7</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I75" t="n">
         <v>100</v>
@@ -3726,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3734,34 +3746,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C76" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D76" t="n">
+        <v>25</v>
+      </c>
+      <c r="E76" t="n">
         <v>75</v>
       </c>
-      <c r="E76" t="n">
-        <v>-8.3</v>
-      </c>
       <c r="F76" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>100</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>50</v>
-      </c>
-      <c r="J76" t="n">
-        <v>25</v>
-      </c>
-      <c r="K76" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -3769,31 +3781,31 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C77" t="n">
-        <v>67.7</v>
+        <v>46.7</v>
       </c>
       <c r="D77" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
-        <v>36.1</v>
+        <v>26.7</v>
       </c>
       <c r="F77" t="n">
-        <v>31.6</v>
+        <v>20</v>
       </c>
       <c r="G77" t="n">
-        <v>13.8</v>
+        <v>75</v>
       </c>
       <c r="H77" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>50</v>
@@ -3801,19 +3813,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C78" t="n">
-        <v>100</v>
-      </c>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
+        <v>66.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>75</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-8.3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>75</v>
+      </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3822,45 +3840,45 @@
         <v>50</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K78" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" t="s">
         <v>93</v>
       </c>
-      <c r="B79" t="s">
-        <v>91</v>
-      </c>
       <c r="C79" t="n">
-        <v>73.1</v>
+        <v>67.7</v>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="E79" t="n">
-        <v>48.1</v>
+        <v>36.1</v>
       </c>
       <c r="F79" t="n">
-        <v>25</v>
+        <v>31.6</v>
       </c>
       <c r="G79" t="n">
-        <v>17.9</v>
+        <v>13.8</v>
       </c>
       <c r="H79" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="I79" t="n">
-        <v>27.3</v>
+        <v>61.5</v>
       </c>
       <c r="J79" t="n">
-        <v>54.5</v>
+        <v>15.4</v>
       </c>
       <c r="K79" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
@@ -3868,20 +3886,14 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C80" t="n">
-        <v>75</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>75</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="G80" t="n">
         <v>0</v>
       </c>
@@ -3889,13 +3901,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
@@ -3903,34 +3915,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C81" t="n">
-        <v>83.9</v>
+        <v>73.1</v>
       </c>
       <c r="D81" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="E81" t="n">
-        <v>76.2</v>
+        <v>48.1</v>
       </c>
       <c r="F81" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="G81" t="n">
-        <v>7.1</v>
+        <v>17.9</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I81" t="n">
-        <v>55.6</v>
+        <v>27.3</v>
       </c>
       <c r="J81" t="n">
-        <v>16.7</v>
+        <v>54.5</v>
       </c>
       <c r="K81" t="n">
-        <v>55.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -3938,34 +3950,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C82" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="D82" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>49.2</v>
+        <v>75</v>
       </c>
       <c r="F82" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K82" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="83">
@@ -3973,34 +3985,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>83.9</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="E83" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H83" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K83" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="84">
@@ -4008,34 +4020,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C84" t="n">
-        <v>73.3</v>
+        <v>58.3</v>
       </c>
       <c r="D84" t="n">
-        <v>41.7</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="n">
-        <v>31.6</v>
+        <v>49.2</v>
       </c>
       <c r="F84" t="n">
-        <v>41.7</v>
+        <v>9.1</v>
       </c>
       <c r="G84" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="H84" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I84" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85">
@@ -4043,34 +4055,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C85" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I85" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86">
@@ -4078,28 +4090,28 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C86" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="D86" t="n">
-        <v>10</v>
+        <v>41.7</v>
       </c>
       <c r="E86" t="n">
-        <v>43.3</v>
+        <v>31.6</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>41.7</v>
       </c>
       <c r="G86" t="n">
-        <v>35</v>
+        <v>17.6</v>
       </c>
       <c r="H86" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J86" t="n">
         <v>50</v>
@@ -4113,34 +4125,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C87" t="n">
-        <v>37.5</v>
+        <v>71.4</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>37.5</v>
+        <v>71.4</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J87" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
@@ -4148,34 +4160,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C88" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>100</v>
+        <v>43.3</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I88" t="n">
         <v>50</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4183,34 +4195,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C89" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="D89" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>43.3</v>
+        <v>37.5</v>
       </c>
       <c r="F89" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="H89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4218,22 +4230,22 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D90" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4242,7 +4254,7 @@
         <v>50</v>
       </c>
       <c r="J90" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
         <v>100</v>
@@ -4253,34 +4265,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C91" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E91" t="n">
-        <v>59.1</v>
+        <v>43.3</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G91" t="n">
-        <v>15.4</v>
+        <v>20</v>
       </c>
       <c r="H91" t="n">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="I91" t="n">
         <v>50</v>
       </c>
       <c r="J91" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="K91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
@@ -4288,31 +4300,31 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E92" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G92" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K92" t="n">
         <v>100</v>
@@ -4323,34 +4335,34 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C93" t="n">
-        <v>75</v>
+        <v>59.1</v>
       </c>
       <c r="D93" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>51.9</v>
+        <v>59.1</v>
       </c>
       <c r="F93" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="H93" t="n">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="I93" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="J93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K93" t="n">
         <v>25</v>
-      </c>
-      <c r="K93" t="n">
-        <v>33.3</v>
       </c>
     </row>
     <row r="94">
@@ -4358,34 +4370,34 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="D94" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="F94" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H94" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -4393,209 +4405,209 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C95" t="n">
-        <v>67.6</v>
+        <v>75</v>
       </c>
       <c r="D95" t="n">
-        <v>7.1</v>
+        <v>23.1</v>
       </c>
       <c r="E95" t="n">
-        <v>60.5</v>
+        <v>51.9</v>
       </c>
       <c r="F95" t="n">
-        <v>7.1</v>
+        <v>23.1</v>
       </c>
       <c r="G95" t="n">
-        <v>7.1</v>
+        <v>19.4</v>
       </c>
       <c r="H95" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="I95" t="n">
-        <v>43.8</v>
+        <v>58.3</v>
       </c>
       <c r="J95" t="n">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="K95" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C96" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C97" t="n">
-        <v>66.7</v>
+        <v>67.6</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E97" t="n">
-        <v>66.7</v>
+        <v>60.5</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="G97" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="H97" t="n">
-        <v>26.7</v>
+        <v>10</v>
       </c>
       <c r="I97" t="n">
-        <v>30</v>
+        <v>43.8</v>
       </c>
       <c r="J97" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="K97" t="n">
-        <v>20</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C98" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D98" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C99" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H99" t="n">
         <v>26.7</v>
       </c>
-      <c r="E99" t="n">
+      <c r="I99" t="n">
+        <v>30</v>
+      </c>
+      <c r="J99" t="n">
+        <v>30</v>
+      </c>
+      <c r="K99" t="n">
         <v>20</v>
-      </c>
-      <c r="F99" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G99" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K99" t="n">
-        <v>37.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" t="s">
         <v>114</v>
       </c>
-      <c r="B100" t="s">
-        <v>112</v>
-      </c>
       <c r="C100" t="n">
-        <v>88.9</v>
+        <v>57.1</v>
       </c>
       <c r="D100" t="n">
-        <v>13.3</v>
+        <v>8.7</v>
       </c>
       <c r="E100" t="n">
-        <v>75.6</v>
+        <v>48.4</v>
       </c>
       <c r="F100" t="n">
-        <v>13.3</v>
+        <v>8.7</v>
       </c>
       <c r="G100" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>80</v>
+      </c>
+      <c r="J100" t="n">
         <v>20</v>
       </c>
-      <c r="H100" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="I100" t="n">
-        <v>20</v>
-      </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>60</v>
-      </c>
-      <c r="K100" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -4603,34 +4615,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C101" t="n">
-        <v>88.9</v>
+        <v>46.7</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="E101" t="n">
-        <v>88.9</v>
+        <v>20</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H101" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="K101" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="102">
@@ -4638,34 +4650,34 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C102" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E102" t="n">
-        <v>78.6</v>
+        <v>75.6</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G102" t="n">
-        <v>9.1</v>
+        <v>20</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I102" t="n">
-        <v>85.7</v>
+        <v>20</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -4673,34 +4685,34 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C103" t="n">
-        <v>57.1</v>
+        <v>88.9</v>
       </c>
       <c r="D103" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>48</v>
+        <v>88.9</v>
       </c>
       <c r="F103" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
@@ -4708,34 +4720,34 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C104" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>64.3</v>
+        <v>78.6</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="H104" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>40</v>
+        <v>85.7</v>
       </c>
       <c r="J104" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4743,34 +4755,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C105" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="D105" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="E105" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F105" t="n">
-        <v>25</v>
+        <v>9.1</v>
       </c>
       <c r="G105" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I105" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
@@ -4778,34 +4790,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C106" t="n">
-        <v>85.7</v>
+        <v>64.3</v>
       </c>
       <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H106" t="n">
         <v>25</v>
       </c>
-      <c r="E106" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F106" t="n">
-        <v>25</v>
-      </c>
-      <c r="G106" t="n">
-        <v>25</v>
-      </c>
-      <c r="H106" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I106" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J106" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107">
@@ -4813,34 +4825,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C107" t="n">
-        <v>43.8</v>
+        <v>80</v>
       </c>
       <c r="D107" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="E107" t="n">
-        <v>34.7</v>
+        <v>55</v>
       </c>
       <c r="F107" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G107" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="H107" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>25</v>
+        <v>57.1</v>
       </c>
       <c r="J107" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K107" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="108">
@@ -4848,25 +4860,31 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C108" t="n">
-        <v>100</v>
-      </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
+        <v>85.7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>25</v>
+      </c>
+      <c r="E108" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F108" t="n">
+        <v>25</v>
+      </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J108" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4877,34 +4895,34 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C109" t="n">
-        <v>92.6</v>
+        <v>43.8</v>
       </c>
       <c r="D109" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="E109" t="n">
-        <v>87.3</v>
+        <v>34.7</v>
       </c>
       <c r="F109" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="H109" t="n">
-        <v>12.5</v>
+        <v>28.6</v>
       </c>
       <c r="I109" t="n">
-        <v>64.3</v>
+        <v>25</v>
       </c>
       <c r="J109" t="n">
-        <v>21.4</v>
+        <v>50</v>
       </c>
       <c r="K109" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110">
@@ -4912,31 +4930,25 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C110" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="D110" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="F110" t="n">
-        <v>12.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
       <c r="G110" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4947,34 +4959,34 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>75</v>
+        <v>92.6</v>
       </c>
       <c r="D111" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H111" t="n">
         <v>12.5</v>
       </c>
-      <c r="E111" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F111" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G111" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H111" t="n">
-        <v>14.3</v>
-      </c>
       <c r="I111" t="n">
-        <v>40</v>
+        <v>64.3</v>
       </c>
       <c r="J111" t="n">
-        <v>40</v>
+        <v>21.4</v>
       </c>
       <c r="K111" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="112">
@@ -4982,34 +4994,34 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C112" t="n">
-        <v>71.4</v>
+        <v>56.2</v>
       </c>
       <c r="D112" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="n">
-        <v>61.7</v>
+        <v>43.7</v>
       </c>
       <c r="F112" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>9.1</v>
       </c>
       <c r="H112" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="I112" t="n">
-        <v>72.7</v>
+        <v>42.9</v>
       </c>
       <c r="J112" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="K112" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5017,34 +5029,34 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C113" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D113" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="n">
-        <v>38.9</v>
+        <v>62.5</v>
       </c>
       <c r="F113" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="G113" t="n">
-        <v>28.6</v>
+        <v>23.1</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I113" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J113" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
@@ -5052,34 +5064,34 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C114" t="n">
-        <v>68.8</v>
+        <v>71.4</v>
       </c>
       <c r="D114" t="n">
-        <v>10.3</v>
+        <v>9.7</v>
       </c>
       <c r="E114" t="n">
-        <v>58.5</v>
+        <v>61.7</v>
       </c>
       <c r="F114" t="n">
-        <v>10.3</v>
+        <v>9.7</v>
       </c>
       <c r="G114" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H114" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="I114" t="n">
-        <v>25</v>
+        <v>72.7</v>
       </c>
       <c r="J114" t="n">
-        <v>8.3</v>
+        <v>18.2</v>
       </c>
       <c r="K114" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="115">
@@ -5087,104 +5099,104 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C115" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D115" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E115" t="n">
-        <v>52.4</v>
+        <v>38.9</v>
       </c>
       <c r="F115" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G115" t="n">
-        <v>35.7</v>
+        <v>28.6</v>
       </c>
       <c r="H115" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>50</v>
       </c>
       <c r="J115" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K115" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C116" t="n">
-        <v>55.6</v>
+        <v>68.8</v>
       </c>
       <c r="D116" t="n">
-        <v>22.2</v>
+        <v>10.3</v>
       </c>
       <c r="E116" t="n">
-        <v>33.4</v>
+        <v>58.5</v>
       </c>
       <c r="F116" t="n">
-        <v>22.2</v>
+        <v>10.3</v>
       </c>
       <c r="G116" t="n">
-        <v>42.9</v>
+        <v>12</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I116" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
+        <v>131</v>
+      </c>
+      <c r="B117" t="s">
         <v>132</v>
       </c>
-      <c r="B117" t="s">
-        <v>130</v>
-      </c>
       <c r="C117" t="n">
-        <v>80.8</v>
+        <v>66.7</v>
       </c>
       <c r="D117" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="E117" t="n">
-        <v>62.6</v>
+        <v>52.4</v>
       </c>
       <c r="F117" t="n">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="G117" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="H117" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="I117" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J117" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="K117" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="118">
@@ -5192,34 +5204,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C118" t="n">
-        <v>91.7</v>
+        <v>55.6</v>
       </c>
       <c r="D118" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="E118" t="n">
-        <v>41.7</v>
+        <v>33.4</v>
       </c>
       <c r="F118" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="G118" t="n">
-        <v>21.4</v>
+        <v>42.9</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="J118" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>71.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5227,34 +5239,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C119" t="n">
-        <v>60</v>
+        <v>80.8</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="E119" t="n">
-        <v>60</v>
+        <v>62.6</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I119" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120">
@@ -5262,34 +5274,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C120" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="D120" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E120" t="n">
-        <v>80</v>
+        <v>41.7</v>
       </c>
       <c r="F120" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G120" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
         <v>28.6</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>66.7</v>
-      </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="121">
@@ -5297,19 +5309,19 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C121" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D121" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5318,13 +5330,13 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J121" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5332,31 +5344,31 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C122" t="n">
         <v>100</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E122" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="J122" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5367,34 +5379,34 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C123" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="D123" t="n">
-        <v>28.6</v>
+        <v>8.3</v>
       </c>
       <c r="E123" t="n">
-        <v>54.7</v>
+        <v>66.7</v>
       </c>
       <c r="F123" t="n">
-        <v>28.6</v>
+        <v>8.3</v>
       </c>
       <c r="G123" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J123" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K123" t="n">
-        <v>16.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="124">
@@ -5402,34 +5414,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C124" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K124" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5437,34 +5449,34 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C125" t="n">
-        <v>70</v>
+        <v>83.3</v>
       </c>
       <c r="D125" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="E125" t="n">
-        <v>32.5</v>
+        <v>54.7</v>
       </c>
       <c r="F125" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="G125" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="J125" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K125" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="126">
@@ -5472,34 +5484,34 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C126" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="D126" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
       <c r="F126" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>46.7</v>
+        <v>25</v>
       </c>
       <c r="H126" t="n">
         <v>14.3</v>
       </c>
       <c r="I126" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K126" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127">
@@ -5507,34 +5519,34 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C127" t="n">
-        <v>84.6</v>
+        <v>70</v>
       </c>
       <c r="D127" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="E127" t="n">
-        <v>70.3</v>
+        <v>32.5</v>
       </c>
       <c r="F127" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13</v>
+        <v>17.6</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>43.8</v>
+        <v>37.5</v>
       </c>
       <c r="J127" t="n">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="K127" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128">
@@ -5542,34 +5554,34 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C128" t="n">
-        <v>68.6</v>
+        <v>75</v>
       </c>
       <c r="D128" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="E128" t="n">
-        <v>59.5</v>
+        <v>53.6</v>
       </c>
       <c r="F128" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="G128" t="n">
-        <v>23.1</v>
+        <v>46.7</v>
       </c>
       <c r="H128" t="n">
-        <v>6.7</v>
+        <v>14.3</v>
       </c>
       <c r="I128" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="J128" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="129">
@@ -5577,34 +5589,34 @@
         <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>50</v>
+        <v>84.6</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E129" t="n">
-        <v>50</v>
+        <v>70.3</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="130">
@@ -5612,34 +5624,34 @@
         <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C130" t="n">
-        <v>90.9</v>
+        <v>68.6</v>
       </c>
       <c r="D130" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="E130" t="n">
-        <v>70.9</v>
+        <v>59.5</v>
       </c>
       <c r="F130" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="G130" t="n">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I130" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J130" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="K130" t="n">
-        <v>50</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="131">
@@ -5647,34 +5659,34 @@
         <v>146</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C131" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D131" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>17.1</v>
+        <v>50</v>
       </c>
       <c r="F131" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J131" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5682,34 +5694,34 @@
         <v>147</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C132" t="n">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="D132" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E132" t="n">
-        <v>73.3</v>
+        <v>70.9</v>
       </c>
       <c r="F132" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G132" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J132" t="n">
         <v>33.3</v>
       </c>
-      <c r="J132" t="n">
-        <v>50</v>
-      </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133">
@@ -5717,34 +5729,34 @@
         <v>148</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C133" t="n">
+        <v>60</v>
+      </c>
+      <c r="D133" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G133" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
         <v>100</v>
       </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="n">
-        <v>100</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J133" t="n">
-        <v>33.3</v>
-      </c>
       <c r="K133" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="134">
@@ -5752,83 +5764,95 @@
         <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C134" t="n">
+        <v>90</v>
+      </c>
+      <c r="D134" t="n">
         <v>16.7</v>
       </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
       <c r="E134" t="n">
-        <v>5.6</v>
+        <v>73.3</v>
       </c>
       <c r="F134" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="G134" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="H134" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I134"/>
-      <c r="J134"/>
-      <c r="K134"/>
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>50</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B135" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C135" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135"/>
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K135" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>151</v>
+      </c>
+      <c r="B136" t="s">
         <v>152</v>
       </c>
-      <c r="B136" t="s">
-        <v>150</v>
-      </c>
       <c r="C136" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I136"/>
       <c r="J136"/>
@@ -5839,104 +5863,92 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C137" t="n">
-        <v>61.1</v>
+        <v>42.9</v>
       </c>
       <c r="D137" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>52</v>
+        <v>42.9</v>
       </c>
       <c r="F137" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>8.3</v>
+        <v>66.7</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>14.3</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
     </row>
     <row r="138">
       <c r="A138" t="s">
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C138" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D138" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>31.8</v>
+        <v>33.3</v>
       </c>
       <c r="F138" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>75</v>
-      </c>
-      <c r="K138" t="n">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I138"/>
+      <c r="J138"/>
+      <c r="K138"/>
     </row>
     <row r="139">
       <c r="A139" t="s">
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C139" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D139" t="n">
-        <v>23.1</v>
+        <v>9.1</v>
       </c>
       <c r="E139" t="n">
-        <v>26.9</v>
+        <v>52</v>
       </c>
       <c r="F139" t="n">
-        <v>23.1</v>
+        <v>9.1</v>
       </c>
       <c r="G139" t="n">
-        <v>37.5</v>
+        <v>8.3</v>
       </c>
       <c r="H139" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="J139" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>66.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="140">
@@ -5944,34 +5956,34 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C140" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D140" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F140" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H140" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>75</v>
+      </c>
+      <c r="K140" t="n">
         <v>25</v>
-      </c>
-      <c r="E140" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F140" t="n">
-        <v>25</v>
-      </c>
-      <c r="G140" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>100</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5979,34 +5991,34 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C141" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E141" t="n">
-        <v>61.5</v>
+        <v>26.9</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="G141" t="n">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="H141" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I141" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J141" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="K141" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="142">
@@ -6014,22 +6026,22 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C142" t="n">
-        <v>45</v>
+        <v>66.7</v>
       </c>
       <c r="D142" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="E142" t="n">
-        <v>28.3</v>
+        <v>41.7</v>
       </c>
       <c r="F142" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="G142" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6049,34 +6061,34 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C143" t="n">
-        <v>71.4</v>
+        <v>61.5</v>
       </c>
       <c r="D143" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>51.4</v>
+        <v>61.5</v>
       </c>
       <c r="F143" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="J143" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="144">
@@ -6084,67 +6096,137 @@
         <v>160</v>
       </c>
       <c r="B144" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C144" t="n">
+        <v>45</v>
+      </c>
+      <c r="D144" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E144" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G144" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>100</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" t="s">
+        <v>152</v>
+      </c>
+      <c r="C145" t="n">
         <v>71.4</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D145" t="n">
+        <v>20</v>
+      </c>
+      <c r="E145" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F145" t="n">
+        <v>20</v>
+      </c>
+      <c r="G145" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>50</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>162</v>
+      </c>
+      <c r="B146" t="s">
+        <v>152</v>
+      </c>
+      <c r="C146" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D146" t="n">
         <v>7.1</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E146" t="n">
         <v>64.3</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F146" t="n">
         <v>7.1</v>
       </c>
-      <c r="G144" t="n">
+      <c r="G146" t="n">
         <v>18.2</v>
       </c>
-      <c r="H144" t="n">
+      <c r="H146" t="n">
         <v>12.5</v>
       </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
         <v>100</v>
       </c>
-      <c r="K144" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145"/>
-      <c r="B145" t="s">
-        <v>161</v>
-      </c>
-      <c r="C145" t="n">
-        <v>68.1</v>
-      </c>
-      <c r="D145" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="F145" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G145" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H145" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="I145" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="J145" t="n">
-        <v>27</v>
-      </c>
-      <c r="K145" t="n">
-        <v>35.7</v>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147"/>
+      <c r="B147" t="s">
+        <v>163</v>
+      </c>
+      <c r="C147" t="n">
+        <v>67.6</v>
+      </c>
+      <c r="D147" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="E147" t="n">
+        <v>53</v>
+      </c>
+      <c r="F147" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G147" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H147" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I147" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="J147" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>35.5</v>
       </c>
     </row>
   </sheetData>
@@ -6176,22 +6258,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6200,13 +6282,13 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -6281,7 +6363,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -6316,7 +6398,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6351,7 +6433,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6386,7 +6468,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6421,7 +6503,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -6526,7 +6608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -6561,7 +6643,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -6594,7 +6676,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -6629,7 +6711,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -6664,7 +6746,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -6699,7 +6781,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -6734,7 +6816,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -6769,7 +6851,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -6804,7 +6886,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -6839,7 +6921,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -6874,7 +6956,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -6909,7 +6991,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
@@ -6944,7 +7026,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -6979,42 +7061,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
         <v>35</v>
       </c>
       <c r="C24" t="n">
-        <v>45.2</v>
+        <v>41.3</v>
       </c>
       <c r="D24" t="n">
-        <v>54.3</v>
+        <v>51.6</v>
       </c>
       <c r="E24" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="F24" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>52.9</v>
+        <v>42.3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.4</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -7049,34 +7131,34 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
       </c>
       <c r="C26" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>55.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F26" t="n">
         <v>66.7</v>
       </c>
       <c r="G26" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
       <c r="H26" t="n">
-        <v>75</v>
+        <v>85.7</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>42.9</v>
+        <v>35.3</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -7084,7 +7166,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
         <v>35</v>
@@ -7093,138 +7175,138 @@
         <v>37.5</v>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>16.7</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="G27" t="n">
         <v>12.5</v>
       </c>
       <c r="H27" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="D28" t="n">
-        <v>59.4</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
-        <v>13.2</v>
+        <v>6.9</v>
       </c>
       <c r="F28" t="n">
-        <v>42.1</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>27</v>
+        <v>14.7</v>
       </c>
       <c r="K28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
         <v>35</v>
       </c>
       <c r="C29" t="n">
-        <v>80</v>
+        <v>51.4</v>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>59.4</v>
       </c>
       <c r="E29" t="n">
-        <v>28.6</v>
+        <v>13.2</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>42.1</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>45.5</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>57.1</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="K30" t="n">
         <v>40</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
@@ -7233,195 +7315,195 @@
         <v>66.7</v>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>57.1</v>
       </c>
       <c r="E31" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="K31" t="n">
-        <v>16.7</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>48.5</v>
+        <v>66.7</v>
       </c>
       <c r="D32" t="n">
-        <v>57.3</v>
+        <v>63</v>
       </c>
       <c r="E32" t="n">
-        <v>6.9</v>
+        <v>23.1</v>
       </c>
       <c r="F32" t="n">
-        <v>11.1</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>37.9</v>
+        <v>60</v>
       </c>
       <c r="I32" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>10.4</v>
+        <v>15.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E33"/>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H33" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>25</v>
       </c>
-      <c r="I33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>57.9</v>
+        <v>48.5</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>57.3</v>
       </c>
       <c r="E34" t="n">
-        <v>9.3</v>
+        <v>6.9</v>
       </c>
       <c r="F34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="G34" t="n">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>37.9</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J34" t="n">
-        <v>23.3</v>
+        <v>10.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.1</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35" t="n">
-        <v>62.8</v>
+        <v>42.9</v>
       </c>
       <c r="D35" t="n">
-        <v>57.5</v>
+        <v>42.3</v>
       </c>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="G35" t="n">
-        <v>9.3</v>
+        <v>28.6</v>
       </c>
       <c r="H35" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>21.7</v>
+        <v>37.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2.3</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>64.7</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7432,376 +7514,382 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" t="n">
-        <v>28.6</v>
+        <v>57.9</v>
       </c>
       <c r="D37" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>9.5</v>
+        <v>9.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="G37" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="H37" t="n">
         <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-28.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>62.8</v>
       </c>
       <c r="D38" t="n">
-        <v>52.2</v>
+        <v>57.5</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="F38" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>9.3</v>
       </c>
       <c r="H38" t="n">
-        <v>91.7</v>
+        <v>48.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
-        <v>23.1</v>
+        <v>21.7</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C39" t="n">
-        <v>71.4</v>
+        <v>45.5</v>
       </c>
       <c r="D39" t="n">
-        <v>70.2</v>
+        <v>52.9</v>
       </c>
       <c r="E39" t="n">
-        <v>23.5</v>
+        <v>5.9</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H39" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>34.8</v>
+        <v>7.7</v>
       </c>
       <c r="K39" t="n">
-        <v>28.6</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="D40" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>9.5</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>6.7</v>
+        <v>28.6</v>
       </c>
       <c r="H40" t="n">
-        <v>18.2</v>
+        <v>50</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
-        <v>19.2</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>6.6</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>52.1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41"/>
+      <c r="F41" t="n">
+        <v>50</v>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H41" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="D42" t="n">
-        <v>46.2</v>
+        <v>52.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="G42" t="n">
-        <v>22.2</v>
+        <v>15</v>
       </c>
       <c r="H42" t="n">
-        <v>14.3</v>
+        <v>91.7</v>
       </c>
       <c r="I42" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
-        <v>44.4</v>
+        <v>62.5</v>
       </c>
       <c r="D43" t="n">
-        <v>49.2</v>
+        <v>61.4</v>
       </c>
       <c r="E43" t="n">
-        <v>9.1</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>11.1</v>
+        <v>8.3</v>
       </c>
       <c r="H43" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D44" t="n">
-        <v>52.9</v>
+        <v>66.7</v>
       </c>
       <c r="E44" t="n">
-        <v>11.8</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
         <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="H44" t="n">
-        <v>37.5</v>
+        <v>18.2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>7.7</v>
+        <v>19.2</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D45" t="n">
-        <v>7.7</v>
+        <v>80</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45"/>
       <c r="G45" t="n">
-        <v>100</v>
-      </c>
-      <c r="H45"/>
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45"/>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C46" t="n">
-        <v>35.3</v>
+        <v>55.6</v>
       </c>
       <c r="D46" t="n">
-        <v>57.6</v>
+        <v>46.2</v>
       </c>
       <c r="E46" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>11.8</v>
+        <v>22.2</v>
       </c>
       <c r="H46" t="n">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="J46" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C47" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="D47" t="n">
-        <v>63.2</v>
+        <v>49.2</v>
       </c>
       <c r="E47" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="G47" t="n">
         <v>11.1</v>
       </c>
       <c r="H47" t="n">
-        <v>28.6</v>
+        <v>46.2</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -7809,34 +7897,34 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>52.9</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H48" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -7844,104 +7932,98 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C49" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>57.8</v>
+        <v>7.7</v>
       </c>
       <c r="E49" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F49" t="n">
-        <v>41.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F49"/>
       <c r="G49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H49"/>
       <c r="I49" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="J49"/>
       <c r="K49" t="n">
-        <v>7.7</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C50" t="n">
-        <v>68.8</v>
+        <v>35.3</v>
       </c>
       <c r="D50" t="n">
-        <v>72.5</v>
+        <v>57.6</v>
       </c>
       <c r="E50" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H50" t="n">
         <v>23.1</v>
       </c>
-      <c r="F50" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>77.8</v>
-      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>29.2</v>
+        <v>23.1</v>
       </c>
       <c r="K50" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="D51" t="n">
-        <v>87.5</v>
+        <v>63.2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H51" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -7949,932 +8031,934 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C52" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>60.8</v>
+        <v>55</v>
       </c>
       <c r="E52" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C53" t="n">
-        <v>69.2</v>
+        <v>63</v>
       </c>
       <c r="D53" t="n">
-        <v>74.7</v>
+        <v>57.8</v>
       </c>
       <c r="E53" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="F53" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="G53" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="H53" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="K53" t="n">
-        <v>19.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C54" t="n">
-        <v>33.3</v>
+        <v>68.8</v>
       </c>
       <c r="D54" t="n">
-        <v>47.6</v>
+        <v>72.5</v>
       </c>
       <c r="E54" t="n">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="F54" t="n">
         <v>66.7</v>
       </c>
       <c r="G54" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="B55" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>56.4</v>
+        <v>87.5</v>
       </c>
       <c r="E55" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
-        <v>60</v>
+        <v>52.9</v>
       </c>
       <c r="D56" t="n">
-        <v>63.3</v>
+        <v>60.8</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="F56" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H56" t="n">
-        <v>88.9</v>
+        <v>42.9</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>23.5</v>
+        <v>32.1</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C57" t="n">
-        <v>36.4</v>
+        <v>69.2</v>
       </c>
       <c r="D57" t="n">
-        <v>60.5</v>
+        <v>74.7</v>
       </c>
       <c r="E57" t="n">
-        <v>5.3</v>
+        <v>28.6</v>
       </c>
       <c r="F57" t="n">
         <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>27.3</v>
+        <v>3.8</v>
       </c>
       <c r="H57" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>11.1</v>
+        <v>24.4</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C58" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="D58" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="E58"/>
+        <v>47.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.7</v>
+      </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="K58" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C59" t="n">
         <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>53.6</v>
+        <v>56.4</v>
       </c>
       <c r="E59" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>29.4</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H59" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="K59" t="n">
-        <v>12.5</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C60" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="E60" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>66.7</v>
+        <v>88.9</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>21.4</v>
+        <v>23.5</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C61" t="n">
-        <v>70</v>
+        <v>36.4</v>
       </c>
       <c r="D61" t="n">
-        <v>70.4</v>
+        <v>60.5</v>
       </c>
       <c r="E61" t="n">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="F61" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>3.3</v>
+        <v>27.3</v>
       </c>
       <c r="H61" t="n">
-        <v>34.8</v>
+        <v>60</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>22</v>
+        <v>11.1</v>
       </c>
       <c r="K61" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C62" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="D62" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="E62" t="n">
-        <v>31.4</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="E62"/>
       <c r="F62" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>8.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C63" t="n">
         <v>50</v>
       </c>
       <c r="D63" t="n">
-        <v>63.2</v>
+        <v>53.6</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>13.3</v>
       </c>
       <c r="F63" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>37.5</v>
+        <v>26.7</v>
       </c>
       <c r="K63" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C64" t="n">
-        <v>46.4</v>
+        <v>61.5</v>
       </c>
       <c r="D64" t="n">
-        <v>53.9</v>
+        <v>63.2</v>
       </c>
       <c r="E64" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>36.4</v>
+        <v>30.8</v>
       </c>
       <c r="G64" t="n">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="H64" t="n">
-        <v>35.3</v>
+        <v>66.7</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>23.7</v>
+        <v>21.4</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D65" t="n">
-        <v>41.2</v>
+        <v>70.4</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="G65" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="H65" t="n">
-        <v>33.3</v>
+        <v>34.8</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>-20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C66" t="n">
-        <v>14.3</v>
+        <v>58.3</v>
       </c>
       <c r="D66" t="n">
-        <v>44.1</v>
+        <v>65.3</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="F66" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="K66" t="n">
-        <v>-14.3</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B67" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
-        <v>38.9</v>
+        <v>63.2</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G67" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="K67" t="n">
-        <v>-66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="D68" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G68" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>28.6</v>
+        <v>23.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-25</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>230</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D69" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" t="n">
         <v>33.3</v>
       </c>
-      <c r="G69" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H69" t="n">
-        <v>50</v>
-      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="K69" t="n">
-        <v>-16.6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C70" t="n">
-        <v>57.1</v>
+        <v>14.3</v>
       </c>
       <c r="D70" t="n">
-        <v>57.5</v>
+        <v>44.1</v>
       </c>
       <c r="E70" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="G70" t="n">
-        <v>20.8</v>
+        <v>28.6</v>
       </c>
       <c r="H70" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K70" t="n">
-        <v>8.4</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>59.3</v>
+        <v>38.9</v>
       </c>
       <c r="E71" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>7.1</v>
+        <v>66.7</v>
       </c>
       <c r="H71" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>7.2</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C72" t="n">
         <v>50</v>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="E72" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>6.7</v>
+        <v>25</v>
       </c>
       <c r="H72" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>29.4</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>16.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C73" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>87.5</v>
+        <v>41.4</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H73" t="n">
         <v>50</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>57.5</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74"/>
+        <v>18.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>51.9</v>
+      </c>
       <c r="G74" t="n">
-        <v>66.7</v>
+        <v>20.8</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>47.8</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>-66.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B75" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C75" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="D75" t="n">
-        <v>63.4</v>
+        <v>59.3</v>
       </c>
       <c r="E75" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H75" t="n">
-        <v>27.3</v>
+        <v>40</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>27.3</v>
+        <v>8.3</v>
       </c>
       <c r="K75" t="n">
-        <v>27.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C76" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D76" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>10.2</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H76" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>29.4</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B77" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C77" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>31.6</v>
+        <v>87.5</v>
       </c>
       <c r="E77" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
         <v>33.3</v>
       </c>
       <c r="K77" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C78" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>57.1</v>
+        <v>20</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
       <c r="H78" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -8883,180 +8967,318 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>-9.1</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="D79" t="n">
-        <v>39.1</v>
+        <v>63.4</v>
       </c>
       <c r="E79" t="n">
-        <v>6.7</v>
+        <v>17.6</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G79" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.3</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C80" t="n">
         <v>66.7</v>
       </c>
       <c r="D80" t="n">
-        <v>53.3</v>
+        <v>80</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>7.1</v>
+        <v>50</v>
       </c>
       <c r="K80" t="n">
-        <v>-11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="C81" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D81" t="n">
-        <v>55.2</v>
+        <v>31.6</v>
       </c>
       <c r="E81" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="F81" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H81" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>14.3</v>
+        <v>33.3</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B82" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C82" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D82" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82"/>
+      <c r="G82" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" t="s">
+        <v>152</v>
+      </c>
+      <c r="C83" t="n">
+        <v>50</v>
+      </c>
+      <c r="D83" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>244</v>
+      </c>
+      <c r="B84" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>245</v>
+      </c>
+      <c r="B85" t="s">
+        <v>152</v>
+      </c>
+      <c r="C85" t="n">
+        <v>52</v>
+      </c>
+      <c r="D85" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>4</v>
+      </c>
+      <c r="J85" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>246</v>
+      </c>
+      <c r="B86" t="s">
+        <v>152</v>
+      </c>
+      <c r="C86" t="n">
         <v>68.8</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D86" t="n">
         <v>59.2</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E86" t="n">
         <v>16</v>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
         <v>5.9</v>
       </c>
-      <c r="H82" t="n">
-        <v>50</v>
-      </c>
-      <c r="I82" t="n">
+      <c r="H86" t="n">
+        <v>50</v>
+      </c>
+      <c r="I86" t="n">
         <v>5.9</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J86" t="n">
         <v>17.4</v>
       </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83"/>
-      <c r="B83" t="s">
-        <v>161</v>
-      </c>
-      <c r="C83" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="D83" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E83" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F83" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H83" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J83" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K83" t="n">
-        <v>-0.5</v>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87" t="s">
+        <v>163</v>
+      </c>
+      <c r="C87" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F87" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>45</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -249,6 +249,9 @@
     <t xml:space="preserve">Sydney Stonehouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Young</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aidan Vivaldi</t>
   </si>
   <si>
@@ -634,6 +637,9 @@
   </si>
   <si>
     <t xml:space="preserve">Noah Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premnath Chayak</t>
   </si>
   <si>
     <t xml:space="preserve">Premnath Nayak</t>
@@ -814,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K148" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K149" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K149"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -834,8 +840,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K89" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K90" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K90"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -1212,31 +1218,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>61.6</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E3" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="F3" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="G3" t="n">
-        <v>14.3</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="I3" t="n">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="K3" t="n">
-        <v>39.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="4">
@@ -1282,31 +1288,31 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>73.9</v>
+        <v>72.2</v>
       </c>
       <c r="D5" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="E5" t="n">
-        <v>60.2</v>
+        <v>57.9</v>
       </c>
       <c r="F5" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="G5" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="J5" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="K5" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -1422,31 +1428,31 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>73.3</v>
+        <v>76.5</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="E9" t="n">
-        <v>67.1</v>
+        <v>70.6</v>
       </c>
       <c r="F9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>26.7</v>
       </c>
       <c r="H9" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1457,31 +1463,31 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>78.8</v>
+        <v>78.9</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="E10" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="G10" t="n">
-        <v>27.4</v>
+        <v>26.5</v>
       </c>
       <c r="H10" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="I10" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="K10" t="n">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="11">
@@ -1492,31 +1498,31 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E11" t="n">
-        <v>69.7</v>
+        <v>68.7</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="H11" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="I11" t="n">
-        <v>44.4</v>
+        <v>44.7</v>
       </c>
       <c r="J11" t="n">
-        <v>25</v>
+        <v>23.7</v>
       </c>
       <c r="K11" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="12">
@@ -1568,19 +1574,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -1591,31 +1597,31 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>59.3</v>
+        <v>64.9</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="E14" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>36.4</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="K14" t="n">
-        <v>27.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1629,28 +1635,28 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="E15" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="F15" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="G15" t="n">
-        <v>30.7</v>
+        <v>31.5</v>
       </c>
       <c r="H15" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="I15" t="n">
-        <v>48.1</v>
+        <v>45.6</v>
       </c>
       <c r="J15" t="n">
-        <v>27.8</v>
+        <v>31.6</v>
       </c>
       <c r="K15" t="n">
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="16">
@@ -1661,31 +1667,31 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>75</v>
+      </c>
+      <c r="J16" t="n">
         <v>25</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
-      <c r="J16" t="n">
-        <v>50</v>
-      </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -1731,31 +1737,31 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>67</v>
+        <v>68.4</v>
       </c>
       <c r="D18" t="n">
-        <v>9.8</v>
+        <v>10.3</v>
       </c>
       <c r="E18" t="n">
-        <v>57.2</v>
+        <v>58.1</v>
       </c>
       <c r="F18" t="n">
-        <v>9.8</v>
+        <v>10.3</v>
       </c>
       <c r="G18" t="n">
-        <v>11.9</v>
+        <v>10.8</v>
       </c>
       <c r="H18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>44.4</v>
+        <v>43.9</v>
       </c>
       <c r="J18" t="n">
-        <v>33.3</v>
+        <v>31.7</v>
       </c>
       <c r="K18" t="n">
-        <v>37.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -1766,31 +1772,31 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>77.2</v>
+        <v>75.8</v>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="E19" t="n">
-        <v>61.9</v>
+        <v>59.9</v>
       </c>
       <c r="F19" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="G19" t="n">
-        <v>29.2</v>
+        <v>30.7</v>
       </c>
       <c r="H19" t="n">
-        <v>10.9</v>
+        <v>9.3</v>
       </c>
       <c r="I19" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="J19" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="K19" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="20">
@@ -1801,31 +1807,31 @@
         <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="D20" t="n">
-        <v>20.8</v>
+        <v>19.7</v>
       </c>
       <c r="E20" t="n">
-        <v>46.9</v>
+        <v>49.3</v>
       </c>
       <c r="F20" t="n">
-        <v>20.8</v>
+        <v>19.7</v>
       </c>
       <c r="G20" t="n">
-        <v>32.1</v>
+        <v>29</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>40.9</v>
+        <v>44</v>
       </c>
       <c r="J20" t="n">
-        <v>22.7</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>52.4</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="21">
@@ -1836,31 +1842,31 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>77.6</v>
+        <v>78.2</v>
       </c>
       <c r="D21" t="n">
         <v>15.3</v>
       </c>
       <c r="E21" t="n">
-        <v>62.3</v>
+        <v>62.9</v>
       </c>
       <c r="F21" t="n">
         <v>15.3</v>
       </c>
       <c r="G21" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>38.5</v>
       </c>
       <c r="J21" t="n">
-        <v>37.1</v>
+        <v>35.4</v>
       </c>
       <c r="K21" t="n">
-        <v>38.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="22">
@@ -1906,31 +1912,31 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>87.5</v>
+        <v>79.2</v>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E23" t="n">
-        <v>70.8</v>
+        <v>64.9</v>
       </c>
       <c r="F23" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J23" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K23" t="n">
-        <v>58.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="24">
@@ -2600,31 +2606,31 @@
         <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>57.7</v>
+        <v>59.1</v>
       </c>
       <c r="D43" t="n">
-        <v>6.5</v>
+        <v>8.7</v>
       </c>
       <c r="E43" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="F43" t="n">
-        <v>6.5</v>
+        <v>8.7</v>
       </c>
       <c r="G43" t="n">
-        <v>28.6</v>
+        <v>20.6</v>
       </c>
       <c r="H43" t="n">
-        <v>31.6</v>
+        <v>25</v>
       </c>
       <c r="I43" t="n">
-        <v>55.6</v>
+        <v>58.8</v>
       </c>
       <c r="J43" t="n">
-        <v>22.2</v>
+        <v>29.4</v>
       </c>
       <c r="K43" t="n">
-        <v>22.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="44">
@@ -2705,31 +2711,31 @@
         <v>55</v>
       </c>
       <c r="C46" t="n">
-        <v>55.6</v>
+        <v>46.4</v>
       </c>
       <c r="D46" t="n">
         <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>35.6</v>
+        <v>26.4</v>
       </c>
       <c r="F46" t="n">
         <v>20</v>
       </c>
       <c r="G46" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="H46" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I46" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K46" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="47">
@@ -2775,31 +2781,31 @@
         <v>55</v>
       </c>
       <c r="C48" t="n">
-        <v>82.4</v>
+        <v>62.1</v>
       </c>
       <c r="D48" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="n">
-        <v>68.1</v>
+        <v>49.6</v>
       </c>
       <c r="F48" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="G48" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I48" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="49">
@@ -2880,31 +2886,31 @@
         <v>55</v>
       </c>
       <c r="C51" t="n">
-        <v>68.4</v>
+        <v>69.2</v>
       </c>
       <c r="D51" t="n">
-        <v>7.7</v>
+        <v>17.6</v>
       </c>
       <c r="E51" t="n">
-        <v>60.7</v>
+        <v>51.6</v>
       </c>
       <c r="F51" t="n">
-        <v>7.7</v>
+        <v>17.6</v>
       </c>
       <c r="G51" t="n">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
       <c r="H51" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="I51" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="52">
@@ -2942,31 +2948,31 @@
         <v>55</v>
       </c>
       <c r="C53" t="n">
-        <v>62.2</v>
+        <v>64.2</v>
       </c>
       <c r="D53" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G53" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H53" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I53" t="n">
-        <v>42.1</v>
+        <v>40.7</v>
       </c>
       <c r="J53" t="n">
-        <v>26.3</v>
+        <v>33.3</v>
       </c>
       <c r="K53" t="n">
-        <v>42.1</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="54">
@@ -2977,28 +2983,28 @@
         <v>55</v>
       </c>
       <c r="C54" t="n">
-        <v>58.8</v>
+        <v>57.1</v>
       </c>
       <c r="D54" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="E54" t="n">
-        <v>49.7</v>
+        <v>46.6</v>
       </c>
       <c r="F54" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="G54" t="n">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="H54" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="I54" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="J54" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="K54" t="n">
         <v>100</v>
@@ -3012,31 +3018,31 @@
         <v>55</v>
       </c>
       <c r="C55" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J55" t="n">
         <v>33.3</v>
       </c>
-      <c r="D55" t="n">
+      <c r="K55" t="n">
         <v>33.3</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>100</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3082,31 +3088,31 @@
         <v>55</v>
       </c>
       <c r="C57" t="n">
-        <v>57.6</v>
+        <v>62.2</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="G57" t="n">
         <v>41.7</v>
       </c>
       <c r="H57" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="I57" t="n">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="58">
@@ -3120,28 +3126,28 @@
         <v>60</v>
       </c>
       <c r="D58" t="n">
-        <v>14.3</v>
+        <v>27.3</v>
       </c>
       <c r="E58" t="n">
-        <v>45.7</v>
+        <v>32.7</v>
       </c>
       <c r="F58" t="n">
-        <v>14.3</v>
+        <v>27.3</v>
       </c>
       <c r="G58" t="n">
-        <v>27.3</v>
+        <v>37.5</v>
       </c>
       <c r="H58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I58" t="n">
         <v>16.7</v>
       </c>
-      <c r="I58" t="n">
-        <v>25</v>
-      </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K58" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="59">
@@ -3187,28 +3193,28 @@
         <v>55</v>
       </c>
       <c r="C60" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="n">
         <v>33.3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G60" t="n">
-        <v>16.7</v>
+        <v>36.4</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3222,31 +3228,31 @@
         <v>55</v>
       </c>
       <c r="C61" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>20</v>
+      </c>
+      <c r="E61" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="F61" t="n">
+        <v>20</v>
+      </c>
+      <c r="G61" t="n">
+        <v>20</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>71.4</v>
       </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>80</v>
-      </c>
       <c r="J61" t="n">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="62">
@@ -3292,22 +3298,22 @@
         <v>55</v>
       </c>
       <c r="C63" t="n">
-        <v>83.3</v>
+        <v>78.6</v>
       </c>
       <c r="D63" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="E63" t="n">
-        <v>65.1</v>
+        <v>57.2</v>
       </c>
       <c r="F63" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
       <c r="G63" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="H63" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="I63" t="n">
         <v>80</v>
@@ -3327,31 +3333,31 @@
         <v>55</v>
       </c>
       <c r="C64" t="n">
-        <v>48.4</v>
+        <v>64.8</v>
       </c>
       <c r="D64" t="n">
-        <v>34.4</v>
+        <v>31.1</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>33.7</v>
       </c>
       <c r="F64" t="n">
-        <v>34.4</v>
+        <v>31.1</v>
       </c>
       <c r="G64" t="n">
-        <v>48.1</v>
+        <v>38</v>
       </c>
       <c r="H64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>50</v>
+      </c>
+      <c r="K64" t="n">
         <v>16.7</v>
-      </c>
-      <c r="I64" t="n">
-        <v>50</v>
-      </c>
-      <c r="J64" t="n">
-        <v>50</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3394,69 +3400,69 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C66" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" t="s">
         <v>80</v>
       </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
       <c r="C67" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="D67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>58.3</v>
+        <v>42.9</v>
       </c>
       <c r="F67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K67" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="68">
@@ -3464,34 +3470,34 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C68" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E68" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="J68" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69">
@@ -3499,34 +3505,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C69" t="n">
+        <v>80</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>80</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>66.7</v>
       </c>
-      <c r="D69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E69" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F69" t="n">
-        <v>20</v>
-      </c>
-      <c r="G69" t="n">
-        <v>20</v>
-      </c>
-      <c r="H69" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I69" t="n">
-        <v>25</v>
-      </c>
       <c r="J69" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="70">
@@ -3534,31 +3540,31 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C70" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D70" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E70" t="n">
-        <v>5.6</v>
+        <v>46.7</v>
       </c>
       <c r="F70" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3569,22 +3575,22 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" t="n">
         <v>55.6</v>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>43.1</v>
+        <v>5.6</v>
       </c>
       <c r="F71" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3596,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3604,31 +3610,31 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C72" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="n">
-        <v>46.7</v>
+        <v>43.1</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="G72" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>100</v>
@@ -3639,34 +3645,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J73" t="n">
         <v>50</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -3674,28 +3680,28 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C74" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>50</v>
@@ -3709,28 +3715,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C75" t="n">
-        <v>80</v>
-      </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
+        <v>75</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50</v>
+      </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J75" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K75" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3738,34 +3750,28 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" t="n">
-        <v>78.6</v>
-      </c>
-      <c r="D76" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="F76" t="n">
-        <v>11.1</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
       <c r="G76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
         <v>33.3</v>
       </c>
-      <c r="I76" t="n">
-        <v>100</v>
-      </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="77">
@@ -3773,25 +3779,25 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>100</v>
+        <v>78.6</v>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I77" t="n">
         <v>100</v>
@@ -3800,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3808,22 +3814,22 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C78" t="n">
-        <v>46.7</v>
+        <v>100</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E78" t="n">
-        <v>26.7</v>
+        <v>75</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G78" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3835,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="79">
@@ -3843,34 +3849,34 @@
         <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C79" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="D79" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20</v>
+      </c>
+      <c r="G79" t="n">
         <v>75</v>
       </c>
-      <c r="E79" t="n">
-        <v>-8.3</v>
-      </c>
-      <c r="F79" t="n">
-        <v>75</v>
-      </c>
-      <c r="G79" t="n">
-        <v>33.3</v>
-      </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
@@ -3878,60 +3884,66 @@
         <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C80" t="n">
-        <v>67.7</v>
+        <v>66.7</v>
       </c>
       <c r="D80" t="n">
-        <v>31.6</v>
+        <v>75</v>
       </c>
       <c r="E80" t="n">
-        <v>36.1</v>
+        <v>-8.3</v>
       </c>
       <c r="F80" t="n">
-        <v>31.6</v>
+        <v>75</v>
       </c>
       <c r="G80" t="n">
-        <v>13.8</v>
+        <v>33.3</v>
       </c>
       <c r="H80" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="K80" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" t="s">
         <v>95</v>
       </c>
-      <c r="B81" t="s">
-        <v>94</v>
-      </c>
       <c r="C81" t="n">
-        <v>100</v>
-      </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
+        <v>67.7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>31.6</v>
+      </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I81" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K81" t="n">
         <v>50</v>
@@ -3942,34 +3954,28 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C82" t="n">
-        <v>73.1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>25</v>
-      </c>
-      <c r="E82" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="F82" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
       <c r="G82" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="J82" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -3977,34 +3983,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>73.1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E83" t="n">
-        <v>75</v>
+        <v>48.1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I83" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="J83" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="K83" t="n">
-        <v>66.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -4012,34 +4018,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C84" t="n">
-        <v>83.9</v>
+        <v>75</v>
       </c>
       <c r="D84" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>76.2</v>
+        <v>75</v>
       </c>
       <c r="F84" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
       <c r="J84" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="K84" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="85">
@@ -4047,34 +4053,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C85" t="n">
-        <v>58.3</v>
+        <v>83.9</v>
       </c>
       <c r="D85" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="E85" t="n">
-        <v>49.2</v>
+        <v>76.2</v>
       </c>
       <c r="F85" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="G85" t="n">
-        <v>25</v>
+        <v>7.1</v>
       </c>
       <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J85" t="n">
         <v>16.7</v>
       </c>
-      <c r="I85" t="n">
-        <v>75</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
       <c r="K85" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="86">
@@ -4082,34 +4088,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C86" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>25</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I86" t="n">
         <v>75</v>
       </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>75</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I86" t="n">
-        <v>60</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -4117,34 +4123,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C87" t="n">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="D87" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>31.6</v>
+        <v>75</v>
       </c>
       <c r="F87" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>12.5</v>
+        <v>28.6</v>
       </c>
       <c r="I87" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J87" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
@@ -4152,34 +4158,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" t="n">
-        <v>71.4</v>
+        <v>73.3</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="E88" t="n">
-        <v>71.4</v>
+        <v>31.6</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="G88" t="n">
-        <v>40</v>
+        <v>17.6</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I88" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4187,34 +4193,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C89" t="n">
-        <v>53.3</v>
+        <v>71.4</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>43.3</v>
+        <v>71.4</v>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H89" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90">
@@ -4222,31 +4228,31 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C90" t="n">
-        <v>37.5</v>
+        <v>53.3</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E90" t="n">
-        <v>37.5</v>
+        <v>43.3</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J90" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4257,34 +4263,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C91" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
         <v>100</v>
       </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>100</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>50</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>50</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
       <c r="K91" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4292,34 +4298,34 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D92" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>43.3</v>
+        <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H92" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
         <v>50</v>
       </c>
       <c r="J92" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -4327,25 +4333,25 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C93" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="D93" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="G93" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
         <v>50</v>
@@ -4354,7 +4360,7 @@
         <v>50</v>
       </c>
       <c r="K93" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
@@ -4362,34 +4368,34 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C94" t="n">
-        <v>59.1</v>
+        <v>83.3</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E94" t="n">
-        <v>59.1</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G94" t="n">
-        <v>15.4</v>
+        <v>42.9</v>
       </c>
       <c r="H94" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>50</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="K94" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -4397,34 +4403,34 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C95" t="n">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>100</v>
+        <v>59.1</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>33.3</v>
+        <v>15.4</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I95" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96">
@@ -4432,34 +4438,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D96" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>51.9</v>
+        <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>19.4</v>
+        <v>33.3</v>
       </c>
       <c r="H96" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -4467,34 +4473,34 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C97" t="n">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="D97" t="n">
-        <v>9.1</v>
+        <v>23.1</v>
       </c>
       <c r="E97" t="n">
-        <v>72.7</v>
+        <v>51.9</v>
       </c>
       <c r="F97" t="n">
-        <v>9.1</v>
+        <v>23.1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="I97" t="n">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="J97" t="n">
         <v>25</v>
       </c>
       <c r="K97" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="98">
@@ -4502,104 +4508,104 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C98" t="n">
-        <v>67.6</v>
+        <v>81.8</v>
       </c>
       <c r="D98" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="E98" t="n">
-        <v>60.5</v>
+        <v>72.7</v>
       </c>
       <c r="F98" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="G98" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I98" t="n">
-        <v>43.8</v>
+        <v>75</v>
       </c>
       <c r="J98" t="n">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="K98" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>67.6</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E99" t="n">
-        <v>50</v>
+        <v>60.5</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C100" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4607,69 +4613,69 @@
         <v>114</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C101" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="D101" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>48.4</v>
+        <v>66.7</v>
       </c>
       <c r="F101" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="H101" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="I101" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="J101" t="n">
+        <v>30</v>
+      </c>
+      <c r="K101" t="n">
         <v>20</v>
-      </c>
-      <c r="K101" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" t="s">
         <v>116</v>
       </c>
-      <c r="B102" t="s">
-        <v>115</v>
-      </c>
       <c r="C102" t="n">
-        <v>46.7</v>
+        <v>57.1</v>
       </c>
       <c r="D102" t="n">
-        <v>26.7</v>
+        <v>8.7</v>
       </c>
       <c r="E102" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="G102" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>80</v>
+      </c>
+      <c r="J102" t="n">
         <v>20</v>
       </c>
-      <c r="F102" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G102" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>62.5</v>
-      </c>
       <c r="K102" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -4677,34 +4683,34 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C103" t="n">
-        <v>88.9</v>
+        <v>46.7</v>
       </c>
       <c r="D103" t="n">
-        <v>13.3</v>
+        <v>26.7</v>
       </c>
       <c r="E103" t="n">
-        <v>75.6</v>
+        <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>13.3</v>
+        <v>26.7</v>
       </c>
       <c r="G103" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="H103" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="K103" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="104">
@@ -4712,34 +4718,34 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C104" t="n">
         <v>88.9</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E104" t="n">
-        <v>88.9</v>
+        <v>75.6</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H104" t="n">
         <v>14.3</v>
       </c>
       <c r="I104" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K104" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105">
@@ -4747,34 +4753,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C105" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>78.6</v>
+        <v>88.9</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I105" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
@@ -4782,34 +4788,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C106" t="n">
-        <v>57.1</v>
+        <v>78.6</v>
       </c>
       <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
         <v>9.1</v>
       </c>
-      <c r="E106" t="n">
-        <v>48</v>
-      </c>
-      <c r="F106" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G106" t="n">
-        <v>40</v>
-      </c>
       <c r="H106" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4817,34 +4823,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C107" t="n">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E107" t="n">
-        <v>64.3</v>
+        <v>48</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="H107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I107" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -4852,34 +4858,34 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="D108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>55</v>
+        <v>64.3</v>
       </c>
       <c r="F108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>11.1</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I108" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="J108" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="K108" t="n">
-        <v>14.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109">
@@ -4887,34 +4893,34 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C109" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="D109" t="n">
         <v>25</v>
       </c>
       <c r="E109" t="n">
-        <v>60.7</v>
+        <v>55</v>
       </c>
       <c r="F109" t="n">
         <v>25</v>
       </c>
       <c r="G109" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="H109" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="J109" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="110">
@@ -4922,34 +4928,34 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C110" t="n">
-        <v>43.8</v>
+        <v>85.7</v>
       </c>
       <c r="D110" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="E110" t="n">
-        <v>34.7</v>
+        <v>60.7</v>
       </c>
       <c r="F110" t="n">
-        <v>9.1</v>
+        <v>25</v>
       </c>
       <c r="G110" t="n">
         <v>25</v>
       </c>
       <c r="H110" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="I110" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J110" t="n">
         <v>50</v>
       </c>
       <c r="K110" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4957,28 +4963,34 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C111" t="n">
-        <v>100</v>
-      </c>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
+        <v>43.8</v>
+      </c>
+      <c r="D111" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9.1</v>
+      </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J111" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112">
@@ -4986,34 +4998,28 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C112" t="n">
-        <v>92.6</v>
-      </c>
-      <c r="D112" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E112" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="F112" t="n">
-        <v>5.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
       <c r="G112" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>64.3</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>21.4</v>
+        <v>100</v>
       </c>
       <c r="K112" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5021,34 +5027,34 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>56.2</v>
+        <v>92.6</v>
       </c>
       <c r="D113" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G113" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H113" t="n">
         <v>12.5</v>
       </c>
-      <c r="E113" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="F113" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G113" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H113" t="n">
-        <v>22.2</v>
-      </c>
       <c r="I113" t="n">
-        <v>42.9</v>
+        <v>64.3</v>
       </c>
       <c r="J113" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="114">
@@ -5056,34 +5062,34 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C114" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D114" t="n">
         <v>12.5</v>
       </c>
       <c r="E114" t="n">
-        <v>62.5</v>
+        <v>43.7</v>
       </c>
       <c r="F114" t="n">
         <v>12.5</v>
       </c>
       <c r="G114" t="n">
-        <v>23.1</v>
+        <v>9.1</v>
       </c>
       <c r="H114" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J114" t="n">
         <v>14.3</v>
       </c>
-      <c r="I114" t="n">
-        <v>40</v>
-      </c>
-      <c r="J114" t="n">
-        <v>40</v>
-      </c>
       <c r="K114" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5091,34 +5097,34 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C115" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D115" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
       <c r="F115" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>23.1</v>
       </c>
       <c r="H115" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I115" t="n">
-        <v>72.7</v>
+        <v>40</v>
       </c>
       <c r="J115" t="n">
-        <v>18.2</v>
+        <v>40</v>
       </c>
       <c r="K115" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116">
@@ -5126,34 +5132,34 @@
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C116" t="n">
-        <v>55.6</v>
+        <v>71.4</v>
       </c>
       <c r="D116" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="E116" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" t="n">
         <v>16.7</v>
       </c>
-      <c r="E116" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F116" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="G116" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
       <c r="I116" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="J116" t="n">
-        <v>25</v>
+        <v>18.2</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="117">
@@ -5161,34 +5167,34 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C117" t="n">
-        <v>68.8</v>
+        <v>55.6</v>
       </c>
       <c r="D117" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="E117" t="n">
-        <v>58.5</v>
+        <v>38.9</v>
       </c>
       <c r="F117" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="G117" t="n">
-        <v>12</v>
+        <v>28.6</v>
       </c>
       <c r="H117" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
+        <v>50</v>
+      </c>
+      <c r="J117" t="n">
         <v>25</v>
       </c>
-      <c r="J117" t="n">
-        <v>8.3</v>
-      </c>
       <c r="K117" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5196,31 +5202,31 @@
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C118" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="D118" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="E118" t="n">
-        <v>52.4</v>
+        <v>58.5</v>
       </c>
       <c r="F118" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="G118" t="n">
-        <v>35.7</v>
+        <v>12</v>
       </c>
       <c r="H118" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
       <c r="I118" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J118" t="n">
-        <v>33.3</v>
+        <v>8.3</v>
       </c>
       <c r="K118" t="n">
         <v>33.3</v>
@@ -5228,37 +5234,37 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>133</v>
+      </c>
+      <c r="B119" t="s">
         <v>134</v>
       </c>
-      <c r="B119" t="s">
-        <v>133</v>
-      </c>
       <c r="C119" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="D119" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="E119" t="n">
-        <v>33.4</v>
+        <v>52.4</v>
       </c>
       <c r="F119" t="n">
-        <v>22.2</v>
+        <v>14.3</v>
       </c>
       <c r="G119" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I119" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="120">
@@ -5266,34 +5272,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C120" t="n">
-        <v>80.8</v>
+        <v>55.6</v>
       </c>
       <c r="D120" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="E120" t="n">
-        <v>62.6</v>
+        <v>33.4</v>
       </c>
       <c r="F120" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="G120" t="n">
-        <v>36</v>
+        <v>42.9</v>
       </c>
       <c r="H120" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J120" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5301,34 +5307,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C121" t="n">
-        <v>91.7</v>
+        <v>80.8</v>
       </c>
       <c r="D121" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="E121" t="n">
-        <v>41.7</v>
+        <v>62.6</v>
       </c>
       <c r="F121" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="G121" t="n">
-        <v>21.4</v>
+        <v>36</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="I121" t="n">
-        <v>28.6</v>
+        <v>62.5</v>
       </c>
       <c r="J121" t="n">
-        <v>42.9</v>
+        <v>12.5</v>
       </c>
       <c r="K121" t="n">
-        <v>71.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
@@ -5336,34 +5342,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C122" t="n">
-        <v>60</v>
+        <v>91.7</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E122" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="123">
@@ -5371,28 +5377,28 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C123" t="n">
+        <v>60</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>60</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
         <v>100</v>
-      </c>
-      <c r="D123" t="n">
-        <v>20</v>
-      </c>
-      <c r="E123" t="n">
-        <v>80</v>
-      </c>
-      <c r="F123" t="n">
-        <v>20</v>
-      </c>
-      <c r="G123" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>66.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5406,34 +5412,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C124" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D124" t="n">
-        <v>8.3</v>
+        <v>20</v>
       </c>
       <c r="E124" t="n">
+        <v>80</v>
+      </c>
+      <c r="F124" t="n">
+        <v>20</v>
+      </c>
+      <c r="G124" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
         <v>66.7</v>
       </c>
-      <c r="F124" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>50</v>
-      </c>
       <c r="J124" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5441,19 +5447,19 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C125" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="E125" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -5462,13 +5468,13 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J125" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="126">
@@ -5476,34 +5482,34 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C126" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D126" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>54.7</v>
+        <v>100</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K126" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5511,34 +5517,34 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C127" t="n">
-        <v>57.1</v>
+        <v>83.3</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="E127" t="n">
-        <v>57.1</v>
+        <v>54.7</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="G127" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="H127" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J127" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K127" t="n">
-        <v>60</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="128">
@@ -5546,34 +5552,34 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C128" t="n">
-        <v>70</v>
+        <v>57.1</v>
       </c>
       <c r="D128" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>32.5</v>
+        <v>57.1</v>
       </c>
       <c r="F128" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="I128" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="J128" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K128" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
@@ -5581,34 +5587,34 @@
         <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C129" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D129" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="E129" t="n">
-        <v>53.6</v>
+        <v>32.5</v>
       </c>
       <c r="F129" t="n">
-        <v>21.4</v>
+        <v>37.5</v>
       </c>
       <c r="G129" t="n">
-        <v>46.7</v>
+        <v>17.6</v>
       </c>
       <c r="H129" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K129" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130">
@@ -5616,34 +5622,34 @@
         <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C130" t="n">
-        <v>84.6</v>
+        <v>75</v>
       </c>
       <c r="D130" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E130" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="H130" t="n">
         <v>14.3</v>
       </c>
-      <c r="E130" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="F130" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G130" t="n">
-        <v>13</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
       <c r="I130" t="n">
-        <v>43.8</v>
+        <v>66.7</v>
       </c>
       <c r="J130" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>12.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="131">
@@ -5651,34 +5657,34 @@
         <v>146</v>
       </c>
       <c r="B131" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>68.6</v>
+        <v>84.6</v>
       </c>
       <c r="D131" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="E131" t="n">
-        <v>59.5</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="G131" t="n">
-        <v>23.1</v>
+        <v>13</v>
       </c>
       <c r="H131" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="J131" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="K131" t="n">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="132">
@@ -5686,34 +5692,34 @@
         <v>147</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C132" t="n">
-        <v>50</v>
+        <v>68.6</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E132" t="n">
-        <v>50</v>
+        <v>59.5</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I132" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="133">
@@ -5721,34 +5727,34 @@
         <v>148</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C133" t="n">
-        <v>90.9</v>
+        <v>50</v>
       </c>
       <c r="D133" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>70.9</v>
+        <v>50</v>
       </c>
       <c r="F133" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5756,31 +5762,31 @@
         <v>149</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C134" t="n">
-        <v>60</v>
+        <v>90.9</v>
       </c>
       <c r="D134" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="E134" t="n">
-        <v>17.1</v>
+        <v>70.9</v>
       </c>
       <c r="F134" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="G134" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J134" t="n">
         <v>33.3</v>
-      </c>
-      <c r="H134" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>100</v>
       </c>
       <c r="K134" t="n">
         <v>50</v>
@@ -5791,34 +5797,34 @@
         <v>150</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C135" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D135" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="E135" t="n">
-        <v>73.3</v>
+        <v>17.1</v>
       </c>
       <c r="F135" t="n">
-        <v>16.7</v>
+        <v>42.9</v>
       </c>
       <c r="G135" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I135" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136">
@@ -5826,22 +5832,22 @@
         <v>151</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C136" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="E136" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -5850,10 +5856,10 @@
         <v>33.3</v>
       </c>
       <c r="J136" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K136" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -5861,51 +5867,57 @@
         <v>152</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C137" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="F137" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="I137"/>
-      <c r="J137"/>
-      <c r="K137"/>
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J137" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K137" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
+        <v>153</v>
+      </c>
+      <c r="B138" t="s">
         <v>154</v>
       </c>
-      <c r="B138" t="s">
-        <v>153</v>
-      </c>
       <c r="C138" t="n">
-        <v>42.9</v>
+        <v>16.7</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="n">
-        <v>42.9</v>
+        <v>5.6</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="G138" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="H138" t="n">
         <v>66.7</v>
@@ -5919,25 +5931,25 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C139" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
@@ -5948,69 +5960,63 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C140" t="n">
-        <v>61.1</v>
+        <v>33.3</v>
       </c>
       <c r="D140" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>52</v>
+        <v>33.3</v>
       </c>
       <c r="F140" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="I140"/>
+      <c r="J140"/>
+      <c r="K140"/>
     </row>
     <row r="141">
       <c r="A141" t="s">
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C141" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D141" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="E141" t="n">
-        <v>31.8</v>
+        <v>52</v>
       </c>
       <c r="F141" t="n">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="G141" t="n">
-        <v>42.9</v>
+        <v>8.3</v>
       </c>
       <c r="H141" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="J141" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="142">
@@ -6018,34 +6024,34 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C142" t="n">
         <v>50</v>
       </c>
       <c r="D142" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="E142" t="n">
-        <v>26.9</v>
+        <v>31.8</v>
       </c>
       <c r="F142" t="n">
-        <v>23.1</v>
+        <v>18.2</v>
       </c>
       <c r="G142" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="H142" t="n">
         <v>16.7</v>
       </c>
       <c r="I142" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="K142" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143">
@@ -6053,34 +6059,34 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C143" t="n">
+        <v>50</v>
+      </c>
+      <c r="D143" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G143" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H143" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I143" t="n">
         <v>66.7</v>
       </c>
-      <c r="D143" t="n">
-        <v>25</v>
-      </c>
-      <c r="E143" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="F143" t="n">
-        <v>25</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="J143" t="n">
         <v>33.3</v>
       </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>100</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="144">
@@ -6088,34 +6094,34 @@
         <v>160</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C144" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E144" t="n">
-        <v>61.5</v>
+        <v>41.7</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G144" t="n">
-        <v>12.5</v>
+        <v>33.3</v>
       </c>
       <c r="H144" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="J144" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -6123,34 +6129,34 @@
         <v>161</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C145" t="n">
-        <v>45</v>
+        <v>61.5</v>
       </c>
       <c r="D145" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>28.3</v>
+        <v>61.5</v>
       </c>
       <c r="F145" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>27.3</v>
+        <v>12.5</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I145" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="146">
@@ -6158,31 +6164,31 @@
         <v>162</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C146" t="n">
-        <v>71.4</v>
+        <v>45</v>
       </c>
       <c r="D146" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E146" t="n">
-        <v>51.4</v>
+        <v>28.3</v>
       </c>
       <c r="F146" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="G146" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J146" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6193,67 +6199,102 @@
         <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C147" t="n">
         <v>71.4</v>
       </c>
       <c r="D147" t="n">
+        <v>20</v>
+      </c>
+      <c r="E147" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F147" t="n">
+        <v>20</v>
+      </c>
+      <c r="G147" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>50</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>164</v>
+      </c>
+      <c r="B148" t="s">
+        <v>154</v>
+      </c>
+      <c r="C148" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="D148" t="n">
         <v>7.1</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E148" t="n">
         <v>64.3</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F148" t="n">
         <v>7.1</v>
       </c>
-      <c r="G147" t="n">
+      <c r="G148" t="n">
         <v>18.2</v>
       </c>
-      <c r="H147" t="n">
+      <c r="H148" t="n">
         <v>12.5</v>
       </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
         <v>100</v>
       </c>
-      <c r="K147" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148"/>
-      <c r="B148" t="s">
-        <v>164</v>
-      </c>
-      <c r="C148" t="n">
-        <v>67.4</v>
-      </c>
-      <c r="D148" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="E148" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="G148" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="H148" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I148" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="J148" t="n">
-        <v>26.6</v>
-      </c>
       <c r="K148" t="n">
-        <v>35.6</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149" t="s">
+        <v>165</v>
+      </c>
+      <c r="C149" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="D149" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E149" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G149" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H149" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I149" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K149" t="n">
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
@@ -6285,22 +6326,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6309,18 +6350,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6411,42 +6452,42 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>60.7</v>
+        <v>62.1</v>
       </c>
       <c r="D5" t="n">
-        <v>66.8</v>
+        <v>67.2</v>
       </c>
       <c r="E5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="F5" t="n">
-        <v>34.9</v>
+        <v>38.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>25.4</v>
+        <v>27.7</v>
       </c>
       <c r="K5" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -6481,7 +6522,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -6516,7 +6557,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -6551,37 +6592,37 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>83.8</v>
+        <v>82.7</v>
       </c>
       <c r="D9" t="n">
-        <v>75.9</v>
+        <v>72.8</v>
       </c>
       <c r="E9" t="n">
-        <v>30.9</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>48.3</v>
+        <v>44.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>51.7</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="K9" t="n">
-        <v>20.6</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="10">
@@ -6656,42 +6697,42 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="D12" t="n">
-        <v>56.4</v>
+        <v>56.8</v>
       </c>
       <c r="E12" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9</v>
+        <v>34.1</v>
       </c>
       <c r="G12" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="H12" t="n">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>20.3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -6724,112 +6765,112 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>60.7</v>
       </c>
       <c r="E14" t="n">
-        <v>31.6</v>
+        <v>21.4</v>
       </c>
       <c r="F14" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>30.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>22.7</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>16.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>55.4</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>65.1</v>
+        <v>66.2</v>
       </c>
       <c r="E15" t="n">
-        <v>19.7</v>
+        <v>21.7</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>38.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>59.6</v>
+        <v>61.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>25.4</v>
+        <v>26.5</v>
       </c>
       <c r="K15" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>44.4</v>
+        <v>56.8</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="E16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>12.1</v>
       </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -6864,7 +6905,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -6899,42 +6940,42 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>46.2</v>
+        <v>42.1</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="E19" t="n">
         <v>5.9</v>
       </c>
       <c r="F19" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="G19" t="n">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="H19" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>16.7</v>
+        <v>28.1</v>
       </c>
       <c r="K19" t="n">
-        <v>-15.4</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -6969,42 +7010,42 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>64.6</v>
+        <v>64.3</v>
       </c>
       <c r="D21" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="E21" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
       <c r="F21" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="G21" t="n">
-        <v>8.6</v>
+        <v>8.2</v>
       </c>
       <c r="H21" t="n">
-        <v>51.8</v>
+        <v>50.8</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="K21" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -7039,7 +7080,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
         <v>37</v>
@@ -7074,7 +7115,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
@@ -7109,7 +7150,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -7144,7 +7185,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
         <v>37</v>
@@ -7179,7 +7220,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -7214,7 +7255,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
@@ -7249,7 +7290,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -7284,7 +7325,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
@@ -7319,7 +7360,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -7354,7 +7395,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
         <v>37</v>
@@ -7389,7 +7430,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
@@ -7424,7 +7465,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
@@ -7457,42 +7498,42 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
       </c>
       <c r="C35" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
       <c r="D35" t="n">
-        <v>57.3</v>
+        <v>58.2</v>
       </c>
       <c r="E35" t="n">
-        <v>6.9</v>
+        <v>12.7</v>
       </c>
       <c r="F35" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="G35" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="H35" t="n">
-        <v>37.9</v>
+        <v>37.2</v>
       </c>
       <c r="I35" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
-        <v>10.4</v>
+        <v>17.9</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" t="s">
         <v>55</v>
@@ -7533,36 +7574,36 @@
         <v>55</v>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>64.7</v>
+        <v>63.3</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>52.9</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
@@ -7597,7 +7638,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
@@ -7632,60 +7673,60 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s">
         <v>55</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>58.9</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H40" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
         <v>55</v>
       </c>
       <c r="C41" t="n">
-        <v>45.5</v>
+        <v>37.5</v>
       </c>
       <c r="D41" t="n">
-        <v>52.9</v>
+        <v>51.8</v>
       </c>
       <c r="E41" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="F41" t="n">
         <v>33.3</v>
       </c>
       <c r="G41" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="H41" t="n">
         <v>50</v>
@@ -7694,50 +7735,50 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7.7</v>
+        <v>14.3</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
       <c r="C42" t="n">
-        <v>28.6</v>
+        <v>42.9</v>
       </c>
       <c r="D42" t="n">
-        <v>37.5</v>
+        <v>43.1</v>
       </c>
       <c r="E42" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>28.6</v>
+        <v>30.8</v>
       </c>
       <c r="H42" t="n">
         <v>50</v>
       </c>
       <c r="I42" t="n">
-        <v>14.3</v>
+        <v>7.7</v>
       </c>
       <c r="J42" t="n">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="K42" t="n">
-        <v>-28.6</v>
+        <v>-30.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
@@ -7772,34 +7813,34 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s">
         <v>55</v>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>52.2</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>91.7</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -7807,207 +7848,207 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
       </c>
       <c r="C45" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
-        <v>61.4</v>
+        <v>52.2</v>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>5.6</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G45" t="n">
-        <v>8.3</v>
+        <v>15</v>
       </c>
       <c r="H45" t="n">
-        <v>46.7</v>
+        <v>91.7</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>41.7</v>
+        <v>23.1</v>
       </c>
       <c r="K45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
       </c>
       <c r="C46" t="n">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
       <c r="D46" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>20.4</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="G46" t="n">
         <v>6.7</v>
       </c>
       <c r="H46" t="n">
-        <v>18.2</v>
+        <v>47.4</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>19.2</v>
+        <v>36.4</v>
       </c>
       <c r="K46" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
       </c>
       <c r="C47" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="D47" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47"/>
+        <v>30</v>
+      </c>
+      <c r="F47" t="n">
+        <v>50</v>
+      </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>18.2</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>46.2</v>
+        <v>80</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
+      <c r="F48"/>
       <c r="G48" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>14.3</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>-22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C49" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="D49" t="n">
-        <v>49.2</v>
+        <v>46.2</v>
       </c>
       <c r="E49" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I49" t="n">
         <v>11.1</v>
       </c>
-      <c r="H49" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="D50" t="n">
-        <v>52.9</v>
+        <v>49.2</v>
       </c>
       <c r="E50" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G50" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="H50" t="n">
-        <v>37.5</v>
+        <v>46.2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>7.7</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -8015,98 +8056,98 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>7.7</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51"/>
-      <c r="G51" t="n">
-        <v>100</v>
-      </c>
-      <c r="H51"/>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51"/>
       <c r="K51" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>57.6</v>
+        <v>7.7</v>
       </c>
       <c r="E52" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F52" t="n">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F52"/>
       <c r="G52" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>23.1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H52"/>
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="J52"/>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C53" t="n">
-        <v>55.6</v>
+        <v>35.3</v>
       </c>
       <c r="D53" t="n">
-        <v>63.2</v>
+        <v>57.6</v>
       </c>
       <c r="E53" t="n">
-        <v>7.1</v>
+        <v>17.6</v>
       </c>
       <c r="F53" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="G53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="H53" t="n">
-        <v>28.6</v>
+        <v>23.1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>10.5</v>
+        <v>23.1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -8114,34 +8155,34 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="D54" t="n">
-        <v>55</v>
+        <v>63.2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="H54" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -8149,679 +8190,679 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>57.8</v>
+        <v>55</v>
       </c>
       <c r="E55" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" t="n">
-        <v>68.8</v>
+        <v>63</v>
       </c>
       <c r="D56" t="n">
-        <v>72.5</v>
+        <v>57.8</v>
       </c>
       <c r="E56" t="n">
-        <v>23.1</v>
+        <v>13.6</v>
       </c>
       <c r="F56" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="H56" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>29.2</v>
+        <v>23.5</v>
       </c>
       <c r="K56" t="n">
-        <v>37.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C57" t="n">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="D57" t="n">
-        <v>87.5</v>
+        <v>72.5</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C58" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="D58" t="n">
-        <v>60.8</v>
+        <v>87.5</v>
       </c>
       <c r="E58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C59" t="n">
-        <v>69.2</v>
+        <v>52.9</v>
       </c>
       <c r="D59" t="n">
-        <v>74.7</v>
+        <v>60.8</v>
       </c>
       <c r="E59" t="n">
-        <v>28.6</v>
+        <v>16.7</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="H59" t="n">
-        <v>57.9</v>
+        <v>42.9</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>24.4</v>
+        <v>32.1</v>
       </c>
       <c r="K59" t="n">
-        <v>19.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C60" t="n">
-        <v>33.3</v>
+        <v>69.2</v>
       </c>
       <c r="D60" t="n">
-        <v>47.6</v>
+        <v>74.7</v>
       </c>
       <c r="E60" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
       <c r="F60" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>33.3</v>
+        <v>3.8</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>28.6</v>
+        <v>24.4</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="D61" t="n">
-        <v>56.4</v>
+        <v>47.6</v>
       </c>
       <c r="E61" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="F61" t="n">
-        <v>29.4</v>
+        <v>66.7</v>
       </c>
       <c r="G61" t="n">
-        <v>15.8</v>
+        <v>33.3</v>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C62" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D62" t="n">
-        <v>63.3</v>
+        <v>56.4</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="F62" t="n">
-        <v>50</v>
+        <v>29.4</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H62" t="n">
-        <v>88.9</v>
+        <v>50</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
-        <v>23.5</v>
+        <v>27.8</v>
       </c>
       <c r="K62" t="n">
-        <v>10</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C63" t="n">
-        <v>36.4</v>
+        <v>60</v>
       </c>
       <c r="D63" t="n">
-        <v>60.5</v>
+        <v>63.3</v>
       </c>
       <c r="E63" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>60</v>
+        <v>88.9</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>11.1</v>
+        <v>23.5</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C64" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="D64" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="E64"/>
+        <v>60.5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5.3</v>
+      </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D65" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>13.3</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="E65"/>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C66" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>63.2</v>
+        <v>53.6</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="F66" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>21.4</v>
+        <v>26.7</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C67" t="n">
-        <v>70</v>
+        <v>61.5</v>
       </c>
       <c r="D67" t="n">
-        <v>70.4</v>
+        <v>63.2</v>
       </c>
       <c r="E67" t="n">
-        <v>15.8</v>
+        <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>37.5</v>
+        <v>30.8</v>
       </c>
       <c r="G67" t="n">
-        <v>3.3</v>
+        <v>15.4</v>
       </c>
       <c r="H67" t="n">
-        <v>34.8</v>
+        <v>66.7</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>22</v>
+        <v>21.4</v>
       </c>
       <c r="K67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C68" t="n">
-        <v>58.3</v>
+        <v>70</v>
       </c>
       <c r="D68" t="n">
-        <v>65.3</v>
+        <v>70.4</v>
       </c>
       <c r="E68" t="n">
-        <v>31.4</v>
+        <v>15.8</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H68" t="n">
-        <v>42.9</v>
+        <v>34.8</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="K68" t="n">
-        <v>8.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="D69" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="E69" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F69" t="n">
         <v>25</v>
       </c>
-      <c r="F69" t="n">
-        <v>66.7</v>
-      </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
-        <v>53.9</v>
+        <v>63.2</v>
       </c>
       <c r="E70" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="F70" t="n">
-        <v>36.4</v>
+        <v>66.7</v>
       </c>
       <c r="G70" t="n">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>35.3</v>
+        <v>50</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>23.7</v>
+        <v>37.5</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>46.4</v>
       </c>
       <c r="D71" t="n">
-        <v>41.2</v>
+        <v>53.9</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>17.9</v>
       </c>
       <c r="H71" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>25</v>
+        <v>23.7</v>
       </c>
       <c r="K71" t="n">
-        <v>-20</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C72" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="D72" t="n">
-        <v>44.1</v>
+        <v>41.2</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" t="n">
         <v>33.3</v>
       </c>
-      <c r="G72" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H72" t="n">
-        <v>50</v>
-      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K72" t="n">
-        <v>-14.3</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D73" t="n">
-        <v>38.9</v>
+        <v>44.1</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G73" t="n">
-        <v>66.7</v>
+        <v>28.6</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K73" t="n">
-        <v>-66.7</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C74" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>57.9</v>
+        <v>38.9</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -8830,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>66.7</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -8839,382 +8880,382 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>-25</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C75" t="n">
         <v>50</v>
       </c>
       <c r="D75" t="n">
-        <v>41.4</v>
+        <v>57.9</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H75" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C76" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="D76" t="n">
-        <v>57.5</v>
+        <v>41.4</v>
       </c>
       <c r="E76" t="n">
-        <v>18.7</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="G76" t="n">
-        <v>20.8</v>
+        <v>33.3</v>
       </c>
       <c r="H76" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="K76" t="n">
-        <v>8.4</v>
+        <v>-16.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C77" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="D77" t="n">
-        <v>59.3</v>
+        <v>57.5</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>51.9</v>
       </c>
       <c r="G77" t="n">
-        <v>7.1</v>
+        <v>20.8</v>
       </c>
       <c r="H77" t="n">
-        <v>40</v>
+        <v>47.8</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C78" t="n">
         <v>50</v>
       </c>
       <c r="D78" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E78" t="n">
-        <v>10.2</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="G78" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H78" t="n">
         <v>40</v>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>29.4</v>
+        <v>8.3</v>
       </c>
       <c r="K78" t="n">
-        <v>16.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C79" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H79" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
-        <v>33.3</v>
+        <v>29.4</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>20</v>
+        <v>87.5</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
-      <c r="F80"/>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C81" t="n">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>63.4</v>
+        <v>20</v>
       </c>
       <c r="E81" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F81" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F81"/>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H81" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>27.8</v>
+        <v>-66.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C82" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>63.4</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B83" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C83" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="D83" t="n">
-        <v>31.6</v>
+        <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>7.1</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K83" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C84" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="D84" t="n">
-        <v>57.1</v>
+        <v>31.6</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84"/>
+        <v>7.1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>100</v>
+      </c>
       <c r="G84" t="n">
-        <v>9.1</v>
+        <v>40</v>
       </c>
       <c r="H84" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-9.1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B85" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="D85" t="n">
-        <v>39.1</v>
+        <v>57.1</v>
       </c>
       <c r="E85" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F85"/>
       <c r="G85" t="n">
-        <v>33.3</v>
+        <v>9.1</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -9223,145 +9264,180 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>-33.3</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B86" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C86" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D86" t="n">
-        <v>53.3</v>
+        <v>39.1</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>11.1</v>
+        <v>33.3</v>
       </c>
       <c r="H86" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>-11.1</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C87" t="n">
-        <v>52</v>
+        <v>66.7</v>
       </c>
       <c r="D87" t="n">
-        <v>55.2</v>
+        <v>53.3</v>
       </c>
       <c r="E87" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H87" t="n">
         <v>28.6</v>
       </c>
-      <c r="G87" t="n">
-        <v>8</v>
-      </c>
-      <c r="H87" t="n">
-        <v>47.4</v>
-      </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B88" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C88" t="n">
+        <v>52</v>
+      </c>
+      <c r="D88" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" t="n">
         <v>68.8</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D89" t="n">
         <v>59.2</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E89" t="n">
         <v>16</v>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
         <v>5.9</v>
       </c>
-      <c r="H88" t="n">
-        <v>50</v>
-      </c>
-      <c r="I88" t="n">
+      <c r="H89" t="n">
+        <v>50</v>
+      </c>
+      <c r="I89" t="n">
         <v>5.9</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J89" t="n">
         <v>17.4</v>
       </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89"/>
-      <c r="B89" t="s">
-        <v>164</v>
-      </c>
-      <c r="C89" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="E89" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90"/>
+      <c r="B90" t="s">
+        <v>165</v>
+      </c>
+      <c r="C90" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="D90" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="E90" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F90" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G90" t="n">
         <v>14.3</v>
       </c>
-      <c r="H89" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J89" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="K89" t="n">
-        <v>-0.8</v>
+      <c r="H90" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>

--- a/oua/data/summary2026oua.xlsx
+++ b/oua/data/summary2026oua.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -252,12 +252,48 @@
     <t xml:space="preserve">Young</t>
   </si>
   <si>
+    <t xml:space="preserve">Alex Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queen's Gaels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brett Hardy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colby Wilhelm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colton Donaldson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Angel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Sartor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick O'Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Opresnick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Shulman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean Skorupski</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aidan Vivaldi</t>
   </si>
   <si>
     <t xml:space="preserve">U of T Varsity Blues</t>
   </si>
   <si>
+    <t xml:space="preserve">Diego Fuentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Elias Rubio Reyes</t>
   </si>
   <si>
@@ -279,6 +315,12 @@
     <t xml:space="preserve">Kirk Gibson</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcus Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Fischer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paul Verman</t>
   </si>
   <s